--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="309">
   <si>
     <t>ZP02</t>
   </si>
@@ -97,43 +97,295 @@
     <t>LG1370機頭P12K,021728_#40,8YU-84,C</t>
   </si>
   <si>
+    <t>REL  PCNF PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006299</t>
+  </si>
+  <si>
+    <t>080200446902</t>
+  </si>
+  <si>
+    <t>5A65E機頭DA15K,032370_BT40,CAWDI</t>
+  </si>
+  <si>
+    <t>200006301</t>
+  </si>
+  <si>
+    <t>080100152306</t>
+  </si>
+  <si>
+    <t>DA15K 主軸,021856_BT40,M60,CWDIN</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006312</t>
+  </si>
+  <si>
+    <t>080200546802</t>
+  </si>
+  <si>
+    <t>MVP11機頭D15K,031859_#40,38F18,C,VKS26</t>
+  </si>
+  <si>
+    <t>200006320</t>
+  </si>
+  <si>
+    <t>080200538802</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,55F23,C</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006321</t>
+  </si>
+  <si>
+    <t>080100116404</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BBT50,CW45</t>
+  </si>
+  <si>
+    <t>200006324</t>
+  </si>
+  <si>
+    <t>080200170704</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011297_780,BBT50,55,C45</t>
+  </si>
+  <si>
+    <t>200006325</t>
+  </si>
+  <si>
+    <t>080100036004</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,C045</t>
+  </si>
+  <si>
+    <t>200006326</t>
+  </si>
+  <si>
+    <t>080300024804</t>
+  </si>
+  <si>
+    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
+  </si>
+  <si>
+    <t>200006330</t>
+  </si>
+  <si>
+    <t>200006344</t>
+  </si>
+  <si>
+    <t>080200158404</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011282_780,BT50,42,CDIN</t>
+  </si>
+  <si>
+    <t>200006345</t>
+  </si>
+  <si>
+    <t>080100023404</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BT50,C0DIN</t>
+  </si>
+  <si>
+    <t>200006349</t>
+  </si>
+  <si>
+    <t>200006361</t>
+  </si>
+  <si>
+    <t>080200527500</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,38F18</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006366</t>
+  </si>
+  <si>
+    <t>080200539403</t>
+  </si>
+  <si>
+    <t>H1682機頭G8K,021565_#50,42F25,C</t>
+  </si>
+  <si>
+    <t>200006367</t>
+  </si>
+  <si>
+    <t>080100122802</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021387_BBT50,CW45</t>
+  </si>
+  <si>
+    <t>200006368</t>
+  </si>
+  <si>
+    <t>080200286203</t>
+  </si>
+  <si>
+    <t>H2110機頭G6K,011026_BT50,42F25,CAW45</t>
+  </si>
+  <si>
     <t>REL  PRC  MACM RMWB SETC</t>
   </si>
   <si>
-    <t>200006299</t>
-  </si>
-  <si>
-    <t>080200446902</t>
-  </si>
-  <si>
-    <t>5A65E機頭DA15K,032370_BT40,CAWDI</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006301</t>
-  </si>
-  <si>
-    <t>080100152306</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021856_BT40,M60,CWDIN</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006312</t>
-  </si>
-  <si>
-    <t>080200546802</t>
-  </si>
-  <si>
-    <t>MVP11機頭D15K,031859_#40,38F18,C,VKS26</t>
-  </si>
-  <si>
-    <t>200006314</t>
+    <t>200006369</t>
+  </si>
+  <si>
+    <t>080100113204</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CW45</t>
+  </si>
+  <si>
+    <t>200006370</t>
+  </si>
+  <si>
+    <t>080200027803</t>
+  </si>
+  <si>
+    <t>PBM135機頭G2.5K,010831_DIN50,HSCDIN</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006371</t>
+  </si>
+  <si>
+    <t>080100033903</t>
+  </si>
+  <si>
+    <t>G2.5K主軸,010830_BT50,C0DIN</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006372</t>
+  </si>
+  <si>
+    <t>080200555000</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,C,AT8</t>
+  </si>
+  <si>
+    <t>200006374</t>
+  </si>
+  <si>
+    <t>080200560900</t>
+  </si>
+  <si>
+    <t>MVP16機頭D12K,031884_#50,42F25</t>
+  </si>
+  <si>
+    <t>200006375</t>
+  </si>
+  <si>
+    <t>080100126002</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021337_BT50,M50,CW45</t>
+  </si>
+  <si>
+    <t>200006376</t>
+  </si>
+  <si>
+    <t>080200548501</t>
+  </si>
+  <si>
+    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006377</t>
+  </si>
+  <si>
+    <t>080100090804</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006385</t>
+  </si>
+  <si>
+    <t>080200169703</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011297_780,BT50,55,045</t>
+  </si>
+  <si>
+    <t>200006386</t>
+  </si>
+  <si>
+    <t>080100022704</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BT50,0045</t>
+  </si>
+  <si>
+    <t>200006387</t>
+  </si>
+  <si>
+    <t>080200015603</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011167_Z1400,55A18,C</t>
+  </si>
+  <si>
+    <t>200006388</t>
+  </si>
+  <si>
+    <t>080300028903</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006389</t>
+  </si>
+  <si>
+    <t>080300029800</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,032936_1°-BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006390</t>
+  </si>
+  <si>
+    <t>080100094004</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006391</t>
+  </si>
+  <si>
+    <t>080200014502</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011166_Z1000,60A30,C</t>
+  </si>
+  <si>
+    <t>200006392</t>
   </si>
   <si>
     <t>080100015101</t>
@@ -142,70 +394,487 @@
     <t>D6K 主軸,010801_BT50,M50E,C045</t>
   </si>
   <si>
+    <t>200006394</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006395</t>
+  </si>
+  <si>
+    <t>REL  PRC  LKD  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006397</t>
+  </si>
+  <si>
+    <t>200006398</t>
+  </si>
+  <si>
+    <t>REL  PRC  LKD  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006403</t>
+  </si>
+  <si>
+    <t>080200549001</t>
+  </si>
+  <si>
+    <t>LG1370 NEO機頭D15K,021941_#40,48F23,C,AT15</t>
+  </si>
+  <si>
+    <t>200006404</t>
+  </si>
+  <si>
+    <t>200006406</t>
+  </si>
+  <si>
+    <t>080200551400</t>
+  </si>
+  <si>
+    <t>SP10機頭P12K,021023_#40,5GT-72,C</t>
+  </si>
+  <si>
+    <t>200006418</t>
+  </si>
+  <si>
+    <t>080200255802</t>
+  </si>
+  <si>
+    <t>5A65E機頭D15K,032370_BBT40,CAW45</t>
+  </si>
+  <si>
+    <t>200006419</t>
+  </si>
+  <si>
+    <t>080100087604</t>
+  </si>
+  <si>
+    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006423</t>
+  </si>
+  <si>
+    <t>080100120402</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021387_BT50,0W45</t>
+  </si>
+  <si>
+    <t>200006425</t>
+  </si>
+  <si>
+    <t>080300019809</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_2.5°-BT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006426</t>
+  </si>
+  <si>
+    <t>200006427</t>
+  </si>
+  <si>
+    <t>200006431</t>
+  </si>
+  <si>
+    <t>200006432</t>
+  </si>
+  <si>
+    <t>080200292203</t>
+  </si>
+  <si>
+    <t>H2110機頭G8K,011366_BT50,55F23,0AW45</t>
+  </si>
+  <si>
+    <t>200006433</t>
+  </si>
+  <si>
+    <t>200006434</t>
+  </si>
+  <si>
+    <t>200006439</t>
+  </si>
+  <si>
+    <t>080100087601</t>
+  </si>
+  <si>
+    <t>200006441</t>
+  </si>
+  <si>
+    <t>080200071201</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
+  </si>
+  <si>
+    <t>200006442</t>
+  </si>
+  <si>
+    <t>080200483300</t>
+  </si>
+  <si>
+    <t>H1365機頭G8K,021863_#40,42F25,C</t>
+  </si>
+  <si>
+    <t>200006443</t>
+  </si>
+  <si>
+    <t>080100110001</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021534_BBT40,CW45</t>
+  </si>
+  <si>
+    <t>200006444</t>
+  </si>
+  <si>
+    <t>080100066804</t>
+  </si>
+  <si>
+    <t>P10K 主軸,021361_BBT40,5GT,CW45</t>
+  </si>
+  <si>
+    <t>200006445</t>
+  </si>
+  <si>
+    <t>080200538902</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,42F25,C</t>
+  </si>
+  <si>
+    <t>200006446</t>
+  </si>
+  <si>
+    <t>080100113505</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CWDIN</t>
+  </si>
+  <si>
+    <t>200006447</t>
+  </si>
+  <si>
+    <t>200006448</t>
+  </si>
+  <si>
+    <t>200006449</t>
+  </si>
+  <si>
+    <t>080200015002</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011164_Z1200,55A18,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>200006450</t>
+  </si>
+  <si>
+    <t>080100015401</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,C0DIN</t>
+  </si>
+  <si>
+    <t>200006451</t>
+  </si>
+  <si>
+    <t>080300021009</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_1°-BT50-DIN-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006452</t>
+  </si>
+  <si>
+    <t>080200159204</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011282_780,BT50,55,CDIN</t>
+  </si>
+  <si>
+    <t>200006453</t>
+  </si>
+  <si>
+    <t>200006454</t>
+  </si>
+  <si>
+    <t>080200565901</t>
+  </si>
+  <si>
+    <t>H1100機頭G6K,021822_#50,48F23,C</t>
+  </si>
+  <si>
+    <t>200006455</t>
+  </si>
+  <si>
+    <t>080100113205</t>
+  </si>
+  <si>
     <t>REL  MSPT PCNF PRC  RMWB SETC</t>
   </si>
   <si>
-    <t>200006320</t>
-  </si>
-  <si>
-    <t>080200538802</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,55F23,C</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006321</t>
-  </si>
-  <si>
-    <t>080100116404</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>200006324</t>
-  </si>
-  <si>
-    <t>080200170704</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011297_780,BBT50,55,C45</t>
-  </si>
-  <si>
-    <t>200006325</t>
-  </si>
-  <si>
-    <t>080100036004</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,C045</t>
-  </si>
-  <si>
-    <t>200006326</t>
-  </si>
-  <si>
-    <t>080300024804</t>
-  </si>
-  <si>
-    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
-  </si>
-  <si>
-    <t>200006327</t>
-  </si>
-  <si>
-    <t>080200015102</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,60A30,C</t>
-  </si>
-  <si>
-    <t>200006328</t>
-  </si>
-  <si>
-    <t>200006329</t>
+    <t>200006456</t>
+  </si>
+  <si>
+    <t>200006457</t>
+  </si>
+  <si>
+    <t>200006458</t>
+  </si>
+  <si>
+    <t>080200229206</t>
+  </si>
+  <si>
+    <t>HEP機頭G6K,021570_780,BT50,48,CDIN</t>
+  </si>
+  <si>
+    <t>200006459</t>
+  </si>
+  <si>
+    <t>200006460</t>
+  </si>
+  <si>
+    <t>200006461</t>
+  </si>
+  <si>
+    <t>200006462</t>
+  </si>
+  <si>
+    <t>080100056404</t>
+  </si>
+  <si>
+    <t>P10K 主軸,021361_BT40,5GT,0W45</t>
+  </si>
+  <si>
+    <t>200006463</t>
+  </si>
+  <si>
+    <t>080200229305</t>
+  </si>
+  <si>
+    <t>HEP機頭G6K,021570_780,BT50,55,045</t>
+  </si>
+  <si>
+    <t>200006464</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006465</t>
+  </si>
+  <si>
+    <t>080200015703</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011167_Z1400,60A30,C</t>
+  </si>
+  <si>
+    <t>200006466</t>
+  </si>
+  <si>
+    <t>080300029103</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006467</t>
+  </si>
+  <si>
+    <t>080300029301</t>
+  </si>
+  <si>
+    <t>自動頭HF-AE50,032022_BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006468</t>
+  </si>
+  <si>
+    <t>080100084704</t>
+  </si>
+  <si>
+    <t>D15K 主軸,010017_BT40,M60,CWDIN</t>
+  </si>
+  <si>
+    <t>200006469</t>
+  </si>
+  <si>
+    <t>200006470</t>
+  </si>
+  <si>
+    <t>080200570600</t>
+  </si>
+  <si>
+    <t>TGV106機頭DA20K,021853_#40,d38F18</t>
+  </si>
+  <si>
+    <t>200006471</t>
+  </si>
+  <si>
+    <t>080100158004</t>
+  </si>
+  <si>
+    <t>DA20K主軸,021853,oil-air_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>200006472</t>
+  </si>
+  <si>
+    <t>080200070801</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>200006473</t>
+  </si>
+  <si>
+    <t>200006474</t>
+  </si>
+  <si>
+    <t>200006475</t>
+  </si>
+  <si>
+    <t>080200237804</t>
+  </si>
+  <si>
+    <t>HEP機頭D20K,021783_780,A63,38,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006476</t>
+  </si>
+  <si>
+    <t>080100050201</t>
+  </si>
+  <si>
+    <t>D20K 主軸,010683_A63,M50,C0</t>
+  </si>
+  <si>
+    <t>200006477</t>
+  </si>
+  <si>
+    <t>080200017802</t>
+  </si>
+  <si>
+    <t>EA機頭G8K,011262_Z1200,48A15,C</t>
+  </si>
+  <si>
+    <t>200006478</t>
+  </si>
+  <si>
+    <t>200006479</t>
+  </si>
+  <si>
+    <t>080100018301</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>200006480</t>
+  </si>
+  <si>
+    <t>080100088406</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021177_BT40,M60,0W45</t>
+  </si>
+  <si>
+    <t>200006481</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006482</t>
+  </si>
+  <si>
+    <t>080300029900</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,032731,G5K_1°-BBT50-45°-5K-C-F</t>
+  </si>
+  <si>
+    <t>200006483</t>
+  </si>
+  <si>
+    <t>ZP09</t>
+  </si>
+  <si>
+    <t>630000326</t>
+  </si>
+  <si>
+    <t>080200014702</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
+  </si>
+  <si>
+    <t>PENNY</t>
+  </si>
+  <si>
+    <t>630000329</t>
+  </si>
+  <si>
+    <t>080300029000</t>
+  </si>
+  <si>
+    <t>HF-AU,032731_1°-BT50-45°-4K-C-F,溫降案</t>
+  </si>
+  <si>
+    <t>630000331</t>
+  </si>
+  <si>
+    <t>080200332002</t>
+  </si>
+  <si>
+    <t>PBM115機頭G4K,011381_BT50,FO2C45</t>
+  </si>
+  <si>
+    <t>630000332</t>
+  </si>
+  <si>
+    <t>080100145201</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M65,0045</t>
+  </si>
+  <si>
+    <t>630000333</t>
+  </si>
+  <si>
+    <t>080200530600</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
+  </si>
+  <si>
+    <t>630000336</t>
+  </si>
+  <si>
+    <t>080100016701</t>
+  </si>
+  <si>
+    <t>D8K 主軸,010801_BT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>630000337</t>
   </si>
   <si>
     <t>080300018208</t>
@@ -214,649 +883,13 @@
     <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
   </si>
   <si>
-    <t>200006330</t>
-  </si>
-  <si>
-    <t>200006344</t>
-  </si>
-  <si>
-    <t>080200158404</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011282_780,BT50,42,CDIN</t>
-  </si>
-  <si>
-    <t>200006345</t>
-  </si>
-  <si>
-    <t>080100023404</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>200006349</t>
-  </si>
-  <si>
-    <t>200006361</t>
-  </si>
-  <si>
-    <t>080200527500</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,38F18</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006366</t>
-  </si>
-  <si>
-    <t>080200539403</t>
-  </si>
-  <si>
-    <t>H1682機頭G8K,021565_#50,42F25,C</t>
-  </si>
-  <si>
-    <t>200006367</t>
-  </si>
-  <si>
-    <t>080100122802</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>200006368</t>
-  </si>
-  <si>
-    <t>080200286203</t>
-  </si>
-  <si>
-    <t>H2110機頭G6K,011026_BT50,42F25,CAW45</t>
-  </si>
-  <si>
-    <t>200006369</t>
-  </si>
-  <si>
-    <t>080100113204</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CW45</t>
-  </si>
-  <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>080200027803</t>
-  </si>
-  <si>
-    <t>PBM135機頭G2.5K,010831_DIN50,HSCDIN</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006371</t>
-  </si>
-  <si>
-    <t>080100033903</t>
-  </si>
-  <si>
-    <t>G2.5K主軸,010830_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006372</t>
-  </si>
-  <si>
-    <t>080200555000</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,C,AT8</t>
-  </si>
-  <si>
-    <t>200006374</t>
-  </si>
-  <si>
-    <t>080200560900</t>
-  </si>
-  <si>
-    <t>MVP16機頭D12K,031884_#50,42F25</t>
-  </si>
-  <si>
-    <t>200006375</t>
-  </si>
-  <si>
-    <t>080100126002</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021337_BT50,M50,CW45</t>
-  </si>
-  <si>
-    <t>200006376</t>
-  </si>
-  <si>
-    <t>080200548501</t>
-  </si>
-  <si>
-    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006377</t>
-  </si>
-  <si>
-    <t>080100090804</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006385</t>
-  </si>
-  <si>
-    <t>080200169703</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011297_780,BT50,55,045</t>
-  </si>
-  <si>
-    <t>200006386</t>
-  </si>
-  <si>
-    <t>080100022704</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BT50,0045</t>
-  </si>
-  <si>
-    <t>200006387</t>
-  </si>
-  <si>
-    <t>080200015603</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011167_Z1400,55A18,C</t>
-  </si>
-  <si>
-    <t>200006388</t>
-  </si>
-  <si>
-    <t>080300028903</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006389</t>
-  </si>
-  <si>
-    <t>080300029800</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,032936_1°-BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006390</t>
-  </si>
-  <si>
-    <t>080100094004</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006391</t>
-  </si>
-  <si>
-    <t>080200014502</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011166_Z1000,60A30,C</t>
-  </si>
-  <si>
-    <t>200006392</t>
-  </si>
-  <si>
-    <t>200006394</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006395</t>
-  </si>
-  <si>
-    <t>200006397</t>
-  </si>
-  <si>
-    <t>200006398</t>
-  </si>
-  <si>
-    <t>200006403</t>
-  </si>
-  <si>
-    <t>080200549001</t>
-  </si>
-  <si>
-    <t>LG1370 NEO機頭D15K,021941_#40,48F23,C,AT15</t>
-  </si>
-  <si>
-    <t>200006404</t>
-  </si>
-  <si>
-    <t>200006406</t>
-  </si>
-  <si>
-    <t>080200551400</t>
-  </si>
-  <si>
-    <t>SP10機頭P12K,021023_#40,5GT-72,C</t>
-  </si>
-  <si>
-    <t>200006412</t>
-  </si>
-  <si>
-    <t>080200532700</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,48F18</t>
-  </si>
-  <si>
-    <t>200006413</t>
-  </si>
-  <si>
-    <t>200006418</t>
-  </si>
-  <si>
-    <t>080200255802</t>
-  </si>
-  <si>
-    <t>5A65E機頭D15K,032370_BBT40,CAW45</t>
-  </si>
-  <si>
-    <t>200006419</t>
-  </si>
-  <si>
-    <t>080100087604</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006423</t>
-  </si>
-  <si>
-    <t>080100120402</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BT50,0W45</t>
-  </si>
-  <si>
-    <t>200006425</t>
-  </si>
-  <si>
-    <t>080300019809</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_2.5°-BT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006426</t>
-  </si>
-  <si>
-    <t>200006427</t>
-  </si>
-  <si>
-    <t>200006431</t>
-  </si>
-  <si>
-    <t>200006432</t>
-  </si>
-  <si>
-    <t>080200292203</t>
-  </si>
-  <si>
-    <t>H2110機頭G8K,011366_BT50,55F23,0AW45</t>
-  </si>
-  <si>
-    <t>200006433</t>
-  </si>
-  <si>
-    <t>200006434</t>
-  </si>
-  <si>
-    <t>200006439</t>
-  </si>
-  <si>
-    <t>080100087601</t>
-  </si>
-  <si>
-    <t>200006441</t>
-  </si>
-  <si>
-    <t>080200071201</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
-  </si>
-  <si>
-    <t>200006442</t>
-  </si>
-  <si>
-    <t>080200483300</t>
-  </si>
-  <si>
-    <t>H1365機頭G8K,021863_#40,42F25,C</t>
-  </si>
-  <si>
-    <t>200006443</t>
-  </si>
-  <si>
-    <t>080100110001</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021534_BBT40,CW45</t>
-  </si>
-  <si>
-    <t>200006444</t>
-  </si>
-  <si>
-    <t>080100066804</t>
-  </si>
-  <si>
-    <t>P10K 主軸,021361_BBT40,5GT,CW45</t>
-  </si>
-  <si>
-    <t>200006445</t>
-  </si>
-  <si>
-    <t>080200538902</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,42F25,C</t>
-  </si>
-  <si>
-    <t>200006446</t>
-  </si>
-  <si>
-    <t>080100113505</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CWDIN</t>
-  </si>
-  <si>
-    <t>200006447</t>
-  </si>
-  <si>
-    <t>200006448</t>
-  </si>
-  <si>
-    <t>200006449</t>
-  </si>
-  <si>
-    <t>080200015002</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>200006450</t>
-  </si>
-  <si>
-    <t>080100015401</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M50E,C0DIN</t>
-  </si>
-  <si>
-    <t>200006451</t>
-  </si>
-  <si>
-    <t>080300021009</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BT50-DIN-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006452</t>
-  </si>
-  <si>
-    <t>080200159204</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011282_780,BT50,55,CDIN</t>
-  </si>
-  <si>
-    <t>200006453</t>
-  </si>
-  <si>
-    <t>200006454</t>
-  </si>
-  <si>
-    <t>080200565901</t>
-  </si>
-  <si>
-    <t>H1100機頭G6K,021822_#50,48F23,C</t>
-  </si>
-  <si>
-    <t>200006455</t>
-  </si>
-  <si>
-    <t>080100113205</t>
-  </si>
-  <si>
-    <t>200006456</t>
-  </si>
-  <si>
-    <t>200006457</t>
-  </si>
-  <si>
-    <t>200006458</t>
-  </si>
-  <si>
-    <t>080200229206</t>
-  </si>
-  <si>
-    <t>HEP機頭G6K,021570_780,BT50,48,CDIN</t>
-  </si>
-  <si>
-    <t>200006459</t>
-  </si>
-  <si>
-    <t>200006460</t>
-  </si>
-  <si>
-    <t>200006461</t>
-  </si>
-  <si>
-    <t>200006462</t>
-  </si>
-  <si>
-    <t>080100056404</t>
-  </si>
-  <si>
-    <t>P10K 主軸,021361_BT40,5GT,0W45</t>
-  </si>
-  <si>
-    <t>200006463</t>
-  </si>
-  <si>
-    <t>080200229305</t>
-  </si>
-  <si>
-    <t>HEP機頭G6K,021570_780,BT50,55,045</t>
-  </si>
-  <si>
-    <t>200006464</t>
-  </si>
-  <si>
-    <t>200006465</t>
-  </si>
-  <si>
-    <t>080200015703</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011167_Z1400,60A30,C</t>
-  </si>
-  <si>
-    <t>200006466</t>
-  </si>
-  <si>
-    <t>080300029103</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006467</t>
-  </si>
-  <si>
-    <t>080300029301</t>
-  </si>
-  <si>
-    <t>自動頭HF-AE50,032022_BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006468</t>
-  </si>
-  <si>
-    <t>080100084704</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BT40,M60,CWDIN</t>
-  </si>
-  <si>
-    <t>200006469</t>
-  </si>
-  <si>
-    <t>200006470</t>
-  </si>
-  <si>
-    <t>080200570600</t>
-  </si>
-  <si>
-    <t>TGV106機頭DA20K,021853_#40,d38F18</t>
-  </si>
-  <si>
-    <t>200006471</t>
-  </si>
-  <si>
-    <t>080100158004</t>
-  </si>
-  <si>
-    <t>DA20K主軸,021853,oil-air_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>200006472</t>
-  </si>
-  <si>
-    <t>080200070801</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
-  </si>
-  <si>
-    <t>200006473</t>
-  </si>
-  <si>
-    <t>200006474</t>
-  </si>
-  <si>
-    <t>200006475</t>
-  </si>
-  <si>
-    <t>080200237804</t>
-  </si>
-  <si>
-    <t>HEP機頭D20K,021783_780,A63,38,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006476</t>
-  </si>
-  <si>
-    <t>080100050201</t>
-  </si>
-  <si>
-    <t>D20K 主軸,010683_A63,M50,C0</t>
-  </si>
-  <si>
-    <t>ZP09</t>
-  </si>
-  <si>
-    <t>630000326</t>
-  </si>
-  <si>
-    <t>080200014702</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
-  </si>
-  <si>
-    <t>PENNY</t>
-  </si>
-  <si>
-    <t>630000329</t>
-  </si>
-  <si>
-    <t>080300029000</t>
-  </si>
-  <si>
-    <t>HF-AU,032731_1°-BT50-45°-4K-C-F,溫降案</t>
-  </si>
-  <si>
-    <t>630000331</t>
-  </si>
-  <si>
-    <t>080200332002</t>
-  </si>
-  <si>
-    <t>PBM115機頭G4K,011381_BT50,FO2C45</t>
-  </si>
-  <si>
-    <t>630000332</t>
-  </si>
-  <si>
-    <t>080100145201</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M65,0045</t>
-  </si>
-  <si>
-    <t>630000333</t>
-  </si>
-  <si>
-    <t>080200530600</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
-  </si>
-  <si>
-    <t>630000334</t>
-  </si>
-  <si>
-    <t>630000335</t>
-  </si>
-  <si>
-    <t>630000336</t>
-  </si>
-  <si>
-    <t>080100016701</t>
-  </si>
-  <si>
-    <t>D8K 主軸,010801_BT50,M50E,C045</t>
+    <t>630000338</t>
+  </si>
+  <si>
+    <t>080200254502</t>
+  </si>
+  <si>
+    <t>5A65E機頭D15K,032370_BT40,CAWDI</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1009,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1032,52 +1065,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1459,7 +1492,7 @@
         <v>46064</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
@@ -1485,19 +1518,19 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>34</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
       </c>
       <c r="G10" s="3">
         <v>45966</v>
@@ -1509,7 +1542,7 @@
         <v>46045</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
@@ -1535,19 +1568,19 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
       </c>
       <c r="G11" s="3">
         <v>45972</v>
@@ -1559,7 +1592,7 @@
         <v>46063</v>
       </c>
       <c r="J11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
@@ -1585,37 +1618,37 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>41</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" s="3">
+        <v>45979</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46101</v>
+      </c>
+      <c r="I12" s="3">
+        <v>46106</v>
+      </c>
+      <c r="J12" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="3">
-        <v>45978</v>
-      </c>
-      <c r="H12" s="3">
-        <v>45995</v>
-      </c>
-      <c r="I12" s="3">
-        <v>46001</v>
-      </c>
-      <c r="J12" t="s">
-        <v>43</v>
-      </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
       <c r="L12" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="M12" t="s">
         <v>6</v>
@@ -1635,31 +1668,31 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>45</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
       </c>
       <c r="G13" s="3">
         <v>45979</v>
       </c>
       <c r="H13" s="3">
+        <v>46098</v>
+      </c>
+      <c r="I13" s="3">
         <v>46101</v>
       </c>
-      <c r="I13" s="3">
-        <v>46106</v>
-      </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
@@ -1685,31 +1718,31 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
         <v>48</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
       </c>
       <c r="G14" s="3">
         <v>45979</v>
       </c>
       <c r="H14" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="I14" s="3">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1735,31 +1768,31 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" t="s">
         <v>51</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
       </c>
       <c r="G15" s="3">
         <v>45979</v>
       </c>
       <c r="H15" s="3">
-        <v>46097</v>
+        <v>46087</v>
       </c>
       <c r="I15" s="3">
-        <v>46100</v>
+        <v>46092</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
@@ -1785,31 +1818,31 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" t="s">
         <v>54</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
       </c>
       <c r="G16" s="3">
         <v>45979</v>
       </c>
       <c r="H16" s="3">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="I16" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1835,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -1844,22 +1877,22 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3">
         <v>45979</v>
       </c>
       <c r="H17" s="3">
-        <v>46094</v>
+        <v>46034</v>
       </c>
       <c r="I17" s="3">
-        <v>46100</v>
+        <v>46037</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -1885,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1894,28 +1927,28 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G18" s="3">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="H18" s="3">
-        <v>46066</v>
+        <v>46135</v>
       </c>
       <c r="I18" s="3">
-        <v>46085</v>
+        <v>46140</v>
       </c>
       <c r="J18" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" s="3">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="M18" t="s">
         <v>6</v>
@@ -1935,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -1944,28 +1977,28 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="3">
+        <v>45986</v>
+      </c>
+      <c r="H19" s="3">
+        <v>46127</v>
+      </c>
+      <c r="I19" s="3">
+        <v>46132</v>
+      </c>
+      <c r="J19" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46059</v>
-      </c>
-      <c r="I19" s="3">
-        <v>46065</v>
-      </c>
-      <c r="J19" t="s">
-        <v>4</v>
-      </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
       <c r="L19" s="3">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="M19" t="s">
         <v>6</v>
@@ -1985,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -1994,28 +2027,28 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="G20" s="3">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="H20" s="3">
-        <v>46120</v>
+        <v>45992</v>
       </c>
       <c r="I20" s="3">
-        <v>46141</v>
+        <v>46056</v>
       </c>
       <c r="J20" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="M20" t="s">
         <v>6</v>
@@ -2035,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -2044,28 +2077,28 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G21" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="H21" s="3">
-        <v>46034</v>
+        <v>46113</v>
       </c>
       <c r="I21" s="3">
-        <v>46037</v>
+        <v>46119</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="M21" t="s">
         <v>6</v>
@@ -2085,37 +2118,37 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>69</v>
       </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
       <c r="G22" s="3">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="H22" s="3">
-        <v>46135</v>
+        <v>46091</v>
       </c>
       <c r="I22" s="3">
-        <v>46140</v>
+        <v>46094</v>
       </c>
       <c r="J22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
       </c>
       <c r="L22" s="3">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="M22" t="s">
         <v>6</v>
@@ -2135,37 +2168,37 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>72</v>
       </c>
-      <c r="F23" t="s">
-        <v>73</v>
-      </c>
       <c r="G23" s="3">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="H23" s="3">
-        <v>46127</v>
+        <v>46086</v>
       </c>
       <c r="I23" s="3">
-        <v>46132</v>
+        <v>46091</v>
       </c>
       <c r="J23" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2185,37 +2218,37 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="G24" s="3">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="H24" s="3">
-        <v>45992</v>
+        <v>46101</v>
       </c>
       <c r="I24" s="3">
-        <v>46056</v>
+        <v>46106</v>
       </c>
       <c r="J24" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="M24" t="s">
         <v>6</v>
@@ -2235,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2244,28 +2277,28 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="H25" s="3">
-        <v>46113</v>
+        <v>46093</v>
       </c>
       <c r="I25" s="3">
-        <v>46119</v>
+        <v>46098</v>
       </c>
       <c r="J25" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="M25" t="s">
         <v>6</v>
@@ -2285,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2294,22 +2327,22 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G26" s="3">
         <v>45995</v>
       </c>
       <c r="H26" s="3">
-        <v>46091</v>
+        <v>46064</v>
       </c>
       <c r="I26" s="3">
-        <v>46094</v>
+        <v>46112</v>
       </c>
       <c r="J26" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -2335,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2344,22 +2377,22 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G27" s="3">
         <v>45995</v>
       </c>
       <c r="H27" s="3">
-        <v>46086</v>
+        <v>46052</v>
       </c>
       <c r="I27" s="3">
-        <v>46091</v>
+        <v>46059</v>
       </c>
       <c r="J27" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -2385,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2394,28 +2427,28 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G28" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H28" s="3">
-        <v>46101</v>
+        <v>46106</v>
       </c>
       <c r="I28" s="3">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="J28" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M28" t="s">
         <v>6</v>
@@ -2435,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2444,28 +2477,28 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G29" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H29" s="3">
-        <v>46093</v>
+        <v>46108</v>
       </c>
       <c r="I29" s="3">
-        <v>46098</v>
+        <v>46111</v>
       </c>
       <c r="J29" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2485,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2494,28 +2527,28 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G30" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H30" s="3">
-        <v>46064</v>
+        <v>46100</v>
       </c>
       <c r="I30" s="3">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="J30" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M30" t="s">
         <v>6</v>
@@ -2535,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2544,28 +2577,28 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G31" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H31" s="3">
-        <v>46052</v>
+        <v>46111</v>
       </c>
       <c r="I31" s="3">
-        <v>46059</v>
+        <v>46113</v>
       </c>
       <c r="J31" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
       <c r="L31" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M31" t="s">
         <v>6</v>
@@ -2585,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2594,22 +2627,22 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G32" s="3">
         <v>46000</v>
       </c>
       <c r="H32" s="3">
-        <v>46106</v>
+        <v>46048</v>
       </c>
       <c r="I32" s="3">
-        <v>46108</v>
+        <v>46056</v>
       </c>
       <c r="J32" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -2635,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2644,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G33" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H33" s="3">
-        <v>46108</v>
+        <v>46063</v>
       </c>
       <c r="I33" s="3">
-        <v>46111</v>
+        <v>46066</v>
       </c>
       <c r="J33" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -2685,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2694,28 +2727,28 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G34" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H34" s="3">
-        <v>46100</v>
+        <v>46058</v>
       </c>
       <c r="I34" s="3">
-        <v>46105</v>
+        <v>46063</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -2735,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2744,28 +2777,28 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G35" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H35" s="3">
-        <v>46111</v>
+        <v>46002</v>
       </c>
       <c r="I35" s="3">
-        <v>46113</v>
+        <v>46013</v>
       </c>
       <c r="J35" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -2785,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -2794,28 +2827,28 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G36" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H36" s="3">
-        <v>46111</v>
+        <v>46021</v>
       </c>
       <c r="I36" s="3">
-        <v>46119</v>
+        <v>46065</v>
       </c>
       <c r="J36" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -2835,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -2844,22 +2877,22 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G37" s="3">
         <v>46002</v>
       </c>
       <c r="H37" s="3">
-        <v>46063</v>
+        <v>46022</v>
       </c>
       <c r="I37" s="3">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
@@ -2885,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -2894,22 +2927,22 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G38" s="3">
         <v>46002</v>
       </c>
       <c r="H38" s="3">
-        <v>46058</v>
+        <v>46105</v>
       </c>
       <c r="I38" s="3">
-        <v>46063</v>
+        <v>46108</v>
       </c>
       <c r="J38" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
@@ -2935,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -2944,28 +2977,28 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G39" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H39" s="3">
-        <v>46002</v>
+        <v>46037</v>
       </c>
       <c r="I39" s="3">
-        <v>46013</v>
+        <v>46048</v>
       </c>
       <c r="J39" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
       </c>
       <c r="L39" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M39" t="s">
         <v>6</v>
@@ -2985,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -2994,28 +3027,28 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G40" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H40" s="3">
-        <v>46013</v>
+        <v>46065</v>
       </c>
       <c r="I40" s="3">
-        <v>46034</v>
+        <v>46078</v>
       </c>
       <c r="J40" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3035,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3044,28 +3077,28 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
+        <v>123</v>
+      </c>
+      <c r="G41" s="3">
+        <v>46007</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46062</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46078</v>
+      </c>
+      <c r="J41" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="3">
-        <v>46002</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46006</v>
-      </c>
-      <c r="I41" s="3">
-        <v>46027</v>
-      </c>
-      <c r="J41" t="s">
-        <v>24</v>
-      </c>
       <c r="K41" t="s">
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3094,28 +3127,28 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" s="3">
+        <v>46007</v>
+      </c>
+      <c r="H42" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I42" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J42" t="s">
         <v>130</v>
       </c>
-      <c r="F42" t="s">
-        <v>131</v>
-      </c>
-      <c r="G42" s="3">
-        <v>46002</v>
-      </c>
-      <c r="H42" s="3">
-        <v>46105</v>
-      </c>
-      <c r="I42" s="3">
-        <v>46108</v>
-      </c>
-      <c r="J42" t="s">
-        <v>47</v>
-      </c>
       <c r="K42" t="s">
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3135,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3144,22 +3177,22 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F43" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="G43" s="3">
         <v>46007</v>
       </c>
       <c r="H43" s="3">
-        <v>46037</v>
+        <v>46066</v>
       </c>
       <c r="I43" s="3">
-        <v>46048</v>
+        <v>46085</v>
       </c>
       <c r="J43" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -3185,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3194,22 +3227,22 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="G44" s="3">
         <v>46007</v>
       </c>
       <c r="H44" s="3">
-        <v>46065</v>
+        <v>46078</v>
       </c>
       <c r="I44" s="3">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="J44" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
@@ -3235,37 +3268,37 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
+        <v>135</v>
+      </c>
+      <c r="F45" t="s">
         <v>136</v>
       </c>
-      <c r="C45" s="2">
-        <v>1</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0</v>
-      </c>
-      <c r="E45" t="s">
-        <v>133</v>
-      </c>
-      <c r="F45" t="s">
-        <v>134</v>
-      </c>
       <c r="G45" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="H45" s="3">
+        <v>46058</v>
+      </c>
+      <c r="I45" s="3">
         <v>46062</v>
       </c>
-      <c r="I45" s="3">
-        <v>46078</v>
-      </c>
       <c r="J45" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3285,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3294,28 +3327,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="G46" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="H46" s="3">
-        <v>46076</v>
+        <v>46038</v>
       </c>
       <c r="I46" s="3">
-        <v>46083</v>
+        <v>46049</v>
       </c>
       <c r="J46" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3335,37 +3368,37 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
         <v>139</v>
       </c>
-      <c r="C47" s="2">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
-        <v>133</v>
-      </c>
       <c r="F47" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G47" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="H47" s="3">
-        <v>46066</v>
+        <v>46132</v>
       </c>
       <c r="I47" s="3">
-        <v>46085</v>
+        <v>46134</v>
       </c>
       <c r="J47" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3385,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3394,28 +3427,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="F48" t="s">
+        <v>143</v>
+      </c>
+      <c r="G48" s="3">
+        <v>46022</v>
+      </c>
+      <c r="H48" s="3">
+        <v>46121</v>
+      </c>
+      <c r="I48" s="3">
+        <v>46126</v>
+      </c>
+      <c r="J48" t="s">
         <v>42</v>
       </c>
-      <c r="G48" s="3">
-        <v>46007</v>
-      </c>
-      <c r="H48" s="3">
-        <v>46078</v>
-      </c>
-      <c r="I48" s="3">
-        <v>46085</v>
-      </c>
-      <c r="J48" t="s">
-        <v>47</v>
-      </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46007</v>
+        <v>46022</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3435,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3444,28 +3477,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F49" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G49" s="3">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="H49" s="3">
-        <v>46058</v>
+        <v>46114</v>
       </c>
       <c r="I49" s="3">
-        <v>46062</v>
+        <v>46121</v>
       </c>
       <c r="J49" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3485,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3494,28 +3527,28 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="F50" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="G50" s="3">
-        <v>46013</v>
+        <v>46028</v>
       </c>
       <c r="H50" s="3">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="I50" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="J50" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46013</v>
+        <v>46028</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3535,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3544,28 +3577,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G51" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="H51" s="3">
-        <v>46132</v>
+        <v>46091</v>
       </c>
       <c r="I51" s="3">
-        <v>46134</v>
+        <v>46114</v>
       </c>
       <c r="J51" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3585,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3594,28 +3627,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F52" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G52" s="3">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="H52" s="3">
-        <v>46086</v>
+        <v>46113</v>
       </c>
       <c r="I52" s="3">
-        <v>46090</v>
+        <v>46136</v>
       </c>
       <c r="J52" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -3635,37 +3668,37 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" t="s">
-        <v>149</v>
-      </c>
       <c r="F53" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G53" s="3">
-        <v>46048</v>
+        <v>46028</v>
       </c>
       <c r="H53" s="3">
-        <v>46086</v>
+        <v>46119</v>
       </c>
       <c r="I53" s="3">
-        <v>46090</v>
+        <v>46142</v>
       </c>
       <c r="J53" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -3685,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3694,28 +3727,28 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F54" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G54" s="3">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="H54" s="3">
-        <v>46121</v>
+        <v>46034</v>
       </c>
       <c r="I54" s="3">
-        <v>46126</v>
+        <v>46037</v>
       </c>
       <c r="J54" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -3735,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -3744,28 +3777,28 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F55" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G55" s="3">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="H55" s="3">
-        <v>46114</v>
+        <v>46078</v>
       </c>
       <c r="I55" s="3">
-        <v>46121</v>
+        <v>46084</v>
       </c>
       <c r="J55" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -3785,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -3794,28 +3827,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F56" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G56" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="H56" s="3">
-        <v>46041</v>
+        <v>46063</v>
       </c>
       <c r="I56" s="3">
-        <v>46044</v>
+        <v>46066</v>
       </c>
       <c r="J56" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K56" t="s">
         <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -3844,28 +3877,28 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="F57" t="s">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="G57" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="H57" s="3">
-        <v>46091</v>
+        <v>46056</v>
       </c>
       <c r="I57" s="3">
-        <v>46114</v>
+        <v>46059</v>
       </c>
       <c r="J57" t="s">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="K57" t="s">
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -3885,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -3894,28 +3927,28 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F58" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="G58" s="3">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="H58" s="3">
-        <v>46113</v>
+        <v>46043</v>
       </c>
       <c r="I58" s="3">
-        <v>46136</v>
+        <v>46048</v>
       </c>
       <c r="J58" t="s">
-        <v>164</v>
+        <v>87</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -3935,37 +3968,37 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>165</v>
+      </c>
+      <c r="F59" t="s">
         <v>166</v>
       </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" t="s">
-        <v>162</v>
-      </c>
-      <c r="F59" t="s">
-        <v>163</v>
-      </c>
       <c r="G59" s="3">
-        <v>46028</v>
+        <v>46043</v>
       </c>
       <c r="H59" s="3">
-        <v>46119</v>
+        <v>46077</v>
       </c>
       <c r="I59" s="3">
-        <v>46142</v>
+        <v>46079</v>
       </c>
       <c r="J59" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46028</v>
+        <v>46043</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -3994,28 +4027,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G60" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="H60" s="3">
-        <v>46034</v>
+        <v>46132</v>
       </c>
       <c r="I60" s="3">
-        <v>46037</v>
+        <v>46135</v>
       </c>
       <c r="J60" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4035,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4044,28 +4077,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F61" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G61" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="H61" s="3">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="I61" s="3">
-        <v>46084</v>
+        <v>46132</v>
       </c>
       <c r="J61" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4085,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4094,28 +4127,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="F62" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G62" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="H62" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="I62" s="3">
-        <v>46066</v>
+        <v>46048</v>
       </c>
       <c r="J62" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4135,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4144,28 +4177,28 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>45</v>
+        <v>177</v>
       </c>
       <c r="F63" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="G63" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="H63" s="3">
-        <v>46056</v>
+        <v>46142</v>
       </c>
       <c r="I63" s="3">
-        <v>46059</v>
+        <v>46148</v>
       </c>
       <c r="J63" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4185,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4194,28 +4227,28 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F64" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="G64" s="3">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="H64" s="3">
-        <v>46043</v>
+        <v>46139</v>
       </c>
       <c r="I64" s="3">
-        <v>46048</v>
+        <v>46142</v>
       </c>
       <c r="J64" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4235,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4244,28 +4277,28 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>176</v>
+        <v>40</v>
       </c>
       <c r="F65" t="s">
-        <v>177</v>
+        <v>41</v>
       </c>
       <c r="G65" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H65" s="3">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="I65" s="3">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="J65" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4285,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4294,28 +4327,28 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G66" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H66" s="3">
-        <v>46132</v>
+        <v>46078</v>
       </c>
       <c r="I66" s="3">
-        <v>46135</v>
+        <v>46084</v>
       </c>
       <c r="J66" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4335,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4344,28 +4377,28 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F67" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G67" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H67" s="3">
-        <v>46127</v>
+        <v>46076</v>
       </c>
       <c r="I67" s="3">
-        <v>46132</v>
+        <v>46086</v>
       </c>
       <c r="J67" t="s">
-        <v>47</v>
+        <v>187</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M67" t="s">
         <v>6</v>
@@ -4385,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4394,28 +4427,28 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F68" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G68" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H68" s="3">
-        <v>46043</v>
+        <v>46063</v>
       </c>
       <c r="I68" s="3">
-        <v>46048</v>
+        <v>46076</v>
       </c>
       <c r="J68" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4435,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4444,22 +4477,22 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F69" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G69" s="3">
         <v>46044</v>
       </c>
       <c r="H69" s="3">
-        <v>46142</v>
+        <v>46126</v>
       </c>
       <c r="I69" s="3">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="J69" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4485,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4494,22 +4527,22 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F70" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G70" s="3">
         <v>46044</v>
       </c>
       <c r="H70" s="3">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="I70" s="3">
-        <v>46142</v>
+        <v>46085</v>
       </c>
       <c r="J70" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4535,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4544,22 +4577,22 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F71" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G71" s="3">
         <v>46044</v>
       </c>
       <c r="H71" s="3">
-        <v>46085</v>
+        <v>46064</v>
       </c>
       <c r="I71" s="3">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="J71" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
@@ -4585,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4594,22 +4627,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F72" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G72" s="3">
         <v>46044</v>
       </c>
       <c r="H72" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="I72" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="J72" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
@@ -4635,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4644,22 +4677,22 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F73" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="G73" s="3">
         <v>46044</v>
       </c>
       <c r="H73" s="3">
-        <v>46076</v>
+        <v>46058</v>
       </c>
       <c r="I73" s="3">
-        <v>46086</v>
+        <v>46063</v>
       </c>
       <c r="J73" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
@@ -4685,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4694,22 +4727,22 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F74" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G74" s="3">
         <v>46044</v>
       </c>
       <c r="H74" s="3">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="I74" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="J74" t="s">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
@@ -4735,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -4744,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>203</v>
+        <v>60</v>
       </c>
       <c r="F75" t="s">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="G75" s="3">
         <v>46044</v>
       </c>
       <c r="H75" s="3">
-        <v>46126</v>
+        <v>46064</v>
       </c>
       <c r="I75" s="3">
-        <v>46150</v>
+        <v>46076</v>
       </c>
       <c r="J75" t="s">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
@@ -4785,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4794,28 +4827,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F76" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G76" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H76" s="3">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="I76" s="3">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="J76" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -4835,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -4844,28 +4877,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F77" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G77" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H77" s="3">
-        <v>46064</v>
+        <v>46084</v>
       </c>
       <c r="I77" s="3">
-        <v>46076</v>
+        <v>46087</v>
       </c>
       <c r="J77" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -4885,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -4894,28 +4927,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="F78" t="s">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="G78" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H78" s="3">
-        <v>46065</v>
+        <v>46085</v>
       </c>
       <c r="I78" s="3">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="J78" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -4935,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -4944,28 +4977,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="F79" t="s">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="G79" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H79" s="3">
-        <v>46058</v>
+        <v>46078</v>
       </c>
       <c r="I79" s="3">
-        <v>46063</v>
+        <v>46084</v>
       </c>
       <c r="J79" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -4985,37 +5018,37 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0</v>
+      </c>
+      <c r="E80" t="s">
+        <v>213</v>
+      </c>
+      <c r="F80" t="s">
         <v>214</v>
       </c>
-      <c r="C80" s="2">
-        <v>1</v>
-      </c>
-      <c r="D80" s="2">
-        <v>0</v>
-      </c>
-      <c r="E80" t="s">
-        <v>206</v>
-      </c>
-      <c r="F80" t="s">
-        <v>207</v>
-      </c>
       <c r="G80" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H80" s="3">
-        <v>46077</v>
+        <v>46051</v>
       </c>
       <c r="I80" s="3">
-        <v>46083</v>
+        <v>46056</v>
       </c>
       <c r="J80" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5044,19 +5077,19 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>72</v>
+        <v>216</v>
       </c>
       <c r="F81" t="s">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="G81" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="H81" s="3">
-        <v>46064</v>
+        <v>46086</v>
       </c>
       <c r="I81" s="3">
-        <v>46076</v>
+        <v>46091</v>
       </c>
       <c r="J81" t="s">
         <v>4</v>
@@ -5065,7 +5098,7 @@
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5085,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5094,28 +5127,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="F82" t="s">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="G82" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="H82" s="3">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="I82" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="J82" t="s">
-        <v>4</v>
+        <v>219</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5135,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5144,28 +5177,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>72</v>
+        <v>221</v>
       </c>
       <c r="F83" t="s">
-        <v>73</v>
+        <v>222</v>
       </c>
       <c r="G83" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H83" s="3">
-        <v>46084</v>
+        <v>46050</v>
       </c>
       <c r="I83" s="3">
-        <v>46087</v>
+        <v>46059</v>
       </c>
       <c r="J83" t="s">
-        <v>4</v>
+        <v>203</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5185,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5194,19 +5227,19 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>224</v>
       </c>
       <c r="F84" t="s">
-        <v>46</v>
+        <v>225</v>
       </c>
       <c r="G84" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H84" s="3">
-        <v>46085</v>
+        <v>46050</v>
       </c>
       <c r="I84" s="3">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="J84" t="s">
         <v>4</v>
@@ -5215,7 +5248,7 @@
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5235,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5244,19 +5277,19 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="F85" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="G85" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H85" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="I85" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="J85" t="s">
         <v>4</v>
@@ -5265,7 +5298,7 @@
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5285,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5294,28 +5327,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F86" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G86" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H86" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="I86" s="3">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="J86" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5335,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5344,28 +5377,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F87" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G87" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H87" s="3">
-        <v>46086</v>
+        <v>46050</v>
       </c>
       <c r="I87" s="3">
-        <v>46091</v>
+        <v>46056</v>
       </c>
       <c r="J87" t="s">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5385,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5394,28 +5427,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="F88" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="G88" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H88" s="3">
-        <v>46083</v>
+        <v>46066</v>
       </c>
       <c r="I88" s="3">
-        <v>46086</v>
+        <v>46078</v>
       </c>
       <c r="J88" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5435,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5444,22 +5477,22 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F89" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G89" s="3">
         <v>46050</v>
       </c>
       <c r="H89" s="3">
-        <v>46050</v>
+        <v>46059</v>
       </c>
       <c r="I89" s="3">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="J89" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
@@ -5485,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5494,22 +5527,22 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F90" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="G90" s="3">
         <v>46050</v>
       </c>
       <c r="H90" s="3">
-        <v>46050</v>
+        <v>46083</v>
       </c>
       <c r="I90" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="J90" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
@@ -5535,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5544,22 +5577,22 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F91" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="G91" s="3">
         <v>46050</v>
       </c>
       <c r="H91" s="3">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="I91" s="3">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="J91" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
@@ -5585,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5594,22 +5627,22 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F92" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G92" s="3">
         <v>46050</v>
       </c>
       <c r="H92" s="3">
-        <v>46050</v>
+        <v>46083</v>
       </c>
       <c r="I92" s="3">
-        <v>46056</v>
+        <v>46084</v>
       </c>
       <c r="J92" t="s">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
@@ -5635,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5644,10 +5677,10 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F93" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G93" s="3">
         <v>46050</v>
@@ -5659,7 +5692,7 @@
         <v>46056</v>
       </c>
       <c r="J93" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
@@ -5685,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5694,22 +5727,22 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F94" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G94" s="3">
         <v>46050</v>
       </c>
       <c r="H94" s="3">
-        <v>46066</v>
+        <v>46050</v>
       </c>
       <c r="I94" s="3">
-        <v>46078</v>
+        <v>46055</v>
       </c>
       <c r="J94" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
@@ -5735,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -5744,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F95" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="G95" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="H95" s="3">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="I95" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="J95" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -5785,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -5794,28 +5827,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="F96" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="G96" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="H96" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="I96" s="3">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="J96" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -5835,37 +5868,37 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C97" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D97" s="2">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="F97" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G97" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="H97" s="3">
-        <v>46086</v>
+        <v>46052</v>
       </c>
       <c r="I97" s="3">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="J97" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -5885,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -5894,19 +5927,19 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F98" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G98" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="H98" s="3">
-        <v>46055</v>
+        <v>46077</v>
       </c>
       <c r="I98" s="3">
-        <v>46056</v>
+        <v>46084</v>
       </c>
       <c r="J98" t="s">
         <v>4</v>
@@ -5915,7 +5948,7 @@
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -5935,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -5944,28 +5977,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="F99" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="G99" s="3">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="H99" s="3">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="I99" s="3">
-        <v>46056</v>
+        <v>46064</v>
       </c>
       <c r="J99" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -5985,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -5994,28 +6027,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F100" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G100" s="3">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="H100" s="3">
-        <v>46050</v>
+        <v>46119</v>
       </c>
       <c r="I100" s="3">
+        <v>46142</v>
+      </c>
+      <c r="J100" t="s">
+        <v>153</v>
+      </c>
+      <c r="K100" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>46055</v>
-      </c>
-      <c r="J100" t="s">
-        <v>164</v>
-      </c>
-      <c r="K100" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>46050</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6032,10 +6065,10 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" t="s">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6044,28 +6077,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="F101" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="G101" s="3">
-        <v>46028</v>
+        <v>46055</v>
       </c>
       <c r="H101" s="3">
-        <v>46028</v>
+        <v>46114</v>
       </c>
       <c r="I101" s="3">
-        <v>46037</v>
+        <v>46136</v>
       </c>
       <c r="J101" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="K101" t="s">
-        <v>264</v>
+        <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46028</v>
+        <v>46055</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6082,10 +6115,10 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B102" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6094,28 +6127,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F102" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G102" s="3">
-        <v>46035</v>
+        <v>46028</v>
       </c>
       <c r="H102" s="3">
-        <v>46044</v>
+        <v>46028</v>
       </c>
       <c r="I102" s="3">
-        <v>46066</v>
+        <v>46037</v>
       </c>
       <c r="J102" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="K102" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="L102" s="3">
-        <v>46035</v>
+        <v>46028</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6132,10 +6165,10 @@
     </row>
     <row r="103" spans="1:16">
       <c r="A103" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B103" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6144,28 +6177,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F103" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G103" s="3">
-        <v>46042</v>
+        <v>46035</v>
       </c>
       <c r="H103" s="3">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="I103" s="3">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="J103" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K103" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="L103" s="3">
-        <v>46042</v>
+        <v>46035</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6182,40 +6215,40 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B104" t="s">
+        <v>275</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
+        <v>276</v>
+      </c>
+      <c r="F104" t="s">
+        <v>277</v>
+      </c>
+      <c r="G104" s="3">
+        <v>46042</v>
+      </c>
+      <c r="H104" s="3">
+        <v>46042</v>
+      </c>
+      <c r="I104" s="3">
+        <v>46043</v>
+      </c>
+      <c r="J104" t="s">
+        <v>35</v>
+      </c>
+      <c r="K104" t="s">
         <v>271</v>
       </c>
-      <c r="C104" s="2">
-        <v>1</v>
-      </c>
-      <c r="D104" s="2">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
-        <v>272</v>
-      </c>
-      <c r="F104" t="s">
-        <v>273</v>
-      </c>
-      <c r="G104" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H104" s="3">
-        <v>46051</v>
-      </c>
-      <c r="I104" s="3">
-        <v>46057</v>
-      </c>
-      <c r="J104" t="s">
-        <v>4</v>
-      </c>
-      <c r="K104" t="s">
-        <v>264</v>
-      </c>
       <c r="L104" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6232,10 +6265,10 @@
     </row>
     <row r="105" spans="1:16">
       <c r="A105" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B105" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6244,28 +6277,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F105" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G105" s="3">
-        <v>46052</v>
+        <v>46043</v>
       </c>
       <c r="H105" s="3">
-        <v>46059</v>
+        <v>46051</v>
       </c>
       <c r="I105" s="3">
-        <v>46062</v>
+        <v>46057</v>
       </c>
       <c r="J105" t="s">
         <v>4</v>
       </c>
       <c r="K105" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="L105" s="3">
-        <v>46052</v>
+        <v>46043</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6282,10 +6315,10 @@
     </row>
     <row r="106" spans="1:16">
       <c r="A106" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B106" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6294,25 +6327,25 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="F106" t="s">
-        <v>31</v>
+        <v>283</v>
       </c>
       <c r="G106" s="3">
         <v>46052</v>
       </c>
       <c r="H106" s="3">
-        <v>46064</v>
+        <v>46059</v>
       </c>
       <c r="I106" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="J106" t="s">
         <v>4</v>
       </c>
       <c r="K106" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="L106" s="3">
         <v>46052</v>
@@ -6332,10 +6365,10 @@
     </row>
     <row r="107" spans="1:16">
       <c r="A107" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B107" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6344,25 +6377,25 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="F107" t="s">
-        <v>35</v>
+        <v>286</v>
       </c>
       <c r="G107" s="3">
         <v>46052</v>
       </c>
       <c r="H107" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="I107" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="J107" t="s">
         <v>4</v>
       </c>
       <c r="K107" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="L107" s="3">
         <v>46052</v>
@@ -6382,10 +6415,10 @@
     </row>
     <row r="108" spans="1:16">
       <c r="A108" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B108" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6394,25 +6427,25 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F108" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G108" s="3">
         <v>46052</v>
       </c>
       <c r="H108" s="3">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="I108" s="3">
-        <v>46058</v>
+        <v>46083</v>
       </c>
       <c r="J108" t="s">
         <v>4</v>
       </c>
       <c r="K108" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="L108" s="3">
         <v>46052</v>
@@ -6427,6 +6460,56 @@
         <v>8</v>
       </c>
       <c r="P108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109" t="s">
+        <v>267</v>
+      </c>
+      <c r="B109" t="s">
+        <v>290</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" t="s">
+        <v>291</v>
+      </c>
+      <c r="F109" t="s">
+        <v>292</v>
+      </c>
+      <c r="G109" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H109" s="3">
+        <v>46064</v>
+      </c>
+      <c r="I109" s="3">
+        <v>46066</v>
+      </c>
+      <c r="J109" t="s">
+        <v>4</v>
+      </c>
+      <c r="K109" t="s">
+        <v>271</v>
+      </c>
+      <c r="L109" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M109" t="s">
+        <v>6</v>
+      </c>
+      <c r="N109" t="s">
+        <v>7</v>
+      </c>
+      <c r="O109" t="s">
+        <v>8</v>
+      </c>
+      <c r="P109" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="322">
   <si>
     <t>ZP02</t>
   </si>
@@ -25,820 +25,901 @@
     <t>H1370機頭G6K,011395_#50,55F23,C</t>
   </si>
   <si>
+    <t>REL  PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>SDCHANG</t>
+  </si>
+  <si>
+    <t>SHEO</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>200006077</t>
+  </si>
+  <si>
+    <t>200006254</t>
+  </si>
+  <si>
+    <t>080300020609</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_1°-BT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006320</t>
+  </si>
+  <si>
+    <t>080200538802</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,55F23,C</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006321</t>
+  </si>
+  <si>
+    <t>080100116404</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BBT50,CW45</t>
+  </si>
+  <si>
+    <t>200006324</t>
+  </si>
+  <si>
+    <t>080200170704</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011297_780,BBT50,55,C45</t>
+  </si>
+  <si>
+    <t>200006325</t>
+  </si>
+  <si>
+    <t>080100036004</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,C045</t>
+  </si>
+  <si>
+    <t>200006326</t>
+  </si>
+  <si>
+    <t>080300024804</t>
+  </si>
+  <si>
+    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
+  </si>
+  <si>
+    <t>200006344</t>
+  </si>
+  <si>
+    <t>080200158404</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011282_780,BT50,42,CDIN</t>
+  </si>
+  <si>
+    <t>200006345</t>
+  </si>
+  <si>
+    <t>080100023404</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BT50,C0DIN</t>
+  </si>
+  <si>
+    <t>200006366</t>
+  </si>
+  <si>
+    <t>080200539403</t>
+  </si>
+  <si>
+    <t>H1682機頭G8K,021565_#50,42F25,C</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006367</t>
+  </si>
+  <si>
+    <t>080100122802</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021387_BBT50,CW45</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006368</t>
+  </si>
+  <si>
+    <t>080200286203</t>
+  </si>
+  <si>
+    <t>H2110機頭G6K,011026_BT50,42F25,CAW45</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006370</t>
+  </si>
+  <si>
+    <t>080200027803</t>
+  </si>
+  <si>
+    <t>PBM135機頭G2.5K,010831_DIN50,HSCDIN</t>
+  </si>
+  <si>
+    <t>200006371</t>
+  </si>
+  <si>
+    <t>080100033903</t>
+  </si>
+  <si>
+    <t>G2.5K主軸,010830_BT50,C0DIN</t>
+  </si>
+  <si>
+    <t>200006372</t>
+  </si>
+  <si>
+    <t>080200555000</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,C,AT8</t>
+  </si>
+  <si>
+    <t>200006374</t>
+  </si>
+  <si>
+    <t>080200560900</t>
+  </si>
+  <si>
+    <t>MVP16機頭D12K,031884_#50,42F25</t>
+  </si>
+  <si>
+    <t>200006376</t>
+  </si>
+  <si>
+    <t>080200548501</t>
+  </si>
+  <si>
+    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006385</t>
+  </si>
+  <si>
+    <t>080200169703</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011297_780,BT50,55,045</t>
+  </si>
+  <si>
+    <t>200006388</t>
+  </si>
+  <si>
+    <t>080300028903</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006389</t>
+  </si>
+  <si>
+    <t>080300029800</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,032936_1°-BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006390</t>
+  </si>
+  <si>
+    <t>080100094004</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006391</t>
+  </si>
+  <si>
+    <t>080200014502</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011166_Z1000,60A30,C</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006392</t>
+  </si>
+  <si>
+    <t>080100015101</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>200006394</t>
+  </si>
+  <si>
+    <t>200006397</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006418</t>
+  </si>
+  <si>
+    <t>080200255802</t>
+  </si>
+  <si>
+    <t>5A65E機頭D15K,032370_BBT40,CAW45</t>
+  </si>
+  <si>
+    <t>200006419</t>
+  </si>
+  <si>
+    <t>080100087604</t>
+  </si>
+  <si>
+    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006423</t>
+  </si>
+  <si>
+    <t>080100120402</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021387_BT50,0W45</t>
+  </si>
+  <si>
+    <t>200006431</t>
+  </si>
+  <si>
+    <t>200006432</t>
+  </si>
+  <si>
+    <t>080200292203</t>
+  </si>
+  <si>
+    <t>H2110機頭G8K,011366_BT50,55F23,0AW45</t>
+  </si>
+  <si>
+    <t>200006433</t>
+  </si>
+  <si>
+    <t>200006442</t>
+  </si>
+  <si>
+    <t>080200483300</t>
+  </si>
+  <si>
+    <t>H1365機頭G8K,021863_#40,42F25,C</t>
+  </si>
+  <si>
+    <t>200006443</t>
+  </si>
+  <si>
+    <t>080100110001</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021534_BBT40,CW45</t>
+  </si>
+  <si>
+    <t>200006445</t>
+  </si>
+  <si>
+    <t>080200538902</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,42F25,C</t>
+  </si>
+  <si>
+    <t>200006446</t>
+  </si>
+  <si>
+    <t>080100113505</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CWDIN</t>
+  </si>
+  <si>
+    <t>200006447</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006448</t>
+  </si>
+  <si>
+    <t>200006449</t>
+  </si>
+  <si>
+    <t>080200015002</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011164_Z1200,55A18,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>200006450</t>
+  </si>
+  <si>
+    <t>080100015401</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,C0DIN</t>
+  </si>
+  <si>
     <t>REL  PRC  MANC SETC</t>
   </si>
   <si>
-    <t>SDCHANG</t>
-  </si>
-  <si>
-    <t>SHEO</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>200006077</t>
-  </si>
-  <si>
-    <t>200006191</t>
-  </si>
-  <si>
-    <t>080300015008</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_5°-BT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006232</t>
-  </si>
-  <si>
-    <t>080300024405</t>
-  </si>
-  <si>
-    <t>半自動頭HF-SU,011002_5°-BT50-45°-2.5K-0</t>
-  </si>
-  <si>
-    <t>200006241</t>
-  </si>
-  <si>
-    <t>080300020309</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BT50-45°-4K-0-F</t>
-  </si>
-  <si>
-    <t>200006254</t>
-  </si>
-  <si>
-    <t>080300020609</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006298</t>
-  </si>
-  <si>
-    <t>080200537201</t>
-  </si>
-  <si>
-    <t>LG1370機頭P12K,021728_#40,8YU-84,C</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006299</t>
-  </si>
-  <si>
-    <t>080200446902</t>
-  </si>
-  <si>
-    <t>5A65E機頭DA15K,032370_BT40,CAWDI</t>
-  </si>
-  <si>
-    <t>200006301</t>
-  </si>
-  <si>
-    <t>080100152306</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021856_BT40,M60,CWDIN</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006312</t>
-  </si>
-  <si>
-    <t>080200546802</t>
-  </si>
-  <si>
-    <t>MVP11機頭D15K,031859_#40,38F18,C,VKS26</t>
-  </si>
-  <si>
-    <t>200006320</t>
-  </si>
-  <si>
-    <t>080200538802</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,55F23,C</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006321</t>
-  </si>
-  <si>
-    <t>080100116404</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>200006324</t>
-  </si>
-  <si>
-    <t>080200170704</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011297_780,BBT50,55,C45</t>
-  </si>
-  <si>
-    <t>200006325</t>
-  </si>
-  <si>
-    <t>080100036004</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,C045</t>
-  </si>
-  <si>
-    <t>200006326</t>
-  </si>
-  <si>
-    <t>080300024804</t>
-  </si>
-  <si>
-    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
-  </si>
-  <si>
-    <t>200006330</t>
-  </si>
-  <si>
-    <t>200006344</t>
-  </si>
-  <si>
-    <t>080200158404</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011282_780,BT50,42,CDIN</t>
-  </si>
-  <si>
-    <t>200006345</t>
-  </si>
-  <si>
-    <t>080100023404</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>200006349</t>
-  </si>
-  <si>
-    <t>200006361</t>
-  </si>
-  <si>
-    <t>080200527500</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,38F18</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006366</t>
-  </si>
-  <si>
-    <t>080200539403</t>
-  </si>
-  <si>
-    <t>H1682機頭G8K,021565_#50,42F25,C</t>
-  </si>
-  <si>
-    <t>200006367</t>
-  </si>
-  <si>
-    <t>080100122802</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>200006368</t>
-  </si>
-  <si>
-    <t>080200286203</t>
-  </si>
-  <si>
-    <t>H2110機頭G6K,011026_BT50,42F25,CAW45</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006369</t>
-  </si>
-  <si>
-    <t>080100113204</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CW45</t>
-  </si>
-  <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>080200027803</t>
-  </si>
-  <si>
-    <t>PBM135機頭G2.5K,010831_DIN50,HSCDIN</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006371</t>
-  </si>
-  <si>
-    <t>080100033903</t>
-  </si>
-  <si>
-    <t>G2.5K主軸,010830_BT50,C0DIN</t>
+    <t>200006452</t>
+  </si>
+  <si>
+    <t>080200159204</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011282_780,BT50,55,CDIN</t>
+  </si>
+  <si>
+    <t>200006453</t>
+  </si>
+  <si>
+    <t>200006454</t>
+  </si>
+  <si>
+    <t>080200565901</t>
+  </si>
+  <si>
+    <t>H1100機頭G6K,021822_#50,48F23,C</t>
+  </si>
+  <si>
+    <t>200006456</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006457</t>
+  </si>
+  <si>
+    <t>200006458</t>
+  </si>
+  <si>
+    <t>080200229206</t>
+  </si>
+  <si>
+    <t>HEP機頭G6K,021570_780,BT50,48,CDIN</t>
+  </si>
+  <si>
+    <t>200006459</t>
+  </si>
+  <si>
+    <t>200006460</t>
+  </si>
+  <si>
+    <t>200006463</t>
+  </si>
+  <si>
+    <t>080200229305</t>
+  </si>
+  <si>
+    <t>HEP機頭G6K,021570_780,BT50,55,045</t>
+  </si>
+  <si>
+    <t>200006466</t>
+  </si>
+  <si>
+    <t>080300029103</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006467</t>
+  </si>
+  <si>
+    <t>080300029301</t>
+  </si>
+  <si>
+    <t>自動頭HF-AE50,032022_BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006468</t>
+  </si>
+  <si>
+    <t>080100084704</t>
+  </si>
+  <si>
+    <t>D15K 主軸,010017_BT40,M60,CWDIN</t>
   </si>
   <si>
     <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>200006372</t>
-  </si>
-  <si>
-    <t>080200555000</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,C,AT8</t>
-  </si>
-  <si>
-    <t>200006374</t>
-  </si>
-  <si>
-    <t>080200560900</t>
-  </si>
-  <si>
-    <t>MVP16機頭D12K,031884_#50,42F25</t>
-  </si>
-  <si>
-    <t>200006375</t>
-  </si>
-  <si>
-    <t>080100126002</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021337_BT50,M50,CW45</t>
-  </si>
-  <si>
-    <t>200006376</t>
-  </si>
-  <si>
-    <t>080200548501</t>
-  </si>
-  <si>
-    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006377</t>
-  </si>
-  <si>
-    <t>080100090804</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006385</t>
-  </si>
-  <si>
-    <t>080200169703</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011297_780,BT50,55,045</t>
-  </si>
-  <si>
-    <t>200006386</t>
-  </si>
-  <si>
-    <t>080100022704</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BT50,0045</t>
-  </si>
-  <si>
-    <t>200006387</t>
-  </si>
-  <si>
-    <t>080200015603</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011167_Z1400,55A18,C</t>
-  </si>
-  <si>
-    <t>200006388</t>
-  </si>
-  <si>
-    <t>080300028903</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006389</t>
-  </si>
-  <si>
-    <t>080300029800</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,032936_1°-BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006390</t>
-  </si>
-  <si>
-    <t>080100094004</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006391</t>
-  </si>
-  <si>
-    <t>080200014502</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011166_Z1000,60A30,C</t>
-  </si>
-  <si>
-    <t>200006392</t>
-  </si>
-  <si>
-    <t>080100015101</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>200006394</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006395</t>
-  </si>
-  <si>
-    <t>REL  PRC  LKD  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006397</t>
-  </si>
-  <si>
-    <t>200006398</t>
-  </si>
-  <si>
-    <t>REL  PRC  LKD  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006403</t>
-  </si>
-  <si>
-    <t>080200549001</t>
-  </si>
-  <si>
-    <t>LG1370 NEO機頭D15K,021941_#40,48F23,C,AT15</t>
-  </si>
-  <si>
-    <t>200006404</t>
-  </si>
-  <si>
-    <t>200006406</t>
-  </si>
-  <si>
-    <t>080200551400</t>
-  </si>
-  <si>
-    <t>SP10機頭P12K,021023_#40,5GT-72,C</t>
-  </si>
-  <si>
-    <t>200006418</t>
-  </si>
-  <si>
-    <t>080200255802</t>
-  </si>
-  <si>
-    <t>5A65E機頭D15K,032370_BBT40,CAW45</t>
-  </si>
-  <si>
-    <t>200006419</t>
-  </si>
-  <si>
-    <t>080100087604</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006423</t>
-  </si>
-  <si>
-    <t>080100120402</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BT50,0W45</t>
-  </si>
-  <si>
-    <t>200006425</t>
-  </si>
-  <si>
-    <t>080300019809</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_2.5°-BT50-45°-4K-C-F</t>
+    <t>200006469</t>
+  </si>
+  <si>
+    <t>200006470</t>
+  </si>
+  <si>
+    <t>080200570600</t>
+  </si>
+  <si>
+    <t>TGV106機頭DA20K,021853_#40,d38F18</t>
+  </si>
+  <si>
+    <t>200006471</t>
+  </si>
+  <si>
+    <t>080100158004</t>
+  </si>
+  <si>
+    <t>DA20K主軸,021853,oil-air_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>200006475</t>
+  </si>
+  <si>
+    <t>080200237804</t>
+  </si>
+  <si>
+    <t>HEP機頭D20K,021783_780,A63,38,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006476</t>
+  </si>
+  <si>
+    <t>080100050201</t>
+  </si>
+  <si>
+    <t>D20K 主軸,010683_A63,M50,C0</t>
+  </si>
+  <si>
+    <t>200006477</t>
+  </si>
+  <si>
+    <t>080200017802</t>
+  </si>
+  <si>
+    <t>EA機頭G8K,011262_Z1200,48A15,C</t>
   </si>
   <si>
     <t>REL  MSPT PRC  MANC SETC</t>
   </si>
   <si>
-    <t>200006426</t>
-  </si>
-  <si>
-    <t>200006427</t>
-  </si>
-  <si>
-    <t>200006431</t>
-  </si>
-  <si>
-    <t>200006432</t>
-  </si>
-  <si>
-    <t>080200292203</t>
-  </si>
-  <si>
-    <t>H2110機頭G8K,011366_BT50,55F23,0AW45</t>
-  </si>
-  <si>
-    <t>200006433</t>
-  </si>
-  <si>
-    <t>200006434</t>
-  </si>
-  <si>
-    <t>200006439</t>
-  </si>
-  <si>
-    <t>080100087601</t>
-  </si>
-  <si>
-    <t>200006441</t>
-  </si>
-  <si>
-    <t>080200071201</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
-  </si>
-  <si>
-    <t>200006442</t>
-  </si>
-  <si>
-    <t>080200483300</t>
-  </si>
-  <si>
-    <t>H1365機頭G8K,021863_#40,42F25,C</t>
-  </si>
-  <si>
-    <t>200006443</t>
-  </si>
-  <si>
-    <t>080100110001</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021534_BBT40,CW45</t>
-  </si>
-  <si>
-    <t>200006444</t>
-  </si>
-  <si>
-    <t>080100066804</t>
-  </si>
-  <si>
-    <t>P10K 主軸,021361_BBT40,5GT,CW45</t>
-  </si>
-  <si>
-    <t>200006445</t>
-  </si>
-  <si>
-    <t>080200538902</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,42F25,C</t>
-  </si>
-  <si>
-    <t>200006446</t>
-  </si>
-  <si>
-    <t>080100113505</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CWDIN</t>
-  </si>
-  <si>
-    <t>200006447</t>
-  </si>
-  <si>
-    <t>200006448</t>
-  </si>
-  <si>
-    <t>200006449</t>
-  </si>
-  <si>
-    <t>080200015002</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>200006450</t>
-  </si>
-  <si>
-    <t>080100015401</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M50E,C0DIN</t>
-  </si>
-  <si>
-    <t>200006451</t>
-  </si>
-  <si>
-    <t>080300021009</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BT50-DIN-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006452</t>
-  </si>
-  <si>
-    <t>080200159204</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011282_780,BT50,55,CDIN</t>
-  </si>
-  <si>
-    <t>200006453</t>
-  </si>
-  <si>
-    <t>200006454</t>
-  </si>
-  <si>
-    <t>080200565901</t>
-  </si>
-  <si>
-    <t>H1100機頭G6K,021822_#50,48F23,C</t>
-  </si>
-  <si>
-    <t>200006455</t>
-  </si>
-  <si>
-    <t>080100113205</t>
+    <t>200006478</t>
+  </si>
+  <si>
+    <t>080200015703</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011167_Z1400,60A30,C</t>
+  </si>
+  <si>
+    <t>200006479</t>
+  </si>
+  <si>
+    <t>080100018301</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>200006482</t>
+  </si>
+  <si>
+    <t>080300029900</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,032731,G5K_1°-BBT50-45°-5K-C-F</t>
+  </si>
+  <si>
+    <t>200006483</t>
+  </si>
+  <si>
+    <t>200006484</t>
+  </si>
+  <si>
+    <t>080200530900</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,48F23,C</t>
+  </si>
+  <si>
+    <t>200006485</t>
+  </si>
+  <si>
+    <t>200006486</t>
+  </si>
+  <si>
+    <t>200006487</t>
+  </si>
+  <si>
+    <t>200006488</t>
+  </si>
+  <si>
+    <t>200006489</t>
+  </si>
+  <si>
+    <t>200006490</t>
+  </si>
+  <si>
+    <t>200006491</t>
+  </si>
+  <si>
+    <t>200006492</t>
+  </si>
+  <si>
+    <t>200006493</t>
+  </si>
+  <si>
+    <t>080200546903</t>
+  </si>
+  <si>
+    <t>MVP11機頭D15K,031859_#40,48F18,0</t>
+  </si>
+  <si>
+    <t>200006494</t>
+  </si>
+  <si>
+    <t>200006495</t>
+  </si>
+  <si>
+    <t>080100090006</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,0W45</t>
+  </si>
+  <si>
+    <t>200006496</t>
+  </si>
+  <si>
+    <t>200006497</t>
+  </si>
+  <si>
+    <t>080200546702</t>
+  </si>
+  <si>
+    <t>MVP11機頭D15K,031859_#40,38F18,C,AT8</t>
+  </si>
+  <si>
+    <t>200006498</t>
+  </si>
+  <si>
+    <t>200006499</t>
+  </si>
+  <si>
+    <t>080100092405</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006500</t>
+  </si>
+  <si>
+    <t>200006501</t>
+  </si>
+  <si>
+    <t>080200531901</t>
+  </si>
+  <si>
+    <t>MVP13機頭D20K,021339_#40,38F18</t>
+  </si>
+  <si>
+    <t>200006502</t>
+  </si>
+  <si>
+    <t>080100157706</t>
+  </si>
+  <si>
+    <t>DA20K主軸,021854,oil-air_A63,M50,CW</t>
   </si>
   <si>
     <t>REL  MSPT PCNF PRC  RMWB SETC</t>
   </si>
   <si>
-    <t>200006456</t>
-  </si>
-  <si>
-    <t>200006457</t>
-  </si>
-  <si>
-    <t>200006458</t>
-  </si>
-  <si>
-    <t>080200229206</t>
-  </si>
-  <si>
-    <t>HEP機頭G6K,021570_780,BT50,48,CDIN</t>
-  </si>
-  <si>
-    <t>200006459</t>
-  </si>
-  <si>
-    <t>200006460</t>
-  </si>
-  <si>
-    <t>200006461</t>
-  </si>
-  <si>
-    <t>200006462</t>
-  </si>
-  <si>
-    <t>080100056404</t>
-  </si>
-  <si>
-    <t>P10K 主軸,021361_BT40,5GT,0W45</t>
-  </si>
-  <si>
-    <t>200006463</t>
-  </si>
-  <si>
-    <t>080200229305</t>
-  </si>
-  <si>
-    <t>HEP機頭G6K,021570_780,BT50,55,045</t>
-  </si>
-  <si>
-    <t>200006464</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006465</t>
-  </si>
-  <si>
-    <t>080200015703</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011167_Z1400,60A30,C</t>
-  </si>
-  <si>
-    <t>200006466</t>
-  </si>
-  <si>
-    <t>080300029103</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006467</t>
-  </si>
-  <si>
-    <t>080300029301</t>
-  </si>
-  <si>
-    <t>自動頭HF-AE50,032022_BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006468</t>
-  </si>
-  <si>
-    <t>080100084704</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BT40,M60,CWDIN</t>
-  </si>
-  <si>
-    <t>200006469</t>
-  </si>
-  <si>
-    <t>200006470</t>
-  </si>
-  <si>
-    <t>080200570600</t>
-  </si>
-  <si>
-    <t>TGV106機頭DA20K,021853_#40,d38F18</t>
-  </si>
-  <si>
-    <t>200006471</t>
-  </si>
-  <si>
-    <t>080100158004</t>
-  </si>
-  <si>
-    <t>DA20K主軸,021853,oil-air_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>200006472</t>
-  </si>
-  <si>
-    <t>080200070801</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
-  </si>
-  <si>
-    <t>200006473</t>
-  </si>
-  <si>
-    <t>200006474</t>
-  </si>
-  <si>
-    <t>200006475</t>
-  </si>
-  <si>
-    <t>080200237804</t>
-  </si>
-  <si>
-    <t>HEP機頭D20K,021783_780,A63,38,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006476</t>
-  </si>
-  <si>
-    <t>080100050201</t>
-  </si>
-  <si>
-    <t>D20K 主軸,010683_A63,M50,C0</t>
-  </si>
-  <si>
-    <t>200006477</t>
-  </si>
-  <si>
-    <t>080200017802</t>
-  </si>
-  <si>
-    <t>EA機頭G8K,011262_Z1200,48A15,C</t>
-  </si>
-  <si>
-    <t>200006478</t>
-  </si>
-  <si>
-    <t>200006479</t>
-  </si>
-  <si>
-    <t>080100018301</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BBT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>200006480</t>
-  </si>
-  <si>
-    <t>080100088406</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021177_BT40,M60,0W45</t>
-  </si>
-  <si>
-    <t>200006481</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006482</t>
-  </si>
-  <si>
-    <t>080300029900</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,032731,G5K_1°-BBT50-45°-5K-C-F</t>
-  </si>
-  <si>
-    <t>200006483</t>
+    <t>200006503</t>
+  </si>
+  <si>
+    <t>200006504</t>
+  </si>
+  <si>
+    <t>200006505</t>
+  </si>
+  <si>
+    <t>080100116405</t>
+  </si>
+  <si>
+    <t>200006506</t>
+  </si>
+  <si>
+    <t>200006507</t>
+  </si>
+  <si>
+    <t>200006508</t>
+  </si>
+  <si>
+    <t>200006509</t>
+  </si>
+  <si>
+    <t>200006510</t>
+  </si>
+  <si>
+    <t>200006511</t>
+  </si>
+  <si>
+    <t>200006512</t>
+  </si>
+  <si>
+    <t>200006513</t>
+  </si>
+  <si>
+    <t>200006514</t>
+  </si>
+  <si>
+    <t>200006515</t>
+  </si>
+  <si>
+    <t>200006516</t>
+  </si>
+  <si>
+    <t>200006517</t>
+  </si>
+  <si>
+    <t>200006518</t>
+  </si>
+  <si>
+    <t>200006519</t>
+  </si>
+  <si>
+    <t>CRTD PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006520</t>
+  </si>
+  <si>
+    <t>200006521</t>
+  </si>
+  <si>
+    <t>200006522</t>
+  </si>
+  <si>
+    <t>200006523</t>
+  </si>
+  <si>
+    <t>080200531102</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D20K,021581_A63,38F18,C</t>
+  </si>
+  <si>
+    <t>200006524</t>
+  </si>
+  <si>
+    <t>200006525</t>
+  </si>
+  <si>
+    <t>200006526</t>
+  </si>
+  <si>
+    <t>080100050703</t>
+  </si>
+  <si>
+    <t>D20K 主軸,021608_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>200006527</t>
+  </si>
+  <si>
+    <t>200006528</t>
+  </si>
+  <si>
+    <t>200006529</t>
+  </si>
+  <si>
+    <t>080200562402</t>
+  </si>
+  <si>
+    <t>MVP16機頭G8K,021487_#50,55F23,0</t>
+  </si>
+  <si>
+    <t>200006530</t>
+  </si>
+  <si>
+    <t>200006531</t>
+  </si>
+  <si>
+    <t>080200546703</t>
+  </si>
+  <si>
+    <t>200006533</t>
+  </si>
+  <si>
+    <t>200006534</t>
+  </si>
+  <si>
+    <t>200006535</t>
+  </si>
+  <si>
+    <t>080100156608</t>
+  </si>
+  <si>
+    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006536</t>
+  </si>
+  <si>
+    <t>200006537</t>
+  </si>
+  <si>
+    <t>200006538</t>
+  </si>
+  <si>
+    <t>200006539</t>
+  </si>
+  <si>
+    <t>200006540</t>
+  </si>
+  <si>
+    <t>200006541</t>
+  </si>
+  <si>
+    <t>200006542</t>
+  </si>
+  <si>
+    <t>200006543</t>
+  </si>
+  <si>
+    <t>200006544</t>
+  </si>
+  <si>
+    <t>200006545</t>
+  </si>
+  <si>
+    <t>080200538402</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,48F23,0</t>
+  </si>
+  <si>
+    <t>200006546</t>
+  </si>
+  <si>
+    <t>200006547</t>
+  </si>
+  <si>
+    <t>200006548</t>
+  </si>
+  <si>
+    <t>200006549</t>
+  </si>
+  <si>
+    <t>080100112405</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,0W45</t>
+  </si>
+  <si>
+    <t>200006550</t>
+  </si>
+  <si>
+    <t>200006551</t>
+  </si>
+  <si>
+    <t>200006552</t>
+  </si>
+  <si>
+    <t>200006553</t>
+  </si>
+  <si>
+    <t>080200548601</t>
+  </si>
+  <si>
+    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C,AT8</t>
   </si>
   <si>
     <t>ZP09</t>
   </si>
   <si>
-    <t>630000326</t>
-  </si>
-  <si>
-    <t>080200014702</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
+    <t>630000329</t>
+  </si>
+  <si>
+    <t>080300029000</t>
+  </si>
+  <si>
+    <t>HF-AU,032731_1°-BT50-45°-4K-C-F,溫降案</t>
   </si>
   <si>
     <t>PENNY</t>
   </si>
   <si>
-    <t>630000329</t>
-  </si>
-  <si>
-    <t>080300029000</t>
-  </si>
-  <si>
-    <t>HF-AU,032731_1°-BT50-45°-4K-C-F,溫降案</t>
-  </si>
-  <si>
-    <t>630000331</t>
+    <t>630000332</t>
+  </si>
+  <si>
+    <t>080100145201</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M65,0045</t>
+  </si>
+  <si>
+    <t>630000333</t>
+  </si>
+  <si>
+    <t>080200530600</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
+  </si>
+  <si>
+    <t>630000336</t>
+  </si>
+  <si>
+    <t>080100016701</t>
+  </si>
+  <si>
+    <t>D8K 主軸,010801_BT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>630000337</t>
+  </si>
+  <si>
+    <t>080300018208</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>630000338</t>
+  </si>
+  <si>
+    <t>080200254502</t>
+  </si>
+  <si>
+    <t>5A65E機頭D15K,032370_BT40,CAWDI</t>
+  </si>
+  <si>
+    <t>630000340</t>
+  </si>
+  <si>
+    <t>630000341</t>
   </si>
   <si>
     <t>080200332002</t>
@@ -847,49 +928,7 @@
     <t>PBM115機頭G4K,011381_BT50,FO2C45</t>
   </si>
   <si>
-    <t>630000332</t>
-  </si>
-  <si>
-    <t>080100145201</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M65,0045</t>
-  </si>
-  <si>
-    <t>630000333</t>
-  </si>
-  <si>
-    <t>080200530600</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
-  </si>
-  <si>
-    <t>630000336</t>
-  </si>
-  <si>
-    <t>080100016701</t>
-  </si>
-  <si>
-    <t>D8K 主軸,010801_BT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>630000337</t>
-  </si>
-  <si>
-    <t>080300018208</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>630000338</t>
-  </si>
-  <si>
-    <t>080200254502</t>
-  </si>
-  <si>
-    <t>5A65E機頭D15K,032370_BT40,CAWDI</t>
+    <t>630000342</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1042,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1050,7 +1089,7 @@
     <col min="3" max="3" bestFit="1" width="9" customWidth="1"/>
     <col min="4" max="4" bestFit="1" width="9" customWidth="1"/>
     <col min="5" max="5" bestFit="1" width="14" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="42" customWidth="1"/>
+    <col min="6" max="6" bestFit="1" width="41" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="13" customWidth="1"/>
     <col min="8" max="8" bestFit="1" width="13" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="13" customWidth="1"/>
@@ -1065,52 +1104,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1233,13 +1272,13 @@
         <v>13</v>
       </c>
       <c r="G4" s="3">
-        <v>45911</v>
+        <v>45946</v>
       </c>
       <c r="H4" s="3">
-        <v>45966</v>
+        <v>45964</v>
       </c>
       <c r="I4" s="3">
-        <v>46044</v>
+        <v>45993</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -1248,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="L4" s="3">
-        <v>45911</v>
+        <v>45946</v>
       </c>
       <c r="M4" t="s">
         <v>6</v>
@@ -1283,22 +1322,22 @@
         <v>17</v>
       </c>
       <c r="G5" s="3">
-        <v>45939</v>
+        <v>45979</v>
       </c>
       <c r="H5" s="3">
-        <v>46009</v>
+        <v>46101</v>
       </c>
       <c r="I5" s="3">
-        <v>46022</v>
+        <v>46106</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
       </c>
       <c r="L5" s="3">
-        <v>45931</v>
+        <v>45979</v>
       </c>
       <c r="M5" t="s">
         <v>6</v>
@@ -1318,37 +1357,37 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3">
+        <v>45979</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46098</v>
+      </c>
+      <c r="I6" s="3">
+        <v>46101</v>
+      </c>
+      <c r="J6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H6" s="3">
-        <v>45985</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46056</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
       <c r="K6" t="s">
         <v>5</v>
       </c>
       <c r="L6" s="3">
-        <v>45943</v>
+        <v>45979</v>
       </c>
       <c r="M6" t="s">
         <v>6</v>
@@ -1368,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1377,28 +1416,28 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3">
-        <v>45946</v>
+        <v>45979</v>
       </c>
       <c r="H7" s="3">
-        <v>45964</v>
+        <v>46097</v>
       </c>
       <c r="I7" s="3">
-        <v>45993</v>
+        <v>46100</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="3">
-        <v>45946</v>
+        <v>45979</v>
       </c>
       <c r="M7" t="s">
         <v>6</v>
@@ -1433,22 +1472,22 @@
         <v>27</v>
       </c>
       <c r="G8" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="H8" s="3">
-        <v>46063</v>
+        <v>46087</v>
       </c>
       <c r="I8" s="3">
-        <v>46065</v>
+        <v>46092</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
       </c>
       <c r="L8" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="M8" t="s">
         <v>6</v>
@@ -1468,37 +1507,37 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
       <c r="G9" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="H9" s="3">
-        <v>46059</v>
+        <v>46094</v>
       </c>
       <c r="I9" s="3">
-        <v>46064</v>
+        <v>46100</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
       </c>
       <c r="L9" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="M9" t="s">
         <v>6</v>
@@ -1518,37 +1557,37 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
-        <v>34</v>
-      </c>
       <c r="G10" s="3">
-        <v>45966</v>
+        <v>45986</v>
       </c>
       <c r="H10" s="3">
-        <v>46038</v>
+        <v>46135</v>
       </c>
       <c r="I10" s="3">
-        <v>46045</v>
+        <v>46140</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
       </c>
       <c r="L10" s="3">
-        <v>45966</v>
+        <v>45986</v>
       </c>
       <c r="M10" t="s">
         <v>6</v>
@@ -1568,37 +1607,37 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
       <c r="G11" s="3">
-        <v>45972</v>
+        <v>45986</v>
       </c>
       <c r="H11" s="3">
-        <v>46059</v>
+        <v>46127</v>
       </c>
       <c r="I11" s="3">
-        <v>46063</v>
+        <v>46132</v>
       </c>
       <c r="J11" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" s="3">
-        <v>45972</v>
+        <v>45986</v>
       </c>
       <c r="M11" t="s">
         <v>6</v>
@@ -1618,37 +1657,37 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="G12" s="3">
+        <v>45995</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46091</v>
+      </c>
+      <c r="I12" s="3">
+        <v>46094</v>
+      </c>
+      <c r="J12" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H12" s="3">
-        <v>46101</v>
-      </c>
-      <c r="I12" s="3">
-        <v>46106</v>
-      </c>
-      <c r="J12" t="s">
-        <v>42</v>
-      </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
       <c r="L12" s="3">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="M12" t="s">
         <v>6</v>
@@ -1668,37 +1707,37 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="G13" s="3">
+        <v>45995</v>
+      </c>
+      <c r="H13" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I13" s="3">
+        <v>46091</v>
+      </c>
+      <c r="J13" t="s">
         <v>44</v>
       </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H13" s="3">
-        <v>46098</v>
-      </c>
-      <c r="I13" s="3">
-        <v>46101</v>
-      </c>
-      <c r="J13" t="s">
-        <v>42</v>
-      </c>
       <c r="K13" t="s">
         <v>5</v>
       </c>
       <c r="L13" s="3">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="M13" t="s">
         <v>6</v>
@@ -1718,37 +1757,37 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>47</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" s="3">
+        <v>45995</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46101</v>
+      </c>
+      <c r="I14" s="3">
+        <v>46106</v>
+      </c>
+      <c r="J14" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46097</v>
-      </c>
-      <c r="I14" s="3">
-        <v>46100</v>
-      </c>
-      <c r="J14" t="s">
-        <v>42</v>
-      </c>
       <c r="K14" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="M14" t="s">
         <v>6</v>
@@ -1783,22 +1822,22 @@
         <v>51</v>
       </c>
       <c r="G15" s="3">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="H15" s="3">
-        <v>46087</v>
+        <v>46064</v>
       </c>
       <c r="I15" s="3">
-        <v>46092</v>
+        <v>46112</v>
       </c>
       <c r="J15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" s="3">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="M15" t="s">
         <v>6</v>
@@ -1833,22 +1872,22 @@
         <v>54</v>
       </c>
       <c r="G16" s="3">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="H16" s="3">
-        <v>46094</v>
+        <v>46052</v>
       </c>
       <c r="I16" s="3">
-        <v>46100</v>
+        <v>46059</v>
       </c>
       <c r="J16" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
       </c>
       <c r="L16" s="3">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="M16" t="s">
         <v>6</v>
@@ -1877,28 +1916,28 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="3">
+        <v>46000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46106</v>
+      </c>
+      <c r="I17" s="3">
+        <v>46108</v>
+      </c>
+      <c r="J17" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H17" s="3">
-        <v>46034</v>
-      </c>
-      <c r="I17" s="3">
-        <v>46037</v>
-      </c>
-      <c r="J17" t="s">
-        <v>28</v>
-      </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" s="3">
-        <v>45979</v>
+        <v>46000</v>
       </c>
       <c r="M17" t="s">
         <v>6</v>
@@ -1918,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1927,28 +1966,28 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G18" s="3">
-        <v>45986</v>
+        <v>46000</v>
       </c>
       <c r="H18" s="3">
-        <v>46135</v>
+        <v>46108</v>
       </c>
       <c r="I18" s="3">
-        <v>46140</v>
+        <v>46111</v>
       </c>
       <c r="J18" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" s="3">
-        <v>45986</v>
+        <v>46000</v>
       </c>
       <c r="M18" t="s">
         <v>6</v>
@@ -1968,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -1977,28 +2016,28 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G19" s="3">
-        <v>45986</v>
+        <v>46000</v>
       </c>
       <c r="H19" s="3">
-        <v>46127</v>
+        <v>46111</v>
       </c>
       <c r="I19" s="3">
-        <v>46132</v>
+        <v>46113</v>
       </c>
       <c r="J19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
       <c r="L19" s="3">
-        <v>45986</v>
+        <v>46000</v>
       </c>
       <c r="M19" t="s">
         <v>6</v>
@@ -2018,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -2027,28 +2066,28 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G20" s="3">
-        <v>45987</v>
+        <v>46002</v>
       </c>
       <c r="H20" s="3">
-        <v>45992</v>
+        <v>46063</v>
       </c>
       <c r="I20" s="3">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="J20" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3">
-        <v>45987</v>
+        <v>46002</v>
       </c>
       <c r="M20" t="s">
         <v>6</v>
@@ -2068,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -2077,28 +2116,28 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G21" s="3">
-        <v>45993</v>
+        <v>46002</v>
       </c>
       <c r="H21" s="3">
-        <v>46113</v>
+        <v>46021</v>
       </c>
       <c r="I21" s="3">
-        <v>46119</v>
+        <v>46065</v>
       </c>
       <c r="J21" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" s="3">
-        <v>45993</v>
+        <v>46002</v>
       </c>
       <c r="M21" t="s">
         <v>6</v>
@@ -2118,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2127,28 +2166,28 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G22" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="H22" s="3">
-        <v>46091</v>
+        <v>46022</v>
       </c>
       <c r="I22" s="3">
-        <v>46094</v>
+        <v>46064</v>
       </c>
       <c r="J22" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
       </c>
       <c r="L22" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="M22" t="s">
         <v>6</v>
@@ -2168,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -2177,28 +2216,28 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G23" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="H23" s="3">
-        <v>46086</v>
+        <v>46105</v>
       </c>
       <c r="I23" s="3">
-        <v>46091</v>
+        <v>46108</v>
       </c>
       <c r="J23" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2218,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -2227,28 +2266,28 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G24" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="H24" s="3">
-        <v>46101</v>
+        <v>46037</v>
       </c>
       <c r="I24" s="3">
-        <v>46106</v>
+        <v>46048</v>
       </c>
       <c r="J24" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="M24" t="s">
         <v>6</v>
@@ -2268,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2277,28 +2316,28 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G25" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="H25" s="3">
-        <v>46093</v>
+        <v>46065</v>
       </c>
       <c r="I25" s="3">
-        <v>46098</v>
+        <v>46078</v>
       </c>
       <c r="J25" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="M25" t="s">
         <v>6</v>
@@ -2318,37 +2357,37 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="3">
+        <v>46007</v>
+      </c>
+      <c r="H26" s="3">
+        <v>46062</v>
+      </c>
+      <c r="I26" s="3">
+        <v>46078</v>
+      </c>
+      <c r="J26" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="3">
-        <v>45995</v>
-      </c>
-      <c r="H26" s="3">
-        <v>46064</v>
-      </c>
-      <c r="I26" s="3">
-        <v>46112</v>
-      </c>
-      <c r="J26" t="s">
-        <v>83</v>
-      </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="M26" t="s">
         <v>6</v>
@@ -2368,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2377,28 +2416,28 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F27" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="3">
+        <v>46007</v>
+      </c>
+      <c r="H27" s="3">
+        <v>46066</v>
+      </c>
+      <c r="I27" s="3">
+        <v>46085</v>
+      </c>
+      <c r="J27" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="3">
-        <v>45995</v>
-      </c>
-      <c r="H27" s="3">
-        <v>46052</v>
-      </c>
-      <c r="I27" s="3">
-        <v>46059</v>
-      </c>
-      <c r="J27" t="s">
-        <v>87</v>
-      </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2418,37 +2457,37 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>89</v>
       </c>
-      <c r="F28" t="s">
-        <v>90</v>
-      </c>
       <c r="G28" s="3">
-        <v>46000</v>
+        <v>46022</v>
       </c>
       <c r="H28" s="3">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="I28" s="3">
-        <v>46108</v>
+        <v>46126</v>
       </c>
       <c r="J28" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" s="3">
-        <v>46000</v>
+        <v>46022</v>
       </c>
       <c r="M28" t="s">
         <v>6</v>
@@ -2468,37 +2507,37 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="2">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>92</v>
       </c>
-      <c r="F29" t="s">
-        <v>93</v>
-      </c>
       <c r="G29" s="3">
-        <v>46000</v>
+        <v>46022</v>
       </c>
       <c r="H29" s="3">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="I29" s="3">
-        <v>46111</v>
+        <v>46121</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>46000</v>
+        <v>46022</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2518,37 +2557,37 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="2">
-        <v>1</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>95</v>
       </c>
-      <c r="F30" t="s">
-        <v>96</v>
-      </c>
       <c r="G30" s="3">
-        <v>46000</v>
+        <v>46028</v>
       </c>
       <c r="H30" s="3">
-        <v>46100</v>
+        <v>46041</v>
       </c>
       <c r="I30" s="3">
-        <v>46105</v>
+        <v>46044</v>
       </c>
       <c r="J30" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" s="3">
-        <v>46000</v>
+        <v>46028</v>
       </c>
       <c r="M30" t="s">
         <v>6</v>
@@ -2568,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2577,28 +2616,28 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G31" s="3">
-        <v>46000</v>
+        <v>46029</v>
       </c>
       <c r="H31" s="3">
-        <v>46111</v>
+        <v>46034</v>
       </c>
       <c r="I31" s="3">
-        <v>46113</v>
+        <v>46037</v>
       </c>
       <c r="J31" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
       <c r="L31" s="3">
-        <v>46000</v>
+        <v>46029</v>
       </c>
       <c r="M31" t="s">
         <v>6</v>
@@ -2618,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2627,28 +2666,28 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G32" s="3">
-        <v>46000</v>
+        <v>46029</v>
       </c>
       <c r="H32" s="3">
-        <v>46048</v>
+        <v>46078</v>
       </c>
       <c r="I32" s="3">
-        <v>46056</v>
+        <v>46084</v>
       </c>
       <c r="J32" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
       <c r="L32" s="3">
-        <v>46000</v>
+        <v>46029</v>
       </c>
       <c r="M32" t="s">
         <v>6</v>
@@ -2668,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2677,13 +2716,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G33" s="3">
-        <v>46002</v>
+        <v>46029</v>
       </c>
       <c r="H33" s="3">
         <v>46063</v>
@@ -2692,13 +2731,13 @@
         <v>46066</v>
       </c>
       <c r="J33" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>46002</v>
+        <v>46029</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -2718,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2727,28 +2766,28 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G34" s="3">
-        <v>46002</v>
+        <v>46043</v>
       </c>
       <c r="H34" s="3">
-        <v>46058</v>
+        <v>46132</v>
       </c>
       <c r="I34" s="3">
-        <v>46063</v>
+        <v>46135</v>
       </c>
       <c r="J34" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46002</v>
+        <v>46043</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -2768,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2777,28 +2816,28 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G35" s="3">
-        <v>46002</v>
+        <v>46043</v>
       </c>
       <c r="H35" s="3">
-        <v>46002</v>
+        <v>46127</v>
       </c>
       <c r="I35" s="3">
-        <v>46013</v>
+        <v>46132</v>
       </c>
       <c r="J35" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46002</v>
+        <v>46043</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -2818,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -2827,28 +2866,28 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G36" s="3">
-        <v>46002</v>
+        <v>46044</v>
       </c>
       <c r="H36" s="3">
-        <v>46021</v>
+        <v>46142</v>
       </c>
       <c r="I36" s="3">
-        <v>46065</v>
+        <v>46148</v>
       </c>
       <c r="J36" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46002</v>
+        <v>46044</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -2868,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -2877,28 +2916,28 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F37" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G37" s="3">
-        <v>46002</v>
+        <v>46044</v>
       </c>
       <c r="H37" s="3">
-        <v>46022</v>
+        <v>46139</v>
       </c>
       <c r="I37" s="3">
-        <v>46064</v>
+        <v>46142</v>
       </c>
       <c r="J37" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>46002</v>
+        <v>46044</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -2918,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -2927,28 +2966,28 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="G38" s="3">
-        <v>46002</v>
+        <v>46044</v>
       </c>
       <c r="H38" s="3">
-        <v>46105</v>
+        <v>46085</v>
       </c>
       <c r="I38" s="3">
-        <v>46108</v>
+        <v>46090</v>
       </c>
       <c r="J38" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
       </c>
       <c r="L38" s="3">
-        <v>46002</v>
+        <v>46044</v>
       </c>
       <c r="M38" t="s">
         <v>6</v>
@@ -2968,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -2977,28 +3016,28 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="G39" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="H39" s="3">
-        <v>46037</v>
+        <v>46078</v>
       </c>
       <c r="I39" s="3">
-        <v>46048</v>
+        <v>46084</v>
       </c>
       <c r="J39" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
       </c>
       <c r="L39" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="M39" t="s">
         <v>6</v>
@@ -3018,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3027,28 +3066,28 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G40" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="H40" s="3">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="I40" s="3">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="J40" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3068,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3077,28 +3116,28 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F41" t="s">
         <v>122</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" s="3">
+        <v>46044</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46063</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46076</v>
+      </c>
+      <c r="J41" t="s">
         <v>123</v>
       </c>
-      <c r="G41" s="3">
-        <v>46007</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46062</v>
-      </c>
-      <c r="I41" s="3">
-        <v>46078</v>
-      </c>
-      <c r="J41" t="s">
-        <v>128</v>
-      </c>
       <c r="K41" t="s">
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3118,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3133,22 +3172,22 @@
         <v>126</v>
       </c>
       <c r="G42" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="H42" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="I42" s="3">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="J42" t="s">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3168,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3177,28 +3216,28 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="F43" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="G43" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="H43" s="3">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="I43" s="3">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="J43" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3218,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3227,28 +3266,28 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F44" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G44" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="H44" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="I44" s="3">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="J44" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3268,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3277,28 +3316,28 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F45" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G45" s="3">
-        <v>46013</v>
+        <v>46044</v>
       </c>
       <c r="H45" s="3">
-        <v>46058</v>
+        <v>46077</v>
       </c>
       <c r="I45" s="3">
-        <v>46062</v>
+        <v>46083</v>
       </c>
       <c r="J45" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>46013</v>
+        <v>46044</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3318,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3327,28 +3366,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="F46" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="G46" s="3">
-        <v>46013</v>
+        <v>46044</v>
       </c>
       <c r="H46" s="3">
-        <v>46038</v>
+        <v>46064</v>
       </c>
       <c r="I46" s="3">
-        <v>46049</v>
+        <v>46076</v>
       </c>
       <c r="J46" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>46013</v>
+        <v>46044</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3368,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3377,28 +3416,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F47" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G47" s="3">
-        <v>46014</v>
+        <v>46048</v>
       </c>
       <c r="H47" s="3">
-        <v>46132</v>
+        <v>46090</v>
       </c>
       <c r="I47" s="3">
-        <v>46134</v>
+        <v>46093</v>
       </c>
       <c r="J47" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46014</v>
+        <v>46048</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3418,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3427,28 +3466,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="F48" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="G48" s="3">
-        <v>46022</v>
+        <v>46048</v>
       </c>
       <c r="H48" s="3">
-        <v>46121</v>
+        <v>46084</v>
       </c>
       <c r="I48" s="3">
-        <v>46126</v>
+        <v>46087</v>
       </c>
       <c r="J48" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46022</v>
+        <v>46048</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3468,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3477,28 +3516,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="G49" s="3">
-        <v>46022</v>
+        <v>46048</v>
       </c>
       <c r="H49" s="3">
-        <v>46114</v>
+        <v>46085</v>
       </c>
       <c r="I49" s="3">
-        <v>46121</v>
+        <v>46090</v>
       </c>
       <c r="J49" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46022</v>
+        <v>46048</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3518,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3527,28 +3566,28 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F50" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G50" s="3">
-        <v>46028</v>
+        <v>46049</v>
       </c>
       <c r="H50" s="3">
-        <v>46041</v>
+        <v>46086</v>
       </c>
       <c r="I50" s="3">
-        <v>46044</v>
+        <v>46091</v>
       </c>
       <c r="J50" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46028</v>
+        <v>46049</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3568,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3577,28 +3616,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F51" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G51" s="3">
-        <v>46028</v>
+        <v>46050</v>
       </c>
       <c r="H51" s="3">
-        <v>46091</v>
+        <v>46065</v>
       </c>
       <c r="I51" s="3">
-        <v>46114</v>
+        <v>46093</v>
       </c>
       <c r="J51" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46028</v>
+        <v>46050</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3618,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3627,28 +3666,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F52" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G52" s="3">
-        <v>46028</v>
+        <v>46050</v>
       </c>
       <c r="H52" s="3">
-        <v>46113</v>
+        <v>46077</v>
       </c>
       <c r="I52" s="3">
-        <v>46136</v>
+        <v>46083</v>
       </c>
       <c r="J52" t="s">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46028</v>
+        <v>46050</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -3668,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -3677,28 +3716,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
+        <v>149</v>
+      </c>
+      <c r="F53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" s="3">
+        <v>46050</v>
+      </c>
+      <c r="H53" s="3">
+        <v>46057</v>
+      </c>
+      <c r="I53" s="3">
+        <v>46063</v>
+      </c>
+      <c r="J53" t="s">
         <v>151</v>
       </c>
-      <c r="F53" t="s">
-        <v>152</v>
-      </c>
-      <c r="G53" s="3">
-        <v>46028</v>
-      </c>
-      <c r="H53" s="3">
-        <v>46119</v>
-      </c>
-      <c r="I53" s="3">
-        <v>46142</v>
-      </c>
-      <c r="J53" t="s">
-        <v>153</v>
-      </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46028</v>
+        <v>46050</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -3718,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3727,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G54" s="3">
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="H54" s="3">
-        <v>46034</v>
+        <v>46057</v>
       </c>
       <c r="I54" s="3">
-        <v>46037</v>
+        <v>46063</v>
       </c>
       <c r="J54" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -3768,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -3777,28 +3816,28 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G55" s="3">
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="H55" s="3">
+        <v>46066</v>
+      </c>
+      <c r="I55" s="3">
         <v>46078</v>
       </c>
-      <c r="I55" s="3">
-        <v>46084</v>
-      </c>
       <c r="J55" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -3818,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -3827,28 +3866,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F56" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="G56" s="3">
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="H56" s="3">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="I56" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="J56" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="K56" t="s">
         <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -3868,37 +3907,37 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>160</v>
+      </c>
+      <c r="F57" t="s">
         <v>161</v>
       </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0</v>
-      </c>
-      <c r="E57" t="s">
-        <v>40</v>
-      </c>
-      <c r="F57" t="s">
-        <v>41</v>
-      </c>
       <c r="G57" s="3">
-        <v>46031</v>
+        <v>46050</v>
       </c>
       <c r="H57" s="3">
+        <v>46050</v>
+      </c>
+      <c r="I57" s="3">
         <v>46056</v>
       </c>
-      <c r="I57" s="3">
-        <v>46059</v>
-      </c>
       <c r="J57" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="K57" t="s">
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46031</v>
+        <v>46050</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -3918,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -3927,28 +3966,28 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F58" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G58" s="3">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="H58" s="3">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="I58" s="3">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="J58" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -3968,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -3977,28 +4016,28 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G59" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="H59" s="3">
-        <v>46077</v>
+        <v>46052</v>
       </c>
       <c r="I59" s="3">
-        <v>46079</v>
+        <v>46063</v>
       </c>
       <c r="J59" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4018,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4027,28 +4066,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F60" t="s">
+        <v>172</v>
+      </c>
+      <c r="G60" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H60" s="3">
+        <v>46077</v>
+      </c>
+      <c r="I60" s="3">
+        <v>46087</v>
+      </c>
+      <c r="J60" t="s">
         <v>169</v>
       </c>
-      <c r="G60" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H60" s="3">
-        <v>46132</v>
-      </c>
-      <c r="I60" s="3">
-        <v>46135</v>
-      </c>
-      <c r="J60" t="s">
-        <v>42</v>
-      </c>
       <c r="K60" t="s">
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4068,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4077,28 +4116,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F61" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G61" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="H61" s="3">
-        <v>46127</v>
+        <v>46076</v>
       </c>
       <c r="I61" s="3">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="J61" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4118,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4127,28 +4166,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F62" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G62" s="3">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="H62" s="3">
-        <v>46043</v>
+        <v>46119</v>
       </c>
       <c r="I62" s="3">
-        <v>46048</v>
+        <v>46142</v>
       </c>
       <c r="J62" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4168,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4177,28 +4216,28 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>177</v>
+        <v>68</v>
       </c>
       <c r="F63" t="s">
-        <v>178</v>
+        <v>69</v>
       </c>
       <c r="G63" s="3">
-        <v>46044</v>
+        <v>46055</v>
       </c>
       <c r="H63" s="3">
-        <v>46142</v>
+        <v>46114</v>
       </c>
       <c r="I63" s="3">
-        <v>46148</v>
+        <v>46136</v>
       </c>
       <c r="J63" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>46044</v>
+        <v>46055</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4218,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4227,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G64" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="H64" s="3">
-        <v>46139</v>
+        <v>46098</v>
       </c>
       <c r="I64" s="3">
-        <v>46142</v>
+        <v>46100</v>
       </c>
       <c r="J64" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4268,37 +4307,37 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
+        <v>181</v>
+      </c>
+      <c r="F65" t="s">
         <v>182</v>
       </c>
-      <c r="C65" s="2">
-        <v>1</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
-        <v>40</v>
-      </c>
-      <c r="F65" t="s">
-        <v>41</v>
-      </c>
       <c r="G65" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="H65" s="3">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="I65" s="3">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="J65" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4318,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4327,19 +4366,19 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="F66" t="s">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="G66" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="H66" s="3">
-        <v>46078</v>
+        <v>46092</v>
       </c>
       <c r="I66" s="3">
-        <v>46084</v>
+        <v>46097</v>
       </c>
       <c r="J66" t="s">
         <v>4</v>
@@ -4348,7 +4387,7 @@
         <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4368,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4377,28 +4416,28 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="F67" t="s">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="G67" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="H67" s="3">
-        <v>46076</v>
+        <v>46092</v>
       </c>
       <c r="I67" s="3">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="J67" t="s">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="M67" t="s">
         <v>6</v>
@@ -4418,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4427,19 +4466,19 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="F68" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="G68" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="H68" s="3">
-        <v>46063</v>
+        <v>46094</v>
       </c>
       <c r="I68" s="3">
-        <v>46076</v>
+        <v>46114</v>
       </c>
       <c r="J68" t="s">
         <v>4</v>
@@ -4448,7 +4487,7 @@
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4468,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4477,28 +4516,28 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="F69" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="G69" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="H69" s="3">
-        <v>46126</v>
+        <v>46114</v>
       </c>
       <c r="I69" s="3">
-        <v>46150</v>
+        <v>46136</v>
       </c>
       <c r="J69" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="M69" t="s">
         <v>6</v>
@@ -4518,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4527,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="F70" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="G70" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="H70" s="3">
-        <v>46079</v>
+        <v>46122</v>
       </c>
       <c r="I70" s="3">
-        <v>46085</v>
+        <v>46142</v>
       </c>
       <c r="J70" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
       </c>
       <c r="L70" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="M70" t="s">
         <v>6</v>
@@ -4568,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4577,28 +4616,28 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
+        <v>175</v>
       </c>
       <c r="G71" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="H71" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="I71" s="3">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="J71" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="M71" t="s">
         <v>6</v>
@@ -4618,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4627,28 +4666,28 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G72" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="H72" s="3">
-        <v>46065</v>
+        <v>46078</v>
       </c>
       <c r="I72" s="3">
-        <v>46076</v>
+        <v>46085</v>
       </c>
       <c r="J72" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="M72" t="s">
         <v>6</v>
@@ -4668,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4677,28 +4716,28 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F73" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="G73" s="3">
-        <v>46044</v>
+        <v>46062</v>
       </c>
       <c r="H73" s="3">
-        <v>46058</v>
+        <v>46099</v>
       </c>
       <c r="I73" s="3">
-        <v>46063</v>
+        <v>46101</v>
       </c>
       <c r="J73" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46044</v>
+        <v>46062</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -4718,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4727,28 +4766,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F74" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G74" s="3">
-        <v>46044</v>
+        <v>46062</v>
       </c>
       <c r="H74" s="3">
-        <v>46077</v>
+        <v>46100</v>
       </c>
       <c r="I74" s="3">
-        <v>46083</v>
+        <v>46104</v>
       </c>
       <c r="J74" t="s">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46044</v>
+        <v>46062</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -4768,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -4777,28 +4816,28 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="F75" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
       <c r="G75" s="3">
-        <v>46044</v>
+        <v>46062</v>
       </c>
       <c r="H75" s="3">
-        <v>46064</v>
+        <v>46092</v>
       </c>
       <c r="I75" s="3">
-        <v>46076</v>
+        <v>46098</v>
       </c>
       <c r="J75" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46044</v>
+        <v>46062</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -4818,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4827,28 +4866,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F76" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G76" s="3">
-        <v>46048</v>
+        <v>46062</v>
       </c>
       <c r="H76" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="I76" s="3">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="J76" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46048</v>
+        <v>46062</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -4868,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -4877,28 +4916,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F77" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="G77" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="H77" s="3">
-        <v>46084</v>
+        <v>46099</v>
       </c>
       <c r="I77" s="3">
-        <v>46087</v>
+        <v>46101</v>
       </c>
       <c r="J77" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -4918,7 +4957,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -4927,28 +4966,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F78" t="s">
-        <v>41</v>
+        <v>201</v>
       </c>
       <c r="G78" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="H78" s="3">
-        <v>46085</v>
+        <v>46163</v>
       </c>
       <c r="I78" s="3">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="J78" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -4968,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -4977,28 +5016,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="F79" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="G79" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="H79" s="3">
-        <v>46078</v>
+        <v>46091</v>
       </c>
       <c r="I79" s="3">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="J79" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5018,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5027,28 +5066,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="F80" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="G80" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="H80" s="3">
-        <v>46051</v>
+        <v>46155</v>
       </c>
       <c r="I80" s="3">
-        <v>46056</v>
+        <v>46160</v>
       </c>
       <c r="J80" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5068,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5077,28 +5116,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F81" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G81" s="3">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="H81" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="I81" s="3">
-        <v>46091</v>
+        <v>46087</v>
       </c>
       <c r="J81" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5118,7 +5157,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5127,28 +5166,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="F82" t="s">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="G82" s="3">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="H82" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="I82" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="J82" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5168,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5177,28 +5216,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>221</v>
+        <v>2</v>
       </c>
       <c r="F83" t="s">
-        <v>222</v>
+        <v>3</v>
       </c>
       <c r="G83" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H83" s="3">
-        <v>46050</v>
+        <v>46176</v>
       </c>
       <c r="I83" s="3">
-        <v>46059</v>
+        <v>46181</v>
       </c>
       <c r="J83" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5218,7 +5257,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5227,28 +5266,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>224</v>
+        <v>2</v>
       </c>
       <c r="F84" t="s">
-        <v>225</v>
+        <v>3</v>
       </c>
       <c r="G84" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H84" s="3">
-        <v>46050</v>
+        <v>46176</v>
       </c>
       <c r="I84" s="3">
-        <v>46083</v>
+        <v>46181</v>
       </c>
       <c r="J84" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5268,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5277,28 +5316,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="F85" t="s">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="G85" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H85" s="3">
-        <v>46077</v>
+        <v>46170</v>
       </c>
       <c r="I85" s="3">
-        <v>46083</v>
+        <v>46175</v>
       </c>
       <c r="J85" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5318,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5327,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="F86" t="s">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="G86" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H86" s="3">
-        <v>46050</v>
+        <v>46170</v>
       </c>
       <c r="I86" s="3">
-        <v>46056</v>
+        <v>46175</v>
       </c>
       <c r="J86" t="s">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5368,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5377,28 +5416,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>231</v>
+        <v>3</v>
       </c>
       <c r="G87" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H87" s="3">
-        <v>46050</v>
+        <v>46240</v>
       </c>
       <c r="I87" s="3">
-        <v>46056</v>
+        <v>46245</v>
       </c>
       <c r="J87" t="s">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5418,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5427,28 +5466,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>235</v>
+        <v>3</v>
       </c>
       <c r="G88" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H88" s="3">
-        <v>46066</v>
+        <v>46240</v>
       </c>
       <c r="I88" s="3">
-        <v>46078</v>
+        <v>46245</v>
       </c>
       <c r="J88" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5468,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5477,28 +5516,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="F89" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="G89" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H89" s="3">
-        <v>46059</v>
+        <v>46234</v>
       </c>
       <c r="I89" s="3">
-        <v>46065</v>
+        <v>46239</v>
       </c>
       <c r="J89" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5518,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5527,28 +5566,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="F90" t="s">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="G90" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H90" s="3">
-        <v>46083</v>
+        <v>46234</v>
       </c>
       <c r="I90" s="3">
-        <v>46084</v>
+        <v>46239</v>
       </c>
       <c r="J90" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5568,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5577,28 +5616,28 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="F91" t="s">
-        <v>241</v>
+        <v>17</v>
       </c>
       <c r="G91" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H91" s="3">
-        <v>46086</v>
+        <v>46146</v>
       </c>
       <c r="I91" s="3">
-        <v>46087</v>
+        <v>46149</v>
       </c>
       <c r="J91" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5618,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5627,28 +5666,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>241</v>
+        <v>17</v>
       </c>
       <c r="G92" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H92" s="3">
-        <v>46083</v>
+        <v>46174</v>
       </c>
       <c r="I92" s="3">
-        <v>46084</v>
+        <v>46177</v>
       </c>
       <c r="J92" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -5668,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5677,28 +5716,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>245</v>
+        <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>246</v>
+        <v>17</v>
       </c>
       <c r="G93" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H93" s="3">
-        <v>46050</v>
+        <v>46238</v>
       </c>
       <c r="I93" s="3">
-        <v>46056</v>
+        <v>46241</v>
       </c>
       <c r="J93" t="s">
-        <v>247</v>
+        <v>123</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5718,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5727,28 +5766,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>249</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>250</v>
+        <v>17</v>
       </c>
       <c r="G94" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H94" s="3">
-        <v>46050</v>
+        <v>46297</v>
       </c>
       <c r="I94" s="3">
-        <v>46055</v>
+        <v>46302</v>
       </c>
       <c r="J94" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -5768,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -5777,28 +5816,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="F95" t="s">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="G95" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="H95" s="3">
-        <v>46052</v>
+        <v>46139</v>
       </c>
       <c r="I95" s="3">
-        <v>46063</v>
+        <v>46142</v>
       </c>
       <c r="J95" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -5818,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -5827,28 +5866,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F96" t="s">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="G96" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="H96" s="3">
-        <v>46077</v>
+        <v>46168</v>
       </c>
       <c r="I96" s="3">
-        <v>46087</v>
+        <v>46171</v>
       </c>
       <c r="J96" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -5868,37 +5907,37 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C97" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D97" s="2">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="F97" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="G97" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="H97" s="3">
-        <v>46052</v>
+        <v>46232</v>
       </c>
       <c r="I97" s="3">
-        <v>46083</v>
+        <v>46237</v>
       </c>
       <c r="J97" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -5918,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -5927,28 +5966,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
       <c r="F98" t="s">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="G98" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="H98" s="3">
-        <v>46077</v>
+        <v>46289</v>
       </c>
       <c r="I98" s="3">
-        <v>46084</v>
+        <v>46296</v>
       </c>
       <c r="J98" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -5968,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -5977,28 +6016,26 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>231</v>
-      </c>
-      <c r="G99" s="3">
-        <v>46055</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G99" s="3"/>
       <c r="H99" s="3">
-        <v>46058</v>
+        <v>46301</v>
       </c>
       <c r="I99" s="3">
+        <v>46307</v>
+      </c>
+      <c r="J99" t="s">
+        <v>232</v>
+      </c>
+      <c r="K99" t="s">
+        <v>5</v>
+      </c>
+      <c r="L99" s="3">
         <v>46064</v>
-      </c>
-      <c r="J99" t="s">
-        <v>262</v>
-      </c>
-      <c r="K99" t="s">
-        <v>5</v>
-      </c>
-      <c r="L99" s="3">
-        <v>46055</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6018,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6027,28 +6064,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>264</v>
+        <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>265</v>
+        <v>3</v>
       </c>
       <c r="G100" s="3">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="H100" s="3">
-        <v>46119</v>
+        <v>46301</v>
       </c>
       <c r="I100" s="3">
-        <v>46142</v>
+        <v>46307</v>
       </c>
       <c r="J100" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6068,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6077,28 +6114,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>113</v>
+        <v>217</v>
       </c>
       <c r="F101" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="G101" s="3">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="H101" s="3">
-        <v>46114</v>
+        <v>46267</v>
       </c>
       <c r="I101" s="3">
-        <v>46136</v>
+        <v>46272</v>
       </c>
       <c r="J101" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6115,10 +6152,10 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6127,28 +6164,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>269</v>
+        <v>217</v>
       </c>
       <c r="F102" t="s">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="G102" s="3">
-        <v>46028</v>
+        <v>46064</v>
       </c>
       <c r="H102" s="3">
-        <v>46028</v>
+        <v>46267</v>
       </c>
       <c r="I102" s="3">
-        <v>46037</v>
+        <v>46272</v>
       </c>
       <c r="J102" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="K102" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46028</v>
+        <v>46064</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6165,10 +6202,10 @@
     </row>
     <row r="103" spans="1:16">
       <c r="A103" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6177,28 +6214,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="G103" s="3">
-        <v>46035</v>
+        <v>46076</v>
       </c>
       <c r="H103" s="3">
-        <v>46044</v>
+        <v>46087</v>
       </c>
       <c r="I103" s="3">
-        <v>46066</v>
+        <v>46091</v>
       </c>
       <c r="J103" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K103" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46035</v>
+        <v>46076</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6215,10 +6252,10 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6227,28 +6264,28 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="G104" s="3">
-        <v>46042</v>
+        <v>46076</v>
       </c>
       <c r="H104" s="3">
-        <v>46042</v>
+        <v>46087</v>
       </c>
       <c r="I104" s="3">
-        <v>46043</v>
+        <v>46091</v>
       </c>
       <c r="J104" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K104" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="L104" s="3">
-        <v>46042</v>
+        <v>46076</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6265,10 +6302,10 @@
     </row>
     <row r="105" spans="1:16">
       <c r="A105" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6277,28 +6314,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="F105" t="s">
-        <v>280</v>
+        <v>238</v>
       </c>
       <c r="G105" s="3">
-        <v>46043</v>
+        <v>46076</v>
       </c>
       <c r="H105" s="3">
-        <v>46051</v>
+        <v>46087</v>
       </c>
       <c r="I105" s="3">
-        <v>46057</v>
+        <v>46091</v>
       </c>
       <c r="J105" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="K105" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46043</v>
+        <v>46076</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6315,10 +6352,10 @@
     </row>
     <row r="106" spans="1:16">
       <c r="A106" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6327,28 +6364,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="F106" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="G106" s="3">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="H106" s="3">
-        <v>46059</v>
+        <v>46083</v>
       </c>
       <c r="I106" s="3">
-        <v>46062</v>
+        <v>46086</v>
       </c>
       <c r="J106" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="K106" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6365,10 +6402,10 @@
     </row>
     <row r="107" spans="1:16">
       <c r="A107" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6377,28 +6414,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="F107" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="G107" s="3">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="H107" s="3">
-        <v>46052</v>
+        <v>46083</v>
       </c>
       <c r="I107" s="3">
-        <v>46058</v>
+        <v>46086</v>
       </c>
       <c r="J107" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="K107" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6415,10 +6452,10 @@
     </row>
     <row r="108" spans="1:16">
       <c r="A108" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6427,28 +6464,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="F108" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="G108" s="3">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="H108" s="3">
-        <v>46058</v>
+        <v>46083</v>
       </c>
       <c r="I108" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="J108" t="s">
-        <v>4</v>
+        <v>169</v>
       </c>
       <c r="K108" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6465,51 +6502,1651 @@
     </row>
     <row r="109" spans="1:16">
       <c r="A109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B109" t="s">
+        <v>246</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" t="s">
+        <v>247</v>
+      </c>
+      <c r="F109" t="s">
+        <v>248</v>
+      </c>
+      <c r="G109" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H109" s="3">
+        <v>46104</v>
+      </c>
+      <c r="I109" s="3">
+        <v>46107</v>
+      </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109" t="s">
+        <v>5</v>
+      </c>
+      <c r="L109" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M109" t="s">
+        <v>6</v>
+      </c>
+      <c r="N109" t="s">
+        <v>7</v>
+      </c>
+      <c r="O109" t="s">
+        <v>8</v>
+      </c>
+      <c r="P109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B110" t="s">
+        <v>249</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
+        <v>94</v>
+      </c>
+      <c r="F110" t="s">
+        <v>95</v>
+      </c>
+      <c r="G110" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H110" s="3">
+        <v>46099</v>
+      </c>
+      <c r="I110" s="3">
+        <v>46104</v>
+      </c>
+      <c r="J110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110" t="s">
+        <v>5</v>
+      </c>
+      <c r="L110" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M110" t="s">
+        <v>6</v>
+      </c>
+      <c r="N110" t="s">
+        <v>7</v>
+      </c>
+      <c r="O110" t="s">
+        <v>8</v>
+      </c>
+      <c r="P110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111" t="s">
+        <v>0</v>
+      </c>
+      <c r="B111" t="s">
+        <v>250</v>
+      </c>
+      <c r="C111" s="2">
+        <v>1</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0</v>
+      </c>
+      <c r="E111" t="s">
+        <v>251</v>
+      </c>
+      <c r="F111" t="s">
+        <v>201</v>
+      </c>
+      <c r="G111" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H111" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I111" s="3">
+        <v>46078</v>
+      </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" t="s">
+        <v>5</v>
+      </c>
+      <c r="L111" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M111" t="s">
+        <v>6</v>
+      </c>
+      <c r="N111" t="s">
+        <v>7</v>
+      </c>
+      <c r="O111" t="s">
+        <v>8</v>
+      </c>
+      <c r="P111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="A112" t="s">
+        <v>0</v>
+      </c>
+      <c r="B112" t="s">
+        <v>252</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+      <c r="E112" t="s">
+        <v>251</v>
+      </c>
+      <c r="F112" t="s">
+        <v>201</v>
+      </c>
+      <c r="G112" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H112" s="3">
+        <v>46162</v>
+      </c>
+      <c r="I112" s="3">
+        <v>46164</v>
+      </c>
+      <c r="J112" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112" t="s">
+        <v>5</v>
+      </c>
+      <c r="L112" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M112" t="s">
+        <v>6</v>
+      </c>
+      <c r="N112" t="s">
+        <v>7</v>
+      </c>
+      <c r="O112" t="s">
+        <v>8</v>
+      </c>
+      <c r="P112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113" t="s">
+        <v>0</v>
+      </c>
+      <c r="B113" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="2">
+        <v>1</v>
+      </c>
+      <c r="D113" s="2">
+        <v>0</v>
+      </c>
+      <c r="E113" t="s">
+        <v>251</v>
+      </c>
+      <c r="F113" t="s">
+        <v>201</v>
+      </c>
+      <c r="G113" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H113" s="3">
+        <v>46162</v>
+      </c>
+      <c r="I113" s="3">
+        <v>46164</v>
+      </c>
+      <c r="J113" t="s">
+        <v>123</v>
+      </c>
+      <c r="K113" t="s">
+        <v>5</v>
+      </c>
+      <c r="L113" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M113" t="s">
+        <v>6</v>
+      </c>
+      <c r="N113" t="s">
+        <v>7</v>
+      </c>
+      <c r="O113" t="s">
+        <v>8</v>
+      </c>
+      <c r="P113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2">
+        <v>0</v>
+      </c>
+      <c r="E114" t="s">
+        <v>255</v>
+      </c>
+      <c r="F114" t="s">
+        <v>256</v>
+      </c>
+      <c r="G114" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H114" s="3">
+        <v>46156</v>
+      </c>
+      <c r="I114" s="3">
+        <v>46161</v>
+      </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114" t="s">
+        <v>5</v>
+      </c>
+      <c r="L114" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M114" t="s">
+        <v>6</v>
+      </c>
+      <c r="N114" t="s">
+        <v>7</v>
+      </c>
+      <c r="O114" t="s">
+        <v>8</v>
+      </c>
+      <c r="P114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" t="s">
+        <v>257</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0</v>
+      </c>
+      <c r="E115" t="s">
+        <v>255</v>
+      </c>
+      <c r="F115" t="s">
+        <v>256</v>
+      </c>
+      <c r="G115" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H115" s="3">
+        <v>46156</v>
+      </c>
+      <c r="I115" s="3">
+        <v>46161</v>
+      </c>
+      <c r="J115" t="s">
+        <v>123</v>
+      </c>
+      <c r="K115" t="s">
+        <v>5</v>
+      </c>
+      <c r="L115" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M115" t="s">
+        <v>6</v>
+      </c>
+      <c r="N115" t="s">
+        <v>7</v>
+      </c>
+      <c r="O115" t="s">
+        <v>8</v>
+      </c>
+      <c r="P115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" t="s">
+        <v>258</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" t="s">
+        <v>251</v>
+      </c>
+      <c r="F116" t="s">
+        <v>201</v>
+      </c>
+      <c r="G116" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H116" s="3">
+        <v>46212</v>
+      </c>
+      <c r="I116" s="3">
+        <v>46216</v>
+      </c>
+      <c r="J116" t="s">
+        <v>18</v>
+      </c>
+      <c r="K116" t="s">
+        <v>5</v>
+      </c>
+      <c r="L116" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M116" t="s">
+        <v>6</v>
+      </c>
+      <c r="N116" t="s">
+        <v>7</v>
+      </c>
+      <c r="O116" t="s">
+        <v>8</v>
+      </c>
+      <c r="P116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117" t="s">
+        <v>0</v>
+      </c>
+      <c r="B117" t="s">
+        <v>259</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2">
+        <v>0</v>
+      </c>
+      <c r="E117" t="s">
+        <v>251</v>
+      </c>
+      <c r="F117" t="s">
+        <v>201</v>
+      </c>
+      <c r="G117" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H117" s="3">
+        <v>46212</v>
+      </c>
+      <c r="I117" s="3">
+        <v>46216</v>
+      </c>
+      <c r="J117" t="s">
+        <v>123</v>
+      </c>
+      <c r="K117" t="s">
+        <v>5</v>
+      </c>
+      <c r="L117" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M117" t="s">
+        <v>6</v>
+      </c>
+      <c r="N117" t="s">
+        <v>7</v>
+      </c>
+      <c r="O117" t="s">
+        <v>8</v>
+      </c>
+      <c r="P117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" t="s">
+        <v>260</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s">
+        <v>255</v>
+      </c>
+      <c r="F118" t="s">
+        <v>256</v>
+      </c>
+      <c r="G118" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H118" s="3">
+        <v>46206</v>
+      </c>
+      <c r="I118" s="3">
+        <v>46211</v>
+      </c>
+      <c r="J118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118" t="s">
+        <v>5</v>
+      </c>
+      <c r="L118" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M118" t="s">
+        <v>6</v>
+      </c>
+      <c r="N118" t="s">
+        <v>7</v>
+      </c>
+      <c r="O118" t="s">
+        <v>8</v>
+      </c>
+      <c r="P118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="A119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" t="s">
+        <v>261</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
+        <v>255</v>
+      </c>
+      <c r="F119" t="s">
+        <v>256</v>
+      </c>
+      <c r="G119" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H119" s="3">
+        <v>46206</v>
+      </c>
+      <c r="I119" s="3">
+        <v>46211</v>
+      </c>
+      <c r="J119" t="s">
+        <v>123</v>
+      </c>
+      <c r="K119" t="s">
+        <v>5</v>
+      </c>
+      <c r="L119" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M119" t="s">
+        <v>6</v>
+      </c>
+      <c r="N119" t="s">
+        <v>7</v>
+      </c>
+      <c r="O119" t="s">
+        <v>8</v>
+      </c>
+      <c r="P119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" t="s">
+        <v>262</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
+        <v>251</v>
+      </c>
+      <c r="F120" t="s">
+        <v>201</v>
+      </c>
+      <c r="G120" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H120" s="3">
+        <v>46251</v>
+      </c>
+      <c r="I120" s="3">
+        <v>46253</v>
+      </c>
+      <c r="J120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120" t="s">
+        <v>5</v>
+      </c>
+      <c r="L120" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M120" t="s">
+        <v>6</v>
+      </c>
+      <c r="N120" t="s">
+        <v>7</v>
+      </c>
+      <c r="O120" t="s">
+        <v>8</v>
+      </c>
+      <c r="P120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B121" t="s">
+        <v>263</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" t="s">
+        <v>251</v>
+      </c>
+      <c r="F121" t="s">
+        <v>201</v>
+      </c>
+      <c r="G121" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H121" s="3">
+        <v>46251</v>
+      </c>
+      <c r="I121" s="3">
+        <v>46253</v>
+      </c>
+      <c r="J121" t="s">
+        <v>123</v>
+      </c>
+      <c r="K121" t="s">
+        <v>5</v>
+      </c>
+      <c r="L121" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M121" t="s">
+        <v>6</v>
+      </c>
+      <c r="N121" t="s">
+        <v>7</v>
+      </c>
+      <c r="O121" t="s">
+        <v>8</v>
+      </c>
+      <c r="P121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="A122" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" t="s">
+        <v>264</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0</v>
+      </c>
+      <c r="E122" t="s">
+        <v>255</v>
+      </c>
+      <c r="F122" t="s">
+        <v>256</v>
+      </c>
+      <c r="G122" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H122" s="3">
+        <v>46245</v>
+      </c>
+      <c r="I122" s="3">
+        <v>46248</v>
+      </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" t="s">
+        <v>5</v>
+      </c>
+      <c r="L122" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M122" t="s">
+        <v>6</v>
+      </c>
+      <c r="N122" t="s">
+        <v>7</v>
+      </c>
+      <c r="O122" t="s">
+        <v>8</v>
+      </c>
+      <c r="P122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
+      <c r="A123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
+        <v>255</v>
+      </c>
+      <c r="F123" t="s">
+        <v>256</v>
+      </c>
+      <c r="G123" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H123" s="3">
+        <v>46245</v>
+      </c>
+      <c r="I123" s="3">
+        <v>46248</v>
+      </c>
+      <c r="J123" t="s">
+        <v>123</v>
+      </c>
+      <c r="K123" t="s">
+        <v>5</v>
+      </c>
+      <c r="L123" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M123" t="s">
+        <v>6</v>
+      </c>
+      <c r="N123" t="s">
+        <v>7</v>
+      </c>
+      <c r="O123" t="s">
+        <v>8</v>
+      </c>
+      <c r="P123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
+      <c r="A124" t="s">
+        <v>0</v>
+      </c>
+      <c r="B124" t="s">
+        <v>266</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124" t="s">
         <v>267</v>
       </c>
-      <c r="B109" t="s">
+      <c r="F124" t="s">
+        <v>268</v>
+      </c>
+      <c r="G124" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H124" s="3">
+        <v>46108</v>
+      </c>
+      <c r="I124" s="3">
+        <v>46113</v>
+      </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124" t="s">
+        <v>5</v>
+      </c>
+      <c r="L124" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M124" t="s">
+        <v>6</v>
+      </c>
+      <c r="N124" t="s">
+        <v>7</v>
+      </c>
+      <c r="O124" t="s">
+        <v>8</v>
+      </c>
+      <c r="P124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
+      <c r="A125" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" t="s">
+        <v>269</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" t="s">
+        <v>267</v>
+      </c>
+      <c r="F125" t="s">
+        <v>268</v>
+      </c>
+      <c r="G125" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H125" s="3">
+        <v>46108</v>
+      </c>
+      <c r="I125" s="3">
+        <v>46113</v>
+      </c>
+      <c r="J125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125" t="s">
+        <v>5</v>
+      </c>
+      <c r="L125" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M125" t="s">
+        <v>6</v>
+      </c>
+      <c r="N125" t="s">
+        <v>7</v>
+      </c>
+      <c r="O125" t="s">
+        <v>8</v>
+      </c>
+      <c r="P125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
+      <c r="A126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" t="s">
+        <v>270</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
+        <v>267</v>
+      </c>
+      <c r="F126" t="s">
+        <v>268</v>
+      </c>
+      <c r="G126" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H126" s="3">
+        <v>46108</v>
+      </c>
+      <c r="I126" s="3">
+        <v>46113</v>
+      </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126" t="s">
+        <v>5</v>
+      </c>
+      <c r="L126" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M126" t="s">
+        <v>6</v>
+      </c>
+      <c r="N126" t="s">
+        <v>7</v>
+      </c>
+      <c r="O126" t="s">
+        <v>8</v>
+      </c>
+      <c r="P126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
+      <c r="A127" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" t="s">
+        <v>271</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" t="s">
+        <v>267</v>
+      </c>
+      <c r="F127" t="s">
+        <v>268</v>
+      </c>
+      <c r="G127" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H127" s="3">
+        <v>46108</v>
+      </c>
+      <c r="I127" s="3">
+        <v>46113</v>
+      </c>
+      <c r="J127" t="s">
+        <v>18</v>
+      </c>
+      <c r="K127" t="s">
+        <v>5</v>
+      </c>
+      <c r="L127" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M127" t="s">
+        <v>6</v>
+      </c>
+      <c r="N127" t="s">
+        <v>7</v>
+      </c>
+      <c r="O127" t="s">
+        <v>8</v>
+      </c>
+      <c r="P127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
+      <c r="A128" t="s">
+        <v>0</v>
+      </c>
+      <c r="B128" t="s">
+        <v>272</v>
+      </c>
+      <c r="C128" s="2">
+        <v>1</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
+        <v>273</v>
+      </c>
+      <c r="F128" t="s">
+        <v>274</v>
+      </c>
+      <c r="G128" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H128" s="3">
+        <v>46104</v>
+      </c>
+      <c r="I128" s="3">
+        <v>46107</v>
+      </c>
+      <c r="J128" t="s">
+        <v>123</v>
+      </c>
+      <c r="K128" t="s">
+        <v>5</v>
+      </c>
+      <c r="L128" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M128" t="s">
+        <v>6</v>
+      </c>
+      <c r="N128" t="s">
+        <v>7</v>
+      </c>
+      <c r="O128" t="s">
+        <v>8</v>
+      </c>
+      <c r="P128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
+      <c r="A129" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" t="s">
+        <v>275</v>
+      </c>
+      <c r="C129" s="2">
+        <v>1</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0</v>
+      </c>
+      <c r="E129" t="s">
+        <v>273</v>
+      </c>
+      <c r="F129" t="s">
+        <v>274</v>
+      </c>
+      <c r="G129" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H129" s="3">
+        <v>46104</v>
+      </c>
+      <c r="I129" s="3">
+        <v>46107</v>
+      </c>
+      <c r="J129" t="s">
+        <v>123</v>
+      </c>
+      <c r="K129" t="s">
+        <v>5</v>
+      </c>
+      <c r="L129" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M129" t="s">
+        <v>6</v>
+      </c>
+      <c r="N129" t="s">
+        <v>7</v>
+      </c>
+      <c r="O129" t="s">
+        <v>8</v>
+      </c>
+      <c r="P129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
+      <c r="A130" t="s">
+        <v>0</v>
+      </c>
+      <c r="B130" t="s">
+        <v>276</v>
+      </c>
+      <c r="C130" s="2">
+        <v>1</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0</v>
+      </c>
+      <c r="E130" t="s">
+        <v>273</v>
+      </c>
+      <c r="F130" t="s">
+        <v>274</v>
+      </c>
+      <c r="G130" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H130" s="3">
+        <v>46104</v>
+      </c>
+      <c r="I130" s="3">
+        <v>46107</v>
+      </c>
+      <c r="J130" t="s">
+        <v>123</v>
+      </c>
+      <c r="K130" t="s">
+        <v>5</v>
+      </c>
+      <c r="L130" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M130" t="s">
+        <v>6</v>
+      </c>
+      <c r="N130" t="s">
+        <v>7</v>
+      </c>
+      <c r="O130" t="s">
+        <v>8</v>
+      </c>
+      <c r="P130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
+      <c r="A131" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" t="s">
+        <v>277</v>
+      </c>
+      <c r="C131" s="2">
+        <v>1</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0</v>
+      </c>
+      <c r="E131" t="s">
+        <v>273</v>
+      </c>
+      <c r="F131" t="s">
+        <v>274</v>
+      </c>
+      <c r="G131" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H131" s="3">
+        <v>46104</v>
+      </c>
+      <c r="I131" s="3">
+        <v>46107</v>
+      </c>
+      <c r="J131" t="s">
+        <v>123</v>
+      </c>
+      <c r="K131" t="s">
+        <v>5</v>
+      </c>
+      <c r="L131" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M131" t="s">
+        <v>6</v>
+      </c>
+      <c r="N131" t="s">
+        <v>7</v>
+      </c>
+      <c r="O131" t="s">
+        <v>8</v>
+      </c>
+      <c r="P131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
+      <c r="A132" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" t="s">
+        <v>278</v>
+      </c>
+      <c r="C132" s="2">
+        <v>1</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0</v>
+      </c>
+      <c r="E132" t="s">
+        <v>279</v>
+      </c>
+      <c r="F132" t="s">
+        <v>280</v>
+      </c>
+      <c r="G132" s="3">
+        <v>46077</v>
+      </c>
+      <c r="H132" s="3">
+        <v>46121</v>
+      </c>
+      <c r="I132" s="3">
+        <v>46125</v>
+      </c>
+      <c r="J132" t="s">
+        <v>123</v>
+      </c>
+      <c r="K132" t="s">
+        <v>5</v>
+      </c>
+      <c r="L132" s="3">
+        <v>46077</v>
+      </c>
+      <c r="M132" t="s">
+        <v>6</v>
+      </c>
+      <c r="N132" t="s">
+        <v>7</v>
+      </c>
+      <c r="O132" t="s">
+        <v>8</v>
+      </c>
+      <c r="P132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133" t="s">
+        <v>281</v>
+      </c>
+      <c r="B133" t="s">
+        <v>282</v>
+      </c>
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
+      <c r="D133" s="2">
+        <v>0</v>
+      </c>
+      <c r="E133" t="s">
+        <v>283</v>
+      </c>
+      <c r="F133" t="s">
+        <v>284</v>
+      </c>
+      <c r="G133" s="3">
+        <v>46035</v>
+      </c>
+      <c r="H133" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I133" s="3">
+        <v>46076</v>
+      </c>
+      <c r="J133" t="s">
+        <v>80</v>
+      </c>
+      <c r="K133" t="s">
+        <v>285</v>
+      </c>
+      <c r="L133" s="3">
+        <v>46035</v>
+      </c>
+      <c r="M133" t="s">
+        <v>6</v>
+      </c>
+      <c r="N133" t="s">
+        <v>7</v>
+      </c>
+      <c r="O133" t="s">
+        <v>8</v>
+      </c>
+      <c r="P133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" t="s">
+        <v>281</v>
+      </c>
+      <c r="B134" t="s">
+        <v>286</v>
+      </c>
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s">
+        <v>287</v>
+      </c>
+      <c r="F134" t="s">
+        <v>288</v>
+      </c>
+      <c r="G134" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H134" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I134" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J134" t="s">
+        <v>123</v>
+      </c>
+      <c r="K134" t="s">
+        <v>285</v>
+      </c>
+      <c r="L134" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M134" t="s">
+        <v>6</v>
+      </c>
+      <c r="N134" t="s">
+        <v>7</v>
+      </c>
+      <c r="O134" t="s">
+        <v>8</v>
+      </c>
+      <c r="P134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" t="s">
+        <v>281</v>
+      </c>
+      <c r="B135" t="s">
+        <v>289</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
         <v>290</v>
       </c>
-      <c r="C109" s="2">
-        <v>1</v>
-      </c>
-      <c r="D109" s="2">
-        <v>0</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F135" t="s">
         <v>291</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G135" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H135" s="3">
+        <v>46059</v>
+      </c>
+      <c r="I135" s="3">
+        <v>46062</v>
+      </c>
+      <c r="J135" t="s">
+        <v>114</v>
+      </c>
+      <c r="K135" t="s">
+        <v>285</v>
+      </c>
+      <c r="L135" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M135" t="s">
+        <v>6</v>
+      </c>
+      <c r="N135" t="s">
+        <v>7</v>
+      </c>
+      <c r="O135" t="s">
+        <v>8</v>
+      </c>
+      <c r="P135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136" t="s">
+        <v>281</v>
+      </c>
+      <c r="B136" t="s">
         <v>292</v>
       </c>
-      <c r="G109" s="3">
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0</v>
+      </c>
+      <c r="E136" t="s">
+        <v>293</v>
+      </c>
+      <c r="F136" t="s">
+        <v>294</v>
+      </c>
+      <c r="G136" s="3">
         <v>46052</v>
       </c>
-      <c r="H109" s="3">
+      <c r="H136" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I136" s="3">
+        <v>46058</v>
+      </c>
+      <c r="J136" t="s">
+        <v>123</v>
+      </c>
+      <c r="K136" t="s">
+        <v>285</v>
+      </c>
+      <c r="L136" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M136" t="s">
+        <v>6</v>
+      </c>
+      <c r="N136" t="s">
+        <v>7</v>
+      </c>
+      <c r="O136" t="s">
+        <v>8</v>
+      </c>
+      <c r="P136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137" t="s">
+        <v>281</v>
+      </c>
+      <c r="B137" t="s">
+        <v>295</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" t="s">
+        <v>296</v>
+      </c>
+      <c r="F137" t="s">
+        <v>297</v>
+      </c>
+      <c r="G137" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H137" s="3">
+        <v>46077</v>
+      </c>
+      <c r="I137" s="3">
+        <v>46094</v>
+      </c>
+      <c r="J137" t="s">
+        <v>4</v>
+      </c>
+      <c r="K137" t="s">
+        <v>285</v>
+      </c>
+      <c r="L137" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M137" t="s">
+        <v>6</v>
+      </c>
+      <c r="N137" t="s">
+        <v>7</v>
+      </c>
+      <c r="O137" t="s">
+        <v>8</v>
+      </c>
+      <c r="P137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138" t="s">
+        <v>281</v>
+      </c>
+      <c r="B138" t="s">
+        <v>298</v>
+      </c>
+      <c r="C138" s="2">
+        <v>1</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0</v>
+      </c>
+      <c r="E138" t="s">
+        <v>299</v>
+      </c>
+      <c r="F138" t="s">
+        <v>300</v>
+      </c>
+      <c r="G138" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H138" s="3">
         <v>46064</v>
       </c>
-      <c r="I109" s="3">
+      <c r="I138" s="3">
         <v>46066</v>
       </c>
-      <c r="J109" t="s">
+      <c r="J138" t="s">
         <v>4</v>
       </c>
-      <c r="K109" t="s">
-        <v>271</v>
-      </c>
-      <c r="L109" s="3">
+      <c r="K138" t="s">
+        <v>285</v>
+      </c>
+      <c r="L138" s="3">
         <v>46052</v>
       </c>
-      <c r="M109" t="s">
-        <v>6</v>
-      </c>
-      <c r="N109" t="s">
-        <v>7</v>
-      </c>
-      <c r="O109" t="s">
-        <v>8</v>
-      </c>
-      <c r="P109" t="s">
+      <c r="M138" t="s">
+        <v>6</v>
+      </c>
+      <c r="N138" t="s">
+        <v>7</v>
+      </c>
+      <c r="O138" t="s">
+        <v>8</v>
+      </c>
+      <c r="P138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139" t="s">
+        <v>281</v>
+      </c>
+      <c r="B139" t="s">
+        <v>301</v>
+      </c>
+      <c r="C139" s="2">
+        <v>1</v>
+      </c>
+      <c r="D139" s="2">
+        <v>0</v>
+      </c>
+      <c r="E139" t="s">
+        <v>174</v>
+      </c>
+      <c r="F139" t="s">
+        <v>175</v>
+      </c>
+      <c r="G139" s="3">
+        <v>46057</v>
+      </c>
+      <c r="H139" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I139" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J139" t="s">
+        <v>123</v>
+      </c>
+      <c r="K139" t="s">
+        <v>285</v>
+      </c>
+      <c r="L139" s="3">
+        <v>46057</v>
+      </c>
+      <c r="M139" t="s">
+        <v>6</v>
+      </c>
+      <c r="N139" t="s">
+        <v>7</v>
+      </c>
+      <c r="O139" t="s">
+        <v>8</v>
+      </c>
+      <c r="P139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140" t="s">
+        <v>281</v>
+      </c>
+      <c r="B140" t="s">
+        <v>302</v>
+      </c>
+      <c r="C140" s="2">
+        <v>1</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0</v>
+      </c>
+      <c r="E140" t="s">
+        <v>303</v>
+      </c>
+      <c r="F140" t="s">
+        <v>304</v>
+      </c>
+      <c r="G140" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H140" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I140" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J140" t="s">
+        <v>114</v>
+      </c>
+      <c r="K140" t="s">
+        <v>285</v>
+      </c>
+      <c r="L140" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M140" t="s">
+        <v>6</v>
+      </c>
+      <c r="N140" t="s">
+        <v>7</v>
+      </c>
+      <c r="O140" t="s">
+        <v>8</v>
+      </c>
+      <c r="P140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141" t="s">
+        <v>281</v>
+      </c>
+      <c r="B141" t="s">
+        <v>305</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>255</v>
+      </c>
+      <c r="F141" t="s">
+        <v>256</v>
+      </c>
+      <c r="G141" s="3">
+        <v>46077</v>
+      </c>
+      <c r="H141" s="3">
+        <v>46078</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46084</v>
+      </c>
+      <c r="J141" t="s">
+        <v>86</v>
+      </c>
+      <c r="K141" t="s">
+        <v>285</v>
+      </c>
+      <c r="L141" s="3">
+        <v>46077</v>
+      </c>
+      <c r="M141" t="s">
+        <v>6</v>
+      </c>
+      <c r="N141" t="s">
+        <v>7</v>
+      </c>
+      <c r="O141" t="s">
+        <v>8</v>
+      </c>
+      <c r="P141" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="353">
   <si>
     <t>ZP02</t>
   </si>
@@ -97,6 +97,9 @@
     <t>G6K 主軸,021327_BBT50,C045</t>
   </si>
   <si>
+    <t>REL  PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
     <t>200006326</t>
   </si>
   <si>
@@ -133,9 +136,6 @@
     <t>H1682機頭G8K,021565_#50,42F25,C</t>
   </si>
   <si>
-    <t>REL  PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
     <t>200006367</t>
   </si>
   <si>
@@ -355,66 +355,66 @@
     <t>200006447</t>
   </si>
   <si>
+    <t>200006448</t>
+  </si>
+  <si>
+    <t>200006449</t>
+  </si>
+  <si>
+    <t>080200015002</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011164_Z1200,55A18,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>200006450</t>
+  </si>
+  <si>
+    <t>080100015401</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,C0DIN</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006452</t>
+  </si>
+  <si>
+    <t>080200159204</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011282_780,BT50,55,CDIN</t>
+  </si>
+  <si>
+    <t>200006453</t>
+  </si>
+  <si>
+    <t>200006454</t>
+  </si>
+  <si>
+    <t>080200565901</t>
+  </si>
+  <si>
+    <t>H1100機頭G6K,021822_#50,48F23,C</t>
+  </si>
+  <si>
+    <t>200006456</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006457</t>
+  </si>
+  <si>
     <t>REL  PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>200006448</t>
-  </si>
-  <si>
-    <t>200006449</t>
-  </si>
-  <si>
-    <t>080200015002</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>200006450</t>
-  </si>
-  <si>
-    <t>080100015401</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M50E,C0DIN</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006452</t>
-  </si>
-  <si>
-    <t>080200159204</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011282_780,BT50,55,CDIN</t>
-  </si>
-  <si>
-    <t>200006453</t>
-  </si>
-  <si>
-    <t>200006454</t>
-  </si>
-  <si>
-    <t>080200565901</t>
-  </si>
-  <si>
-    <t>H1100機頭G6K,021822_#50,48F23,C</t>
-  </si>
-  <si>
-    <t>200006456</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006457</t>
-  </si>
-  <si>
     <t>200006458</t>
   </si>
   <si>
@@ -499,9 +499,6 @@
     <t>HEP機頭D20K,021783_780,A63,38,C</t>
   </si>
   <si>
-    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
     <t>200006476</t>
   </si>
   <si>
@@ -745,6 +742,9 @@
     <t>D20K 主軸,021608_A63,M50,CW</t>
   </si>
   <si>
+    <t>REL  MSPT PRC  RMWB SETC</t>
+  </si>
+  <si>
     <t>200006527</t>
   </si>
   <si>
@@ -854,6 +854,99 @@
   </si>
   <si>
     <t>LG1370 NEO機頭D15K,021941_#40,38F18,C,AT8</t>
+  </si>
+  <si>
+    <t>200006554</t>
+  </si>
+  <si>
+    <t>080200037902</t>
+  </si>
+  <si>
+    <t>HSA機頭G6K,021563_1200,BBT50,55,045</t>
+  </si>
+  <si>
+    <t>200006555</t>
+  </si>
+  <si>
+    <t>080100035602</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,0045</t>
+  </si>
+  <si>
+    <t>200006556</t>
+  </si>
+  <si>
+    <t>080200069201</t>
+  </si>
+  <si>
+    <t>L800機頭P8K,021615_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006557</t>
+  </si>
+  <si>
+    <t>200006558</t>
+  </si>
+  <si>
+    <t>200006559</t>
+  </si>
+  <si>
+    <t>080200527500</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,38F18</t>
+  </si>
+  <si>
+    <t>200006560</t>
+  </si>
+  <si>
+    <t>200006561</t>
+  </si>
+  <si>
+    <t>080200538702</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,48F23,C</t>
+  </si>
+  <si>
+    <t>200006562</t>
+  </si>
+  <si>
+    <t>200006563</t>
+  </si>
+  <si>
+    <t>200006564</t>
+  </si>
+  <si>
+    <t>080100113205</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CW45</t>
+  </si>
+  <si>
+    <t>CRTD MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>200006565</t>
+  </si>
+  <si>
+    <t>200006566</t>
+  </si>
+  <si>
+    <t>200006567</t>
+  </si>
+  <si>
+    <t>080300028606</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_1°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006568</t>
   </si>
   <si>
     <t>ZP09</t>
@@ -1081,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P156"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1104,52 +1197,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1481,7 +1574,7 @@
         <v>46092</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
@@ -1507,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1516,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" s="3">
         <v>45979</v>
@@ -1557,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
@@ -1566,10 +1659,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" s="3">
         <v>45986</v>
@@ -1607,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -1616,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" s="3">
         <v>45986</v>
@@ -1657,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1666,10 +1759,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" s="3">
         <v>45995</v>
@@ -1681,7 +1774,7 @@
         <v>46094</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
@@ -2981,7 +3074,7 @@
         <v>46090</v>
       </c>
       <c r="J38" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
@@ -3007,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3057,19 +3150,19 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="2">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>117</v>
-      </c>
-      <c r="F40" t="s">
-        <v>118</v>
       </c>
       <c r="G40" s="3">
         <v>46044</v>
@@ -3081,7 +3174,7 @@
         <v>46086</v>
       </c>
       <c r="J40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
@@ -3107,19 +3200,19 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="2">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>121</v>
-      </c>
-      <c r="F41" t="s">
-        <v>122</v>
       </c>
       <c r="G41" s="3">
         <v>46044</v>
@@ -3131,7 +3224,7 @@
         <v>46076</v>
       </c>
       <c r="J41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
@@ -3157,19 +3250,19 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="2">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>125</v>
-      </c>
-      <c r="F42" t="s">
-        <v>126</v>
       </c>
       <c r="G42" s="3">
         <v>46044</v>
@@ -3207,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3216,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G43" s="3">
         <v>46044</v>
@@ -3231,7 +3324,7 @@
         <v>46076</v>
       </c>
       <c r="J43" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -3257,19 +3350,19 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="2">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>129</v>
-      </c>
-      <c r="F44" t="s">
-        <v>130</v>
       </c>
       <c r="G44" s="3">
         <v>46044</v>
@@ -3307,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3316,10 +3409,10 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" t="s">
         <v>125</v>
-      </c>
-      <c r="F45" t="s">
-        <v>126</v>
       </c>
       <c r="G45" s="3">
         <v>46044</v>
@@ -3331,7 +3424,7 @@
         <v>46083</v>
       </c>
       <c r="J45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
@@ -3357,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3366,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G46" s="3">
         <v>46044</v>
@@ -3381,7 +3474,7 @@
         <v>46076</v>
       </c>
       <c r="J46" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
@@ -3431,7 +3524,7 @@
         <v>46093</v>
       </c>
       <c r="J47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
@@ -3466,10 +3559,10 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G48" s="3">
         <v>46048</v>
@@ -3481,7 +3574,7 @@
         <v>46087</v>
       </c>
       <c r="J48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
@@ -3531,7 +3624,7 @@
         <v>46090</v>
       </c>
       <c r="J49" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
@@ -3581,7 +3674,7 @@
         <v>46091</v>
       </c>
       <c r="J50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
@@ -3631,7 +3724,7 @@
         <v>46093</v>
       </c>
       <c r="J51" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
@@ -3931,7 +4024,7 @@
         <v>46056</v>
       </c>
       <c r="J57" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="K57" t="s">
         <v>5</v>
@@ -3957,19 +4050,19 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
         <v>163</v>
       </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>164</v>
-      </c>
-      <c r="F58" t="s">
-        <v>165</v>
       </c>
       <c r="G58" s="3">
         <v>46050</v>
@@ -4007,19 +4100,19 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
         <v>166</v>
       </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>167</v>
-      </c>
-      <c r="F59" t="s">
-        <v>168</v>
       </c>
       <c r="G59" s="3">
         <v>46052</v>
@@ -4031,7 +4124,7 @@
         <v>46063</v>
       </c>
       <c r="J59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
@@ -4057,19 +4150,19 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
+        <v>169</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
         <v>170</v>
       </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>171</v>
-      </c>
-      <c r="F60" t="s">
-        <v>172</v>
       </c>
       <c r="G60" s="3">
         <v>46052</v>
@@ -4081,7 +4174,7 @@
         <v>46087</v>
       </c>
       <c r="J60" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
@@ -4107,19 +4200,19 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
+        <v>172</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
         <v>173</v>
       </c>
-      <c r="C61" s="2">
-        <v>1</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>174</v>
-      </c>
-      <c r="F61" t="s">
-        <v>175</v>
       </c>
       <c r="G61" s="3">
         <v>46052</v>
@@ -4131,7 +4224,7 @@
         <v>46083</v>
       </c>
       <c r="J61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
@@ -4157,19 +4250,19 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
+        <v>175</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
         <v>176</v>
       </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>177</v>
-      </c>
-      <c r="F62" t="s">
-        <v>178</v>
       </c>
       <c r="G62" s="3">
         <v>46055</v>
@@ -4181,7 +4274,7 @@
         <v>46142</v>
       </c>
       <c r="J62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
@@ -4207,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4231,7 +4324,7 @@
         <v>46136</v>
       </c>
       <c r="J63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
@@ -4257,19 +4350,19 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
+        <v>179</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
         <v>180</v>
       </c>
-      <c r="C64" s="2">
-        <v>1</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>181</v>
-      </c>
-      <c r="F64" t="s">
-        <v>182</v>
       </c>
       <c r="G64" s="3">
         <v>46057</v>
@@ -4281,7 +4374,7 @@
         <v>46100</v>
       </c>
       <c r="J64" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
@@ -4307,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4316,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
+        <v>180</v>
+      </c>
+      <c r="F65" t="s">
         <v>181</v>
-      </c>
-      <c r="F65" t="s">
-        <v>182</v>
       </c>
       <c r="G65" s="3">
         <v>46057</v>
@@ -4331,7 +4424,7 @@
         <v>46100</v>
       </c>
       <c r="J65" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4357,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4407,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4457,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4507,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4531,7 +4624,7 @@
         <v>46136</v>
       </c>
       <c r="J69" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4557,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4581,7 +4674,7 @@
         <v>46142</v>
       </c>
       <c r="J70" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4607,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4616,10 +4709,10 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
+        <v>173</v>
+      </c>
+      <c r="F71" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" t="s">
-        <v>175</v>
       </c>
       <c r="G71" s="3">
         <v>46058</v>
@@ -4657,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4666,10 +4759,10 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
+        <v>173</v>
+      </c>
+      <c r="F72" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>175</v>
       </c>
       <c r="G72" s="3">
         <v>46058</v>
@@ -4707,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
+        <v>190</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
         <v>191</v>
       </c>
-      <c r="C73" s="2">
-        <v>1</v>
-      </c>
-      <c r="D73" s="2">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>192</v>
-      </c>
-      <c r="F73" t="s">
-        <v>193</v>
       </c>
       <c r="G73" s="3">
         <v>46062</v>
@@ -4757,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4766,10 +4859,10 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
+        <v>191</v>
+      </c>
+      <c r="F74" t="s">
         <v>192</v>
-      </c>
-      <c r="F74" t="s">
-        <v>193</v>
       </c>
       <c r="G74" s="3">
         <v>46062</v>
@@ -4807,19 +4900,19 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
+        <v>194</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
         <v>195</v>
       </c>
-      <c r="C75" s="2">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2">
-        <v>0</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>196</v>
-      </c>
-      <c r="F75" t="s">
-        <v>197</v>
       </c>
       <c r="G75" s="3">
         <v>46062</v>
@@ -4831,7 +4924,7 @@
         <v>46098</v>
       </c>
       <c r="J75" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
@@ -4857,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4866,10 +4959,10 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
+        <v>195</v>
+      </c>
+      <c r="F76" t="s">
         <v>196</v>
-      </c>
-      <c r="F76" t="s">
-        <v>197</v>
       </c>
       <c r="G76" s="3">
         <v>46062</v>
@@ -4881,7 +4974,7 @@
         <v>46099</v>
       </c>
       <c r="J76" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
@@ -4907,19 +5000,19 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
+        <v>198</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0</v>
+      </c>
+      <c r="E77" t="s">
         <v>199</v>
       </c>
-      <c r="C77" s="2">
-        <v>1</v>
-      </c>
-      <c r="D77" s="2">
-        <v>0</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>200</v>
-      </c>
-      <c r="F77" t="s">
-        <v>201</v>
       </c>
       <c r="G77" s="3">
         <v>46063</v>
@@ -4957,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -4966,10 +5059,10 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
+        <v>199</v>
+      </c>
+      <c r="F78" t="s">
         <v>200</v>
-      </c>
-      <c r="F78" t="s">
-        <v>201</v>
       </c>
       <c r="G78" s="3">
         <v>46063</v>
@@ -5007,19 +5100,19 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
+        <v>202</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0</v>
+      </c>
+      <c r="E79" t="s">
         <v>203</v>
       </c>
-      <c r="C79" s="2">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
-        <v>0</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>204</v>
-      </c>
-      <c r="F79" t="s">
-        <v>205</v>
       </c>
       <c r="G79" s="3">
         <v>46063</v>
@@ -5031,7 +5124,7 @@
         <v>46094</v>
       </c>
       <c r="J79" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
@@ -5057,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5066,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
+        <v>203</v>
+      </c>
+      <c r="F80" t="s">
         <v>204</v>
-      </c>
-      <c r="F80" t="s">
-        <v>205</v>
       </c>
       <c r="G80" s="3">
         <v>46063</v>
@@ -5107,19 +5200,19 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
+        <v>206</v>
+      </c>
+      <c r="C81" s="2">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
         <v>207</v>
       </c>
-      <c r="C81" s="2">
-        <v>1</v>
-      </c>
-      <c r="D81" s="2">
-        <v>0</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>208</v>
-      </c>
-      <c r="F81" t="s">
-        <v>209</v>
       </c>
       <c r="G81" s="3">
         <v>46064</v>
@@ -5131,7 +5224,7 @@
         <v>46087</v>
       </c>
       <c r="J81" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
@@ -5157,19 +5250,19 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
+        <v>209</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0</v>
+      </c>
+      <c r="E82" t="s">
         <v>210</v>
       </c>
-      <c r="C82" s="2">
-        <v>1</v>
-      </c>
-      <c r="D82" s="2">
-        <v>0</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>211</v>
-      </c>
-      <c r="F82" t="s">
-        <v>212</v>
       </c>
       <c r="G82" s="3">
         <v>46064</v>
@@ -5181,7 +5274,7 @@
         <v>46092</v>
       </c>
       <c r="J82" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
@@ -5207,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5257,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5281,7 +5374,7 @@
         <v>46181</v>
       </c>
       <c r="J84" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
@@ -5307,16 +5400,16 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
+        <v>215</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
         <v>216</v>
-      </c>
-      <c r="C85" s="2">
-        <v>1</v>
-      </c>
-      <c r="D85" s="2">
-        <v>0</v>
-      </c>
-      <c r="E85" t="s">
-        <v>217</v>
       </c>
       <c r="F85" t="s">
         <v>21</v>
@@ -5357,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5366,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F86" t="s">
         <v>21</v>
@@ -5381,7 +5474,7 @@
         <v>46175</v>
       </c>
       <c r="J86" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
@@ -5407,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5457,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5481,7 +5574,7 @@
         <v>46245</v>
       </c>
       <c r="J88" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
@@ -5507,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5516,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F89" t="s">
         <v>21</v>
@@ -5557,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5566,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F90" t="s">
         <v>21</v>
@@ -5581,7 +5674,7 @@
         <v>46239</v>
       </c>
       <c r="J90" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
@@ -5607,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5631,7 +5724,7 @@
         <v>46149</v>
       </c>
       <c r="J91" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
@@ -5657,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5681,7 +5774,7 @@
         <v>46177</v>
       </c>
       <c r="J92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
@@ -5707,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5731,7 +5824,7 @@
         <v>46241</v>
       </c>
       <c r="J93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
@@ -5757,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5781,7 +5874,7 @@
         <v>46302</v>
       </c>
       <c r="J94" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
@@ -5807,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -5816,7 +5909,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" t="s">
         <v>21</v>
@@ -5831,7 +5924,7 @@
         <v>46142</v>
       </c>
       <c r="J95" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
@@ -5857,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -5866,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F96" t="s">
         <v>21</v>
@@ -5881,7 +5974,7 @@
         <v>46171</v>
       </c>
       <c r="J96" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
@@ -5907,7 +6000,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -5916,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F97" t="s">
         <v>21</v>
@@ -5931,7 +6024,7 @@
         <v>46237</v>
       </c>
       <c r="J97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
@@ -5957,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -5966,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" t="s">
         <v>21</v>
@@ -5981,7 +6074,7 @@
         <v>46296</v>
       </c>
       <c r="J98" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
@@ -6007,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6029,7 +6122,7 @@
         <v>46307</v>
       </c>
       <c r="J99" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
@@ -6055,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6079,7 +6172,7 @@
         <v>46307</v>
       </c>
       <c r="J100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
@@ -6105,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6114,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F101" t="s">
         <v>21</v>
@@ -6129,7 +6222,7 @@
         <v>46272</v>
       </c>
       <c r="J101" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
@@ -6155,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6164,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F102" t="s">
         <v>21</v>
@@ -6179,7 +6272,7 @@
         <v>46272</v>
       </c>
       <c r="J102" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
@@ -6205,19 +6298,19 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
+        <v>235</v>
+      </c>
+      <c r="C103" s="2">
+        <v>1</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
         <v>236</v>
       </c>
-      <c r="C103" s="2">
-        <v>1</v>
-      </c>
-      <c r="D103" s="2">
-        <v>0</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>237</v>
-      </c>
-      <c r="F103" t="s">
-        <v>238</v>
       </c>
       <c r="G103" s="3">
         <v>46076</v>
@@ -6255,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6264,10 +6357,10 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
+        <v>236</v>
+      </c>
+      <c r="F104" t="s">
         <v>237</v>
-      </c>
-      <c r="F104" t="s">
-        <v>238</v>
       </c>
       <c r="G104" s="3">
         <v>46076</v>
@@ -6305,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6314,10 +6407,10 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
+        <v>236</v>
+      </c>
+      <c r="F105" t="s">
         <v>237</v>
-      </c>
-      <c r="F105" t="s">
-        <v>238</v>
       </c>
       <c r="G105" s="3">
         <v>46076</v>
@@ -6329,7 +6422,7 @@
         <v>46091</v>
       </c>
       <c r="J105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
@@ -6355,19 +6448,19 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
         <v>241</v>
       </c>
-      <c r="C106" s="2">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2">
-        <v>0</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>242</v>
-      </c>
-      <c r="F106" t="s">
-        <v>243</v>
       </c>
       <c r="G106" s="3">
         <v>46076</v>
@@ -6379,7 +6472,7 @@
         <v>46086</v>
       </c>
       <c r="J106" t="s">
-        <v>119</v>
+        <v>243</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
@@ -6414,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
+        <v>241</v>
+      </c>
+      <c r="F107" t="s">
         <v>242</v>
-      </c>
-      <c r="F107" t="s">
-        <v>243</v>
       </c>
       <c r="G107" s="3">
         <v>46076</v>
@@ -6429,7 +6522,7 @@
         <v>46086</v>
       </c>
       <c r="J107" t="s">
-        <v>119</v>
+        <v>243</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
@@ -6464,10 +6557,10 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
+        <v>241</v>
+      </c>
+      <c r="F108" t="s">
         <v>242</v>
-      </c>
-      <c r="F108" t="s">
-        <v>243</v>
       </c>
       <c r="G108" s="3">
         <v>46076</v>
@@ -6479,7 +6572,7 @@
         <v>46086</v>
       </c>
       <c r="J108" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
@@ -6579,7 +6672,7 @@
         <v>46104</v>
       </c>
       <c r="J110" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
@@ -6617,19 +6710,19 @@
         <v>251</v>
       </c>
       <c r="F111" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G111" s="3">
         <v>46076</v>
       </c>
       <c r="H111" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="I111" s="3">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="J111" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
@@ -6667,7 +6760,7 @@
         <v>251</v>
       </c>
       <c r="F112" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G112" s="3">
         <v>46076</v>
@@ -6717,7 +6810,7 @@
         <v>251</v>
       </c>
       <c r="F113" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G113" s="3">
         <v>46076</v>
@@ -6729,7 +6822,7 @@
         <v>46164</v>
       </c>
       <c r="J113" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
@@ -6829,7 +6922,7 @@
         <v>46161</v>
       </c>
       <c r="J115" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
@@ -6867,7 +6960,7 @@
         <v>251</v>
       </c>
       <c r="F116" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G116" s="3">
         <v>46076</v>
@@ -6917,7 +7010,7 @@
         <v>251</v>
       </c>
       <c r="F117" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G117" s="3">
         <v>46076</v>
@@ -6929,7 +7022,7 @@
         <v>46216</v>
       </c>
       <c r="J117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
@@ -7029,7 +7122,7 @@
         <v>46211</v>
       </c>
       <c r="J119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
@@ -7067,7 +7160,7 @@
         <v>251</v>
       </c>
       <c r="F120" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G120" s="3">
         <v>46076</v>
@@ -7117,7 +7210,7 @@
         <v>251</v>
       </c>
       <c r="F121" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G121" s="3">
         <v>46076</v>
@@ -7129,7 +7222,7 @@
         <v>46253</v>
       </c>
       <c r="J121" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
@@ -7229,7 +7322,7 @@
         <v>46248</v>
       </c>
       <c r="J123" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
@@ -7479,7 +7572,7 @@
         <v>46107</v>
       </c>
       <c r="J128" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
@@ -7529,7 +7622,7 @@
         <v>46107</v>
       </c>
       <c r="J129" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
@@ -7579,7 +7672,7 @@
         <v>46107</v>
       </c>
       <c r="J130" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
@@ -7629,7 +7722,7 @@
         <v>46107</v>
       </c>
       <c r="J131" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
@@ -7679,7 +7772,7 @@
         <v>46125</v>
       </c>
       <c r="J132" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
@@ -7702,40 +7795,40 @@
     </row>
     <row r="133" spans="1:16">
       <c r="A133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B133" t="s">
         <v>281</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
+      <c r="D133" s="2">
+        <v>0</v>
+      </c>
+      <c r="E133" t="s">
         <v>282</v>
       </c>
-      <c r="C133" s="2">
-        <v>1</v>
-      </c>
-      <c r="D133" s="2">
-        <v>0</v>
-      </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>283</v>
       </c>
-      <c r="F133" t="s">
-        <v>284</v>
-      </c>
       <c r="G133" s="3">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="H133" s="3">
-        <v>46052</v>
+        <v>46155</v>
       </c>
       <c r="I133" s="3">
-        <v>46076</v>
+        <v>46160</v>
       </c>
       <c r="J133" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="K133" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -7752,40 +7845,40 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B134" t="s">
+        <v>284</v>
+      </c>
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s">
+        <v>285</v>
+      </c>
+      <c r="F134" t="s">
         <v>286</v>
       </c>
-      <c r="C134" s="2">
-        <v>1</v>
-      </c>
-      <c r="D134" s="2">
-        <v>0</v>
-      </c>
-      <c r="E134" t="s">
-        <v>287</v>
-      </c>
-      <c r="F134" t="s">
-        <v>288</v>
-      </c>
       <c r="G134" s="3">
-        <v>46043</v>
+        <v>46079</v>
       </c>
       <c r="H134" s="3">
-        <v>46051</v>
+        <v>46147</v>
       </c>
       <c r="I134" s="3">
-        <v>46057</v>
+        <v>46150</v>
       </c>
       <c r="J134" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K134" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46043</v>
+        <v>46079</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -7802,40 +7895,40 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B135" t="s">
+        <v>287</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
+        <v>288</v>
+      </c>
+      <c r="F135" t="s">
         <v>289</v>
       </c>
-      <c r="C135" s="2">
-        <v>1</v>
-      </c>
-      <c r="D135" s="2">
-        <v>0</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="G135" s="3">
+        <v>46079</v>
+      </c>
+      <c r="H135" s="3">
+        <v>46079</v>
+      </c>
+      <c r="I135" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J135" t="s">
         <v>290</v>
       </c>
-      <c r="F135" t="s">
-        <v>291</v>
-      </c>
-      <c r="G135" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H135" s="3">
-        <v>46059</v>
-      </c>
-      <c r="I135" s="3">
-        <v>46062</v>
-      </c>
-      <c r="J135" t="s">
-        <v>114</v>
-      </c>
       <c r="K135" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -7852,10 +7945,10 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -7864,28 +7957,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F136" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G136" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="H136" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="I136" s="3">
-        <v>46058</v>
+        <v>46083</v>
       </c>
       <c r="J136" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="K136" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -7902,10 +7995,10 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -7914,28 +8007,28 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F137" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="G137" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="H137" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="I137" s="3">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="J137" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K137" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
       <c r="L137" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -7952,10 +8045,10 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -7964,28 +8057,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F138" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G138" s="3">
-        <v>46052</v>
+        <v>46083</v>
       </c>
       <c r="H138" s="3">
-        <v>46064</v>
+        <v>46083</v>
       </c>
       <c r="I138" s="3">
-        <v>46066</v>
+        <v>46085</v>
       </c>
       <c r="J138" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="K138" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46052</v>
+        <v>46083</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8002,10 +8095,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8014,28 +8107,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>174</v>
+        <v>294</v>
       </c>
       <c r="F139" t="s">
-        <v>175</v>
+        <v>295</v>
       </c>
       <c r="G139" s="3">
-        <v>46057</v>
+        <v>46083</v>
       </c>
       <c r="H139" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="I139" s="3">
+        <v>46085</v>
+      </c>
+      <c r="J139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139" t="s">
+        <v>5</v>
+      </c>
+      <c r="L139" s="3">
         <v>46083</v>
-      </c>
-      <c r="J139" t="s">
-        <v>123</v>
-      </c>
-      <c r="K139" t="s">
-        <v>285</v>
-      </c>
-      <c r="L139" s="3">
-        <v>46057</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8052,10 +8145,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8064,28 +8157,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F140" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G140" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H140" s="3">
-        <v>46114</v>
+        <v>46090</v>
       </c>
       <c r="I140" s="3">
-        <v>46119</v>
+        <v>46093</v>
       </c>
       <c r="J140" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K140" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
       <c r="L140" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8102,51 +8195,795 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="B141" t="s">
+        <v>300</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>298</v>
+      </c>
+      <c r="F141" t="s">
+        <v>299</v>
+      </c>
+      <c r="G141" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H141" s="3">
+        <v>46090</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46093</v>
+      </c>
+      <c r="J141" t="s">
+        <v>122</v>
+      </c>
+      <c r="K141" t="s">
+        <v>5</v>
+      </c>
+      <c r="L141" s="3">
+        <v>46083</v>
+      </c>
+      <c r="M141" t="s">
+        <v>6</v>
+      </c>
+      <c r="N141" t="s">
+        <v>7</v>
+      </c>
+      <c r="O141" t="s">
+        <v>8</v>
+      </c>
+      <c r="P141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" t="s">
+        <v>301</v>
+      </c>
+      <c r="C142" s="2">
+        <v>1</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s">
+        <v>298</v>
+      </c>
+      <c r="F142" t="s">
+        <v>299</v>
+      </c>
+      <c r="G142" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H142" s="3">
+        <v>46090</v>
+      </c>
+      <c r="I142" s="3">
+        <v>46093</v>
+      </c>
+      <c r="J142" t="s">
+        <v>122</v>
+      </c>
+      <c r="K142" t="s">
+        <v>5</v>
+      </c>
+      <c r="L142" s="3">
+        <v>46083</v>
+      </c>
+      <c r="M142" t="s">
+        <v>6</v>
+      </c>
+      <c r="N142" t="s">
+        <v>7</v>
+      </c>
+      <c r="O142" t="s">
+        <v>8</v>
+      </c>
+      <c r="P142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" t="s">
+        <v>302</v>
+      </c>
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
+        <v>303</v>
+      </c>
+      <c r="F143" t="s">
+        <v>304</v>
+      </c>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3">
+        <v>46084</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46087</v>
+      </c>
+      <c r="J143" t="s">
         <v>305</v>
       </c>
-      <c r="C141" s="2">
-        <v>1</v>
-      </c>
-      <c r="D141" s="2">
-        <v>0</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="K143" t="s">
+        <v>5</v>
+      </c>
+      <c r="L143" s="3">
+        <v>46083</v>
+      </c>
+      <c r="M143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N143" t="s">
+        <v>7</v>
+      </c>
+      <c r="O143" t="s">
+        <v>8</v>
+      </c>
+      <c r="P143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" t="s">
+        <v>306</v>
+      </c>
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2">
+        <v>0</v>
+      </c>
+      <c r="E144" t="s">
+        <v>303</v>
+      </c>
+      <c r="F144" t="s">
+        <v>304</v>
+      </c>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3">
+        <v>46084</v>
+      </c>
+      <c r="I144" s="3">
+        <v>46087</v>
+      </c>
+      <c r="J144" t="s">
+        <v>305</v>
+      </c>
+      <c r="K144" t="s">
+        <v>5</v>
+      </c>
+      <c r="L144" s="3">
+        <v>46083</v>
+      </c>
+      <c r="M144" t="s">
+        <v>6</v>
+      </c>
+      <c r="N144" t="s">
+        <v>7</v>
+      </c>
+      <c r="O144" t="s">
+        <v>8</v>
+      </c>
+      <c r="P144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" t="s">
+        <v>0</v>
+      </c>
+      <c r="B145" t="s">
+        <v>307</v>
+      </c>
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0</v>
+      </c>
+      <c r="E145" t="s">
+        <v>303</v>
+      </c>
+      <c r="F145" t="s">
+        <v>304</v>
+      </c>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3">
+        <v>46084</v>
+      </c>
+      <c r="I145" s="3">
+        <v>46087</v>
+      </c>
+      <c r="J145" t="s">
+        <v>305</v>
+      </c>
+      <c r="K145" t="s">
+        <v>5</v>
+      </c>
+      <c r="L145" s="3">
+        <v>46083</v>
+      </c>
+      <c r="M145" t="s">
+        <v>6</v>
+      </c>
+      <c r="N145" t="s">
+        <v>7</v>
+      </c>
+      <c r="O145" t="s">
+        <v>8</v>
+      </c>
+      <c r="P145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B146" t="s">
+        <v>308</v>
+      </c>
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="E146" t="s">
+        <v>309</v>
+      </c>
+      <c r="F146" t="s">
+        <v>310</v>
+      </c>
+      <c r="G146" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H146" s="3">
+        <v>46083</v>
+      </c>
+      <c r="I146" s="3">
+        <v>46107</v>
+      </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146" t="s">
+        <v>5</v>
+      </c>
+      <c r="L146" s="3">
+        <v>46083</v>
+      </c>
+      <c r="M146" t="s">
+        <v>6</v>
+      </c>
+      <c r="N146" t="s">
+        <v>7</v>
+      </c>
+      <c r="O146" t="s">
+        <v>8</v>
+      </c>
+      <c r="P146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" t="s">
+        <v>311</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>143</v>
+      </c>
+      <c r="F147" t="s">
+        <v>144</v>
+      </c>
+      <c r="G147" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H147" s="3">
+        <v>46084</v>
+      </c>
+      <c r="I147" s="3">
+        <v>46107</v>
+      </c>
+      <c r="J147" t="s">
+        <v>18</v>
+      </c>
+      <c r="K147" t="s">
+        <v>5</v>
+      </c>
+      <c r="L147" s="3">
+        <v>46083</v>
+      </c>
+      <c r="M147" t="s">
+        <v>6</v>
+      </c>
+      <c r="N147" t="s">
+        <v>7</v>
+      </c>
+      <c r="O147" t="s">
+        <v>8</v>
+      </c>
+      <c r="P147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148" t="s">
+        <v>312</v>
+      </c>
+      <c r="B148" t="s">
+        <v>313</v>
+      </c>
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0</v>
+      </c>
+      <c r="E148" t="s">
+        <v>314</v>
+      </c>
+      <c r="F148" t="s">
+        <v>315</v>
+      </c>
+      <c r="G148" s="3">
+        <v>46035</v>
+      </c>
+      <c r="H148" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I148" s="3">
+        <v>46076</v>
+      </c>
+      <c r="J148" t="s">
+        <v>80</v>
+      </c>
+      <c r="K148" t="s">
+        <v>316</v>
+      </c>
+      <c r="L148" s="3">
+        <v>46035</v>
+      </c>
+      <c r="M148" t="s">
+        <v>6</v>
+      </c>
+      <c r="N148" t="s">
+        <v>7</v>
+      </c>
+      <c r="O148" t="s">
+        <v>8</v>
+      </c>
+      <c r="P148" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
+      <c r="A149" t="s">
+        <v>312</v>
+      </c>
+      <c r="B149" t="s">
+        <v>317</v>
+      </c>
+      <c r="C149" s="2">
+        <v>1</v>
+      </c>
+      <c r="D149" s="2">
+        <v>0</v>
+      </c>
+      <c r="E149" t="s">
+        <v>318</v>
+      </c>
+      <c r="F149" t="s">
+        <v>319</v>
+      </c>
+      <c r="G149" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H149" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I149" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J149" t="s">
+        <v>122</v>
+      </c>
+      <c r="K149" t="s">
+        <v>316</v>
+      </c>
+      <c r="L149" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M149" t="s">
+        <v>6</v>
+      </c>
+      <c r="N149" t="s">
+        <v>7</v>
+      </c>
+      <c r="O149" t="s">
+        <v>8</v>
+      </c>
+      <c r="P149" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
+      <c r="A150" t="s">
+        <v>312</v>
+      </c>
+      <c r="B150" t="s">
+        <v>320</v>
+      </c>
+      <c r="C150" s="2">
+        <v>1</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" t="s">
+        <v>321</v>
+      </c>
+      <c r="F150" t="s">
+        <v>322</v>
+      </c>
+      <c r="G150" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H150" s="3">
+        <v>46059</v>
+      </c>
+      <c r="I150" s="3">
+        <v>46062</v>
+      </c>
+      <c r="J150" t="s">
+        <v>133</v>
+      </c>
+      <c r="K150" t="s">
+        <v>316</v>
+      </c>
+      <c r="L150" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M150" t="s">
+        <v>6</v>
+      </c>
+      <c r="N150" t="s">
+        <v>7</v>
+      </c>
+      <c r="O150" t="s">
+        <v>8</v>
+      </c>
+      <c r="P150" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
+      <c r="A151" t="s">
+        <v>312</v>
+      </c>
+      <c r="B151" t="s">
+        <v>323</v>
+      </c>
+      <c r="C151" s="2">
+        <v>1</v>
+      </c>
+      <c r="D151" s="2">
+        <v>0</v>
+      </c>
+      <c r="E151" t="s">
+        <v>324</v>
+      </c>
+      <c r="F151" t="s">
+        <v>325</v>
+      </c>
+      <c r="G151" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H151" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I151" s="3">
+        <v>46058</v>
+      </c>
+      <c r="J151" t="s">
+        <v>4</v>
+      </c>
+      <c r="K151" t="s">
+        <v>316</v>
+      </c>
+      <c r="L151" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M151" t="s">
+        <v>6</v>
+      </c>
+      <c r="N151" t="s">
+        <v>7</v>
+      </c>
+      <c r="O151" t="s">
+        <v>8</v>
+      </c>
+      <c r="P151" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152" t="s">
+        <v>312</v>
+      </c>
+      <c r="B152" t="s">
+        <v>326</v>
+      </c>
+      <c r="C152" s="2">
+        <v>1</v>
+      </c>
+      <c r="D152" s="2">
+        <v>0</v>
+      </c>
+      <c r="E152" t="s">
+        <v>327</v>
+      </c>
+      <c r="F152" t="s">
+        <v>328</v>
+      </c>
+      <c r="G152" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H152" s="3">
+        <v>46077</v>
+      </c>
+      <c r="I152" s="3">
+        <v>46094</v>
+      </c>
+      <c r="J152" t="s">
+        <v>4</v>
+      </c>
+      <c r="K152" t="s">
+        <v>316</v>
+      </c>
+      <c r="L152" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M152" t="s">
+        <v>6</v>
+      </c>
+      <c r="N152" t="s">
+        <v>7</v>
+      </c>
+      <c r="O152" t="s">
+        <v>8</v>
+      </c>
+      <c r="P152" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153" t="s">
+        <v>312</v>
+      </c>
+      <c r="B153" t="s">
+        <v>329</v>
+      </c>
+      <c r="C153" s="2">
+        <v>1</v>
+      </c>
+      <c r="D153" s="2">
+        <v>0</v>
+      </c>
+      <c r="E153" t="s">
+        <v>330</v>
+      </c>
+      <c r="F153" t="s">
+        <v>331</v>
+      </c>
+      <c r="G153" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H153" s="3">
+        <v>46064</v>
+      </c>
+      <c r="I153" s="3">
+        <v>46066</v>
+      </c>
+      <c r="J153" t="s">
+        <v>4</v>
+      </c>
+      <c r="K153" t="s">
+        <v>316</v>
+      </c>
+      <c r="L153" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M153" t="s">
+        <v>6</v>
+      </c>
+      <c r="N153" t="s">
+        <v>7</v>
+      </c>
+      <c r="O153" t="s">
+        <v>8</v>
+      </c>
+      <c r="P153" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
+      <c r="A154" t="s">
+        <v>312</v>
+      </c>
+      <c r="B154" t="s">
+        <v>332</v>
+      </c>
+      <c r="C154" s="2">
+        <v>1</v>
+      </c>
+      <c r="D154" s="2">
+        <v>0</v>
+      </c>
+      <c r="E154" t="s">
+        <v>173</v>
+      </c>
+      <c r="F154" t="s">
+        <v>174</v>
+      </c>
+      <c r="G154" s="3">
+        <v>46057</v>
+      </c>
+      <c r="H154" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I154" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J154" t="s">
+        <v>122</v>
+      </c>
+      <c r="K154" t="s">
+        <v>316</v>
+      </c>
+      <c r="L154" s="3">
+        <v>46057</v>
+      </c>
+      <c r="M154" t="s">
+        <v>6</v>
+      </c>
+      <c r="N154" t="s">
+        <v>7</v>
+      </c>
+      <c r="O154" t="s">
+        <v>8</v>
+      </c>
+      <c r="P154" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+      <c r="B155" t="s">
+        <v>333</v>
+      </c>
+      <c r="C155" s="2">
+        <v>1</v>
+      </c>
+      <c r="D155" s="2">
+        <v>0</v>
+      </c>
+      <c r="E155" t="s">
+        <v>334</v>
+      </c>
+      <c r="F155" t="s">
+        <v>335</v>
+      </c>
+      <c r="G155" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H155" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I155" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J155" t="s">
+        <v>133</v>
+      </c>
+      <c r="K155" t="s">
+        <v>316</v>
+      </c>
+      <c r="L155" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M155" t="s">
+        <v>6</v>
+      </c>
+      <c r="N155" t="s">
+        <v>7</v>
+      </c>
+      <c r="O155" t="s">
+        <v>8</v>
+      </c>
+      <c r="P155" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
+      <c r="A156" t="s">
+        <v>312</v>
+      </c>
+      <c r="B156" t="s">
+        <v>336</v>
+      </c>
+      <c r="C156" s="2">
+        <v>1</v>
+      </c>
+      <c r="D156" s="2">
+        <v>0</v>
+      </c>
+      <c r="E156" t="s">
         <v>255</v>
       </c>
-      <c r="F141" t="s">
+      <c r="F156" t="s">
         <v>256</v>
       </c>
-      <c r="G141" s="3">
+      <c r="G156" s="3">
         <v>46077</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H156" s="3">
         <v>46078</v>
       </c>
-      <c r="I141" s="3">
+      <c r="I156" s="3">
         <v>46084</v>
       </c>
-      <c r="J141" t="s">
-        <v>86</v>
-      </c>
-      <c r="K141" t="s">
-        <v>285</v>
-      </c>
-      <c r="L141" s="3">
+      <c r="J156" t="s">
+        <v>4</v>
+      </c>
+      <c r="K156" t="s">
+        <v>316</v>
+      </c>
+      <c r="L156" s="3">
         <v>46077</v>
       </c>
-      <c r="M141" t="s">
-        <v>6</v>
-      </c>
-      <c r="N141" t="s">
-        <v>7</v>
-      </c>
-      <c r="O141" t="s">
-        <v>8</v>
-      </c>
-      <c r="P141" t="s">
+      <c r="M156" t="s">
+        <v>6</v>
+      </c>
+      <c r="N156" t="s">
+        <v>7</v>
+      </c>
+      <c r="O156" t="s">
+        <v>8</v>
+      </c>
+      <c r="P156" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,12 +11,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="325">
   <si>
     <t>ZP02</t>
   </si>
   <si>
-    <t>200006076</t>
+    <t>200006254</t>
+  </si>
+  <si>
+    <t>080300020609</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_1°-BT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>SDCHANG</t>
+  </si>
+  <si>
+    <t>SHEO</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>200006418</t>
+  </si>
+  <si>
+    <t>080200255802</t>
+  </si>
+  <si>
+    <t>5A65E機頭D15K,032370_BBT40,CAW45</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006419</t>
+  </si>
+  <si>
+    <t>080100087604</t>
+  </si>
+  <si>
+    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006445</t>
+  </si>
+  <si>
+    <t>080200538902</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,42F25,C</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006482</t>
+  </si>
+  <si>
+    <t>080300029900</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,032731,G5K_1°-BBT50-45°-5K-C-F</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006483</t>
+  </si>
+  <si>
+    <t>080300028903</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006488</t>
+  </si>
+  <si>
+    <t>080300029103</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006489</t>
+  </si>
+  <si>
+    <t>200006490</t>
+  </si>
+  <si>
+    <t>200006498</t>
+  </si>
+  <si>
+    <t>080200546702</t>
+  </si>
+  <si>
+    <t>MVP11機頭D15K,031859_#40,38F18,C,AT8</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006500</t>
+  </si>
+  <si>
+    <t>080100092405</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006503</t>
   </si>
   <si>
     <t>080200545001</t>
@@ -25,40 +145,37 @@
     <t>H1370機頭G6K,011395_#50,55F23,C</t>
   </si>
   <si>
-    <t>REL  PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>SDCHANG</t>
-  </si>
-  <si>
-    <t>SHEO</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>200006077</t>
-  </si>
-  <si>
-    <t>200006254</t>
-  </si>
-  <si>
-    <t>080300020609</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006320</t>
+    <t>200006504</t>
+  </si>
+  <si>
+    <t>200006506</t>
+  </si>
+  <si>
+    <t>080100116405</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BBT50,CW45</t>
+  </si>
+  <si>
+    <t>200006507</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006508</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006509</t>
+  </si>
+  <si>
+    <t>200006510</t>
+  </si>
+  <si>
+    <t>200006511</t>
   </si>
   <si>
     <t>080200538802</t>
@@ -67,28 +184,235 @@
     <t>H1682機頭G6K,021314_#50,55F23,C</t>
   </si>
   <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006321</t>
-  </si>
-  <si>
-    <t>080100116404</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>200006324</t>
-  </si>
-  <si>
-    <t>080200170704</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011297_780,BBT50,55,C45</t>
-  </si>
-  <si>
-    <t>200006325</t>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006512</t>
+  </si>
+  <si>
+    <t>200006513</t>
+  </si>
+  <si>
+    <t>200006514</t>
+  </si>
+  <si>
+    <t>200006516</t>
+  </si>
+  <si>
+    <t>200006517</t>
+  </si>
+  <si>
+    <t>200006518</t>
+  </si>
+  <si>
+    <t>200006519</t>
+  </si>
+  <si>
+    <t>200006520</t>
+  </si>
+  <si>
+    <t>200006521</t>
+  </si>
+  <si>
+    <t>200006522</t>
+  </si>
+  <si>
+    <t>200006529</t>
+  </si>
+  <si>
+    <t>080200562402</t>
+  </si>
+  <si>
+    <t>MVP16機頭G8K,021487_#50,55F23,0</t>
+  </si>
+  <si>
+    <t>200006533</t>
+  </si>
+  <si>
+    <t>080200546703</t>
+  </si>
+  <si>
+    <t>200006534</t>
+  </si>
+  <si>
+    <t>200006535</t>
+  </si>
+  <si>
+    <t>080100156608</t>
+  </si>
+  <si>
+    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006536</t>
+  </si>
+  <si>
+    <t>200006537</t>
+  </si>
+  <si>
+    <t>200006538</t>
+  </si>
+  <si>
+    <t>200006539</t>
+  </si>
+  <si>
+    <t>200006540</t>
+  </si>
+  <si>
+    <t>200006541</t>
+  </si>
+  <si>
+    <t>200006542</t>
+  </si>
+  <si>
+    <t>200006543</t>
+  </si>
+  <si>
+    <t>200006544</t>
+  </si>
+  <si>
+    <t>200006548</t>
+  </si>
+  <si>
+    <t>080200538402</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,48F23,0</t>
+  </si>
+  <si>
+    <t>200006554</t>
+  </si>
+  <si>
+    <t>080200037902</t>
+  </si>
+  <si>
+    <t>HSA機頭G6K,021563_1200,BBT50,55,045</t>
+  </si>
+  <si>
+    <t>200006555</t>
+  </si>
+  <si>
+    <t>080100035602</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,0045</t>
+  </si>
+  <si>
+    <t>200006567</t>
+  </si>
+  <si>
+    <t>080300028606</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_1°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006568</t>
+  </si>
+  <si>
+    <t>200006569</t>
+  </si>
+  <si>
+    <t>080300030000</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,032731,G5K_1°-BT50-DIN-5K-C-F</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006573</t>
+  </si>
+  <si>
+    <t>080300024804</t>
+  </si>
+  <si>
+    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
+  </si>
+  <si>
+    <t>200006574</t>
+  </si>
+  <si>
+    <t>080200014702</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
+  </si>
+  <si>
+    <t>200006575</t>
+  </si>
+  <si>
+    <t>080300017908</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-0</t>
+  </si>
+  <si>
+    <t>200006576</t>
+  </si>
+  <si>
+    <t>080200408704</t>
+  </si>
+  <si>
+    <t>HMC機頭B10K,202488 _BBT50,F45</t>
+  </si>
+  <si>
+    <t>200006577</t>
+  </si>
+  <si>
+    <t>080100134803</t>
+  </si>
+  <si>
+    <t>B10K 主軸,021472_BBT50,F0CW45</t>
+  </si>
+  <si>
+    <t>200006578</t>
+  </si>
+  <si>
+    <t>080200020004</t>
+  </si>
+  <si>
+    <t>EA機頭HB10K,011050_Z1200,50FANUC,C45</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>200006579</t>
+  </si>
+  <si>
+    <t>080100021502</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006580</t>
+  </si>
+  <si>
+    <t>080300018208</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006585</t>
+  </si>
+  <si>
+    <t>080200033404</t>
+  </si>
+  <si>
+    <t>HSA機頭G6K,021563_780,BBT50,55,C45</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>200006586</t>
   </si>
   <si>
     <t>080100036004</t>
@@ -97,106 +421,7 @@
     <t>G6K 主軸,021327_BBT50,C045</t>
   </si>
   <si>
-    <t>REL  PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006326</t>
-  </si>
-  <si>
-    <t>080300024804</t>
-  </si>
-  <si>
-    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
-  </si>
-  <si>
-    <t>200006344</t>
-  </si>
-  <si>
-    <t>080200158404</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011282_780,BT50,42,CDIN</t>
-  </si>
-  <si>
-    <t>200006345</t>
-  </si>
-  <si>
-    <t>080100023404</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>200006366</t>
-  </si>
-  <si>
-    <t>080200539403</t>
-  </si>
-  <si>
-    <t>H1682機頭G8K,021565_#50,42F25,C</t>
-  </si>
-  <si>
-    <t>200006367</t>
-  </si>
-  <si>
-    <t>080100122802</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006368</t>
-  </si>
-  <si>
-    <t>080200286203</t>
-  </si>
-  <si>
-    <t>H2110機頭G6K,011026_BT50,42F25,CAW45</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>080200027803</t>
-  </si>
-  <si>
-    <t>PBM135機頭G2.5K,010831_DIN50,HSCDIN</t>
-  </si>
-  <si>
-    <t>200006371</t>
-  </si>
-  <si>
-    <t>080100033903</t>
-  </si>
-  <si>
-    <t>G2.5K主軸,010830_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>200006372</t>
-  </si>
-  <si>
-    <t>080200555000</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,C,AT8</t>
-  </si>
-  <si>
-    <t>200006374</t>
-  </si>
-  <si>
-    <t>080200560900</t>
-  </si>
-  <si>
-    <t>MVP16機頭D12K,031884_#50,42F25</t>
-  </si>
-  <si>
-    <t>200006376</t>
+    <t>200006587</t>
   </si>
   <si>
     <t>080200548501</t>
@@ -205,34 +430,7 @@
     <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
   </si>
   <si>
-    <t>200006385</t>
-  </si>
-  <si>
-    <t>080200169703</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011297_780,BT50,55,045</t>
-  </si>
-  <si>
-    <t>200006388</t>
-  </si>
-  <si>
-    <t>080300028903</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006389</t>
-  </si>
-  <si>
-    <t>080300029800</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,032936_1°-BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006390</t>
+    <t>200006588</t>
   </si>
   <si>
     <t>080100094004</t>
@@ -241,109 +439,127 @@
     <t>D15K 主軸,021177_BBT40,M60,CW45</t>
   </si>
   <si>
+    <t>200006593</t>
+  </si>
+  <si>
+    <t>080200531201</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_A63,48F18,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006597</t>
+  </si>
+  <si>
+    <t>080200570000</t>
+  </si>
+  <si>
+    <t>5A95Q機頭BA24K,032918_A63,C</t>
+  </si>
+  <si>
+    <t>200006604</t>
+  </si>
+  <si>
+    <t>200006605</t>
+  </si>
+  <si>
+    <t>200006606</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006616</t>
+  </si>
+  <si>
+    <t>080200530800</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,48F23,0</t>
+  </si>
+  <si>
+    <t>200006617</t>
+  </si>
+  <si>
+    <t>200006618</t>
+  </si>
+  <si>
+    <t>200006622</t>
+  </si>
+  <si>
+    <t>080100050703</t>
+  </si>
+  <si>
+    <t>D20K 主軸,021608_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>200006623</t>
+  </si>
+  <si>
+    <t>200006624</t>
+  </si>
+  <si>
+    <t>200006627</t>
+  </si>
+  <si>
+    <t>080100091606</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021177_BBT40,M60,0W45</t>
+  </si>
+  <si>
     <t>REL  PCNF PRC  MACM RMWB SETC</t>
   </si>
   <si>
-    <t>200006391</t>
-  </si>
-  <si>
-    <t>080200014502</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011166_Z1000,60A30,C</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006392</t>
-  </si>
-  <si>
-    <t>080100015101</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>200006394</t>
-  </si>
-  <si>
-    <t>200006397</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006418</t>
-  </si>
-  <si>
-    <t>080200255802</t>
-  </si>
-  <si>
-    <t>5A65E機頭D15K,032370_BBT40,CAW45</t>
-  </si>
-  <si>
-    <t>200006419</t>
-  </si>
-  <si>
-    <t>080100087604</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006423</t>
-  </si>
-  <si>
-    <t>080100120402</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BT50,0W45</t>
-  </si>
-  <si>
-    <t>200006431</t>
-  </si>
-  <si>
-    <t>200006432</t>
-  </si>
-  <si>
-    <t>080200292203</t>
-  </si>
-  <si>
-    <t>H2110機頭G8K,011366_BT50,55F23,0AW45</t>
-  </si>
-  <si>
-    <t>200006433</t>
-  </si>
-  <si>
-    <t>200006442</t>
-  </si>
-  <si>
-    <t>080200483300</t>
-  </si>
-  <si>
-    <t>H1365機頭G8K,021863_#40,42F25,C</t>
-  </si>
-  <si>
-    <t>200006443</t>
-  </si>
-  <si>
-    <t>080100110001</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021534_BBT40,CW45</t>
-  </si>
-  <si>
-    <t>200006445</t>
-  </si>
-  <si>
-    <t>080200538902</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,42F25,C</t>
-  </si>
-  <si>
-    <t>200006446</t>
+    <t>200006628</t>
+  </si>
+  <si>
+    <t>200006629</t>
+  </si>
+  <si>
+    <t>080200565801</t>
+  </si>
+  <si>
+    <t>H1100機頭G6K,021822_#50,48F23,0</t>
+  </si>
+  <si>
+    <t>200006634</t>
+  </si>
+  <si>
+    <t>200006635</t>
+  </si>
+  <si>
+    <t>080100090804</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006637</t>
+  </si>
+  <si>
+    <t>080100051201</t>
+  </si>
+  <si>
+    <t>D12K 主軸,031723_BT30,M38,0045</t>
+  </si>
+  <si>
+    <t>200006640</t>
+  </si>
+  <si>
+    <t>080200527500</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,38F18</t>
+  </si>
+  <si>
+    <t>200006642</t>
+  </si>
+  <si>
+    <t>200006643</t>
   </si>
   <si>
     <t>080100113505</t>
@@ -352,184 +568,325 @@
     <t>G6K 主軸,021305_BT50,CWDIN</t>
   </si>
   <si>
-    <t>200006447</t>
-  </si>
-  <si>
-    <t>200006448</t>
-  </si>
-  <si>
-    <t>200006449</t>
-  </si>
-  <si>
-    <t>080200015002</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>200006450</t>
-  </si>
-  <si>
-    <t>080100015401</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M50E,C0DIN</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006452</t>
-  </si>
-  <si>
-    <t>080200159204</t>
-  </si>
-  <si>
-    <t>SW機頭G6K,011282_780,BT50,55,CDIN</t>
-  </si>
-  <si>
-    <t>200006453</t>
-  </si>
-  <si>
-    <t>200006454</t>
-  </si>
-  <si>
-    <t>080200565901</t>
-  </si>
-  <si>
-    <t>H1100機頭G6K,021822_#50,48F23,C</t>
-  </si>
-  <si>
-    <t>200006456</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006457</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006458</t>
-  </si>
-  <si>
-    <t>080200229206</t>
-  </si>
-  <si>
-    <t>HEP機頭G6K,021570_780,BT50,48,CDIN</t>
-  </si>
-  <si>
-    <t>200006459</t>
-  </si>
-  <si>
-    <t>200006460</t>
-  </si>
-  <si>
-    <t>200006463</t>
-  </si>
-  <si>
-    <t>080200229305</t>
-  </si>
-  <si>
-    <t>HEP機頭G6K,021570_780,BT50,55,045</t>
-  </si>
-  <si>
-    <t>200006466</t>
-  </si>
-  <si>
-    <t>080300029103</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006467</t>
-  </si>
-  <si>
-    <t>080300029301</t>
-  </si>
-  <si>
-    <t>自動頭HF-AE50,032022_BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006468</t>
-  </si>
-  <si>
-    <t>080100084704</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BT40,M60,CWDIN</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006469</t>
-  </si>
-  <si>
-    <t>200006470</t>
-  </si>
-  <si>
-    <t>080200570600</t>
-  </si>
-  <si>
-    <t>TGV106機頭DA20K,021853_#40,d38F18</t>
-  </si>
-  <si>
-    <t>200006471</t>
-  </si>
-  <si>
-    <t>080100158004</t>
-  </si>
-  <si>
-    <t>DA20K主軸,021853,oil-air_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>200006475</t>
-  </si>
-  <si>
-    <t>080200237804</t>
-  </si>
-  <si>
-    <t>HEP機頭D20K,021783_780,A63,38,C</t>
-  </si>
-  <si>
-    <t>200006476</t>
-  </si>
-  <si>
-    <t>080100050201</t>
-  </si>
-  <si>
-    <t>D20K 主軸,010683_A63,M50,C0</t>
-  </si>
-  <si>
-    <t>200006477</t>
-  </si>
-  <si>
-    <t>080200017802</t>
-  </si>
-  <si>
-    <t>EA機頭G8K,011262_Z1200,48A15,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006478</t>
-  </si>
-  <si>
-    <t>080200015703</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011167_Z1400,60A30,C</t>
-  </si>
-  <si>
-    <t>200006479</t>
+    <t>200006644</t>
+  </si>
+  <si>
+    <t>080200557700</t>
+  </si>
+  <si>
+    <t>MVP-16機頭D15K,021451_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006645</t>
+  </si>
+  <si>
+    <t>200006646</t>
+  </si>
+  <si>
+    <t>080200551300</t>
+  </si>
+  <si>
+    <t>SP10機頭P12K,021023_#40,5GT-72,0</t>
+  </si>
+  <si>
+    <t>200006647</t>
+  </si>
+  <si>
+    <t>080200530400</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,0</t>
+  </si>
+  <si>
+    <t>200006648</t>
+  </si>
+  <si>
+    <t>200006649</t>
+  </si>
+  <si>
+    <t>200006650</t>
+  </si>
+  <si>
+    <t>080100090006</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,0W45</t>
+  </si>
+  <si>
+    <t>200006651</t>
+  </si>
+  <si>
+    <t>200006652</t>
+  </si>
+  <si>
+    <t>200006653</t>
+  </si>
+  <si>
+    <t>200006654</t>
+  </si>
+  <si>
+    <t>200006655</t>
+  </si>
+  <si>
+    <t>200006656</t>
+  </si>
+  <si>
+    <t>200006657</t>
+  </si>
+  <si>
+    <t>080200286503</t>
+  </si>
+  <si>
+    <t>H2110機頭G6K,011026_BT50,42F25,CAWDI</t>
+  </si>
+  <si>
+    <t>200006658</t>
+  </si>
+  <si>
+    <t>080100113504</t>
+  </si>
+  <si>
+    <t>200006659</t>
+  </si>
+  <si>
+    <t>080200530500</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006660</t>
+  </si>
+  <si>
+    <t>200006661</t>
+  </si>
+  <si>
+    <t>200006662</t>
+  </si>
+  <si>
+    <t>200006663</t>
+  </si>
+  <si>
+    <t>080200532700</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,48F18</t>
+  </si>
+  <si>
+    <t>200006664</t>
+  </si>
+  <si>
+    <t>080200537901</t>
+  </si>
+  <si>
+    <t>LG1370機頭D15K,021720_#40,38F18,C,VKS26</t>
+  </si>
+  <si>
+    <t>200006666</t>
+  </si>
+  <si>
+    <t>200006668</t>
+  </si>
+  <si>
+    <t>080200071201</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
+  </si>
+  <si>
+    <t>200006669</t>
+  </si>
+  <si>
+    <t>200006670</t>
+  </si>
+  <si>
+    <t>080200546201</t>
+  </si>
+  <si>
+    <t>MVP13機頭P12K,021677_#40,8YU-82,C</t>
+  </si>
+  <si>
+    <t>200006671</t>
+  </si>
+  <si>
+    <t>080200243400</t>
+  </si>
+  <si>
+    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>200006674</t>
+  </si>
+  <si>
+    <t>080100081204</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BBT40,8YU,CW45</t>
+  </si>
+  <si>
+    <t>200006675</t>
+  </si>
+  <si>
+    <t>080200244200</t>
+  </si>
+  <si>
+    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45I</t>
+  </si>
+  <si>
+    <t>200006676</t>
+  </si>
+  <si>
+    <t>080200235502</t>
+  </si>
+  <si>
+    <t>HEP機頭D12K,021573_780,BBT50,48,C45</t>
+  </si>
+  <si>
+    <t>200006677</t>
+  </si>
+  <si>
+    <t>080100045203</t>
+  </si>
+  <si>
+    <t>D12K 主軸,021274_BBT50,M50,C045</t>
+  </si>
+  <si>
+    <t>200006678</t>
+  </si>
+  <si>
+    <t>080200571500</t>
+  </si>
+  <si>
+    <t>L800機頭D15K,021616_#40,48F18,0</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006679</t>
+  </si>
+  <si>
+    <t>080100096404</t>
+  </si>
+  <si>
+    <t>D12K 主軸,011207_BT40,M32,0W45</t>
+  </si>
+  <si>
+    <t>200006681</t>
+  </si>
+  <si>
+    <t>200006682</t>
+  </si>
+  <si>
+    <t>200006683</t>
+  </si>
+  <si>
+    <t>080200070801</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>200006684</t>
+  </si>
+  <si>
+    <t>200006685</t>
+  </si>
+  <si>
+    <t>200006686</t>
+  </si>
+  <si>
+    <t>080100050702</t>
+  </si>
+  <si>
+    <t>200006687</t>
+  </si>
+  <si>
+    <t>200006688</t>
+  </si>
+  <si>
+    <t>080100112405</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,0W45</t>
+  </si>
+  <si>
+    <t>200006689</t>
+  </si>
+  <si>
+    <t>080100113205</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CW45</t>
+  </si>
+  <si>
+    <t>200006690</t>
+  </si>
+  <si>
+    <t>200006691</t>
+  </si>
+  <si>
+    <t>200006692</t>
+  </si>
+  <si>
+    <t>200006693</t>
+  </si>
+  <si>
+    <t>080200538702</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,48F23,C</t>
+  </si>
+  <si>
+    <t>200006694</t>
+  </si>
+  <si>
+    <t>200006695</t>
+  </si>
+  <si>
+    <t>200006696</t>
+  </si>
+  <si>
+    <t>200006697</t>
+  </si>
+  <si>
+    <t>200006698</t>
+  </si>
+  <si>
+    <t>080200558601</t>
+  </si>
+  <si>
+    <t>MVP-16機頭D20K,021825_A63,38F18,C</t>
+  </si>
+  <si>
+    <t>200006699</t>
+  </si>
+  <si>
+    <t>080100050303</t>
+  </si>
+  <si>
+    <t>D20K 主軸,010683_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>200006700</t>
+  </si>
+  <si>
+    <t>ZP09</t>
+  </si>
+  <si>
+    <t>630000332</t>
+  </si>
+  <si>
+    <t>080100145201</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M65,0045</t>
+  </si>
+  <si>
+    <t>PENNY</t>
+  </si>
+  <si>
+    <t>630000340</t>
   </si>
   <si>
     <t>080100018301</t>
@@ -538,490 +895,49 @@
     <t>D6K 主軸,010801_BBT50,M50E,C045</t>
   </si>
   <si>
-    <t>200006482</t>
-  </si>
-  <si>
-    <t>080300029900</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,032731,G5K_1°-BBT50-45°-5K-C-F</t>
-  </si>
-  <si>
-    <t>200006483</t>
-  </si>
-  <si>
-    <t>200006484</t>
-  </si>
-  <si>
-    <t>080200530900</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,48F23,C</t>
-  </si>
-  <si>
-    <t>200006485</t>
-  </si>
-  <si>
-    <t>200006486</t>
-  </si>
-  <si>
-    <t>200006487</t>
-  </si>
-  <si>
-    <t>200006488</t>
-  </si>
-  <si>
-    <t>200006489</t>
-  </si>
-  <si>
-    <t>200006490</t>
-  </si>
-  <si>
-    <t>200006491</t>
-  </si>
-  <si>
-    <t>200006492</t>
-  </si>
-  <si>
-    <t>200006493</t>
-  </si>
-  <si>
-    <t>080200546903</t>
-  </si>
-  <si>
-    <t>MVP11機頭D15K,031859_#40,48F18,0</t>
-  </si>
-  <si>
-    <t>200006494</t>
-  </si>
-  <si>
-    <t>200006495</t>
-  </si>
-  <si>
-    <t>080100090006</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BT40,M60,0W45</t>
-  </si>
-  <si>
-    <t>200006496</t>
-  </si>
-  <si>
-    <t>200006497</t>
-  </si>
-  <si>
-    <t>080200546702</t>
-  </si>
-  <si>
-    <t>MVP11機頭D15K,031859_#40,38F18,C,AT8</t>
-  </si>
-  <si>
-    <t>200006498</t>
-  </si>
-  <si>
-    <t>200006499</t>
-  </si>
-  <si>
-    <t>080100092405</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021177_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006500</t>
-  </si>
-  <si>
-    <t>200006501</t>
-  </si>
-  <si>
-    <t>080200531901</t>
-  </si>
-  <si>
-    <t>MVP13機頭D20K,021339_#40,38F18</t>
-  </si>
-  <si>
-    <t>200006502</t>
-  </si>
-  <si>
-    <t>080100157706</t>
-  </si>
-  <si>
-    <t>DA20K主軸,021854,oil-air_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006503</t>
-  </si>
-  <si>
-    <t>200006504</t>
-  </si>
-  <si>
-    <t>200006505</t>
-  </si>
-  <si>
-    <t>080100116405</t>
-  </si>
-  <si>
-    <t>200006506</t>
-  </si>
-  <si>
-    <t>200006507</t>
-  </si>
-  <si>
-    <t>200006508</t>
-  </si>
-  <si>
-    <t>200006509</t>
-  </si>
-  <si>
-    <t>200006510</t>
-  </si>
-  <si>
-    <t>200006511</t>
-  </si>
-  <si>
-    <t>200006512</t>
-  </si>
-  <si>
-    <t>200006513</t>
-  </si>
-  <si>
-    <t>200006514</t>
-  </si>
-  <si>
-    <t>200006515</t>
-  </si>
-  <si>
-    <t>200006516</t>
-  </si>
-  <si>
-    <t>200006517</t>
-  </si>
-  <si>
-    <t>200006518</t>
-  </si>
-  <si>
-    <t>200006519</t>
-  </si>
-  <si>
-    <t>CRTD PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006520</t>
-  </si>
-  <si>
-    <t>200006521</t>
-  </si>
-  <si>
-    <t>200006522</t>
-  </si>
-  <si>
-    <t>200006523</t>
-  </si>
-  <si>
-    <t>080200531102</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D20K,021581_A63,38F18,C</t>
-  </si>
-  <si>
-    <t>200006524</t>
-  </si>
-  <si>
-    <t>200006525</t>
-  </si>
-  <si>
-    <t>200006526</t>
-  </si>
-  <si>
-    <t>080100050703</t>
-  </si>
-  <si>
-    <t>D20K 主軸,021608_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006527</t>
-  </si>
-  <si>
-    <t>200006528</t>
-  </si>
-  <si>
-    <t>200006529</t>
-  </si>
-  <si>
-    <t>080200562402</t>
-  </si>
-  <si>
-    <t>MVP16機頭G8K,021487_#50,55F23,0</t>
-  </si>
-  <si>
-    <t>200006530</t>
-  </si>
-  <si>
-    <t>200006531</t>
-  </si>
-  <si>
-    <t>080200546703</t>
-  </si>
-  <si>
-    <t>200006533</t>
-  </si>
-  <si>
-    <t>200006534</t>
-  </si>
-  <si>
-    <t>200006535</t>
-  </si>
-  <si>
-    <t>080100156608</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006536</t>
-  </si>
-  <si>
-    <t>200006537</t>
-  </si>
-  <si>
-    <t>200006538</t>
-  </si>
-  <si>
-    <t>200006539</t>
-  </si>
-  <si>
-    <t>200006540</t>
-  </si>
-  <si>
-    <t>200006541</t>
-  </si>
-  <si>
-    <t>200006542</t>
-  </si>
-  <si>
-    <t>200006543</t>
-  </si>
-  <si>
-    <t>200006544</t>
-  </si>
-  <si>
-    <t>200006545</t>
-  </si>
-  <si>
-    <t>080200538402</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,48F23,0</t>
-  </si>
-  <si>
-    <t>200006546</t>
-  </si>
-  <si>
-    <t>200006547</t>
-  </si>
-  <si>
-    <t>200006548</t>
-  </si>
-  <si>
-    <t>200006549</t>
-  </si>
-  <si>
-    <t>080100112405</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,0W45</t>
-  </si>
-  <si>
-    <t>200006550</t>
-  </si>
-  <si>
-    <t>200006551</t>
-  </si>
-  <si>
-    <t>200006552</t>
-  </si>
-  <si>
-    <t>200006553</t>
-  </si>
-  <si>
-    <t>080200548601</t>
-  </si>
-  <si>
-    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C,AT8</t>
-  </si>
-  <si>
-    <t>200006554</t>
-  </si>
-  <si>
-    <t>080200037902</t>
-  </si>
-  <si>
-    <t>HSA機頭G6K,021563_1200,BBT50,55,045</t>
-  </si>
-  <si>
-    <t>200006555</t>
-  </si>
-  <si>
-    <t>080100035602</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,0045</t>
-  </si>
-  <si>
-    <t>200006556</t>
-  </si>
-  <si>
-    <t>080200069201</t>
-  </si>
-  <si>
-    <t>L800機頭P8K,021615_BBT40,5GT,0AW45</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006557</t>
-  </si>
-  <si>
-    <t>200006558</t>
-  </si>
-  <si>
-    <t>200006559</t>
-  </si>
-  <si>
-    <t>080200527500</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,38F18</t>
-  </si>
-  <si>
-    <t>200006560</t>
-  </si>
-  <si>
-    <t>200006561</t>
-  </si>
-  <si>
-    <t>080200538702</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,48F23,C</t>
-  </si>
-  <si>
-    <t>200006562</t>
-  </si>
-  <si>
-    <t>200006563</t>
-  </si>
-  <si>
-    <t>200006564</t>
-  </si>
-  <si>
-    <t>080100113205</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CW45</t>
-  </si>
-  <si>
-    <t>CRTD MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>200006565</t>
-  </si>
-  <si>
-    <t>200006566</t>
-  </si>
-  <si>
-    <t>200006567</t>
-  </si>
-  <si>
-    <t>080300028606</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BBT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006568</t>
-  </si>
-  <si>
-    <t>ZP09</t>
-  </si>
-  <si>
-    <t>630000329</t>
-  </si>
-  <si>
-    <t>080300029000</t>
-  </si>
-  <si>
-    <t>HF-AU,032731_1°-BT50-45°-4K-C-F,溫降案</t>
-  </si>
-  <si>
-    <t>PENNY</t>
-  </si>
-  <si>
-    <t>630000332</t>
-  </si>
-  <si>
-    <t>080100145201</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M65,0045</t>
-  </si>
-  <si>
-    <t>630000333</t>
-  </si>
-  <si>
-    <t>080200530600</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
-  </si>
-  <si>
-    <t>630000336</t>
-  </si>
-  <si>
-    <t>080100016701</t>
-  </si>
-  <si>
-    <t>D8K 主軸,010801_BT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>630000337</t>
-  </si>
-  <si>
-    <t>080300018208</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>630000338</t>
-  </si>
-  <si>
-    <t>080200254502</t>
-  </si>
-  <si>
-    <t>5A65E機頭D15K,032370_BT40,CAWDI</t>
-  </si>
-  <si>
-    <t>630000340</t>
-  </si>
-  <si>
-    <t>630000341</t>
-  </si>
-  <si>
-    <t>080200332002</t>
-  </si>
-  <si>
-    <t>PBM115機頭G4K,011381_BT50,FO2C45</t>
-  </si>
-  <si>
-    <t>630000342</t>
+    <t>630000348</t>
+  </si>
+  <si>
+    <t>080200570900</t>
+  </si>
+  <si>
+    <t>SMC-5機頭D24K,031793_#40,28F15,0</t>
+  </si>
+  <si>
+    <t>630000349</t>
+  </si>
+  <si>
+    <t>080200563200</t>
+  </si>
+  <si>
+    <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
+  </si>
+  <si>
+    <t>630000351</t>
+  </si>
+  <si>
+    <t>080100076704</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
+  </si>
+  <si>
+    <t>630000352</t>
+  </si>
+  <si>
+    <t>080100059604</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021361_BT40,5GT,0W45</t>
+  </si>
+  <si>
+    <t>630000354</t>
+  </si>
+  <si>
+    <t>080200017902</t>
+  </si>
+  <si>
+    <t>EA機頭G8K,011262_Z1200,55A22,C</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1174,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P156"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1197,52 +1113,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1265,13 +1181,13 @@
         <v>3</v>
       </c>
       <c r="G2" s="3">
-        <v>45835</v>
+        <v>45946</v>
       </c>
       <c r="H2" s="3">
-        <v>46087</v>
+        <v>45964</v>
       </c>
       <c r="I2" s="3">
-        <v>46092</v>
+        <v>45993</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
@@ -1280,7 +1196,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="3">
-        <v>45835</v>
+        <v>45946</v>
       </c>
       <c r="M2" t="s">
         <v>6</v>
@@ -1309,28 +1225,28 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3">
-        <v>45835</v>
+        <v>46022</v>
       </c>
       <c r="H3" s="3">
-        <v>46087</v>
+        <v>46121</v>
       </c>
       <c r="I3" s="3">
-        <v>46092</v>
+        <v>46126</v>
       </c>
       <c r="J3" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="3">
-        <v>45835</v>
+        <v>46022</v>
       </c>
       <c r="M3" t="s">
         <v>6</v>
@@ -1350,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -1359,28 +1275,28 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3">
+        <v>46022</v>
+      </c>
+      <c r="H4" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I4" s="3">
+        <v>46121</v>
+      </c>
+      <c r="J4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="3">
-        <v>45946</v>
-      </c>
-      <c r="H4" s="3">
-        <v>45964</v>
-      </c>
-      <c r="I4" s="3">
-        <v>45993</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
       <c r="K4" t="s">
         <v>5</v>
       </c>
       <c r="L4" s="3">
-        <v>45946</v>
+        <v>46022</v>
       </c>
       <c r="M4" t="s">
         <v>6</v>
@@ -1400,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -1409,28 +1325,28 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
-        <v>45979</v>
+        <v>46044</v>
       </c>
       <c r="H5" s="3">
-        <v>46101</v>
+        <v>46142</v>
       </c>
       <c r="I5" s="3">
-        <v>46106</v>
+        <v>46148</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
       </c>
       <c r="L5" s="3">
-        <v>45979</v>
+        <v>46044</v>
       </c>
       <c r="M5" t="s">
         <v>6</v>
@@ -1450,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1459,28 +1375,28 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3">
-        <v>45979</v>
+        <v>46055</v>
       </c>
       <c r="H6" s="3">
-        <v>46098</v>
+        <v>46125</v>
       </c>
       <c r="I6" s="3">
-        <v>46101</v>
+        <v>46146</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
       </c>
       <c r="L6" s="3">
-        <v>45979</v>
+        <v>46055</v>
       </c>
       <c r="M6" t="s">
         <v>6</v>
@@ -1500,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1509,28 +1425,28 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G7" s="3">
-        <v>45979</v>
+        <v>46055</v>
       </c>
       <c r="H7" s="3">
-        <v>46097</v>
+        <v>46125</v>
       </c>
       <c r="I7" s="3">
-        <v>46100</v>
+        <v>46140</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="3">
-        <v>45979</v>
+        <v>46055</v>
       </c>
       <c r="M7" t="s">
         <v>6</v>
@@ -1550,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -1559,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G8" s="3">
-        <v>45979</v>
+        <v>46058</v>
       </c>
       <c r="H8" s="3">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="I8" s="3">
-        <v>46092</v>
+        <v>46114</v>
       </c>
       <c r="J8" t="s">
         <v>28</v>
@@ -1580,7 +1496,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="3">
-        <v>45979</v>
+        <v>46058</v>
       </c>
       <c r="M8" t="s">
         <v>6</v>
@@ -1600,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1615,22 +1531,22 @@
         <v>31</v>
       </c>
       <c r="G9" s="3">
-        <v>45979</v>
+        <v>46058</v>
       </c>
       <c r="H9" s="3">
         <v>46094</v>
       </c>
       <c r="I9" s="3">
-        <v>46100</v>
+        <v>46146</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
       </c>
       <c r="L9" s="3">
-        <v>45979</v>
+        <v>46058</v>
       </c>
       <c r="M9" t="s">
         <v>6</v>
@@ -1650,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
@@ -1659,28 +1575,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G10" s="3">
-        <v>45986</v>
+        <v>46058</v>
       </c>
       <c r="H10" s="3">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="I10" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
       </c>
       <c r="L10" s="3">
-        <v>45986</v>
+        <v>46058</v>
       </c>
       <c r="M10" t="s">
         <v>6</v>
@@ -1700,37 +1616,37 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>36</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" s="3">
+        <v>46063</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46163</v>
+      </c>
+      <c r="I11" s="3">
+        <v>46167</v>
+      </c>
+      <c r="J11" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="3">
-        <v>45986</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46127</v>
-      </c>
-      <c r="I11" s="3">
-        <v>46132</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" s="3">
-        <v>45986</v>
+        <v>46063</v>
       </c>
       <c r="M11" t="s">
         <v>6</v>
@@ -1765,22 +1681,22 @@
         <v>40</v>
       </c>
       <c r="G12" s="3">
-        <v>45995</v>
+        <v>46063</v>
       </c>
       <c r="H12" s="3">
-        <v>46091</v>
+        <v>46155</v>
       </c>
       <c r="I12" s="3">
-        <v>46094</v>
+        <v>46160</v>
       </c>
       <c r="J12" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
       <c r="L12" s="3">
-        <v>45995</v>
+        <v>46063</v>
       </c>
       <c r="M12" t="s">
         <v>6</v>
@@ -1815,22 +1731,22 @@
         <v>43</v>
       </c>
       <c r="G13" s="3">
-        <v>45995</v>
+        <v>46064</v>
       </c>
       <c r="H13" s="3">
-        <v>46086</v>
+        <v>46134</v>
       </c>
       <c r="I13" s="3">
-        <v>46091</v>
+        <v>46139</v>
       </c>
       <c r="J13" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
       </c>
       <c r="L13" s="3">
-        <v>45995</v>
+        <v>46064</v>
       </c>
       <c r="M13" t="s">
         <v>6</v>
@@ -1850,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -1859,28 +1775,28 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G14" s="3">
-        <v>45995</v>
+        <v>46064</v>
       </c>
       <c r="H14" s="3">
-        <v>46101</v>
+        <v>46134</v>
       </c>
       <c r="I14" s="3">
-        <v>46106</v>
+        <v>46139</v>
       </c>
       <c r="J14" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3">
-        <v>45995</v>
+        <v>46064</v>
       </c>
       <c r="M14" t="s">
         <v>6</v>
@@ -1900,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -1909,28 +1825,28 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3">
-        <v>45995</v>
+        <v>46064</v>
       </c>
       <c r="H15" s="3">
+        <v>46127</v>
+      </c>
+      <c r="I15" s="3">
+        <v>46134</v>
+      </c>
+      <c r="J15" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3">
         <v>46064</v>
-      </c>
-      <c r="I15" s="3">
-        <v>46112</v>
-      </c>
-      <c r="J15" t="s">
-        <v>44</v>
-      </c>
-      <c r="K15" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3">
-        <v>45995</v>
       </c>
       <c r="M15" t="s">
         <v>6</v>
@@ -1950,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -1959,28 +1875,28 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G16" s="3">
-        <v>45995</v>
+        <v>46064</v>
       </c>
       <c r="H16" s="3">
-        <v>46052</v>
+        <v>46240</v>
       </c>
       <c r="I16" s="3">
-        <v>46059</v>
+        <v>46245</v>
       </c>
       <c r="J16" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
       </c>
       <c r="L16" s="3">
-        <v>45995</v>
+        <v>46064</v>
       </c>
       <c r="M16" t="s">
         <v>6</v>
@@ -2000,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -2009,28 +1925,28 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G17" s="3">
-        <v>46000</v>
+        <v>46064</v>
       </c>
       <c r="H17" s="3">
-        <v>46106</v>
+        <v>46240</v>
       </c>
       <c r="I17" s="3">
-        <v>46108</v>
+        <v>46245</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" s="3">
-        <v>46000</v>
+        <v>46064</v>
       </c>
       <c r="M17" t="s">
         <v>6</v>
@@ -2050,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -2059,28 +1975,28 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3">
-        <v>46000</v>
+        <v>46064</v>
       </c>
       <c r="H18" s="3">
-        <v>46108</v>
+        <v>46234</v>
       </c>
       <c r="I18" s="3">
-        <v>46111</v>
+        <v>46239</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" s="3">
-        <v>46000</v>
+        <v>46064</v>
       </c>
       <c r="M18" t="s">
         <v>6</v>
@@ -2100,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -2109,28 +2025,28 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3">
-        <v>46000</v>
+        <v>46064</v>
       </c>
       <c r="H19" s="3">
-        <v>46111</v>
+        <v>46234</v>
       </c>
       <c r="I19" s="3">
-        <v>46113</v>
+        <v>46239</v>
       </c>
       <c r="J19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
       <c r="L19" s="3">
-        <v>46000</v>
+        <v>46064</v>
       </c>
       <c r="M19" t="s">
         <v>6</v>
@@ -2150,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -2159,28 +2075,28 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G20" s="3">
-        <v>46002</v>
+        <v>46064</v>
       </c>
       <c r="H20" s="3">
-        <v>46063</v>
+        <v>46146</v>
       </c>
       <c r="I20" s="3">
-        <v>46066</v>
+        <v>46149</v>
       </c>
       <c r="J20" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3">
-        <v>46002</v>
+        <v>46064</v>
       </c>
       <c r="M20" t="s">
         <v>6</v>
@@ -2200,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -2209,28 +2125,28 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G21" s="3">
-        <v>46002</v>
+        <v>46064</v>
       </c>
       <c r="H21" s="3">
-        <v>46021</v>
+        <v>46174</v>
       </c>
       <c r="I21" s="3">
-        <v>46065</v>
+        <v>46177</v>
       </c>
       <c r="J21" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" s="3">
-        <v>46002</v>
+        <v>46064</v>
       </c>
       <c r="M21" t="s">
         <v>6</v>
@@ -2250,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2259,28 +2175,28 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="G22" s="3">
-        <v>46002</v>
+        <v>46064</v>
       </c>
       <c r="H22" s="3">
-        <v>46022</v>
+        <v>46238</v>
       </c>
       <c r="I22" s="3">
+        <v>46241</v>
+      </c>
+      <c r="J22" t="s">
+        <v>51</v>
+      </c>
+      <c r="K22" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>46064</v>
-      </c>
-      <c r="J22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
-        <v>46002</v>
       </c>
       <c r="M22" t="s">
         <v>6</v>
@@ -2300,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -2309,28 +2225,28 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G23" s="3">
-        <v>46002</v>
+        <v>46064</v>
       </c>
       <c r="H23" s="3">
-        <v>46105</v>
+        <v>46297</v>
       </c>
       <c r="I23" s="3">
-        <v>46108</v>
+        <v>46302</v>
       </c>
       <c r="J23" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>46002</v>
+        <v>46064</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2350,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -2359,28 +2275,28 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G24" s="3">
-        <v>46007</v>
+        <v>46064</v>
       </c>
       <c r="H24" s="3">
-        <v>46037</v>
+        <v>46168</v>
       </c>
       <c r="I24" s="3">
-        <v>46048</v>
+        <v>46171</v>
       </c>
       <c r="J24" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3">
-        <v>46007</v>
+        <v>46064</v>
       </c>
       <c r="M24" t="s">
         <v>6</v>
@@ -2400,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2409,28 +2325,28 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="G25" s="3">
-        <v>46007</v>
+        <v>46064</v>
       </c>
       <c r="H25" s="3">
-        <v>46065</v>
+        <v>46232</v>
       </c>
       <c r="I25" s="3">
-        <v>46078</v>
+        <v>46237</v>
       </c>
       <c r="J25" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="3">
-        <v>46007</v>
+        <v>46064</v>
       </c>
       <c r="M25" t="s">
         <v>6</v>
@@ -2450,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2459,28 +2375,28 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G26" s="3">
-        <v>46007</v>
+        <v>46064</v>
       </c>
       <c r="H26" s="3">
-        <v>46062</v>
+        <v>46289</v>
       </c>
       <c r="I26" s="3">
-        <v>46078</v>
+        <v>46296</v>
       </c>
       <c r="J26" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>46007</v>
+        <v>46064</v>
       </c>
       <c r="M26" t="s">
         <v>6</v>
@@ -2500,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2509,28 +2425,28 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="G27" s="3">
-        <v>46007</v>
+        <v>46090</v>
       </c>
       <c r="H27" s="3">
-        <v>46066</v>
+        <v>46301</v>
       </c>
       <c r="I27" s="3">
-        <v>46085</v>
+        <v>46307</v>
       </c>
       <c r="J27" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>46007</v>
+        <v>46064</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2550,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2559,28 +2475,28 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="G28" s="3">
-        <v>46022</v>
+        <v>46064</v>
       </c>
       <c r="H28" s="3">
-        <v>46121</v>
+        <v>46301</v>
       </c>
       <c r="I28" s="3">
-        <v>46126</v>
+        <v>46307</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" s="3">
-        <v>46022</v>
+        <v>46064</v>
       </c>
       <c r="M28" t="s">
         <v>6</v>
@@ -2600,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2609,28 +2525,28 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="G29" s="3">
-        <v>46022</v>
+        <v>46064</v>
       </c>
       <c r="H29" s="3">
-        <v>46114</v>
+        <v>46267</v>
       </c>
       <c r="I29" s="3">
-        <v>46121</v>
+        <v>46272</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>46022</v>
+        <v>46064</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2650,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2659,28 +2575,28 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G30" s="3">
-        <v>46028</v>
+        <v>46064</v>
       </c>
       <c r="H30" s="3">
-        <v>46041</v>
+        <v>46267</v>
       </c>
       <c r="I30" s="3">
-        <v>46044</v>
+        <v>46272</v>
       </c>
       <c r="J30" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" s="3">
-        <v>46028</v>
+        <v>46064</v>
       </c>
       <c r="M30" t="s">
         <v>6</v>
@@ -2700,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2709,28 +2625,28 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="G31" s="3">
-        <v>46029</v>
+        <v>46076</v>
       </c>
       <c r="H31" s="3">
-        <v>46034</v>
+        <v>46104</v>
       </c>
       <c r="I31" s="3">
-        <v>46037</v>
+        <v>46107</v>
       </c>
       <c r="J31" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
       <c r="L31" s="3">
-        <v>46029</v>
+        <v>46076</v>
       </c>
       <c r="M31" t="s">
         <v>6</v>
@@ -2750,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2759,28 +2675,28 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="G32" s="3">
-        <v>46029</v>
+        <v>46076</v>
       </c>
       <c r="H32" s="3">
-        <v>46078</v>
+        <v>46162</v>
       </c>
       <c r="I32" s="3">
-        <v>46084</v>
+        <v>46164</v>
       </c>
       <c r="J32" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
       <c r="L32" s="3">
-        <v>46029</v>
+        <v>46076</v>
       </c>
       <c r="M32" t="s">
         <v>6</v>
@@ -2800,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2809,28 +2725,28 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="G33" s="3">
-        <v>46029</v>
+        <v>46076</v>
       </c>
       <c r="H33" s="3">
-        <v>46063</v>
+        <v>46162</v>
       </c>
       <c r="I33" s="3">
-        <v>46066</v>
+        <v>46164</v>
       </c>
       <c r="J33" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>46029</v>
+        <v>46076</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -2850,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2859,28 +2775,28 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="G34" s="3">
-        <v>46043</v>
+        <v>46076</v>
       </c>
       <c r="H34" s="3">
-        <v>46132</v>
+        <v>46156</v>
       </c>
       <c r="I34" s="3">
-        <v>46135</v>
+        <v>46161</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46043</v>
+        <v>46076</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -2900,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2909,28 +2825,28 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="G35" s="3">
-        <v>46043</v>
+        <v>46076</v>
       </c>
       <c r="H35" s="3">
-        <v>46127</v>
+        <v>46156</v>
       </c>
       <c r="I35" s="3">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46043</v>
+        <v>46076</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -2950,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -2959,28 +2875,28 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="G36" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H36" s="3">
-        <v>46142</v>
+        <v>46212</v>
       </c>
       <c r="I36" s="3">
-        <v>46148</v>
+        <v>46216</v>
       </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -3000,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -3009,28 +2925,28 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="F37" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="G37" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H37" s="3">
-        <v>46139</v>
+        <v>46212</v>
       </c>
       <c r="I37" s="3">
-        <v>46142</v>
+        <v>46216</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -3050,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -3059,28 +2975,28 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="G38" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H38" s="3">
-        <v>46085</v>
+        <v>46206</v>
       </c>
       <c r="I38" s="3">
-        <v>46090</v>
+        <v>46211</v>
       </c>
       <c r="J38" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
       </c>
       <c r="L38" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="M38" t="s">
         <v>6</v>
@@ -3100,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3109,28 +3025,28 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G39" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H39" s="3">
-        <v>46078</v>
+        <v>46206</v>
       </c>
       <c r="I39" s="3">
-        <v>46084</v>
+        <v>46211</v>
       </c>
       <c r="J39" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
       </c>
       <c r="L39" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="M39" t="s">
         <v>6</v>
@@ -3150,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3159,28 +3075,28 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="G40" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H40" s="3">
+        <v>46251</v>
+      </c>
+      <c r="I40" s="3">
+        <v>46253</v>
+      </c>
+      <c r="J40" t="s">
+        <v>51</v>
+      </c>
+      <c r="K40" t="s">
+        <v>5</v>
+      </c>
+      <c r="L40" s="3">
         <v>46076</v>
-      </c>
-      <c r="I40" s="3">
-        <v>46086</v>
-      </c>
-      <c r="J40" t="s">
-        <v>118</v>
-      </c>
-      <c r="K40" t="s">
-        <v>5</v>
-      </c>
-      <c r="L40" s="3">
-        <v>46044</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3200,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3209,28 +3125,28 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="F41" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="G41" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H41" s="3">
-        <v>46063</v>
+        <v>46251</v>
       </c>
       <c r="I41" s="3">
+        <v>46253</v>
+      </c>
+      <c r="J41" t="s">
+        <v>51</v>
+      </c>
+      <c r="K41" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3">
         <v>46076</v>
-      </c>
-      <c r="J41" t="s">
-        <v>122</v>
-      </c>
-      <c r="K41" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
-        <v>46044</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3250,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3259,28 +3175,28 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="G42" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H42" s="3">
-        <v>46079</v>
+        <v>46245</v>
       </c>
       <c r="I42" s="3">
-        <v>46085</v>
+        <v>46248</v>
       </c>
       <c r="J42" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3300,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3309,28 +3225,28 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G43" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H43" s="3">
-        <v>46064</v>
+        <v>46245</v>
       </c>
       <c r="I43" s="3">
+        <v>46248</v>
+      </c>
+      <c r="J43" t="s">
+        <v>51</v>
+      </c>
+      <c r="K43" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
         <v>46076</v>
-      </c>
-      <c r="J43" t="s">
-        <v>28</v>
-      </c>
-      <c r="K43" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3">
-        <v>46044</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3350,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3359,28 +3275,28 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="F44" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="G44" s="3">
-        <v>46044</v>
+        <v>46076</v>
       </c>
       <c r="H44" s="3">
-        <v>46065</v>
+        <v>46108</v>
       </c>
       <c r="I44" s="3">
+        <v>46113</v>
+      </c>
+      <c r="J44" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>46076</v>
-      </c>
-      <c r="J44" t="s">
-        <v>44</v>
-      </c>
-      <c r="K44" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3">
-        <v>46044</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3400,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3409,28 +3325,28 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="G45" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="H45" s="3">
-        <v>46077</v>
+        <v>46155</v>
       </c>
       <c r="I45" s="3">
-        <v>46083</v>
+        <v>46160</v>
       </c>
       <c r="J45" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3450,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3459,28 +3375,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F46" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="G46" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="H46" s="3">
-        <v>46064</v>
+        <v>46147</v>
       </c>
       <c r="I46" s="3">
-        <v>46076</v>
+        <v>46150</v>
       </c>
       <c r="J46" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3500,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3509,28 +3425,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="G47" s="3">
-        <v>46048</v>
+        <v>46083</v>
       </c>
       <c r="H47" s="3">
-        <v>46090</v>
+        <v>46148</v>
       </c>
       <c r="I47" s="3">
-        <v>46093</v>
+        <v>46171</v>
       </c>
       <c r="J47" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46048</v>
+        <v>46083</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3550,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3559,28 +3475,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G48" s="3">
-        <v>46048</v>
+        <v>46083</v>
       </c>
       <c r="H48" s="3">
-        <v>46084</v>
+        <v>46148</v>
       </c>
       <c r="I48" s="3">
-        <v>46087</v>
+        <v>46171</v>
       </c>
       <c r="J48" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46048</v>
+        <v>46083</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3600,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3609,28 +3525,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="G49" s="3">
-        <v>46048</v>
+        <v>46084</v>
       </c>
       <c r="H49" s="3">
-        <v>46085</v>
+        <v>46135</v>
       </c>
       <c r="I49" s="3">
-        <v>46090</v>
+        <v>46157</v>
       </c>
       <c r="J49" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46048</v>
+        <v>46084</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3650,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3659,28 +3575,28 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="F50" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="G50" s="3">
-        <v>46049</v>
+        <v>46086</v>
       </c>
       <c r="H50" s="3">
+        <v>46167</v>
+      </c>
+      <c r="I50" s="3">
+        <v>46171</v>
+      </c>
+      <c r="J50" t="s">
+        <v>37</v>
+      </c>
+      <c r="K50" t="s">
+        <v>5</v>
+      </c>
+      <c r="L50" s="3">
         <v>46086</v>
-      </c>
-      <c r="I50" s="3">
-        <v>46091</v>
-      </c>
-      <c r="J50" t="s">
-        <v>122</v>
-      </c>
-      <c r="K50" t="s">
-        <v>5</v>
-      </c>
-      <c r="L50" s="3">
-        <v>46049</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3700,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3709,28 +3625,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="F51" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="G51" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="H51" s="3">
-        <v>46065</v>
+        <v>46112</v>
       </c>
       <c r="I51" s="3">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="J51" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3750,7 +3666,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3759,28 +3675,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="G52" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="H52" s="3">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="I52" s="3">
-        <v>46083</v>
+        <v>46185</v>
       </c>
       <c r="J52" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -3800,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -3809,28 +3725,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="F53" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="G53" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="H53" s="3">
-        <v>46057</v>
+        <v>46213</v>
       </c>
       <c r="I53" s="3">
-        <v>46063</v>
+        <v>46217</v>
       </c>
       <c r="J53" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -3850,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3859,28 +3775,28 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="G54" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="H54" s="3">
-        <v>46057</v>
+        <v>46191</v>
       </c>
       <c r="I54" s="3">
-        <v>46063</v>
+        <v>46210</v>
       </c>
       <c r="J54" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -3900,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -3909,28 +3825,28 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="G55" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="H55" s="3">
-        <v>46066</v>
+        <v>46106</v>
       </c>
       <c r="I55" s="3">
-        <v>46078</v>
+        <v>46114</v>
       </c>
       <c r="J55" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="K55" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L55" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -3950,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -3959,28 +3875,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="F56" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="G56" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="H56" s="3">
-        <v>46059</v>
+        <v>46097</v>
       </c>
       <c r="I56" s="3">
-        <v>46065</v>
+        <v>46101</v>
       </c>
       <c r="J56" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="K56" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L56" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -4000,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -4009,28 +3925,28 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="F57" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="G57" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="H57" s="3">
-        <v>46050</v>
+        <v>46153</v>
       </c>
       <c r="I57" s="3">
-        <v>46056</v>
+        <v>46171</v>
       </c>
       <c r="J57" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="K57" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L57" s="3">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -4050,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -4059,28 +3975,28 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="F58" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="G58" s="3">
-        <v>46050</v>
+        <v>46090</v>
       </c>
       <c r="H58" s="3">
-        <v>46050</v>
+        <v>46170</v>
       </c>
       <c r="I58" s="3">
-        <v>46055</v>
+        <v>46175</v>
       </c>
       <c r="J58" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="K58" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L58" s="3">
-        <v>46050</v>
+        <v>46090</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4100,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4109,28 +4025,28 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="F59" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="G59" s="3">
-        <v>46052</v>
+        <v>46090</v>
       </c>
       <c r="H59" s="3">
-        <v>46052</v>
+        <v>46162</v>
       </c>
       <c r="I59" s="3">
-        <v>46063</v>
+        <v>46167</v>
       </c>
       <c r="J59" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L59" s="3">
-        <v>46052</v>
+        <v>46090</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4150,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4159,28 +4075,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="F60" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="G60" s="3">
-        <v>46052</v>
+        <v>46090</v>
       </c>
       <c r="H60" s="3">
-        <v>46077</v>
+        <v>46206</v>
       </c>
       <c r="I60" s="3">
-        <v>46087</v>
+        <v>46210</v>
       </c>
       <c r="J60" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
       <c r="K60" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L60" s="3">
-        <v>46052</v>
+        <v>46090</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4200,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4209,28 +4125,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="F61" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="G61" s="3">
-        <v>46052</v>
+        <v>46090</v>
       </c>
       <c r="H61" s="3">
-        <v>46076</v>
+        <v>46202</v>
       </c>
       <c r="I61" s="3">
-        <v>46083</v>
+        <v>46205</v>
       </c>
       <c r="J61" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="K61" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L61" s="3">
-        <v>46052</v>
+        <v>46090</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4250,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4259,28 +4175,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="F62" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="G62" s="3">
-        <v>46055</v>
+        <v>46091</v>
       </c>
       <c r="H62" s="3">
-        <v>46119</v>
+        <v>46105</v>
       </c>
       <c r="I62" s="3">
-        <v>46142</v>
+        <v>46107</v>
       </c>
       <c r="J62" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46055</v>
+        <v>46091</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4300,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4309,28 +4225,28 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="F63" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="G63" s="3">
-        <v>46055</v>
+        <v>46092</v>
       </c>
       <c r="H63" s="3">
-        <v>46114</v>
+        <v>46092</v>
       </c>
       <c r="I63" s="3">
-        <v>46136</v>
+        <v>46094</v>
       </c>
       <c r="J63" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>46055</v>
+        <v>46092</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4350,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4359,28 +4275,28 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="F64" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="G64" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="H64" s="3">
-        <v>46098</v>
+        <v>46167</v>
       </c>
       <c r="I64" s="3">
-        <v>46100</v>
+        <v>46169</v>
       </c>
       <c r="J64" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4400,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4409,28 +4325,28 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="F65" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="G65" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="H65" s="3">
-        <v>46098</v>
+        <v>46167</v>
       </c>
       <c r="I65" s="3">
-        <v>46100</v>
+        <v>46169</v>
       </c>
       <c r="J65" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4450,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4459,28 +4375,28 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="F66" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="G66" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="H66" s="3">
-        <v>46092</v>
+        <v>46167</v>
       </c>
       <c r="I66" s="3">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="J66" t="s">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4500,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4509,28 +4425,28 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="F67" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="G67" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="H67" s="3">
-        <v>46092</v>
+        <v>46161</v>
       </c>
       <c r="I67" s="3">
-        <v>46097</v>
+        <v>46163</v>
       </c>
       <c r="J67" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>46057</v>
+        <v>46093</v>
       </c>
       <c r="M67" t="s">
         <v>6</v>
@@ -4550,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4559,28 +4475,28 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F68" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G68" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="H68" s="3">
-        <v>46094</v>
+        <v>46161</v>
       </c>
       <c r="I68" s="3">
-        <v>46114</v>
+        <v>46163</v>
       </c>
       <c r="J68" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4600,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4609,28 +4525,28 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F69" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G69" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="H69" s="3">
-        <v>46114</v>
+        <v>46161</v>
       </c>
       <c r="I69" s="3">
-        <v>46136</v>
+        <v>46163</v>
       </c>
       <c r="J69" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="M69" t="s">
         <v>6</v>
@@ -4650,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4659,28 +4575,28 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F70" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="G70" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="H70" s="3">
-        <v>46122</v>
+        <v>46161</v>
       </c>
       <c r="I70" s="3">
-        <v>46142</v>
+        <v>46164</v>
       </c>
       <c r="J70" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
       </c>
       <c r="L70" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="M70" t="s">
         <v>6</v>
@@ -4700,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4709,28 +4625,28 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="F71" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G71" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="H71" s="3">
-        <v>46065</v>
+        <v>46161</v>
       </c>
       <c r="I71" s="3">
-        <v>46078</v>
+        <v>46164</v>
       </c>
       <c r="J71" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="M71" t="s">
         <v>6</v>
@@ -4750,7 +4666,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4759,28 +4675,28 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="F72" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G72" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="H72" s="3">
-        <v>46078</v>
+        <v>46161</v>
       </c>
       <c r="I72" s="3">
-        <v>46085</v>
+        <v>46164</v>
       </c>
       <c r="J72" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="M72" t="s">
         <v>6</v>
@@ -4800,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4809,28 +4725,28 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="F73" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G73" s="3">
-        <v>46062</v>
+        <v>46093</v>
       </c>
       <c r="H73" s="3">
-        <v>46099</v>
+        <v>46155</v>
       </c>
       <c r="I73" s="3">
-        <v>46101</v>
+        <v>46160</v>
       </c>
       <c r="J73" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46062</v>
+        <v>46093</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -4850,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4859,28 +4775,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="F74" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G74" s="3">
-        <v>46062</v>
+        <v>46093</v>
       </c>
       <c r="H74" s="3">
-        <v>46100</v>
+        <v>46155</v>
       </c>
       <c r="I74" s="3">
-        <v>46104</v>
+        <v>46160</v>
       </c>
       <c r="J74" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46062</v>
+        <v>46093</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -4900,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -4909,28 +4825,28 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="F75" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G75" s="3">
-        <v>46062</v>
+        <v>46094</v>
       </c>
       <c r="H75" s="3">
-        <v>46092</v>
+        <v>46146</v>
       </c>
       <c r="I75" s="3">
-        <v>46098</v>
+        <v>46148</v>
       </c>
       <c r="J75" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46062</v>
+        <v>46094</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -4950,7 +4866,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4959,28 +4875,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F76" t="s">
-        <v>196</v>
+        <v>138</v>
       </c>
       <c r="G76" s="3">
-        <v>46062</v>
+        <v>46105</v>
       </c>
       <c r="H76" s="3">
-        <v>46093</v>
+        <v>46219</v>
       </c>
       <c r="I76" s="3">
-        <v>46099</v>
+        <v>46223</v>
       </c>
       <c r="J76" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46062</v>
+        <v>46105</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -5000,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5009,28 +4925,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F77" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="G77" s="3">
-        <v>46063</v>
+        <v>46105</v>
       </c>
       <c r="H77" s="3">
-        <v>46099</v>
+        <v>46212</v>
       </c>
       <c r="I77" s="3">
-        <v>46101</v>
+        <v>46218</v>
       </c>
       <c r="J77" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46063</v>
+        <v>46105</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -5050,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5059,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="F78" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="G78" s="3">
-        <v>46063</v>
+        <v>46105</v>
       </c>
       <c r="H78" s="3">
-        <v>46163</v>
+        <v>46136</v>
       </c>
       <c r="I78" s="3">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="J78" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46063</v>
+        <v>46105</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5100,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5109,28 +5025,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="F79" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G79" s="3">
-        <v>46063</v>
+        <v>46106</v>
       </c>
       <c r="H79" s="3">
-        <v>46091</v>
+        <v>46227</v>
       </c>
       <c r="I79" s="3">
-        <v>46094</v>
+        <v>46231</v>
       </c>
       <c r="J79" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="K79" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L79" s="3">
-        <v>46063</v>
+        <v>46106</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5150,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5159,28 +5075,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>204</v>
+        <v>19</v>
       </c>
       <c r="G80" s="3">
-        <v>46063</v>
+        <v>46106</v>
       </c>
       <c r="H80" s="3">
-        <v>46155</v>
+        <v>46211</v>
       </c>
       <c r="I80" s="3">
-        <v>46160</v>
+        <v>46216</v>
       </c>
       <c r="J80" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K80" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L80" s="3">
-        <v>46063</v>
+        <v>46106</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5200,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5209,28 +5125,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="F81" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="G81" s="3">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="H81" s="3">
-        <v>46085</v>
+        <v>46205</v>
       </c>
       <c r="I81" s="3">
-        <v>46087</v>
+        <v>46210</v>
       </c>
       <c r="J81" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="K81" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L81" s="3">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5250,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5259,28 +5175,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="F82" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="G82" s="3">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="H82" s="3">
-        <v>46086</v>
+        <v>46225</v>
       </c>
       <c r="I82" s="3">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="J82" t="s">
-        <v>212</v>
+        <v>51</v>
       </c>
       <c r="K82" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L82" s="3">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5300,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5309,28 +5225,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="F83" t="s">
-        <v>3</v>
+        <v>141</v>
       </c>
       <c r="G83" s="3">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="H83" s="3">
-        <v>46176</v>
+        <v>46219</v>
       </c>
       <c r="I83" s="3">
-        <v>46181</v>
+        <v>46224</v>
       </c>
       <c r="J83" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K83" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L83" s="3">
-        <v>46064</v>
+        <v>46106</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5350,7 +5266,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5359,28 +5275,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="F84" t="s">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="G84" s="3">
-        <v>46064</v>
+        <v>46107</v>
       </c>
       <c r="H84" s="3">
-        <v>46176</v>
+        <v>46136</v>
       </c>
       <c r="I84" s="3">
-        <v>46181</v>
+        <v>46140</v>
       </c>
       <c r="J84" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="K84" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L84" s="3">
-        <v>46064</v>
+        <v>46107</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5400,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5409,28 +5325,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="F85" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="G85" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H85" s="3">
+        <v>46168</v>
+      </c>
+      <c r="I85" s="3">
         <v>46170</v>
       </c>
-      <c r="I85" s="3">
-        <v>46175</v>
-      </c>
       <c r="J85" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5450,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5459,28 +5375,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="F86" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="G86" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H86" s="3">
+        <v>46168</v>
+      </c>
+      <c r="I86" s="3">
         <v>46170</v>
       </c>
-      <c r="I86" s="3">
-        <v>46175</v>
-      </c>
       <c r="J86" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5500,7 +5416,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5509,28 +5425,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="F87" t="s">
-        <v>3</v>
+        <v>194</v>
       </c>
       <c r="G87" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H87" s="3">
-        <v>46240</v>
+        <v>46168</v>
       </c>
       <c r="I87" s="3">
-        <v>46245</v>
+        <v>46170</v>
       </c>
       <c r="J87" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5550,7 +5466,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5559,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="F88" t="s">
-        <v>3</v>
+        <v>199</v>
       </c>
       <c r="G88" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H88" s="3">
-        <v>46240</v>
+        <v>46161</v>
       </c>
       <c r="I88" s="3">
-        <v>46245</v>
+        <v>46167</v>
       </c>
       <c r="J88" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5600,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5609,28 +5525,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="F89" t="s">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="G89" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H89" s="3">
-        <v>46234</v>
+        <v>46161</v>
       </c>
       <c r="I89" s="3">
-        <v>46239</v>
+        <v>46167</v>
       </c>
       <c r="J89" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5650,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5659,28 +5575,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="F90" t="s">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="G90" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H90" s="3">
-        <v>46234</v>
+        <v>46161</v>
       </c>
       <c r="I90" s="3">
-        <v>46239</v>
+        <v>46167</v>
       </c>
       <c r="J90" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5700,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5709,28 +5625,28 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="F91" t="s">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="G91" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H91" s="3">
-        <v>46146</v>
+        <v>46232</v>
       </c>
       <c r="I91" s="3">
-        <v>46149</v>
+        <v>46234</v>
       </c>
       <c r="J91" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5750,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5759,28 +5675,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="F92" t="s">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="G92" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H92" s="3">
-        <v>46174</v>
+        <v>46232</v>
       </c>
       <c r="I92" s="3">
-        <v>46177</v>
+        <v>46234</v>
       </c>
       <c r="J92" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -5800,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5809,28 +5725,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="F93" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="G93" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H93" s="3">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="I93" s="3">
-        <v>46241</v>
+        <v>46231</v>
       </c>
       <c r="J93" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5850,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5859,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="F94" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="G94" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H94" s="3">
-        <v>46297</v>
+        <v>46225</v>
       </c>
       <c r="I94" s="3">
-        <v>46302</v>
+        <v>46231</v>
       </c>
       <c r="J94" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -5900,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -5909,28 +5825,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F95" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="G95" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H95" s="3">
-        <v>46139</v>
+        <v>46232</v>
       </c>
       <c r="I95" s="3">
-        <v>46142</v>
+        <v>46237</v>
       </c>
       <c r="J95" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -5950,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -5959,28 +5875,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F96" t="s">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="G96" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="H96" s="3">
-        <v>46168</v>
+        <v>46224</v>
       </c>
       <c r="I96" s="3">
-        <v>46171</v>
+        <v>46227</v>
       </c>
       <c r="J96" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -6000,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6009,28 +5925,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F97" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="G97" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="H97" s="3">
-        <v>46232</v>
+        <v>46149</v>
       </c>
       <c r="I97" s="3">
-        <v>46237</v>
+        <v>46153</v>
       </c>
       <c r="J97" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -6050,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6059,28 +5975,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F98" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="G98" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="H98" s="3">
-        <v>46289</v>
+        <v>46149</v>
       </c>
       <c r="I98" s="3">
-        <v>46296</v>
+        <v>46153</v>
       </c>
       <c r="J98" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6100,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6109,26 +6025,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="F99" t="s">
-        <v>3</v>
-      </c>
-      <c r="G99" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="G99" s="3">
+        <v>46114</v>
+      </c>
       <c r="H99" s="3">
-        <v>46301</v>
+        <v>46141</v>
       </c>
       <c r="I99" s="3">
-        <v>46307</v>
+        <v>46148</v>
       </c>
       <c r="J99" t="s">
-        <v>231</v>
+        <v>145</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6148,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6157,28 +6075,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="F100" t="s">
-        <v>3</v>
+        <v>174</v>
       </c>
       <c r="G100" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="H100" s="3">
-        <v>46301</v>
+        <v>46141</v>
       </c>
       <c r="I100" s="3">
-        <v>46307</v>
+        <v>46148</v>
       </c>
       <c r="J100" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6198,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6207,28 +6125,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F101" t="s">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="G101" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="H101" s="3">
-        <v>46267</v>
+        <v>46160</v>
       </c>
       <c r="I101" s="3">
-        <v>46272</v>
+        <v>46162</v>
       </c>
       <c r="J101" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46064</v>
+        <v>46114</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6248,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6257,28 +6175,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F102" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="G102" s="3">
-        <v>46064</v>
+        <v>46119</v>
       </c>
       <c r="H102" s="3">
-        <v>46267</v>
+        <v>46134</v>
       </c>
       <c r="I102" s="3">
-        <v>46272</v>
+        <v>46136</v>
       </c>
       <c r="J102" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46064</v>
+        <v>46119</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6298,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6307,28 +6225,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="G103" s="3">
-        <v>46076</v>
+        <v>46120</v>
       </c>
       <c r="H103" s="3">
-        <v>46087</v>
+        <v>46160</v>
       </c>
       <c r="I103" s="3">
-        <v>46091</v>
+        <v>46162</v>
       </c>
       <c r="J103" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46076</v>
+        <v>46120</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6348,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6357,28 +6275,28 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G104" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="H104" s="3">
-        <v>46087</v>
+        <v>46162</v>
       </c>
       <c r="I104" s="3">
-        <v>46091</v>
+        <v>46164</v>
       </c>
       <c r="J104" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
       </c>
       <c r="L104" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6398,7 +6316,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6407,28 +6325,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G105" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="H105" s="3">
-        <v>46087</v>
+        <v>46162</v>
       </c>
       <c r="I105" s="3">
-        <v>46091</v>
+        <v>46164</v>
       </c>
       <c r="J105" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6448,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6457,28 +6375,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F106" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G106" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="H106" s="3">
-        <v>46083</v>
+        <v>46153</v>
       </c>
       <c r="I106" s="3">
-        <v>46086</v>
+        <v>46155</v>
       </c>
       <c r="J106" t="s">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6498,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6507,28 +6425,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="F107" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="G107" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="H107" s="3">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="I107" s="3">
-        <v>46086</v>
+        <v>46136</v>
       </c>
       <c r="J107" t="s">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6548,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6557,28 +6475,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F108" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G108" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="H108" s="3">
-        <v>46083</v>
+        <v>46147</v>
       </c>
       <c r="I108" s="3">
-        <v>46086</v>
+        <v>46150</v>
       </c>
       <c r="J108" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46076</v>
+        <v>46122</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6598,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6607,28 +6525,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="F109" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="G109" s="3">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="H109" s="3">
-        <v>46104</v>
+        <v>46136</v>
       </c>
       <c r="I109" s="3">
-        <v>46107</v>
+        <v>46140</v>
       </c>
       <c r="J109" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6648,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6657,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>94</v>
+        <v>241</v>
       </c>
       <c r="F110" t="s">
-        <v>95</v>
+        <v>242</v>
       </c>
       <c r="G110" s="3">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="H110" s="3">
-        <v>46099</v>
+        <v>46150</v>
       </c>
       <c r="I110" s="3">
-        <v>46104</v>
+        <v>46156</v>
       </c>
       <c r="J110" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6698,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6707,28 +6625,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F111" t="s">
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="G111" s="3">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="H111" s="3">
-        <v>46079</v>
+        <v>46140</v>
       </c>
       <c r="I111" s="3">
-        <v>46084</v>
+        <v>46147</v>
       </c>
       <c r="J111" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46076</v>
+        <v>46125</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6748,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6757,28 +6675,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F112" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="G112" s="3">
-        <v>46076</v>
+        <v>46126</v>
       </c>
       <c r="H112" s="3">
-        <v>46162</v>
+        <v>46142</v>
       </c>
       <c r="I112" s="3">
-        <v>46164</v>
+        <v>46147</v>
       </c>
       <c r="J112" t="s">
-        <v>18</v>
+        <v>249</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46076</v>
+        <v>46126</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -6798,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -6810,25 +6728,25 @@
         <v>251</v>
       </c>
       <c r="F113" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="G113" s="3">
-        <v>46076</v>
+        <v>46126</v>
       </c>
       <c r="H113" s="3">
-        <v>46162</v>
+        <v>46132</v>
       </c>
       <c r="I113" s="3">
-        <v>46164</v>
+        <v>46135</v>
       </c>
       <c r="J113" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46076</v>
+        <v>46126</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -6848,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -6857,28 +6775,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="F114" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="G114" s="3">
-        <v>46076</v>
+        <v>46132</v>
       </c>
       <c r="H114" s="3">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="I114" s="3">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="J114" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46076</v>
+        <v>46132</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -6898,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -6907,28 +6825,28 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="F115" t="s">
-        <v>256</v>
+        <v>76</v>
       </c>
       <c r="G115" s="3">
-        <v>46076</v>
+        <v>46132</v>
       </c>
       <c r="H115" s="3">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="I115" s="3">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="J115" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46076</v>
+        <v>46132</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -6948,7 +6866,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -6957,28 +6875,28 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F116" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="G116" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="H116" s="3">
-        <v>46212</v>
+        <v>46170</v>
       </c>
       <c r="I116" s="3">
-        <v>46216</v>
+        <v>46171</v>
       </c>
       <c r="J116" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -6998,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7007,28 +6925,28 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F117" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="G117" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="H117" s="3">
-        <v>46212</v>
+        <v>46170</v>
       </c>
       <c r="I117" s="3">
-        <v>46216</v>
+        <v>46171</v>
       </c>
       <c r="J117" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
       </c>
       <c r="L117" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
@@ -7048,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7057,28 +6975,28 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G118" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="H118" s="3">
-        <v>46206</v>
+        <v>46170</v>
       </c>
       <c r="I118" s="3">
-        <v>46211</v>
+        <v>46171</v>
       </c>
       <c r="J118" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7098,37 +7016,37 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
+        <v>260</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
         <v>261</v>
       </c>
-      <c r="C119" s="2">
-        <v>1</v>
-      </c>
-      <c r="D119" s="2">
-        <v>0</v>
-      </c>
-      <c r="E119" t="s">
-        <v>255</v>
-      </c>
       <c r="F119" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="G119" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="H119" s="3">
-        <v>46206</v>
+        <v>46133</v>
       </c>
       <c r="I119" s="3">
-        <v>46211</v>
+        <v>46136</v>
       </c>
       <c r="J119" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46076</v>
+        <v>46133</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7157,28 +7075,28 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>251</v>
+        <v>87</v>
       </c>
       <c r="F120" t="s">
-        <v>200</v>
+        <v>88</v>
       </c>
       <c r="G120" s="3">
-        <v>46076</v>
+        <v>46134</v>
       </c>
       <c r="H120" s="3">
-        <v>46251</v>
+        <v>46134</v>
       </c>
       <c r="I120" s="3">
-        <v>46253</v>
+        <v>46139</v>
       </c>
       <c r="J120" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
       </c>
       <c r="L120" s="3">
-        <v>46076</v>
+        <v>46134</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
@@ -7207,28 +7125,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F121" t="s">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="G121" s="3">
-        <v>46076</v>
+        <v>46134</v>
       </c>
       <c r="H121" s="3">
-        <v>46251</v>
+        <v>46135</v>
       </c>
       <c r="I121" s="3">
-        <v>46253</v>
+        <v>46140</v>
       </c>
       <c r="J121" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46076</v>
+        <v>46134</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7248,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7257,28 +7175,28 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F122" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="G122" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H122" s="3">
-        <v>46245</v>
+        <v>46139</v>
       </c>
       <c r="I122" s="3">
-        <v>46248</v>
+        <v>46142</v>
       </c>
       <c r="J122" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K122" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L122" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7298,7 +7216,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7307,28 +7225,28 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F123" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="G123" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H123" s="3">
-        <v>46245</v>
+        <v>46139</v>
       </c>
       <c r="I123" s="3">
-        <v>46248</v>
+        <v>46142</v>
       </c>
       <c r="J123" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="K123" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L123" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7348,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7363,22 +7281,22 @@
         <v>268</v>
       </c>
       <c r="G124" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H124" s="3">
-        <v>46108</v>
+        <v>46139</v>
       </c>
       <c r="I124" s="3">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="J124" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K124" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L124" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7398,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7413,22 +7331,22 @@
         <v>268</v>
       </c>
       <c r="G125" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H125" s="3">
-        <v>46108</v>
+        <v>46139</v>
       </c>
       <c r="I125" s="3">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="J125" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K125" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L125" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7448,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7457,28 +7375,28 @@
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F126" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G126" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H126" s="3">
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="I126" s="3">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="J126" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K126" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L126" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7498,7 +7416,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7507,28 +7425,28 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F127" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G127" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H127" s="3">
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="I127" s="3">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="J127" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="K127" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L127" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7548,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7563,22 +7481,22 @@
         <v>274</v>
       </c>
       <c r="G128" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H128" s="3">
-        <v>46104</v>
+        <v>46136</v>
       </c>
       <c r="I128" s="3">
-        <v>46107</v>
+        <v>46141</v>
       </c>
       <c r="J128" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K128" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L128" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7598,7 +7516,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7613,22 +7531,22 @@
         <v>274</v>
       </c>
       <c r="G129" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H129" s="3">
-        <v>46104</v>
+        <v>46136</v>
       </c>
       <c r="I129" s="3">
-        <v>46107</v>
+        <v>46141</v>
       </c>
       <c r="J129" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K129" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L129" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7648,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7657,28 +7575,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>273</v>
+        <v>87</v>
       </c>
       <c r="F130" t="s">
-        <v>274</v>
+        <v>88</v>
       </c>
       <c r="G130" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="H130" s="3">
-        <v>46104</v>
+        <v>46136</v>
       </c>
       <c r="I130" s="3">
-        <v>46107</v>
+        <v>46141</v>
       </c>
       <c r="J130" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K130" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="L130" s="3">
-        <v>46076</v>
+        <v>46136</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7698,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7707,28 +7625,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F131" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G131" s="3">
-        <v>46076</v>
+        <v>46139</v>
       </c>
       <c r="H131" s="3">
-        <v>46104</v>
+        <v>46170</v>
       </c>
       <c r="I131" s="3">
-        <v>46107</v>
+        <v>46174</v>
       </c>
       <c r="J131" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46076</v>
+        <v>46139</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -7748,7 +7666,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -7757,28 +7675,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F132" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G132" s="3">
-        <v>46077</v>
+        <v>46139</v>
       </c>
       <c r="H132" s="3">
-        <v>46121</v>
+        <v>46164</v>
       </c>
       <c r="I132" s="3">
-        <v>46125</v>
+        <v>46169</v>
       </c>
       <c r="J132" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46077</v>
+        <v>46139</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -7798,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -7807,28 +7725,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c r="F133" t="s">
-        <v>283</v>
+        <v>47</v>
       </c>
       <c r="G133" s="3">
-        <v>46079</v>
+        <v>46139</v>
       </c>
       <c r="H133" s="3">
-        <v>46155</v>
+        <v>46139</v>
       </c>
       <c r="I133" s="3">
-        <v>46160</v>
+        <v>46142</v>
       </c>
       <c r="J133" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46079</v>
+        <v>46139</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -7845,10 +7763,10 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" t="s">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="B134" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -7857,28 +7775,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F134" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G134" s="3">
-        <v>46079</v>
+        <v>46043</v>
       </c>
       <c r="H134" s="3">
-        <v>46147</v>
+        <v>46051</v>
       </c>
       <c r="I134" s="3">
-        <v>46150</v>
+        <v>46057</v>
       </c>
       <c r="J134" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="K134" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="L134" s="3">
-        <v>46079</v>
+        <v>46043</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -7895,10 +7813,10 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" t="s">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="B135" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -7907,28 +7825,28 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F135" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G135" s="3">
-        <v>46079</v>
+        <v>46057</v>
       </c>
       <c r="H135" s="3">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="I135" s="3">
         <v>46083</v>
       </c>
       <c r="J135" t="s">
+        <v>28</v>
+      </c>
+      <c r="K135" t="s">
         <v>290</v>
       </c>
-      <c r="K135" t="s">
-        <v>5</v>
-      </c>
       <c r="L135" s="3">
-        <v>46079</v>
+        <v>46057</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -7945,10 +7863,10 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" t="s">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="B136" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -7957,28 +7875,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="F136" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="G136" s="3">
-        <v>46079</v>
+        <v>46113</v>
       </c>
       <c r="H136" s="3">
-        <v>46079</v>
+        <v>46121</v>
       </c>
       <c r="I136" s="3">
-        <v>46083</v>
+        <v>46122</v>
       </c>
       <c r="J136" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K136" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="L136" s="3">
-        <v>46079</v>
+        <v>46113</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -7995,10 +7913,10 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="B137" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -8007,28 +7925,28 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F137" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="G137" s="3">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="H137" s="3">
-        <v>46079</v>
+        <v>46148</v>
       </c>
       <c r="I137" s="3">
-        <v>46083</v>
+        <v>46148</v>
       </c>
       <c r="J137" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K137" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="L137" s="3">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -8045,10 +7963,10 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="B138" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -8057,28 +7975,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F138" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="G138" s="3">
-        <v>46083</v>
+        <v>46122</v>
       </c>
       <c r="H138" s="3">
-        <v>46083</v>
+        <v>46142</v>
       </c>
       <c r="I138" s="3">
-        <v>46085</v>
+        <v>46148</v>
       </c>
       <c r="J138" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="K138" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="L138" s="3">
-        <v>46083</v>
+        <v>46122</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8095,10 +8013,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="B139" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8107,28 +8025,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="F139" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="G139" s="3">
-        <v>46083</v>
+        <v>46127</v>
       </c>
       <c r="H139" s="3">
-        <v>46083</v>
+        <v>46132</v>
       </c>
       <c r="I139" s="3">
-        <v>46085</v>
+        <v>46136</v>
       </c>
       <c r="J139" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K139" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="L139" s="3">
-        <v>46083</v>
+        <v>46127</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8145,10 +8063,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="B140" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8157,28 +8075,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="F140" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="G140" s="3">
-        <v>46083</v>
+        <v>46135</v>
       </c>
       <c r="H140" s="3">
-        <v>46090</v>
+        <v>46135</v>
       </c>
       <c r="I140" s="3">
-        <v>46093</v>
+        <v>46147</v>
       </c>
       <c r="J140" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="K140" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="L140" s="3">
-        <v>46083</v>
+        <v>46135</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8190,800 +8108,6 @@
         <v>8</v>
       </c>
       <c r="P140" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16">
-      <c r="A141" t="s">
-        <v>0</v>
-      </c>
-      <c r="B141" t="s">
-        <v>300</v>
-      </c>
-      <c r="C141" s="2">
-        <v>1</v>
-      </c>
-      <c r="D141" s="2">
-        <v>0</v>
-      </c>
-      <c r="E141" t="s">
-        <v>298</v>
-      </c>
-      <c r="F141" t="s">
-        <v>299</v>
-      </c>
-      <c r="G141" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H141" s="3">
-        <v>46090</v>
-      </c>
-      <c r="I141" s="3">
-        <v>46093</v>
-      </c>
-      <c r="J141" t="s">
-        <v>122</v>
-      </c>
-      <c r="K141" t="s">
-        <v>5</v>
-      </c>
-      <c r="L141" s="3">
-        <v>46083</v>
-      </c>
-      <c r="M141" t="s">
-        <v>6</v>
-      </c>
-      <c r="N141" t="s">
-        <v>7</v>
-      </c>
-      <c r="O141" t="s">
-        <v>8</v>
-      </c>
-      <c r="P141" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16">
-      <c r="A142" t="s">
-        <v>0</v>
-      </c>
-      <c r="B142" t="s">
-        <v>301</v>
-      </c>
-      <c r="C142" s="2">
-        <v>1</v>
-      </c>
-      <c r="D142" s="2">
-        <v>0</v>
-      </c>
-      <c r="E142" t="s">
-        <v>298</v>
-      </c>
-      <c r="F142" t="s">
-        <v>299</v>
-      </c>
-      <c r="G142" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H142" s="3">
-        <v>46090</v>
-      </c>
-      <c r="I142" s="3">
-        <v>46093</v>
-      </c>
-      <c r="J142" t="s">
-        <v>122</v>
-      </c>
-      <c r="K142" t="s">
-        <v>5</v>
-      </c>
-      <c r="L142" s="3">
-        <v>46083</v>
-      </c>
-      <c r="M142" t="s">
-        <v>6</v>
-      </c>
-      <c r="N142" t="s">
-        <v>7</v>
-      </c>
-      <c r="O142" t="s">
-        <v>8</v>
-      </c>
-      <c r="P142" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16">
-      <c r="A143" t="s">
-        <v>0</v>
-      </c>
-      <c r="B143" t="s">
-        <v>302</v>
-      </c>
-      <c r="C143" s="2">
-        <v>1</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
-        <v>303</v>
-      </c>
-      <c r="F143" t="s">
-        <v>304</v>
-      </c>
-      <c r="G143" s="3"/>
-      <c r="H143" s="3">
-        <v>46084</v>
-      </c>
-      <c r="I143" s="3">
-        <v>46087</v>
-      </c>
-      <c r="J143" t="s">
-        <v>305</v>
-      </c>
-      <c r="K143" t="s">
-        <v>5</v>
-      </c>
-      <c r="L143" s="3">
-        <v>46083</v>
-      </c>
-      <c r="M143" t="s">
-        <v>6</v>
-      </c>
-      <c r="N143" t="s">
-        <v>7</v>
-      </c>
-      <c r="O143" t="s">
-        <v>8</v>
-      </c>
-      <c r="P143" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16">
-      <c r="A144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B144" t="s">
-        <v>306</v>
-      </c>
-      <c r="C144" s="2">
-        <v>1</v>
-      </c>
-      <c r="D144" s="2">
-        <v>0</v>
-      </c>
-      <c r="E144" t="s">
-        <v>303</v>
-      </c>
-      <c r="F144" t="s">
-        <v>304</v>
-      </c>
-      <c r="G144" s="3"/>
-      <c r="H144" s="3">
-        <v>46084</v>
-      </c>
-      <c r="I144" s="3">
-        <v>46087</v>
-      </c>
-      <c r="J144" t="s">
-        <v>305</v>
-      </c>
-      <c r="K144" t="s">
-        <v>5</v>
-      </c>
-      <c r="L144" s="3">
-        <v>46083</v>
-      </c>
-      <c r="M144" t="s">
-        <v>6</v>
-      </c>
-      <c r="N144" t="s">
-        <v>7</v>
-      </c>
-      <c r="O144" t="s">
-        <v>8</v>
-      </c>
-      <c r="P144" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16">
-      <c r="A145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" t="s">
-        <v>307</v>
-      </c>
-      <c r="C145" s="2">
-        <v>1</v>
-      </c>
-      <c r="D145" s="2">
-        <v>0</v>
-      </c>
-      <c r="E145" t="s">
-        <v>303</v>
-      </c>
-      <c r="F145" t="s">
-        <v>304</v>
-      </c>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3">
-        <v>46084</v>
-      </c>
-      <c r="I145" s="3">
-        <v>46087</v>
-      </c>
-      <c r="J145" t="s">
-        <v>305</v>
-      </c>
-      <c r="K145" t="s">
-        <v>5</v>
-      </c>
-      <c r="L145" s="3">
-        <v>46083</v>
-      </c>
-      <c r="M145" t="s">
-        <v>6</v>
-      </c>
-      <c r="N145" t="s">
-        <v>7</v>
-      </c>
-      <c r="O145" t="s">
-        <v>8</v>
-      </c>
-      <c r="P145" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16">
-      <c r="A146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B146" t="s">
-        <v>308</v>
-      </c>
-      <c r="C146" s="2">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>309</v>
-      </c>
-      <c r="F146" t="s">
-        <v>310</v>
-      </c>
-      <c r="G146" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H146" s="3">
-        <v>46083</v>
-      </c>
-      <c r="I146" s="3">
-        <v>46107</v>
-      </c>
-      <c r="J146" t="s">
-        <v>18</v>
-      </c>
-      <c r="K146" t="s">
-        <v>5</v>
-      </c>
-      <c r="L146" s="3">
-        <v>46083</v>
-      </c>
-      <c r="M146" t="s">
-        <v>6</v>
-      </c>
-      <c r="N146" t="s">
-        <v>7</v>
-      </c>
-      <c r="O146" t="s">
-        <v>8</v>
-      </c>
-      <c r="P146" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16">
-      <c r="A147" t="s">
-        <v>0</v>
-      </c>
-      <c r="B147" t="s">
-        <v>311</v>
-      </c>
-      <c r="C147" s="2">
-        <v>1</v>
-      </c>
-      <c r="D147" s="2">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>143</v>
-      </c>
-      <c r="F147" t="s">
-        <v>144</v>
-      </c>
-      <c r="G147" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H147" s="3">
-        <v>46084</v>
-      </c>
-      <c r="I147" s="3">
-        <v>46107</v>
-      </c>
-      <c r="J147" t="s">
-        <v>18</v>
-      </c>
-      <c r="K147" t="s">
-        <v>5</v>
-      </c>
-      <c r="L147" s="3">
-        <v>46083</v>
-      </c>
-      <c r="M147" t="s">
-        <v>6</v>
-      </c>
-      <c r="N147" t="s">
-        <v>7</v>
-      </c>
-      <c r="O147" t="s">
-        <v>8</v>
-      </c>
-      <c r="P147" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16">
-      <c r="A148" t="s">
-        <v>312</v>
-      </c>
-      <c r="B148" t="s">
-        <v>313</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1</v>
-      </c>
-      <c r="D148" s="2">
-        <v>0</v>
-      </c>
-      <c r="E148" t="s">
-        <v>314</v>
-      </c>
-      <c r="F148" t="s">
-        <v>315</v>
-      </c>
-      <c r="G148" s="3">
-        <v>46035</v>
-      </c>
-      <c r="H148" s="3">
-        <v>46052</v>
-      </c>
-      <c r="I148" s="3">
-        <v>46076</v>
-      </c>
-      <c r="J148" t="s">
-        <v>80</v>
-      </c>
-      <c r="K148" t="s">
-        <v>316</v>
-      </c>
-      <c r="L148" s="3">
-        <v>46035</v>
-      </c>
-      <c r="M148" t="s">
-        <v>6</v>
-      </c>
-      <c r="N148" t="s">
-        <v>7</v>
-      </c>
-      <c r="O148" t="s">
-        <v>8</v>
-      </c>
-      <c r="P148" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16">
-      <c r="A149" t="s">
-        <v>312</v>
-      </c>
-      <c r="B149" t="s">
-        <v>317</v>
-      </c>
-      <c r="C149" s="2">
-        <v>1</v>
-      </c>
-      <c r="D149" s="2">
-        <v>0</v>
-      </c>
-      <c r="E149" t="s">
-        <v>318</v>
-      </c>
-      <c r="F149" t="s">
-        <v>319</v>
-      </c>
-      <c r="G149" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H149" s="3">
-        <v>46051</v>
-      </c>
-      <c r="I149" s="3">
-        <v>46057</v>
-      </c>
-      <c r="J149" t="s">
-        <v>122</v>
-      </c>
-      <c r="K149" t="s">
-        <v>316</v>
-      </c>
-      <c r="L149" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M149" t="s">
-        <v>6</v>
-      </c>
-      <c r="N149" t="s">
-        <v>7</v>
-      </c>
-      <c r="O149" t="s">
-        <v>8</v>
-      </c>
-      <c r="P149" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16">
-      <c r="A150" t="s">
-        <v>312</v>
-      </c>
-      <c r="B150" t="s">
-        <v>320</v>
-      </c>
-      <c r="C150" s="2">
-        <v>1</v>
-      </c>
-      <c r="D150" s="2">
-        <v>0</v>
-      </c>
-      <c r="E150" t="s">
-        <v>321</v>
-      </c>
-      <c r="F150" t="s">
-        <v>322</v>
-      </c>
-      <c r="G150" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H150" s="3">
-        <v>46059</v>
-      </c>
-      <c r="I150" s="3">
-        <v>46062</v>
-      </c>
-      <c r="J150" t="s">
-        <v>133</v>
-      </c>
-      <c r="K150" t="s">
-        <v>316</v>
-      </c>
-      <c r="L150" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M150" t="s">
-        <v>6</v>
-      </c>
-      <c r="N150" t="s">
-        <v>7</v>
-      </c>
-      <c r="O150" t="s">
-        <v>8</v>
-      </c>
-      <c r="P150" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16">
-      <c r="A151" t="s">
-        <v>312</v>
-      </c>
-      <c r="B151" t="s">
-        <v>323</v>
-      </c>
-      <c r="C151" s="2">
-        <v>1</v>
-      </c>
-      <c r="D151" s="2">
-        <v>0</v>
-      </c>
-      <c r="E151" t="s">
-        <v>324</v>
-      </c>
-      <c r="F151" t="s">
-        <v>325</v>
-      </c>
-      <c r="G151" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H151" s="3">
-        <v>46052</v>
-      </c>
-      <c r="I151" s="3">
-        <v>46058</v>
-      </c>
-      <c r="J151" t="s">
-        <v>4</v>
-      </c>
-      <c r="K151" t="s">
-        <v>316</v>
-      </c>
-      <c r="L151" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M151" t="s">
-        <v>6</v>
-      </c>
-      <c r="N151" t="s">
-        <v>7</v>
-      </c>
-      <c r="O151" t="s">
-        <v>8</v>
-      </c>
-      <c r="P151" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16">
-      <c r="A152" t="s">
-        <v>312</v>
-      </c>
-      <c r="B152" t="s">
-        <v>326</v>
-      </c>
-      <c r="C152" s="2">
-        <v>1</v>
-      </c>
-      <c r="D152" s="2">
-        <v>0</v>
-      </c>
-      <c r="E152" t="s">
-        <v>327</v>
-      </c>
-      <c r="F152" t="s">
-        <v>328</v>
-      </c>
-      <c r="G152" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H152" s="3">
-        <v>46077</v>
-      </c>
-      <c r="I152" s="3">
-        <v>46094</v>
-      </c>
-      <c r="J152" t="s">
-        <v>4</v>
-      </c>
-      <c r="K152" t="s">
-        <v>316</v>
-      </c>
-      <c r="L152" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M152" t="s">
-        <v>6</v>
-      </c>
-      <c r="N152" t="s">
-        <v>7</v>
-      </c>
-      <c r="O152" t="s">
-        <v>8</v>
-      </c>
-      <c r="P152" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16">
-      <c r="A153" t="s">
-        <v>312</v>
-      </c>
-      <c r="B153" t="s">
-        <v>329</v>
-      </c>
-      <c r="C153" s="2">
-        <v>1</v>
-      </c>
-      <c r="D153" s="2">
-        <v>0</v>
-      </c>
-      <c r="E153" t="s">
-        <v>330</v>
-      </c>
-      <c r="F153" t="s">
-        <v>331</v>
-      </c>
-      <c r="G153" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H153" s="3">
-        <v>46064</v>
-      </c>
-      <c r="I153" s="3">
-        <v>46066</v>
-      </c>
-      <c r="J153" t="s">
-        <v>4</v>
-      </c>
-      <c r="K153" t="s">
-        <v>316</v>
-      </c>
-      <c r="L153" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M153" t="s">
-        <v>6</v>
-      </c>
-      <c r="N153" t="s">
-        <v>7</v>
-      </c>
-      <c r="O153" t="s">
-        <v>8</v>
-      </c>
-      <c r="P153" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16">
-      <c r="A154" t="s">
-        <v>312</v>
-      </c>
-      <c r="B154" t="s">
-        <v>332</v>
-      </c>
-      <c r="C154" s="2">
-        <v>1</v>
-      </c>
-      <c r="D154" s="2">
-        <v>0</v>
-      </c>
-      <c r="E154" t="s">
-        <v>173</v>
-      </c>
-      <c r="F154" t="s">
-        <v>174</v>
-      </c>
-      <c r="G154" s="3">
-        <v>46057</v>
-      </c>
-      <c r="H154" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I154" s="3">
-        <v>46083</v>
-      </c>
-      <c r="J154" t="s">
-        <v>122</v>
-      </c>
-      <c r="K154" t="s">
-        <v>316</v>
-      </c>
-      <c r="L154" s="3">
-        <v>46057</v>
-      </c>
-      <c r="M154" t="s">
-        <v>6</v>
-      </c>
-      <c r="N154" t="s">
-        <v>7</v>
-      </c>
-      <c r="O154" t="s">
-        <v>8</v>
-      </c>
-      <c r="P154" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16">
-      <c r="A155" t="s">
-        <v>312</v>
-      </c>
-      <c r="B155" t="s">
-        <v>333</v>
-      </c>
-      <c r="C155" s="2">
-        <v>1</v>
-      </c>
-      <c r="D155" s="2">
-        <v>0</v>
-      </c>
-      <c r="E155" t="s">
-        <v>334</v>
-      </c>
-      <c r="F155" t="s">
-        <v>335</v>
-      </c>
-      <c r="G155" s="3">
-        <v>46076</v>
-      </c>
-      <c r="H155" s="3">
-        <v>46114</v>
-      </c>
-      <c r="I155" s="3">
-        <v>46119</v>
-      </c>
-      <c r="J155" t="s">
-        <v>133</v>
-      </c>
-      <c r="K155" t="s">
-        <v>316</v>
-      </c>
-      <c r="L155" s="3">
-        <v>46076</v>
-      </c>
-      <c r="M155" t="s">
-        <v>6</v>
-      </c>
-      <c r="N155" t="s">
-        <v>7</v>
-      </c>
-      <c r="O155" t="s">
-        <v>8</v>
-      </c>
-      <c r="P155" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16">
-      <c r="A156" t="s">
-        <v>312</v>
-      </c>
-      <c r="B156" t="s">
-        <v>336</v>
-      </c>
-      <c r="C156" s="2">
-        <v>1</v>
-      </c>
-      <c r="D156" s="2">
-        <v>0</v>
-      </c>
-      <c r="E156" t="s">
-        <v>255</v>
-      </c>
-      <c r="F156" t="s">
-        <v>256</v>
-      </c>
-      <c r="G156" s="3">
-        <v>46077</v>
-      </c>
-      <c r="H156" s="3">
-        <v>46078</v>
-      </c>
-      <c r="I156" s="3">
-        <v>46084</v>
-      </c>
-      <c r="J156" t="s">
-        <v>4</v>
-      </c>
-      <c r="K156" t="s">
-        <v>316</v>
-      </c>
-      <c r="L156" s="3">
-        <v>46077</v>
-      </c>
-      <c r="M156" t="s">
-        <v>6</v>
-      </c>
-      <c r="N156" t="s">
-        <v>7</v>
-      </c>
-      <c r="O156" t="s">
-        <v>8</v>
-      </c>
-      <c r="P156" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="328">
   <si>
     <t>ZP02</t>
   </si>
@@ -136,7 +136,10 @@
     <t>D10K 主軸,021177_BBT40,M60,CW45</t>
   </si>
   <si>
-    <t>200006503</t>
+    <t>REL  PCNF PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006504</t>
   </si>
   <si>
     <t>080200545001</t>
@@ -145,10 +148,19 @@
     <t>H1370機頭G6K,011395_#50,55F23,C</t>
   </si>
   <si>
-    <t>200006504</t>
-  </si>
-  <si>
-    <t>200006506</t>
+    <t>200006507</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006508</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006509</t>
   </si>
   <si>
     <t>080100116405</t>
@@ -157,21 +169,6 @@
     <t>G6K 主軸,021305_BBT50,CW45</t>
   </si>
   <si>
-    <t>200006507</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006508</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006509</t>
-  </si>
-  <si>
     <t>200006510</t>
   </si>
   <si>
@@ -502,7 +499,7 @@
     <t>200006624</t>
   </si>
   <si>
-    <t>200006627</t>
+    <t>200006628</t>
   </si>
   <si>
     <t>080100091606</t>
@@ -511,12 +508,6 @@
     <t>D10K 主軸,021177_BBT40,M60,0W45</t>
   </si>
   <si>
-    <t>REL  PCNF PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006628</t>
-  </si>
-  <si>
     <t>200006629</t>
   </si>
   <si>
@@ -580,15 +571,6 @@
     <t>200006645</t>
   </si>
   <si>
-    <t>200006646</t>
-  </si>
-  <si>
-    <t>080200551300</t>
-  </si>
-  <si>
-    <t>SP10機頭P12K,021023_#40,5GT-72,0</t>
-  </si>
-  <si>
     <t>200006647</t>
   </si>
   <si>
@@ -673,15 +655,6 @@
     <t>SP10機頭D12K,021256_#40,48F18</t>
   </si>
   <si>
-    <t>200006664</t>
-  </si>
-  <si>
-    <t>080200537901</t>
-  </si>
-  <si>
-    <t>LG1370機頭D15K,021720_#40,38F18,C,VKS26</t>
-  </si>
-  <si>
     <t>200006666</t>
   </si>
   <si>
@@ -871,6 +844,51 @@
     <t>200006700</t>
   </si>
   <si>
+    <t>200006701</t>
+  </si>
+  <si>
+    <t>080200547500</t>
+  </si>
+  <si>
+    <t>MVP13機頭D15K,011237_#40,38F18</t>
+  </si>
+  <si>
+    <t>200006702</t>
+  </si>
+  <si>
+    <t>200006703</t>
+  </si>
+  <si>
+    <t>080200422904</t>
+  </si>
+  <si>
+    <t>HEP機頭G8K,011194_780,55A18,C</t>
+  </si>
+  <si>
+    <t>200006704</t>
+  </si>
+  <si>
+    <t>200006705</t>
+  </si>
+  <si>
+    <t>080100037203</t>
+  </si>
+  <si>
+    <t>D8K 主軸,021274_BT50,M50,C045</t>
+  </si>
+  <si>
+    <t>200006706</t>
+  </si>
+  <si>
+    <t>200006707</t>
+  </si>
+  <si>
+    <t>080100045603</t>
+  </si>
+  <si>
+    <t>D12K 主軸,021274_BBT50,M50,CW45</t>
+  </si>
+  <si>
     <t>ZP09</t>
   </si>
   <si>
@@ -895,15 +913,6 @@
     <t>D6K 主軸,010801_BBT50,M50E,C045</t>
   </si>
   <si>
-    <t>630000348</t>
-  </si>
-  <si>
-    <t>080200570900</t>
-  </si>
-  <si>
-    <t>SMC-5機頭D24K,031793_#40,28F15,0</t>
-  </si>
-  <si>
     <t>630000349</t>
   </si>
   <si>
@@ -922,15 +931,6 @@
     <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
   </si>
   <si>
-    <t>630000352</t>
-  </si>
-  <si>
-    <t>080100059604</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021361_BT40,5GT,0W45</t>
-  </si>
-  <si>
     <t>630000354</t>
   </si>
   <si>
@@ -938,6 +938,15 @@
   </si>
   <si>
     <t>EA機頭G8K,011262_Z1200,55A22,C</t>
+  </si>
+  <si>
+    <t>630000355</t>
+  </si>
+  <si>
+    <t>080100145601</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,0045</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1090,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1113,52 +1122,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1690,7 +1699,7 @@
         <v>46160</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
@@ -1716,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -1725,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3">
         <v>46064</v>
@@ -1766,31 +1775,31 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
         <v>44</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
       </c>
       <c r="G14" s="3">
         <v>46064</v>
       </c>
       <c r="H14" s="3">
-        <v>46134</v>
+        <v>46240</v>
       </c>
       <c r="I14" s="3">
-        <v>46139</v>
+        <v>46245</v>
       </c>
       <c r="J14" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1816,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -1825,22 +1834,22 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3">
         <v>46064</v>
       </c>
       <c r="H15" s="3">
-        <v>46127</v>
+        <v>46240</v>
       </c>
       <c r="I15" s="3">
-        <v>46134</v>
+        <v>46245</v>
       </c>
       <c r="J15" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
@@ -1866,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -1875,22 +1884,22 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G16" s="3">
         <v>46064</v>
       </c>
       <c r="H16" s="3">
-        <v>46240</v>
+        <v>46234</v>
       </c>
       <c r="I16" s="3">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="J16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1916,31 +1925,31 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>42</v>
-      </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3">
         <v>46064</v>
       </c>
       <c r="H17" s="3">
-        <v>46240</v>
+        <v>46234</v>
       </c>
       <c r="I17" s="3">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="J17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -1966,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1975,22 +1984,22 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3">
         <v>46064</v>
       </c>
       <c r="H18" s="3">
-        <v>46234</v>
+        <v>46146</v>
       </c>
       <c r="I18" s="3">
-        <v>46239</v>
+        <v>46149</v>
       </c>
       <c r="J18" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -2016,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -2025,22 +2034,22 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G19" s="3">
         <v>46064</v>
       </c>
       <c r="H19" s="3">
-        <v>46234</v>
+        <v>46174</v>
       </c>
       <c r="I19" s="3">
-        <v>46239</v>
+        <v>46177</v>
       </c>
       <c r="J19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -2066,31 +2075,31 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="2">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>55</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
       </c>
       <c r="G20" s="3">
         <v>46064</v>
       </c>
       <c r="H20" s="3">
-        <v>46146</v>
+        <v>46238</v>
       </c>
       <c r="I20" s="3">
-        <v>46149</v>
+        <v>46241</v>
       </c>
       <c r="J20" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -2116,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -2125,22 +2134,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" t="s">
         <v>55</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
       </c>
       <c r="G21" s="3">
         <v>46064</v>
       </c>
       <c r="H21" s="3">
-        <v>46174</v>
+        <v>46297</v>
       </c>
       <c r="I21" s="3">
-        <v>46177</v>
+        <v>46302</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
@@ -2166,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2175,22 +2184,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G22" s="3">
         <v>46064</v>
       </c>
       <c r="H22" s="3">
-        <v>46238</v>
+        <v>46168</v>
       </c>
       <c r="I22" s="3">
-        <v>46241</v>
+        <v>46171</v>
       </c>
       <c r="J22" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -2216,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -2225,22 +2234,22 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G23" s="3">
         <v>46064</v>
       </c>
       <c r="H23" s="3">
-        <v>46297</v>
+        <v>46232</v>
       </c>
       <c r="I23" s="3">
-        <v>46302</v>
+        <v>46237</v>
       </c>
       <c r="J23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
@@ -2266,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -2275,22 +2284,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G24" s="3">
         <v>46064</v>
       </c>
       <c r="H24" s="3">
-        <v>46168</v>
+        <v>46289</v>
       </c>
       <c r="I24" s="3">
-        <v>46171</v>
+        <v>46296</v>
       </c>
       <c r="J24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -2316,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2325,22 +2334,22 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G25" s="3">
-        <v>46064</v>
+        <v>46090</v>
       </c>
       <c r="H25" s="3">
-        <v>46232</v>
+        <v>46301</v>
       </c>
       <c r="I25" s="3">
-        <v>46237</v>
+        <v>46307</v>
       </c>
       <c r="J25" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
@@ -2366,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2375,22 +2384,22 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G26" s="3">
         <v>46064</v>
       </c>
       <c r="H26" s="3">
-        <v>46289</v>
+        <v>46301</v>
       </c>
       <c r="I26" s="3">
-        <v>46296</v>
+        <v>46307</v>
       </c>
       <c r="J26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -2416,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2425,22 +2434,22 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G27" s="3">
-        <v>46090</v>
+        <v>46064</v>
       </c>
       <c r="H27" s="3">
-        <v>46301</v>
+        <v>46267</v>
       </c>
       <c r="I27" s="3">
-        <v>46307</v>
+        <v>46272</v>
       </c>
       <c r="J27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -2466,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2475,22 +2484,22 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G28" s="3">
         <v>46064</v>
       </c>
       <c r="H28" s="3">
-        <v>46301</v>
+        <v>46267</v>
       </c>
       <c r="I28" s="3">
-        <v>46307</v>
+        <v>46272</v>
       </c>
       <c r="J28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -2516,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2525,28 +2534,28 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="G29" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H29" s="3">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="I29" s="3">
-        <v>46272</v>
+        <v>46107</v>
       </c>
       <c r="J29" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2566,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2575,28 +2584,28 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G30" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H30" s="3">
-        <v>46267</v>
+        <v>46162</v>
       </c>
       <c r="I30" s="3">
-        <v>46272</v>
+        <v>46164</v>
       </c>
       <c r="J30" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M30" t="s">
         <v>6</v>
@@ -2616,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2625,22 +2634,22 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="G31" s="3">
         <v>46076</v>
       </c>
       <c r="H31" s="3">
-        <v>46104</v>
+        <v>46162</v>
       </c>
       <c r="I31" s="3">
-        <v>46107</v>
+        <v>46164</v>
       </c>
       <c r="J31" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -2666,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2675,22 +2684,22 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G32" s="3">
         <v>46076</v>
       </c>
       <c r="H32" s="3">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="I32" s="3">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="J32" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -2716,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2725,22 +2734,22 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G33" s="3">
         <v>46076</v>
       </c>
       <c r="H33" s="3">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="I33" s="3">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="J33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -2766,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2775,22 +2784,22 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="G34" s="3">
         <v>46076</v>
       </c>
       <c r="H34" s="3">
-        <v>46156</v>
+        <v>46212</v>
       </c>
       <c r="I34" s="3">
-        <v>46161</v>
+        <v>46216</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
@@ -2816,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2825,22 +2834,22 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F35" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="G35" s="3">
         <v>46076</v>
       </c>
       <c r="H35" s="3">
-        <v>46156</v>
+        <v>46212</v>
       </c>
       <c r="I35" s="3">
-        <v>46161</v>
+        <v>46216</v>
       </c>
       <c r="J35" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
@@ -2866,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -2875,22 +2884,22 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G36" s="3">
         <v>46076</v>
       </c>
       <c r="H36" s="3">
-        <v>46212</v>
+        <v>46206</v>
       </c>
       <c r="I36" s="3">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="J36" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
@@ -2916,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -2925,22 +2934,22 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G37" s="3">
         <v>46076</v>
       </c>
       <c r="H37" s="3">
-        <v>46212</v>
+        <v>46206</v>
       </c>
       <c r="I37" s="3">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="J37" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
@@ -2966,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -2975,22 +2984,22 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="G38" s="3">
         <v>46076</v>
       </c>
       <c r="H38" s="3">
-        <v>46206</v>
+        <v>46251</v>
       </c>
       <c r="I38" s="3">
-        <v>46211</v>
+        <v>46253</v>
       </c>
       <c r="J38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
@@ -3016,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3025,22 +3034,22 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F39" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="G39" s="3">
         <v>46076</v>
       </c>
       <c r="H39" s="3">
-        <v>46206</v>
+        <v>46251</v>
       </c>
       <c r="I39" s="3">
-        <v>46211</v>
+        <v>46253</v>
       </c>
       <c r="J39" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
@@ -3066,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3075,22 +3084,22 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G40" s="3">
         <v>46076</v>
       </c>
       <c r="H40" s="3">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="I40" s="3">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="J40" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
@@ -3116,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3125,22 +3134,22 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F41" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G41" s="3">
         <v>46076</v>
       </c>
       <c r="H41" s="3">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="I41" s="3">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="J41" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
@@ -3166,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3175,22 +3184,22 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G42" s="3">
         <v>46076</v>
       </c>
       <c r="H42" s="3">
-        <v>46245</v>
+        <v>46108</v>
       </c>
       <c r="I42" s="3">
-        <v>46248</v>
+        <v>46113</v>
       </c>
       <c r="J42" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
@@ -3216,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3225,28 +3234,28 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F43" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="G43" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H43" s="3">
-        <v>46245</v>
+        <v>46155</v>
       </c>
       <c r="I43" s="3">
-        <v>46248</v>
+        <v>46160</v>
       </c>
       <c r="J43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3266,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3275,28 +3284,28 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F44" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G44" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H44" s="3">
-        <v>46108</v>
+        <v>46147</v>
       </c>
       <c r="I44" s="3">
-        <v>46113</v>
+        <v>46150</v>
       </c>
       <c r="J44" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3316,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3325,28 +3334,28 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F45" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G45" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="H45" s="3">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="I45" s="3">
-        <v>46160</v>
+        <v>46171</v>
       </c>
       <c r="J45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3366,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3375,28 +3384,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F46" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="G46" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="H46" s="3">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="I46" s="3">
-        <v>46150</v>
+        <v>46171</v>
       </c>
       <c r="J46" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3416,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3425,28 +3434,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="H47" s="3">
-        <v>46148</v>
+        <v>46135</v>
       </c>
       <c r="I47" s="3">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="J47" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3466,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3475,28 +3484,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="G48" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H48" s="3">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="I48" s="3">
         <v>46171</v>
       </c>
       <c r="J48" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3516,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3525,28 +3534,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F49" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G49" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="H49" s="3">
-        <v>46135</v>
+        <v>46112</v>
       </c>
       <c r="I49" s="3">
-        <v>46157</v>
+        <v>46125</v>
       </c>
       <c r="J49" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3566,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3575,10 +3584,10 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G50" s="3">
         <v>46086</v>
@@ -3587,10 +3596,10 @@
         <v>46167</v>
       </c>
       <c r="I50" s="3">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="J50" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
@@ -3616,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3625,22 +3634,22 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G51" s="3">
         <v>46086</v>
       </c>
       <c r="H51" s="3">
-        <v>46112</v>
+        <v>46213</v>
       </c>
       <c r="I51" s="3">
-        <v>46125</v>
+        <v>46217</v>
       </c>
       <c r="J51" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
@@ -3666,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3675,22 +3684,22 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F52" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G52" s="3">
         <v>46086</v>
       </c>
       <c r="H52" s="3">
-        <v>46167</v>
+        <v>46191</v>
       </c>
       <c r="I52" s="3">
-        <v>46185</v>
+        <v>46210</v>
       </c>
       <c r="J52" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
@@ -3716,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -3725,25 +3734,25 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F53" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G53" s="3">
         <v>46086</v>
       </c>
       <c r="H53" s="3">
-        <v>46213</v>
+        <v>46106</v>
       </c>
       <c r="I53" s="3">
-        <v>46217</v>
+        <v>46114</v>
       </c>
       <c r="J53" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="K53" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L53" s="3">
         <v>46086</v>
@@ -3766,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3775,25 +3784,25 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F54" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G54" s="3">
         <v>46086</v>
       </c>
       <c r="H54" s="3">
-        <v>46191</v>
+        <v>46097</v>
       </c>
       <c r="I54" s="3">
-        <v>46210</v>
+        <v>46101</v>
       </c>
       <c r="J54" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="K54" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L54" s="3">
         <v>46086</v>
@@ -3816,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -3825,25 +3834,25 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F55" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G55" s="3">
         <v>46086</v>
       </c>
       <c r="H55" s="3">
-        <v>46106</v>
+        <v>46153</v>
       </c>
       <c r="I55" s="3">
-        <v>46114</v>
+        <v>46171</v>
       </c>
       <c r="J55" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="K55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L55" s="3">
         <v>46086</v>
@@ -3866,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -3875,28 +3884,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F56" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G56" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H56" s="3">
-        <v>46097</v>
+        <v>46170</v>
       </c>
       <c r="I56" s="3">
-        <v>46101</v>
+        <v>46175</v>
       </c>
       <c r="J56" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K56" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L56" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -3916,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -3925,28 +3934,28 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F57" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G57" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H57" s="3">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="I57" s="3">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="J57" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L57" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -3966,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -3975,25 +3984,25 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F58" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G58" s="3">
         <v>46090</v>
       </c>
       <c r="H58" s="3">
-        <v>46170</v>
+        <v>46206</v>
       </c>
       <c r="I58" s="3">
-        <v>46175</v>
+        <v>46210</v>
       </c>
       <c r="J58" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="K58" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L58" s="3">
         <v>46090</v>
@@ -4016,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4025,25 +4034,25 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F59" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G59" s="3">
         <v>46090</v>
       </c>
       <c r="H59" s="3">
-        <v>46162</v>
+        <v>46202</v>
       </c>
       <c r="I59" s="3">
-        <v>46167</v>
+        <v>46205</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="K59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L59" s="3">
         <v>46090</v>
@@ -4066,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4075,28 +4084,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F60" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G60" s="3">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="H60" s="3">
-        <v>46206</v>
+        <v>46105</v>
       </c>
       <c r="I60" s="3">
-        <v>46210</v>
+        <v>46107</v>
       </c>
       <c r="J60" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="K60" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4116,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4125,28 +4134,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F61" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G61" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="H61" s="3">
-        <v>46202</v>
+        <v>46092</v>
       </c>
       <c r="I61" s="3">
-        <v>46205</v>
+        <v>46094</v>
       </c>
       <c r="J61" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K61" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4166,37 +4175,37 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
+        <v>148</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
         <v>142</v>
       </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>143</v>
       </c>
-      <c r="F62" t="s">
-        <v>144</v>
-      </c>
       <c r="G62" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="H62" s="3">
-        <v>46105</v>
+        <v>46167</v>
       </c>
       <c r="I62" s="3">
-        <v>46107</v>
+        <v>46169</v>
       </c>
       <c r="J62" t="s">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4216,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4225,28 +4234,28 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F63" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G63" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="H63" s="3">
-        <v>46092</v>
+        <v>46167</v>
       </c>
       <c r="I63" s="3">
-        <v>46094</v>
+        <v>46169</v>
       </c>
       <c r="J63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4266,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4275,10 +4284,10 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" t="s">
         <v>143</v>
-      </c>
-      <c r="F64" t="s">
-        <v>144</v>
       </c>
       <c r="G64" s="3">
         <v>46093</v>
@@ -4290,7 +4299,7 @@
         <v>46169</v>
       </c>
       <c r="J64" t="s">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
@@ -4316,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4325,22 +4334,22 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F65" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G65" s="3">
         <v>46093</v>
       </c>
       <c r="H65" s="3">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="I65" s="3">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="J65" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4366,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4375,22 +4384,22 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F66" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G66" s="3">
         <v>46093</v>
       </c>
       <c r="H66" s="3">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="I66" s="3">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="J66" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
@@ -4416,19 +4425,19 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
+        <v>156</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="2">
-        <v>1</v>
-      </c>
-      <c r="D67" s="2">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>154</v>
-      </c>
-      <c r="F67" t="s">
-        <v>155</v>
       </c>
       <c r="G67" s="3">
         <v>46093</v>
@@ -4440,7 +4449,7 @@
         <v>46163</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
@@ -4466,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4475,10 +4484,10 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F68" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G68" s="3">
         <v>46093</v>
@@ -4487,10 +4496,10 @@
         <v>46161</v>
       </c>
       <c r="I68" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="J68" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4516,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4525,10 +4534,10 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F69" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G69" s="3">
         <v>46093</v>
@@ -4537,10 +4546,10 @@
         <v>46161</v>
       </c>
       <c r="I69" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="J69" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4566,19 +4575,19 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
         <v>158</v>
       </c>
-      <c r="C70" s="2">
-        <v>1</v>
-      </c>
-      <c r="D70" s="2">
-        <v>0</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>159</v>
-      </c>
-      <c r="F70" t="s">
-        <v>160</v>
       </c>
       <c r="G70" s="3">
         <v>46093</v>
@@ -4590,7 +4599,7 @@
         <v>46164</v>
       </c>
       <c r="J70" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4616,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4625,22 +4634,22 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F71" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G71" s="3">
         <v>46093</v>
       </c>
       <c r="H71" s="3">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="I71" s="3">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="J71" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
@@ -4666,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4675,28 +4684,28 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F72" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G72" s="3">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H72" s="3">
-        <v>46161</v>
+        <v>46146</v>
       </c>
       <c r="I72" s="3">
-        <v>46164</v>
+        <v>46148</v>
       </c>
       <c r="J72" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="M72" t="s">
         <v>6</v>
@@ -4716,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4725,28 +4734,28 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="F73" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="G73" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="H73" s="3">
-        <v>46155</v>
+        <v>46219</v>
       </c>
       <c r="I73" s="3">
-        <v>46160</v>
+        <v>46223</v>
       </c>
       <c r="J73" t="s">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -4766,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4775,28 +4784,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="F74" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G74" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="H74" s="3">
-        <v>46155</v>
+        <v>46212</v>
       </c>
       <c r="I74" s="3">
-        <v>46160</v>
+        <v>46218</v>
       </c>
       <c r="J74" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -4816,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -4825,28 +4834,28 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F75" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G75" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="H75" s="3">
-        <v>46146</v>
+        <v>46136</v>
       </c>
       <c r="I75" s="3">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="J75" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -4866,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4875,28 +4884,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F76" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="G76" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H76" s="3">
-        <v>46219</v>
+        <v>46227</v>
       </c>
       <c r="I76" s="3">
-        <v>46223</v>
+        <v>46231</v>
       </c>
       <c r="J76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K76" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L76" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -4916,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -4925,28 +4934,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="G77" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H77" s="3">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="I77" s="3">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="J77" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K77" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L77" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -4966,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -4975,28 +4984,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F78" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G78" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H78" s="3">
-        <v>46136</v>
+        <v>46205</v>
       </c>
       <c r="I78" s="3">
-        <v>46141</v>
+        <v>46210</v>
       </c>
       <c r="J78" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="K78" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L78" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5016,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5025,25 +5034,25 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F79" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G79" s="3">
         <v>46106</v>
       </c>
       <c r="H79" s="3">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="I79" s="3">
-        <v>46231</v>
+        <v>46226</v>
       </c>
       <c r="J79" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L79" s="3">
         <v>46106</v>
@@ -5066,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5075,25 +5084,25 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="F80" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="G80" s="3">
         <v>46106</v>
       </c>
       <c r="H80" s="3">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="I80" s="3">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="J80" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K80" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L80" s="3">
         <v>46106</v>
@@ -5116,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5125,28 +5134,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F81" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G81" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H81" s="3">
-        <v>46205</v>
+        <v>46168</v>
       </c>
       <c r="I81" s="3">
-        <v>46210</v>
+        <v>46170</v>
       </c>
       <c r="J81" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K81" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5166,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5175,28 +5184,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F82" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G82" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H82" s="3">
-        <v>46225</v>
+        <v>46168</v>
       </c>
       <c r="I82" s="3">
-        <v>46226</v>
+        <v>46170</v>
       </c>
       <c r="J82" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K82" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5216,37 +5225,37 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
+        <v>190</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
+        <v>187</v>
+      </c>
+      <c r="F83" t="s">
         <v>188</v>
       </c>
-      <c r="C83" s="2">
-        <v>1</v>
-      </c>
-      <c r="D83" s="2">
-        <v>0</v>
-      </c>
-      <c r="E83" t="s">
-        <v>140</v>
-      </c>
-      <c r="F83" t="s">
-        <v>141</v>
-      </c>
       <c r="G83" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H83" s="3">
-        <v>46219</v>
+        <v>46168</v>
       </c>
       <c r="I83" s="3">
-        <v>46224</v>
+        <v>46170</v>
       </c>
       <c r="J83" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K83" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5266,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5275,28 +5284,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G84" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="H84" s="3">
-        <v>46136</v>
+        <v>46161</v>
       </c>
       <c r="I84" s="3">
-        <v>46140</v>
+        <v>46167</v>
       </c>
       <c r="J84" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K84" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5316,31 +5325,31 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
+        <v>194</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="2">
-        <v>1</v>
-      </c>
-      <c r="D85" s="2">
-        <v>0</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>193</v>
-      </c>
-      <c r="F85" t="s">
-        <v>194</v>
       </c>
       <c r="G85" s="3">
         <v>46113</v>
       </c>
       <c r="H85" s="3">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="I85" s="3">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="J85" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
@@ -5375,22 +5384,22 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
+        <v>192</v>
+      </c>
+      <c r="F86" t="s">
         <v>193</v>
-      </c>
-      <c r="F86" t="s">
-        <v>194</v>
       </c>
       <c r="G86" s="3">
         <v>46113</v>
       </c>
       <c r="H86" s="3">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="I86" s="3">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="J86" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
@@ -5425,22 +5434,22 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F87" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G87" s="3">
         <v>46113</v>
       </c>
       <c r="H87" s="3">
-        <v>46168</v>
+        <v>46232</v>
       </c>
       <c r="I87" s="3">
-        <v>46170</v>
+        <v>46234</v>
       </c>
       <c r="J87" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
@@ -5475,22 +5484,22 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F88" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G88" s="3">
         <v>46113</v>
       </c>
       <c r="H88" s="3">
-        <v>46161</v>
+        <v>46232</v>
       </c>
       <c r="I88" s="3">
-        <v>46167</v>
+        <v>46234</v>
       </c>
       <c r="J88" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
@@ -5516,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5525,22 +5534,22 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F89" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G89" s="3">
         <v>46113</v>
       </c>
       <c r="H89" s="3">
-        <v>46161</v>
+        <v>46225</v>
       </c>
       <c r="I89" s="3">
-        <v>46167</v>
+        <v>46231</v>
       </c>
       <c r="J89" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
@@ -5566,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5575,22 +5584,22 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F90" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G90" s="3">
         <v>46113</v>
       </c>
       <c r="H90" s="3">
-        <v>46161</v>
+        <v>46225</v>
       </c>
       <c r="I90" s="3">
-        <v>46167</v>
+        <v>46231</v>
       </c>
       <c r="J90" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
@@ -5616,19 +5625,19 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
+        <v>200</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
+        <v>201</v>
+      </c>
+      <c r="F91" t="s">
         <v>202</v>
-      </c>
-      <c r="C91" s="2">
-        <v>1</v>
-      </c>
-      <c r="D91" s="2">
-        <v>0</v>
-      </c>
-      <c r="E91" t="s">
-        <v>193</v>
-      </c>
-      <c r="F91" t="s">
-        <v>194</v>
       </c>
       <c r="G91" s="3">
         <v>46113</v>
@@ -5637,10 +5646,10 @@
         <v>46232</v>
       </c>
       <c r="I91" s="3">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="J91" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
@@ -5675,22 +5684,22 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F92" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G92" s="3">
         <v>46113</v>
       </c>
       <c r="H92" s="3">
-        <v>46232</v>
+        <v>46224</v>
       </c>
       <c r="I92" s="3">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="J92" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
@@ -5716,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5725,28 +5734,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="F93" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G93" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H93" s="3">
-        <v>46225</v>
+        <v>46149</v>
       </c>
       <c r="I93" s="3">
-        <v>46231</v>
+        <v>46153</v>
       </c>
       <c r="J93" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5766,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5775,28 +5784,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="F94" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G94" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H94" s="3">
-        <v>46225</v>
+        <v>46149</v>
       </c>
       <c r="I94" s="3">
-        <v>46231</v>
+        <v>46153</v>
       </c>
       <c r="J94" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -5816,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -5825,28 +5834,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="F95" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="G95" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H95" s="3">
-        <v>46232</v>
+        <v>46141</v>
       </c>
       <c r="I95" s="3">
-        <v>46237</v>
+        <v>46148</v>
       </c>
       <c r="J95" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -5866,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -5875,28 +5884,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="F96" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G96" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H96" s="3">
-        <v>46224</v>
+        <v>46141</v>
       </c>
       <c r="I96" s="3">
-        <v>46227</v>
+        <v>46148</v>
       </c>
       <c r="J96" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -5934,13 +5943,13 @@
         <v>46114</v>
       </c>
       <c r="H97" s="3">
-        <v>46149</v>
+        <v>46160</v>
       </c>
       <c r="I97" s="3">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="J97" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
@@ -5981,22 +5990,22 @@
         <v>213</v>
       </c>
       <c r="G98" s="3">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="H98" s="3">
-        <v>46149</v>
+        <v>46160</v>
       </c>
       <c r="I98" s="3">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="J98" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6025,28 +6034,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="F99" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="G99" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H99" s="3">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="I99" s="3">
-        <v>46148</v>
+        <v>46164</v>
       </c>
       <c r="J99" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6066,37 +6075,37 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
+        <v>218</v>
+      </c>
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0</v>
+      </c>
+      <c r="E100" t="s">
         <v>216</v>
       </c>
-      <c r="C100" s="2">
-        <v>1</v>
-      </c>
-      <c r="D100" s="2">
-        <v>0</v>
-      </c>
-      <c r="E100" t="s">
-        <v>173</v>
-      </c>
       <c r="F100" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="G100" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H100" s="3">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="I100" s="3">
-        <v>46148</v>
+        <v>46164</v>
       </c>
       <c r="J100" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6116,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6125,19 +6134,19 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F101" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G101" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H101" s="3">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="I101" s="3">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="J101" t="s">
         <v>20</v>
@@ -6146,7 +6155,7 @@
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6166,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6175,13 +6184,13 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F102" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G102" s="3">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="H102" s="3">
         <v>46134</v>
@@ -6190,13 +6199,13 @@
         <v>46136</v>
       </c>
       <c r="J102" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6216,7 +6225,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6225,28 +6234,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F103" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G103" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="H103" s="3">
-        <v>46160</v>
+        <v>46147</v>
       </c>
       <c r="I103" s="3">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="J103" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6266,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6275,28 +6284,28 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G104" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H104" s="3">
-        <v>46162</v>
+        <v>46136</v>
       </c>
       <c r="I104" s="3">
-        <v>46164</v>
+        <v>46140</v>
       </c>
       <c r="J104" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
       </c>
       <c r="L104" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6316,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6325,28 +6334,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G105" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H105" s="3">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="I105" s="3">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="J105" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6366,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6375,28 +6384,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F106" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G106" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H106" s="3">
-        <v>46153</v>
+        <v>46140</v>
       </c>
       <c r="I106" s="3">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="J106" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6416,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6425,28 +6434,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F107" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G107" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="H107" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="I107" s="3">
-        <v>46136</v>
+        <v>46147</v>
       </c>
       <c r="J107" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6466,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6475,28 +6484,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F108" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="G108" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="H108" s="3">
-        <v>46147</v>
+        <v>46132</v>
       </c>
       <c r="I108" s="3">
-        <v>46150</v>
+        <v>46135</v>
       </c>
       <c r="J108" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6516,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6525,28 +6534,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>238</v>
+        <v>183</v>
       </c>
       <c r="F109" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="G109" s="3">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="H109" s="3">
-        <v>46136</v>
+        <v>46178</v>
       </c>
       <c r="I109" s="3">
-        <v>46140</v>
+        <v>46181</v>
       </c>
       <c r="J109" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6566,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6575,28 +6584,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>241</v>
+        <v>74</v>
       </c>
       <c r="F110" t="s">
-        <v>242</v>
+        <v>75</v>
       </c>
       <c r="G110" s="3">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="H110" s="3">
-        <v>46150</v>
+        <v>46174</v>
       </c>
       <c r="I110" s="3">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="J110" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6616,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6625,28 +6634,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F111" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G111" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H111" s="3">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="I111" s="3">
-        <v>46147</v>
+        <v>46171</v>
       </c>
       <c r="J111" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6666,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6681,22 +6690,22 @@
         <v>248</v>
       </c>
       <c r="G112" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="H112" s="3">
-        <v>46142</v>
+        <v>46170</v>
       </c>
       <c r="I112" s="3">
-        <v>46147</v>
+        <v>46171</v>
       </c>
       <c r="J112" t="s">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -6725,28 +6734,28 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F113" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G113" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="H113" s="3">
-        <v>46132</v>
+        <v>46170</v>
       </c>
       <c r="I113" s="3">
-        <v>46135</v>
+        <v>46171</v>
       </c>
       <c r="J113" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -6766,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -6775,28 +6784,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="F114" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="G114" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H114" s="3">
-        <v>46178</v>
+        <v>46133</v>
       </c>
       <c r="I114" s="3">
-        <v>46181</v>
+        <v>46136</v>
       </c>
       <c r="J114" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -6816,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -6825,28 +6834,28 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F115" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G115" s="3">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H115" s="3">
-        <v>46174</v>
+        <v>46134</v>
       </c>
       <c r="I115" s="3">
-        <v>46177</v>
+        <v>46139</v>
       </c>
       <c r="J115" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -6866,37 +6875,37 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
+        <v>254</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" t="s">
         <v>255</v>
       </c>
-      <c r="C116" s="2">
-        <v>1</v>
-      </c>
-      <c r="D116" s="2">
-        <v>0</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>256</v>
       </c>
-      <c r="F116" t="s">
-        <v>257</v>
-      </c>
       <c r="G116" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H116" s="3">
-        <v>46170</v>
+        <v>46135</v>
       </c>
       <c r="I116" s="3">
-        <v>46171</v>
+        <v>46140</v>
       </c>
       <c r="J116" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -6916,37 +6925,37 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
+        <v>257</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2">
+        <v>0</v>
+      </c>
+      <c r="E117" t="s">
         <v>258</v>
       </c>
-      <c r="C117" s="2">
-        <v>1</v>
-      </c>
-      <c r="D117" s="2">
-        <v>0</v>
-      </c>
-      <c r="E117" t="s">
-        <v>256</v>
-      </c>
       <c r="F117" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G117" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H117" s="3">
-        <v>46170</v>
+        <v>46139</v>
       </c>
       <c r="I117" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J117" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K117" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L117" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
@@ -6966,37 +6975,37 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
+        <v>260</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s">
+        <v>258</v>
+      </c>
+      <c r="F118" t="s">
         <v>259</v>
       </c>
-      <c r="C118" s="2">
-        <v>1</v>
-      </c>
-      <c r="D118" s="2">
-        <v>0</v>
-      </c>
-      <c r="E118" t="s">
-        <v>256</v>
-      </c>
-      <c r="F118" t="s">
-        <v>257</v>
-      </c>
       <c r="G118" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H118" s="3">
-        <v>46170</v>
+        <v>46139</v>
       </c>
       <c r="I118" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J118" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K118" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L118" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7016,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7025,28 +7034,28 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F119" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="G119" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H119" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="I119" s="3">
+        <v>46142</v>
+      </c>
+      <c r="J119" t="s">
+        <v>46</v>
+      </c>
+      <c r="K119" t="s">
+        <v>120</v>
+      </c>
+      <c r="L119" s="3">
         <v>46136</v>
-      </c>
-      <c r="J119" t="s">
-        <v>24</v>
-      </c>
-      <c r="K119" t="s">
-        <v>5</v>
-      </c>
-      <c r="L119" s="3">
-        <v>46133</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7075,28 +7084,28 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>87</v>
+        <v>258</v>
       </c>
       <c r="F120" t="s">
-        <v>88</v>
+        <v>259</v>
       </c>
       <c r="G120" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="H120" s="3">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="I120" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="J120" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K120" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L120" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
@@ -7131,22 +7140,22 @@
         <v>265</v>
       </c>
       <c r="G121" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="H121" s="3">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="I121" s="3">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="J121" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K121" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L121" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7175,25 +7184,25 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F122" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G122" s="3">
         <v>46136</v>
       </c>
       <c r="H122" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I122" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J122" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K122" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L122" s="3">
         <v>46136</v>
@@ -7216,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7225,25 +7234,25 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F123" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G123" s="3">
         <v>46136</v>
       </c>
       <c r="H123" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I123" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J123" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K123" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L123" s="3">
         <v>46136</v>
@@ -7266,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7275,25 +7284,25 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F124" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G124" s="3">
         <v>46136</v>
       </c>
       <c r="H124" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I124" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J124" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K124" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L124" s="3">
         <v>46136</v>
@@ -7316,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7325,25 +7334,25 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>267</v>
+        <v>86</v>
       </c>
       <c r="F125" t="s">
-        <v>268</v>
+        <v>87</v>
       </c>
       <c r="G125" s="3">
         <v>46136</v>
       </c>
       <c r="H125" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I125" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J125" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K125" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L125" s="3">
         <v>46136</v>
@@ -7366,37 +7375,37 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
+        <v>270</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
+        <v>271</v>
+      </c>
+      <c r="F126" t="s">
         <v>272</v>
       </c>
-      <c r="C126" s="2">
-        <v>1</v>
-      </c>
-      <c r="D126" s="2">
-        <v>0</v>
-      </c>
-      <c r="E126" t="s">
-        <v>273</v>
-      </c>
-      <c r="F126" t="s">
-        <v>274</v>
-      </c>
       <c r="G126" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H126" s="3">
-        <v>46136</v>
+        <v>46170</v>
       </c>
       <c r="I126" s="3">
-        <v>46141</v>
+        <v>46174</v>
       </c>
       <c r="J126" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="K126" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7416,37 +7425,37 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
+        <v>273</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" t="s">
+        <v>274</v>
+      </c>
+      <c r="F127" t="s">
         <v>275</v>
       </c>
-      <c r="C127" s="2">
-        <v>1</v>
-      </c>
-      <c r="D127" s="2">
-        <v>0</v>
-      </c>
-      <c r="E127" t="s">
-        <v>273</v>
-      </c>
-      <c r="F127" t="s">
-        <v>274</v>
-      </c>
       <c r="G127" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H127" s="3">
-        <v>46136</v>
+        <v>46164</v>
       </c>
       <c r="I127" s="3">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="J127" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K127" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L127" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7475,28 +7484,28 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>273</v>
+        <v>50</v>
       </c>
       <c r="F128" t="s">
-        <v>274</v>
+        <v>51</v>
       </c>
       <c r="G128" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H128" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="I128" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="J128" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K128" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L128" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7525,28 +7534,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F129" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G129" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H129" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I129" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="J129" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K129" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L129" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7566,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7575,28 +7584,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="F130" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="G130" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H130" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I130" s="3">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="J130" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K130" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7616,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7625,28 +7634,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F131" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G131" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H131" s="3">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="I131" s="3">
-        <v>46174</v>
+        <v>46190</v>
       </c>
       <c r="J131" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -7666,37 +7675,37 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
+        <v>284</v>
+      </c>
+      <c r="C132" s="2">
+        <v>1</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0</v>
+      </c>
+      <c r="E132" t="s">
         <v>282</v>
       </c>
-      <c r="C132" s="2">
-        <v>1</v>
-      </c>
-      <c r="D132" s="2">
-        <v>0</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>283</v>
       </c>
-      <c r="F132" t="s">
-        <v>284</v>
-      </c>
       <c r="G132" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H132" s="3">
-        <v>46164</v>
+        <v>46183</v>
       </c>
       <c r="I132" s="3">
-        <v>46169</v>
+        <v>46190</v>
       </c>
       <c r="J132" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -7725,28 +7734,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="F133" t="s">
-        <v>47</v>
+        <v>287</v>
       </c>
       <c r="G133" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H133" s="3">
-        <v>46139</v>
+        <v>46176</v>
       </c>
       <c r="I133" s="3">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="J133" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -7763,40 +7772,40 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" t="s">
+        <v>0</v>
+      </c>
+      <c r="B134" t="s">
+        <v>288</v>
+      </c>
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s">
         <v>286</v>
       </c>
-      <c r="B134" t="s">
+      <c r="F134" t="s">
         <v>287</v>
       </c>
-      <c r="C134" s="2">
-        <v>1</v>
-      </c>
-      <c r="D134" s="2">
-        <v>0</v>
-      </c>
-      <c r="E134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F134" t="s">
-        <v>289</v>
-      </c>
       <c r="G134" s="3">
-        <v>46043</v>
+        <v>46140</v>
       </c>
       <c r="H134" s="3">
-        <v>46051</v>
+        <v>46176</v>
       </c>
       <c r="I134" s="3">
-        <v>46057</v>
+        <v>46182</v>
       </c>
       <c r="J134" t="s">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="K134" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46043</v>
+        <v>46140</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -7813,40 +7822,40 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" t="s">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="B135" t="s">
+        <v>289</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
+        <v>290</v>
+      </c>
+      <c r="F135" t="s">
         <v>291</v>
       </c>
-      <c r="C135" s="2">
-        <v>1</v>
-      </c>
-      <c r="D135" s="2">
-        <v>0</v>
-      </c>
-      <c r="E135" t="s">
-        <v>292</v>
-      </c>
-      <c r="F135" t="s">
-        <v>293</v>
-      </c>
       <c r="G135" s="3">
-        <v>46057</v>
+        <v>46140</v>
       </c>
       <c r="H135" s="3">
-        <v>46076</v>
+        <v>46140</v>
       </c>
       <c r="I135" s="3">
-        <v>46083</v>
+        <v>46147</v>
       </c>
       <c r="J135" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K135" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46057</v>
+        <v>46140</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -7863,40 +7872,40 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B136" t="s">
+        <v>293</v>
+      </c>
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0</v>
+      </c>
+      <c r="E136" t="s">
         <v>294</v>
       </c>
-      <c r="C136" s="2">
-        <v>1</v>
-      </c>
-      <c r="D136" s="2">
-        <v>0</v>
-      </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>295</v>
       </c>
-      <c r="F136" t="s">
+      <c r="G136" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H136" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I136" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J136" t="s">
+        <v>48</v>
+      </c>
+      <c r="K136" t="s">
         <v>296</v>
       </c>
-      <c r="G136" s="3">
-        <v>46113</v>
-      </c>
-      <c r="H136" s="3">
-        <v>46121</v>
-      </c>
-      <c r="I136" s="3">
-        <v>46122</v>
-      </c>
-      <c r="J136" t="s">
-        <v>37</v>
-      </c>
-      <c r="K136" t="s">
-        <v>290</v>
-      </c>
       <c r="L136" s="3">
-        <v>46113</v>
+        <v>46043</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -7913,7 +7922,7 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B137" t="s">
         <v>297</v>
@@ -7931,22 +7940,22 @@
         <v>299</v>
       </c>
       <c r="G137" s="3">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="H137" s="3">
-        <v>46148</v>
+        <v>46076</v>
       </c>
       <c r="I137" s="3">
-        <v>46148</v>
+        <v>46083</v>
       </c>
       <c r="J137" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="K137" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="L137" s="3">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -7963,7 +7972,7 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B138" t="s">
         <v>300</v>
@@ -7981,22 +7990,22 @@
         <v>302</v>
       </c>
       <c r="G138" s="3">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="H138" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="I138" s="3">
         <v>46148</v>
       </c>
       <c r="J138" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K138" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="L138" s="3">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8013,7 +8022,7 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B139" t="s">
         <v>303</v>
@@ -8031,22 +8040,22 @@
         <v>305</v>
       </c>
       <c r="G139" s="3">
-        <v>46127</v>
+        <v>46122</v>
       </c>
       <c r="H139" s="3">
-        <v>46132</v>
+        <v>46142</v>
       </c>
       <c r="I139" s="3">
-        <v>46136</v>
+        <v>46148</v>
       </c>
       <c r="J139" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K139" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="L139" s="3">
-        <v>46127</v>
+        <v>46122</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8063,7 +8072,7 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B140" t="s">
         <v>306</v>
@@ -8093,7 +8102,7 @@
         <v>37</v>
       </c>
       <c r="K140" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="L140" s="3">
         <v>46135</v>
@@ -8108,6 +8117,56 @@
         <v>8</v>
       </c>
       <c r="P140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141" t="s">
+        <v>292</v>
+      </c>
+      <c r="B141" t="s">
+        <v>309</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>310</v>
+      </c>
+      <c r="F141" t="s">
+        <v>311</v>
+      </c>
+      <c r="G141" s="3">
+        <v>46140</v>
+      </c>
+      <c r="H141" s="3">
+        <v>46140</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J141" t="s">
+        <v>48</v>
+      </c>
+      <c r="K141" t="s">
+        <v>296</v>
+      </c>
+      <c r="L141" s="3">
+        <v>46140</v>
+      </c>
+      <c r="M141" t="s">
+        <v>6</v>
+      </c>
+      <c r="N141" t="s">
+        <v>7</v>
+      </c>
+      <c r="O141" t="s">
+        <v>8</v>
+      </c>
+      <c r="P141" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -3849,7 +3849,7 @@
         <v>46171</v>
       </c>
       <c r="J55" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="K55" t="s">
         <v>120</v>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="339">
   <si>
     <t>ZP02</t>
   </si>
@@ -43,27 +43,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>200006418</t>
-  </si>
-  <si>
-    <t>080200255802</t>
-  </si>
-  <si>
-    <t>5A65E機頭D15K,032370_BBT40,CAW45</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006419</t>
-  </si>
-  <si>
-    <t>080100087604</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
-  </si>
-  <si>
     <t>200006445</t>
   </si>
   <si>
@@ -115,160 +94,586 @@
     <t>200006490</t>
   </si>
   <si>
-    <t>200006498</t>
-  </si>
-  <si>
-    <t>080200546702</t>
+    <t>200006500</t>
+  </si>
+  <si>
+    <t>080100092405</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006511</t>
+  </si>
+  <si>
+    <t>080200538802</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,55F23,C</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006512</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006513</t>
+  </si>
+  <si>
+    <t>200006514</t>
+  </si>
+  <si>
+    <t>200006516</t>
+  </si>
+  <si>
+    <t>080100116405</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BBT50,CW45</t>
+  </si>
+  <si>
+    <t>200006517</t>
+  </si>
+  <si>
+    <t>200006518</t>
+  </si>
+  <si>
+    <t>200006519</t>
+  </si>
+  <si>
+    <t>080200545001</t>
+  </si>
+  <si>
+    <t>H1370機頭G6K,011395_#50,55F23,C</t>
+  </si>
+  <si>
+    <t>200006520</t>
+  </si>
+  <si>
+    <t>200006521</t>
+  </si>
+  <si>
+    <t>200006522</t>
+  </si>
+  <si>
+    <t>200006533</t>
+  </si>
+  <si>
+    <t>080200546703</t>
   </si>
   <si>
     <t>MVP11機頭D15K,031859_#40,38F18,C,AT8</t>
   </si>
   <si>
+    <t>200006534</t>
+  </si>
+  <si>
+    <t>200006535</t>
+  </si>
+  <si>
+    <t>080100156608</t>
+  </si>
+  <si>
+    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006536</t>
+  </si>
+  <si>
+    <t>REL  PCNF DLV  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006537</t>
+  </si>
+  <si>
+    <t>200006538</t>
+  </si>
+  <si>
+    <t>200006539</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006540</t>
+  </si>
+  <si>
+    <t>200006541</t>
+  </si>
+  <si>
+    <t>200006542</t>
+  </si>
+  <si>
+    <t>200006543</t>
+  </si>
+  <si>
+    <t>200006544</t>
+  </si>
+  <si>
+    <t>200006554</t>
+  </si>
+  <si>
+    <t>080200037902</t>
+  </si>
+  <si>
+    <t>HSA機頭G6K,021563_1200,BBT50,55,045</t>
+  </si>
+  <si>
     <t>REL  PCNF PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>200006500</t>
-  </si>
-  <si>
-    <t>080100092405</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021177_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006504</t>
-  </si>
-  <si>
-    <t>080200545001</t>
-  </si>
-  <si>
-    <t>H1370機頭G6K,011395_#50,55F23,C</t>
-  </si>
-  <si>
-    <t>200006507</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006508</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006509</t>
-  </si>
-  <si>
-    <t>080100116405</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>200006510</t>
-  </si>
-  <si>
-    <t>200006511</t>
-  </si>
-  <si>
-    <t>080200538802</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,55F23,C</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006512</t>
-  </si>
-  <si>
-    <t>200006513</t>
-  </si>
-  <si>
-    <t>200006514</t>
-  </si>
-  <si>
-    <t>200006516</t>
-  </si>
-  <si>
-    <t>200006517</t>
-  </si>
-  <si>
-    <t>200006518</t>
-  </si>
-  <si>
-    <t>200006519</t>
-  </si>
-  <si>
-    <t>200006520</t>
-  </si>
-  <si>
-    <t>200006521</t>
-  </si>
-  <si>
-    <t>200006522</t>
-  </si>
-  <si>
-    <t>200006529</t>
-  </si>
-  <si>
-    <t>080200562402</t>
-  </si>
-  <si>
-    <t>MVP16機頭G8K,021487_#50,55F23,0</t>
-  </si>
-  <si>
-    <t>200006533</t>
-  </si>
-  <si>
-    <t>080200546703</t>
-  </si>
-  <si>
-    <t>200006534</t>
-  </si>
-  <si>
-    <t>200006535</t>
-  </si>
-  <si>
-    <t>080100156608</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006536</t>
-  </si>
-  <si>
-    <t>200006537</t>
-  </si>
-  <si>
-    <t>200006538</t>
-  </si>
-  <si>
-    <t>200006539</t>
-  </si>
-  <si>
-    <t>200006540</t>
-  </si>
-  <si>
-    <t>200006541</t>
-  </si>
-  <si>
-    <t>200006542</t>
-  </si>
-  <si>
-    <t>200006543</t>
-  </si>
-  <si>
-    <t>200006544</t>
-  </si>
-  <si>
-    <t>200006548</t>
+    <t>200006555</t>
+  </si>
+  <si>
+    <t>080100035602</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,0045</t>
+  </si>
+  <si>
+    <t>200006567</t>
+  </si>
+  <si>
+    <t>080300028606</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_1°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006568</t>
+  </si>
+  <si>
+    <t>200006569</t>
+  </si>
+  <si>
+    <t>080300030000</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,032731,G5K_1°-BT50-DIN-5K-C-F</t>
+  </si>
+  <si>
+    <t>200006573</t>
+  </si>
+  <si>
+    <t>080300024804</t>
+  </si>
+  <si>
+    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
+  </si>
+  <si>
+    <t>200006574</t>
+  </si>
+  <si>
+    <t>080200014702</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
+  </si>
+  <si>
+    <t>200006575</t>
+  </si>
+  <si>
+    <t>080300017908</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-0</t>
+  </si>
+  <si>
+    <t>200006576</t>
+  </si>
+  <si>
+    <t>080200408704</t>
+  </si>
+  <si>
+    <t>HMC機頭B10K,202488 _BBT50,F45</t>
+  </si>
+  <si>
+    <t>200006577</t>
+  </si>
+  <si>
+    <t>080100134803</t>
+  </si>
+  <si>
+    <t>B10K 主軸,021472_BBT50,F0CW45</t>
+  </si>
+  <si>
+    <t>200006578</t>
+  </si>
+  <si>
+    <t>080200020004</t>
+  </si>
+  <si>
+    <t>EA機頭HB10K,011050_Z1200,50FANUC,C45</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>200006579</t>
+  </si>
+  <si>
+    <t>080100021502</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006580</t>
+  </si>
+  <si>
+    <t>080300018208</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006585</t>
+  </si>
+  <si>
+    <t>080200033404</t>
+  </si>
+  <si>
+    <t>HSA機頭G6K,021563_780,BBT50,55,C45</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>200006586</t>
+  </si>
+  <si>
+    <t>080100036004</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,C045</t>
+  </si>
+  <si>
+    <t>200006587</t>
+  </si>
+  <si>
+    <t>080200548501</t>
+  </si>
+  <si>
+    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006588</t>
+  </si>
+  <si>
+    <t>080100094004</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006593</t>
+  </si>
+  <si>
+    <t>080200531201</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_A63,48F18,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006597</t>
+  </si>
+  <si>
+    <t>080200570000</t>
+  </si>
+  <si>
+    <t>5A95Q機頭BA24K,032918_A63,C</t>
+  </si>
+  <si>
+    <t>200006604</t>
+  </si>
+  <si>
+    <t>200006605</t>
+  </si>
+  <si>
+    <t>200006606</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006616</t>
+  </si>
+  <si>
+    <t>080200530800</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,48F23,0</t>
+  </si>
+  <si>
+    <t>REL  PCNF DLV  PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006617</t>
+  </si>
+  <si>
+    <t>200006618</t>
+  </si>
+  <si>
+    <t>200006622</t>
+  </si>
+  <si>
+    <t>080100050703</t>
+  </si>
+  <si>
+    <t>D20K 主軸,021608_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>200006623</t>
+  </si>
+  <si>
+    <t>200006624</t>
+  </si>
+  <si>
+    <t>200006634</t>
+  </si>
+  <si>
+    <t>200006635</t>
+  </si>
+  <si>
+    <t>080100090804</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006640</t>
+  </si>
+  <si>
+    <t>080200527500</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,38F18</t>
+  </si>
+  <si>
+    <t>200006642</t>
+  </si>
+  <si>
+    <t>200006643</t>
+  </si>
+  <si>
+    <t>080100113505</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CWDIN</t>
+  </si>
+  <si>
+    <t>200006644</t>
+  </si>
+  <si>
+    <t>080200557700</t>
+  </si>
+  <si>
+    <t>MVP-16機頭D15K,021451_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006645</t>
+  </si>
+  <si>
+    <t>200006647</t>
+  </si>
+  <si>
+    <t>080200530400</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,0</t>
+  </si>
+  <si>
+    <t>200006648</t>
+  </si>
+  <si>
+    <t>200006649</t>
+  </si>
+  <si>
+    <t>200006650</t>
+  </si>
+  <si>
+    <t>080100090006</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,0W45</t>
+  </si>
+  <si>
+    <t>200006651</t>
+  </si>
+  <si>
+    <t>200006652</t>
+  </si>
+  <si>
+    <t>200006653</t>
+  </si>
+  <si>
+    <t>200006654</t>
+  </si>
+  <si>
+    <t>200006655</t>
+  </si>
+  <si>
+    <t>200006656</t>
+  </si>
+  <si>
+    <t>200006657</t>
+  </si>
+  <si>
+    <t>080200286503</t>
+  </si>
+  <si>
+    <t>H2110機頭G6K,011026_BT50,42F25,CAWDI</t>
+  </si>
+  <si>
+    <t>200006658</t>
+  </si>
+  <si>
+    <t>080100113504</t>
+  </si>
+  <si>
+    <t>200006659</t>
+  </si>
+  <si>
+    <t>080200530500</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006660</t>
+  </si>
+  <si>
+    <t>200006661</t>
+  </si>
+  <si>
+    <t>200006662</t>
+  </si>
+  <si>
+    <t>200006666</t>
+  </si>
+  <si>
+    <t>080200532700</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,48F18</t>
+  </si>
+  <si>
+    <t>200006669</t>
+  </si>
+  <si>
+    <t>080200071201</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
+  </si>
+  <si>
+    <t>200006670</t>
+  </si>
+  <si>
+    <t>080200546201</t>
+  </si>
+  <si>
+    <t>MVP13機頭P12K,021677_#40,8YU-82,C</t>
+  </si>
+  <si>
+    <t>200006671</t>
+  </si>
+  <si>
+    <t>080200243400</t>
+  </si>
+  <si>
+    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>200006674</t>
+  </si>
+  <si>
+    <t>080100081204</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BBT40,8YU,CW45</t>
+  </si>
+  <si>
+    <t>200006675</t>
+  </si>
+  <si>
+    <t>080200244200</t>
+  </si>
+  <si>
+    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45I</t>
+  </si>
+  <si>
+    <t>200006676</t>
+  </si>
+  <si>
+    <t>080200235502</t>
+  </si>
+  <si>
+    <t>HEP機頭D12K,021573_780,BBT50,48,C45</t>
+  </si>
+  <si>
+    <t>200006677</t>
+  </si>
+  <si>
+    <t>080100045203</t>
+  </si>
+  <si>
+    <t>D12K 主軸,021274_BBT50,M50,C045</t>
+  </si>
+  <si>
+    <t>200006678</t>
+  </si>
+  <si>
+    <t>080200571500</t>
+  </si>
+  <si>
+    <t>L800機頭D15K,021616_#40,48F18,0</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF DLV  PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006681</t>
+  </si>
+  <si>
+    <t>200006682</t>
+  </si>
+  <si>
+    <t>200006683</t>
+  </si>
+  <si>
+    <t>080200070801</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>200006684</t>
+  </si>
+  <si>
+    <t>200006685</t>
+  </si>
+  <si>
+    <t>200006686</t>
+  </si>
+  <si>
+    <t>080100050702</t>
+  </si>
+  <si>
+    <t>200006687</t>
   </si>
   <si>
     <t>080200538402</t>
@@ -277,504 +682,6 @@
     <t>H1682機頭G6K,021314_#50,48F23,0</t>
   </si>
   <si>
-    <t>200006554</t>
-  </si>
-  <si>
-    <t>080200037902</t>
-  </si>
-  <si>
-    <t>HSA機頭G6K,021563_1200,BBT50,55,045</t>
-  </si>
-  <si>
-    <t>200006555</t>
-  </si>
-  <si>
-    <t>080100035602</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,0045</t>
-  </si>
-  <si>
-    <t>200006567</t>
-  </si>
-  <si>
-    <t>080300028606</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BBT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006568</t>
-  </si>
-  <si>
-    <t>200006569</t>
-  </si>
-  <si>
-    <t>080300030000</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,032731,G5K_1°-BT50-DIN-5K-C-F</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006573</t>
-  </si>
-  <si>
-    <t>080300024804</t>
-  </si>
-  <si>
-    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
-  </si>
-  <si>
-    <t>200006574</t>
-  </si>
-  <si>
-    <t>080200014702</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
-  </si>
-  <si>
-    <t>200006575</t>
-  </si>
-  <si>
-    <t>080300017908</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-0</t>
-  </si>
-  <si>
-    <t>200006576</t>
-  </si>
-  <si>
-    <t>080200408704</t>
-  </si>
-  <si>
-    <t>HMC機頭B10K,202488 _BBT50,F45</t>
-  </si>
-  <si>
-    <t>200006577</t>
-  </si>
-  <si>
-    <t>080100134803</t>
-  </si>
-  <si>
-    <t>B10K 主軸,021472_BBT50,F0CW45</t>
-  </si>
-  <si>
-    <t>200006578</t>
-  </si>
-  <si>
-    <t>080200020004</t>
-  </si>
-  <si>
-    <t>EA機頭HB10K,011050_Z1200,50FANUC,C45</t>
-  </si>
-  <si>
-    <t>LUMI</t>
-  </si>
-  <si>
-    <t>200006579</t>
-  </si>
-  <si>
-    <t>080100021502</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006580</t>
-  </si>
-  <si>
-    <t>080300018208</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006585</t>
-  </si>
-  <si>
-    <t>080200033404</t>
-  </si>
-  <si>
-    <t>HSA機頭G6K,021563_780,BBT50,55,C45</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>200006586</t>
-  </si>
-  <si>
-    <t>080100036004</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,C045</t>
-  </si>
-  <si>
-    <t>200006587</t>
-  </si>
-  <si>
-    <t>080200548501</t>
-  </si>
-  <si>
-    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006588</t>
-  </si>
-  <si>
-    <t>080100094004</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006593</t>
-  </si>
-  <si>
-    <t>080200531201</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_A63,48F18,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006597</t>
-  </si>
-  <si>
-    <t>080200570000</t>
-  </si>
-  <si>
-    <t>5A95Q機頭BA24K,032918_A63,C</t>
-  </si>
-  <si>
-    <t>200006604</t>
-  </si>
-  <si>
-    <t>200006605</t>
-  </si>
-  <si>
-    <t>200006606</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006616</t>
-  </si>
-  <si>
-    <t>080200530800</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,48F23,0</t>
-  </si>
-  <si>
-    <t>200006617</t>
-  </si>
-  <si>
-    <t>200006618</t>
-  </si>
-  <si>
-    <t>200006622</t>
-  </si>
-  <si>
-    <t>080100050703</t>
-  </si>
-  <si>
-    <t>D20K 主軸,021608_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>200006623</t>
-  </si>
-  <si>
-    <t>200006624</t>
-  </si>
-  <si>
-    <t>200006628</t>
-  </si>
-  <si>
-    <t>080100091606</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021177_BBT40,M60,0W45</t>
-  </si>
-  <si>
-    <t>200006629</t>
-  </si>
-  <si>
-    <t>080200565801</t>
-  </si>
-  <si>
-    <t>H1100機頭G6K,021822_#50,48F23,0</t>
-  </si>
-  <si>
-    <t>200006634</t>
-  </si>
-  <si>
-    <t>200006635</t>
-  </si>
-  <si>
-    <t>080100090804</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006637</t>
-  </si>
-  <si>
-    <t>080100051201</t>
-  </si>
-  <si>
-    <t>D12K 主軸,031723_BT30,M38,0045</t>
-  </si>
-  <si>
-    <t>200006640</t>
-  </si>
-  <si>
-    <t>080200527500</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,38F18</t>
-  </si>
-  <si>
-    <t>200006642</t>
-  </si>
-  <si>
-    <t>200006643</t>
-  </si>
-  <si>
-    <t>080100113505</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CWDIN</t>
-  </si>
-  <si>
-    <t>200006644</t>
-  </si>
-  <si>
-    <t>080200557700</t>
-  </si>
-  <si>
-    <t>MVP-16機頭D15K,021451_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006645</t>
-  </si>
-  <si>
-    <t>200006647</t>
-  </si>
-  <si>
-    <t>080200530400</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,0</t>
-  </si>
-  <si>
-    <t>200006648</t>
-  </si>
-  <si>
-    <t>200006649</t>
-  </si>
-  <si>
-    <t>200006650</t>
-  </si>
-  <si>
-    <t>080100090006</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BT40,M60,0W45</t>
-  </si>
-  <si>
-    <t>200006651</t>
-  </si>
-  <si>
-    <t>200006652</t>
-  </si>
-  <si>
-    <t>200006653</t>
-  </si>
-  <si>
-    <t>200006654</t>
-  </si>
-  <si>
-    <t>200006655</t>
-  </si>
-  <si>
-    <t>200006656</t>
-  </si>
-  <si>
-    <t>200006657</t>
-  </si>
-  <si>
-    <t>080200286503</t>
-  </si>
-  <si>
-    <t>H2110機頭G6K,011026_BT50,42F25,CAWDI</t>
-  </si>
-  <si>
-    <t>200006658</t>
-  </si>
-  <si>
-    <t>080100113504</t>
-  </si>
-  <si>
-    <t>200006659</t>
-  </si>
-  <si>
-    <t>080200530500</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006660</t>
-  </si>
-  <si>
-    <t>200006661</t>
-  </si>
-  <si>
-    <t>200006662</t>
-  </si>
-  <si>
-    <t>200006663</t>
-  </si>
-  <si>
-    <t>080200532700</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,48F18</t>
-  </si>
-  <si>
-    <t>200006666</t>
-  </si>
-  <si>
-    <t>200006668</t>
-  </si>
-  <si>
-    <t>080200071201</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
-  </si>
-  <si>
-    <t>200006669</t>
-  </si>
-  <si>
-    <t>200006670</t>
-  </si>
-  <si>
-    <t>080200546201</t>
-  </si>
-  <si>
-    <t>MVP13機頭P12K,021677_#40,8YU-82,C</t>
-  </si>
-  <si>
-    <t>200006671</t>
-  </si>
-  <si>
-    <t>080200243400</t>
-  </si>
-  <si>
-    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45</t>
-  </si>
-  <si>
-    <t>200006674</t>
-  </si>
-  <si>
-    <t>080100081204</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BBT40,8YU,CW45</t>
-  </si>
-  <si>
-    <t>200006675</t>
-  </si>
-  <si>
-    <t>080200244200</t>
-  </si>
-  <si>
-    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45I</t>
-  </si>
-  <si>
-    <t>200006676</t>
-  </si>
-  <si>
-    <t>080200235502</t>
-  </si>
-  <si>
-    <t>HEP機頭D12K,021573_780,BBT50,48,C45</t>
-  </si>
-  <si>
-    <t>200006677</t>
-  </si>
-  <si>
-    <t>080100045203</t>
-  </si>
-  <si>
-    <t>D12K 主軸,021274_BBT50,M50,C045</t>
-  </si>
-  <si>
-    <t>200006678</t>
-  </si>
-  <si>
-    <t>080200571500</t>
-  </si>
-  <si>
-    <t>L800機頭D15K,021616_#40,48F18,0</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006679</t>
-  </si>
-  <si>
-    <t>080100096404</t>
-  </si>
-  <si>
-    <t>D12K 主軸,011207_BT40,M32,0W45</t>
-  </si>
-  <si>
-    <t>200006681</t>
-  </si>
-  <si>
-    <t>200006682</t>
-  </si>
-  <si>
-    <t>200006683</t>
-  </si>
-  <si>
-    <t>080200070801</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
-  </si>
-  <si>
-    <t>200006684</t>
-  </si>
-  <si>
-    <t>200006685</t>
-  </si>
-  <si>
-    <t>200006686</t>
-  </si>
-  <si>
-    <t>080100050702</t>
-  </si>
-  <si>
-    <t>200006687</t>
-  </si>
-  <si>
     <t>200006688</t>
   </si>
   <si>
@@ -889,6 +796,138 @@
     <t>D12K 主軸,021274_BBT50,M50,CW45</t>
   </si>
   <si>
+    <t>200006708</t>
+  </si>
+  <si>
+    <t>080200546502</t>
+  </si>
+  <si>
+    <t>MVP11機頭D15K,031859_#40,32F18,0</t>
+  </si>
+  <si>
+    <t>200006709</t>
+  </si>
+  <si>
+    <t>200006710</t>
+  </si>
+  <si>
+    <t>200006711</t>
+  </si>
+  <si>
+    <t>200006712</t>
+  </si>
+  <si>
+    <t>200006713</t>
+  </si>
+  <si>
+    <t>200006714</t>
+  </si>
+  <si>
+    <t>200006715</t>
+  </si>
+  <si>
+    <t>200006716</t>
+  </si>
+  <si>
+    <t>200006717</t>
+  </si>
+  <si>
+    <t>200006718</t>
+  </si>
+  <si>
+    <t>200006719</t>
+  </si>
+  <si>
+    <t>200006720</t>
+  </si>
+  <si>
+    <t>080200551400</t>
+  </si>
+  <si>
+    <t>SP10機頭P12K,021023_#40,5GT-72,C</t>
+  </si>
+  <si>
+    <t>200006721</t>
+  </si>
+  <si>
+    <t>080200095202</t>
+  </si>
+  <si>
+    <t>HSA機頭G8K,011147_1000,55A22,C</t>
+  </si>
+  <si>
+    <t>200006722</t>
+  </si>
+  <si>
+    <t>080100048401</t>
+  </si>
+  <si>
+    <t>G8K 主軸,011119_BBT50,M50,C045</t>
+  </si>
+  <si>
+    <t>200006723</t>
+  </si>
+  <si>
+    <t>080200026005</t>
+  </si>
+  <si>
+    <t>PBM135機頭G2.5K,010831_BT50,MO1C45</t>
+  </si>
+  <si>
+    <t>200006724</t>
+  </si>
+  <si>
+    <t>080100033603</t>
+  </si>
+  <si>
+    <t>G2.5K主軸,010830_BT50,C045</t>
+  </si>
+  <si>
+    <t>200006725</t>
+  </si>
+  <si>
+    <t>080200483300</t>
+  </si>
+  <si>
+    <t>H1365機頭G8K,021863_#40,42F25,C</t>
+  </si>
+  <si>
+    <t>200006726</t>
+  </si>
+  <si>
+    <t>080100108701</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021534_BT40,CWDIN</t>
+  </si>
+  <si>
+    <t>200006727</t>
+  </si>
+  <si>
+    <t>080200563000</t>
+  </si>
+  <si>
+    <t>LG1370NEO機頭P12K,021964_#40,8YU-84,C</t>
+  </si>
+  <si>
+    <t>200006728</t>
+  </si>
+  <si>
+    <t>080100076704</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
+  </si>
+  <si>
+    <t>200006729</t>
+  </si>
+  <si>
+    <t>080200572200</t>
+  </si>
+  <si>
+    <t>L2100機頭D12K,021634_#40,48F23</t>
+  </si>
+  <si>
     <t>ZP09</t>
   </si>
   <si>
@@ -923,12 +962,6 @@
   </si>
   <si>
     <t>630000351</t>
-  </si>
-  <si>
-    <t>080100076704</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
   </si>
   <si>
     <t>630000354</t>
@@ -1099,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1122,52 +1155,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1240,13 +1273,13 @@
         <v>12</v>
       </c>
       <c r="G3" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="H3" s="3">
-        <v>46121</v>
+        <v>46142</v>
       </c>
       <c r="I3" s="3">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="J3" t="s">
         <v>13</v>
@@ -1255,7 +1288,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="M3" t="s">
         <v>6</v>
@@ -1290,22 +1323,22 @@
         <v>16</v>
       </c>
       <c r="G4" s="3">
-        <v>46022</v>
+        <v>46055</v>
       </c>
       <c r="H4" s="3">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="I4" s="3">
-        <v>46121</v>
+        <v>46146</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
       </c>
       <c r="L4" s="3">
-        <v>46022</v>
+        <v>46055</v>
       </c>
       <c r="M4" t="s">
         <v>6</v>
@@ -1325,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -1334,28 +1367,28 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>46044</v>
+        <v>46055</v>
       </c>
       <c r="H5" s="3">
-        <v>46142</v>
+        <v>46125</v>
       </c>
       <c r="I5" s="3">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
       </c>
       <c r="L5" s="3">
-        <v>46044</v>
+        <v>46055</v>
       </c>
       <c r="M5" t="s">
         <v>6</v>
@@ -1375,37 +1408,37 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="3">
+        <v>46058</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46094</v>
+      </c>
+      <c r="I6" s="3">
+        <v>46114</v>
+      </c>
+      <c r="J6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="3">
-        <v>46055</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46125</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46146</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
       <c r="K6" t="s">
         <v>5</v>
       </c>
       <c r="L6" s="3">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="M6" t="s">
         <v>6</v>
@@ -1434,28 +1467,28 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="H7" s="3">
-        <v>46125</v>
+        <v>46094</v>
       </c>
       <c r="I7" s="3">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="3">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="M7" t="s">
         <v>6</v>
@@ -1475,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -1484,22 +1517,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G8" s="3">
         <v>46058</v>
       </c>
       <c r="H8" s="3">
-        <v>46094</v>
+        <v>46122</v>
       </c>
       <c r="I8" s="3">
-        <v>46114</v>
+        <v>46142</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
@@ -1525,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1534,28 +1567,28 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="3">
+        <v>46063</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46155</v>
+      </c>
+      <c r="I9" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="3">
-        <v>46058</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46094</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46146</v>
-      </c>
-      <c r="J9" t="s">
-        <v>28</v>
-      </c>
       <c r="K9" t="s">
         <v>5</v>
       </c>
       <c r="L9" s="3">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="M9" t="s">
         <v>6</v>
@@ -1575,37 +1608,37 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
       <c r="G10" s="3">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="H10" s="3">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="I10" s="3">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="J10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
       </c>
       <c r="L10" s="3">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="M10" t="s">
         <v>6</v>
@@ -1625,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -1634,28 +1667,28 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="3">
+        <v>46064</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46174</v>
+      </c>
+      <c r="I11" s="3">
+        <v>46177</v>
+      </c>
+      <c r="J11" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="3">
-        <v>46063</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46163</v>
-      </c>
-      <c r="I11" s="3">
-        <v>46167</v>
-      </c>
-      <c r="J11" t="s">
-        <v>37</v>
-      </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M11" t="s">
         <v>6</v>
@@ -1675,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1684,28 +1717,28 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G12" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H12" s="3">
-        <v>46155</v>
+        <v>46238</v>
       </c>
       <c r="I12" s="3">
-        <v>46160</v>
+        <v>46241</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
       <c r="L12" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M12" t="s">
         <v>6</v>
@@ -1725,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -1734,22 +1767,22 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G13" s="3">
         <v>46064</v>
       </c>
       <c r="H13" s="3">
-        <v>46134</v>
+        <v>46297</v>
       </c>
       <c r="I13" s="3">
-        <v>46139</v>
+        <v>46302</v>
       </c>
       <c r="J13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
@@ -1775,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -1784,22 +1817,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3">
         <v>46064</v>
       </c>
       <c r="H14" s="3">
-        <v>46240</v>
+        <v>46168</v>
       </c>
       <c r="I14" s="3">
-        <v>46245</v>
+        <v>46171</v>
       </c>
       <c r="J14" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1825,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -1834,22 +1867,22 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G15" s="3">
         <v>46064</v>
       </c>
       <c r="H15" s="3">
-        <v>46240</v>
+        <v>46232</v>
       </c>
       <c r="I15" s="3">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="J15" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
@@ -1875,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -1884,22 +1917,22 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G16" s="3">
         <v>46064</v>
       </c>
       <c r="H16" s="3">
-        <v>46234</v>
+        <v>46289</v>
       </c>
       <c r="I16" s="3">
-        <v>46239</v>
+        <v>46296</v>
       </c>
       <c r="J16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1925,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -1934,22 +1967,22 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3">
-        <v>46064</v>
+        <v>46090</v>
       </c>
       <c r="H17" s="3">
-        <v>46234</v>
+        <v>46301</v>
       </c>
       <c r="I17" s="3">
-        <v>46239</v>
+        <v>46307</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -1975,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1984,22 +2017,22 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3">
         <v>46064</v>
       </c>
       <c r="H18" s="3">
-        <v>46146</v>
+        <v>46301</v>
       </c>
       <c r="I18" s="3">
-        <v>46149</v>
+        <v>46307</v>
       </c>
       <c r="J18" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -2025,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -2034,22 +2067,22 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3">
         <v>46064</v>
       </c>
       <c r="H19" s="3">
-        <v>46174</v>
+        <v>46267</v>
       </c>
       <c r="I19" s="3">
-        <v>46177</v>
+        <v>46272</v>
       </c>
       <c r="J19" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -2075,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -2084,22 +2117,22 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G20" s="3">
         <v>46064</v>
       </c>
       <c r="H20" s="3">
-        <v>46238</v>
+        <v>46267</v>
       </c>
       <c r="I20" s="3">
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="J20" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -2125,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -2134,28 +2167,28 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H21" s="3">
-        <v>46297</v>
+        <v>46162</v>
       </c>
       <c r="I21" s="3">
-        <v>46302</v>
+        <v>46164</v>
       </c>
       <c r="J21" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M21" t="s">
         <v>6</v>
@@ -2175,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2184,28 +2217,28 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H22" s="3">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="I22" s="3">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="J22" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
       </c>
       <c r="L22" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M22" t="s">
         <v>6</v>
@@ -2225,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -2234,28 +2267,28 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G23" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H23" s="3">
-        <v>46232</v>
+        <v>46156</v>
       </c>
       <c r="I23" s="3">
-        <v>46237</v>
+        <v>46161</v>
       </c>
       <c r="J23" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2275,37 +2308,37 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G24" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H24" s="3">
-        <v>46289</v>
+        <v>46156</v>
       </c>
       <c r="I24" s="3">
-        <v>46296</v>
+        <v>46161</v>
       </c>
       <c r="J24" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M24" t="s">
         <v>6</v>
@@ -2325,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2334,28 +2367,28 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G25" s="3">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="H25" s="3">
-        <v>46301</v>
+        <v>46212</v>
       </c>
       <c r="I25" s="3">
-        <v>46307</v>
+        <v>46216</v>
       </c>
       <c r="J25" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M25" t="s">
         <v>6</v>
@@ -2375,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2384,28 +2417,28 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G26" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H26" s="3">
-        <v>46301</v>
+        <v>46212</v>
       </c>
       <c r="I26" s="3">
-        <v>46307</v>
+        <v>46216</v>
       </c>
       <c r="J26" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M26" t="s">
         <v>6</v>
@@ -2425,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2434,28 +2467,28 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G27" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H27" s="3">
-        <v>46267</v>
+        <v>46206</v>
       </c>
       <c r="I27" s="3">
-        <v>46272</v>
+        <v>46211</v>
       </c>
       <c r="J27" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2475,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2484,28 +2517,28 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G28" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H28" s="3">
-        <v>46267</v>
+        <v>46206</v>
       </c>
       <c r="I28" s="3">
-        <v>46272</v>
+        <v>46211</v>
       </c>
       <c r="J28" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M28" t="s">
         <v>6</v>
@@ -2525,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2534,22 +2567,22 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G29" s="3">
         <v>46076</v>
       </c>
       <c r="H29" s="3">
-        <v>46104</v>
+        <v>46251</v>
       </c>
       <c r="I29" s="3">
-        <v>46107</v>
+        <v>46253</v>
       </c>
       <c r="J29" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
@@ -2575,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2584,22 +2617,22 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G30" s="3">
         <v>46076</v>
       </c>
       <c r="H30" s="3">
-        <v>46162</v>
+        <v>46251</v>
       </c>
       <c r="I30" s="3">
-        <v>46164</v>
+        <v>46253</v>
       </c>
       <c r="J30" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -2625,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2634,22 +2667,22 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G31" s="3">
         <v>46076</v>
       </c>
       <c r="H31" s="3">
-        <v>46162</v>
+        <v>46245</v>
       </c>
       <c r="I31" s="3">
-        <v>46164</v>
+        <v>46248</v>
       </c>
       <c r="J31" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -2675,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2684,22 +2717,22 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G32" s="3">
         <v>46076</v>
       </c>
       <c r="H32" s="3">
-        <v>46156</v>
+        <v>46245</v>
       </c>
       <c r="I32" s="3">
-        <v>46161</v>
+        <v>46248</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -2725,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2734,28 +2767,28 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G33" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H33" s="3">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="I33" s="3">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="J33" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -2775,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2784,28 +2817,28 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="G34" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H34" s="3">
-        <v>46212</v>
+        <v>46147</v>
       </c>
       <c r="I34" s="3">
-        <v>46216</v>
+        <v>46150</v>
       </c>
       <c r="J34" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -2825,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2834,28 +2867,28 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F35" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H35" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I35" s="3">
+        <v>46171</v>
+      </c>
+      <c r="J35" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="3">
-        <v>46076</v>
-      </c>
-      <c r="H35" s="3">
-        <v>46212</v>
-      </c>
-      <c r="I35" s="3">
-        <v>46216</v>
-      </c>
-      <c r="J35" t="s">
-        <v>48</v>
-      </c>
       <c r="K35" t="s">
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -2875,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -2884,28 +2917,28 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G36" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H36" s="3">
-        <v>46206</v>
+        <v>46148</v>
       </c>
       <c r="I36" s="3">
-        <v>46211</v>
+        <v>46171</v>
       </c>
       <c r="J36" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -2925,37 +2958,37 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="2">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0</v>
-      </c>
-      <c r="E37" t="s">
-        <v>74</v>
-      </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G37" s="3">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="H37" s="3">
-        <v>46206</v>
+        <v>46135</v>
       </c>
       <c r="I37" s="3">
-        <v>46211</v>
+        <v>46157</v>
       </c>
       <c r="J37" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -2975,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -2984,28 +3017,28 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H38" s="3">
+        <v>46167</v>
+      </c>
+      <c r="I38" s="3">
+        <v>46171</v>
+      </c>
+      <c r="J38" t="s">
         <v>71</v>
       </c>
-      <c r="F38" t="s">
-        <v>36</v>
-      </c>
-      <c r="G38" s="3">
-        <v>46076</v>
-      </c>
-      <c r="H38" s="3">
-        <v>46251</v>
-      </c>
-      <c r="I38" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J38" t="s">
-        <v>48</v>
-      </c>
       <c r="K38" t="s">
         <v>5</v>
       </c>
       <c r="L38" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M38" t="s">
         <v>6</v>
@@ -3025,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3034,28 +3067,28 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="F39" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="G39" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="H39" s="3">
-        <v>46251</v>
+        <v>46112</v>
       </c>
       <c r="I39" s="3">
-        <v>46253</v>
+        <v>46125</v>
       </c>
       <c r="J39" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
       </c>
       <c r="L39" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M39" t="s">
         <v>6</v>
@@ -3075,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3084,28 +3117,28 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F40" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G40" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="H40" s="3">
-        <v>46245</v>
+        <v>46167</v>
       </c>
       <c r="I40" s="3">
-        <v>46248</v>
+        <v>46185</v>
       </c>
       <c r="J40" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3125,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3134,28 +3167,28 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F41" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G41" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="H41" s="3">
-        <v>46245</v>
+        <v>46213</v>
       </c>
       <c r="I41" s="3">
-        <v>46248</v>
+        <v>46217</v>
       </c>
       <c r="J41" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3175,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3184,28 +3217,28 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F42" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G42" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="H42" s="3">
-        <v>46108</v>
+        <v>46191</v>
       </c>
       <c r="I42" s="3">
-        <v>46113</v>
+        <v>46210</v>
       </c>
       <c r="J42" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3225,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3234,28 +3267,28 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G43" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="H43" s="3">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="I43" s="3">
-        <v>46160</v>
+        <v>46114</v>
       </c>
       <c r="J43" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3275,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3284,28 +3317,28 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G44" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="H44" s="3">
-        <v>46147</v>
+        <v>46097</v>
       </c>
       <c r="I44" s="3">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="J44" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="K44" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L44" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3325,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3334,28 +3367,28 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F45" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G45" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H45" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="I45" s="3">
         <v>46171</v>
       </c>
       <c r="J45" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="K45" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3375,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3384,28 +3417,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="G46" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="H46" s="3">
-        <v>46148</v>
+        <v>46170</v>
       </c>
       <c r="I46" s="3">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="J46" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="K46" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L46" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3425,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3434,28 +3467,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F47" t="s">
+        <v>114</v>
+      </c>
+      <c r="G47" s="3">
+        <v>46090</v>
+      </c>
+      <c r="H47" s="3">
+        <v>46162</v>
+      </c>
+      <c r="I47" s="3">
+        <v>46167</v>
+      </c>
+      <c r="J47" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47" t="s">
         <v>100</v>
       </c>
-      <c r="G47" s="3">
-        <v>46084</v>
-      </c>
-      <c r="H47" s="3">
-        <v>46135</v>
-      </c>
-      <c r="I47" s="3">
-        <v>46157</v>
-      </c>
-      <c r="J47" t="s">
-        <v>101</v>
-      </c>
-      <c r="K47" t="s">
-        <v>5</v>
-      </c>
       <c r="L47" s="3">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3475,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3484,28 +3517,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F48" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="G48" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H48" s="3">
-        <v>46167</v>
+        <v>46206</v>
       </c>
       <c r="I48" s="3">
-        <v>46171</v>
+        <v>46210</v>
       </c>
       <c r="J48" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="K48" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3525,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3534,28 +3567,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F49" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G49" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H49" s="3">
-        <v>46112</v>
+        <v>46202</v>
       </c>
       <c r="I49" s="3">
-        <v>46125</v>
+        <v>46205</v>
       </c>
       <c r="J49" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K49" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L49" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3575,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3584,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F50" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="G50" s="3">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="H50" s="3">
-        <v>46167</v>
+        <v>46105</v>
       </c>
       <c r="I50" s="3">
-        <v>46185</v>
+        <v>46107</v>
       </c>
       <c r="J50" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3625,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3634,28 +3667,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F51" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G51" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="H51" s="3">
-        <v>46213</v>
+        <v>46092</v>
       </c>
       <c r="I51" s="3">
-        <v>46217</v>
+        <v>46094</v>
       </c>
       <c r="J51" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3675,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3684,28 +3717,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G52" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="H52" s="3">
-        <v>46191</v>
+        <v>46167</v>
       </c>
       <c r="I52" s="3">
-        <v>46210</v>
+        <v>46169</v>
       </c>
       <c r="J52" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -3725,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -3734,28 +3767,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F53" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G53" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="H53" s="3">
-        <v>46106</v>
+        <v>46167</v>
       </c>
       <c r="I53" s="3">
-        <v>46114</v>
+        <v>46169</v>
       </c>
       <c r="J53" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K53" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -3775,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3790,22 +3823,22 @@
         <v>123</v>
       </c>
       <c r="G54" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="H54" s="3">
-        <v>46097</v>
+        <v>46167</v>
       </c>
       <c r="I54" s="3">
-        <v>46101</v>
+        <v>46169</v>
       </c>
       <c r="J54" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K54" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -3825,37 +3858,37 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
       </c>
       <c r="D55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F55" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G55" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="H55" s="3">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="I55" s="3">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="J55" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="K55" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -3875,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -3884,28 +3917,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F56" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G56" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="H56" s="3">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="I56" s="3">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="J56" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
       <c r="K56" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -3925,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -3940,22 +3973,22 @@
         <v>134</v>
       </c>
       <c r="G57" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="H57" s="3">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="I57" s="3">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K57" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -3975,37 +4008,37 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
+        <v>138</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F58" t="s">
+        <v>140</v>
+      </c>
+      <c r="G58" s="3">
+        <v>46093</v>
+      </c>
+      <c r="H58" s="3">
+        <v>46161</v>
+      </c>
+      <c r="I58" s="3">
+        <v>46164</v>
+      </c>
+      <c r="J58" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
-        <v>136</v>
-      </c>
-      <c r="F58" t="s">
-        <v>137</v>
-      </c>
-      <c r="G58" s="3">
-        <v>46090</v>
-      </c>
-      <c r="H58" s="3">
-        <v>46206</v>
-      </c>
-      <c r="I58" s="3">
-        <v>46210</v>
-      </c>
-      <c r="J58" t="s">
-        <v>46</v>
-      </c>
       <c r="K58" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4025,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4040,22 +4073,22 @@
         <v>140</v>
       </c>
       <c r="G59" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="H59" s="3">
-        <v>46202</v>
+        <v>46161</v>
       </c>
       <c r="I59" s="3">
-        <v>46205</v>
+        <v>46164</v>
       </c>
       <c r="J59" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K59" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4075,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4084,28 +4117,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F60" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G60" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="H60" s="3">
-        <v>46105</v>
+        <v>46161</v>
       </c>
       <c r="I60" s="3">
-        <v>46107</v>
+        <v>46164</v>
       </c>
       <c r="J60" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4125,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4134,28 +4167,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F61" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="G61" s="3">
-        <v>46092</v>
+        <v>46105</v>
       </c>
       <c r="H61" s="3">
-        <v>46092</v>
+        <v>46219</v>
       </c>
       <c r="I61" s="3">
-        <v>46094</v>
+        <v>46223</v>
       </c>
       <c r="J61" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46092</v>
+        <v>46105</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4175,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4184,28 +4217,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F62" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G62" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="H62" s="3">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="I62" s="3">
-        <v>46169</v>
+        <v>46218</v>
       </c>
       <c r="J62" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4225,37 +4258,37 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2">
+        <v>0</v>
+      </c>
+      <c r="E63" t="s">
+        <v>148</v>
+      </c>
+      <c r="F63" t="s">
         <v>149</v>
       </c>
-      <c r="C63" s="2">
-        <v>1</v>
-      </c>
-      <c r="D63" s="2">
-        <v>0</v>
-      </c>
-      <c r="E63" t="s">
-        <v>142</v>
-      </c>
-      <c r="F63" t="s">
-        <v>143</v>
-      </c>
       <c r="G63" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H63" s="3">
-        <v>46167</v>
+        <v>46227</v>
       </c>
       <c r="I63" s="3">
-        <v>46169</v>
+        <v>46231</v>
       </c>
       <c r="J63" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K63" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L63" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4284,28 +4317,28 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="G64" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H64" s="3">
-        <v>46167</v>
+        <v>46211</v>
       </c>
       <c r="I64" s="3">
-        <v>46169</v>
+        <v>46216</v>
       </c>
       <c r="J64" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="K64" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L64" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4325,37 +4358,37 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="2">
-        <v>1</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>153</v>
       </c>
-      <c r="F65" t="s">
-        <v>154</v>
-      </c>
       <c r="G65" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H65" s="3">
-        <v>46161</v>
+        <v>46205</v>
       </c>
       <c r="I65" s="3">
-        <v>46163</v>
+        <v>46210</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K65" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L65" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4375,37 +4408,37 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
         <v>155</v>
       </c>
-      <c r="C66" s="2">
-        <v>1</v>
-      </c>
-      <c r="D66" s="2">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>153</v>
-      </c>
       <c r="F66" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G66" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H66" s="3">
-        <v>46161</v>
+        <v>46225</v>
       </c>
       <c r="I66" s="3">
-        <v>46163</v>
+        <v>46226</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K66" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L66" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4425,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4434,28 +4467,28 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="G67" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H67" s="3">
-        <v>46161</v>
+        <v>46219</v>
       </c>
       <c r="I67" s="3">
-        <v>46163</v>
+        <v>46224</v>
       </c>
       <c r="J67" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K67" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L67" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M67" t="s">
         <v>6</v>
@@ -4475,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4484,28 +4517,28 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G68" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="H68" s="3">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="I68" s="3">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="J68" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4525,37 +4558,37 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" t="s">
         <v>160</v>
       </c>
-      <c r="C69" s="2">
-        <v>1</v>
-      </c>
-      <c r="D69" s="2">
-        <v>0</v>
-      </c>
-      <c r="E69" t="s">
-        <v>158</v>
-      </c>
-      <c r="F69" t="s">
-        <v>159</v>
-      </c>
       <c r="G69" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="H69" s="3">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="I69" s="3">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="J69" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="M69" t="s">
         <v>6</v>
@@ -4575,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4584,28 +4617,28 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G70" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="H70" s="3">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="I70" s="3">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="J70" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
       </c>
       <c r="L70" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="M70" t="s">
         <v>6</v>
@@ -4625,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4634,28 +4667,28 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F71" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G71" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="H71" s="3">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="I71" s="3">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="J71" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="M71" t="s">
         <v>6</v>
@@ -4675,37 +4708,37 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
+        <v>166</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>164</v>
+      </c>
+      <c r="F72" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="2">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
-        <v>166</v>
-      </c>
-      <c r="F72" t="s">
-        <v>167</v>
-      </c>
       <c r="G72" s="3">
-        <v>46094</v>
+        <v>46113</v>
       </c>
       <c r="H72" s="3">
-        <v>46146</v>
+        <v>46161</v>
       </c>
       <c r="I72" s="3">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="J72" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3">
-        <v>46094</v>
+        <v>46113</v>
       </c>
       <c r="M72" t="s">
         <v>6</v>
@@ -4725,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4734,28 +4767,28 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F73" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="G73" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="H73" s="3">
-        <v>46219</v>
+        <v>46161</v>
       </c>
       <c r="I73" s="3">
-        <v>46223</v>
+        <v>46167</v>
       </c>
       <c r="J73" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -4775,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4784,28 +4817,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F74" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G74" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="H74" s="3">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="I74" s="3">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="J74" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -4825,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -4834,28 +4867,28 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="F75" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G75" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="H75" s="3">
-        <v>46136</v>
+        <v>46232</v>
       </c>
       <c r="I75" s="3">
-        <v>46141</v>
+        <v>46234</v>
       </c>
       <c r="J75" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -4875,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4884,28 +4917,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F76" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="G76" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H76" s="3">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="I76" s="3">
         <v>46231</v>
       </c>
       <c r="J76" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K76" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -4925,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -4934,28 +4967,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F77" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="G77" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H77" s="3">
-        <v>46211</v>
+        <v>46225</v>
       </c>
       <c r="I77" s="3">
-        <v>46216</v>
+        <v>46231</v>
       </c>
       <c r="J77" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K77" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -4975,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -4984,28 +5017,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F78" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G78" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H78" s="3">
-        <v>46205</v>
+        <v>46232</v>
       </c>
       <c r="I78" s="3">
-        <v>46210</v>
+        <v>46237</v>
       </c>
       <c r="J78" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K78" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5025,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5034,28 +5067,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F79" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="G79" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H79" s="3">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="I79" s="3">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="J79" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K79" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5075,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5084,28 +5117,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="F80" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="G80" s="3">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="H80" s="3">
-        <v>46219</v>
+        <v>46149</v>
       </c>
       <c r="I80" s="3">
-        <v>46224</v>
+        <v>46153</v>
       </c>
       <c r="J80" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K80" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5125,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5134,28 +5167,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G81" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H81" s="3">
-        <v>46168</v>
+        <v>46149</v>
       </c>
       <c r="I81" s="3">
-        <v>46170</v>
+        <v>46153</v>
       </c>
       <c r="J81" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5175,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5184,28 +5217,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="F82" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="G82" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H82" s="3">
-        <v>46168</v>
+        <v>46141</v>
       </c>
       <c r="I82" s="3">
-        <v>46170</v>
+        <v>46148</v>
       </c>
       <c r="J82" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5225,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5234,28 +5267,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="F83" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="G83" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H83" s="3">
-        <v>46168</v>
+        <v>46141</v>
       </c>
       <c r="I83" s="3">
-        <v>46170</v>
+        <v>46148</v>
       </c>
       <c r="J83" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5275,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5284,28 +5317,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F84" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G84" s="3">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="H84" s="3">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="I84" s="3">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="J84" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5325,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5334,28 +5367,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F85" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G85" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H85" s="3">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="I85" s="3">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="J85" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5375,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5384,28 +5417,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F86" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G86" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H86" s="3">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="I86" s="3">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="J86" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5425,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5434,28 +5467,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F87" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G87" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H87" s="3">
-        <v>46232</v>
+        <v>46134</v>
       </c>
       <c r="I87" s="3">
-        <v>46234</v>
+        <v>46136</v>
       </c>
       <c r="J87" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5475,37 +5508,37 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0</v>
+      </c>
+      <c r="E88" t="s">
+        <v>196</v>
+      </c>
+      <c r="F88" t="s">
         <v>197</v>
       </c>
-      <c r="C88" s="2">
-        <v>1</v>
-      </c>
-      <c r="D88" s="2">
-        <v>0</v>
-      </c>
-      <c r="E88" t="s">
-        <v>187</v>
-      </c>
-      <c r="F88" t="s">
-        <v>188</v>
-      </c>
       <c r="G88" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H88" s="3">
-        <v>46232</v>
+        <v>46147</v>
       </c>
       <c r="I88" s="3">
-        <v>46234</v>
+        <v>46150</v>
       </c>
       <c r="J88" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5534,28 +5567,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F89" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G89" s="3">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="H89" s="3">
-        <v>46225</v>
+        <v>46136</v>
       </c>
       <c r="I89" s="3">
-        <v>46231</v>
+        <v>46140</v>
       </c>
       <c r="J89" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5575,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5584,28 +5617,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="F90" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G90" s="3">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="H90" s="3">
-        <v>46225</v>
+        <v>46150</v>
       </c>
       <c r="I90" s="3">
-        <v>46231</v>
+        <v>46156</v>
       </c>
       <c r="J90" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" s="3">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5625,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5634,28 +5667,28 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F91" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G91" s="3">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="H91" s="3">
-        <v>46232</v>
+        <v>46140</v>
       </c>
       <c r="I91" s="3">
-        <v>46237</v>
+        <v>46147</v>
       </c>
       <c r="J91" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5675,37 +5708,37 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
       </c>
       <c r="D92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F92" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="G92" s="3">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="H92" s="3">
-        <v>46224</v>
+        <v>46142</v>
       </c>
       <c r="I92" s="3">
-        <v>46227</v>
+        <v>46147</v>
       </c>
       <c r="J92" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -5725,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5734,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="F93" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="G93" s="3">
-        <v>46114</v>
+        <v>46132</v>
       </c>
       <c r="H93" s="3">
-        <v>46149</v>
+        <v>46178</v>
       </c>
       <c r="I93" s="3">
-        <v>46153</v>
+        <v>46181</v>
       </c>
       <c r="J93" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46114</v>
+        <v>46132</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5775,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5784,28 +5817,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>206</v>
+        <v>55</v>
       </c>
       <c r="F94" t="s">
-        <v>207</v>
+        <v>56</v>
       </c>
       <c r="G94" s="3">
-        <v>46114</v>
+        <v>46132</v>
       </c>
       <c r="H94" s="3">
-        <v>46149</v>
+        <v>46174</v>
       </c>
       <c r="I94" s="3">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="J94" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46114</v>
+        <v>46132</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -5825,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -5834,28 +5867,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="F95" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="G95" s="3">
-        <v>46114</v>
+        <v>46133</v>
       </c>
       <c r="H95" s="3">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="I95" s="3">
-        <v>46148</v>
+        <v>46171</v>
       </c>
       <c r="J95" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46114</v>
+        <v>46133</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -5875,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -5884,28 +5917,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="F96" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="G96" s="3">
-        <v>46114</v>
+        <v>46133</v>
       </c>
       <c r="H96" s="3">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="I96" s="3">
-        <v>46148</v>
+        <v>46171</v>
       </c>
       <c r="J96" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46114</v>
+        <v>46133</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -5925,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -5934,28 +5967,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F97" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G97" s="3">
-        <v>46114</v>
+        <v>46133</v>
       </c>
       <c r="H97" s="3">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="I97" s="3">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="J97" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46114</v>
+        <v>46133</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -5975,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -5984,28 +6017,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F98" t="s">
-        <v>213</v>
+        <v>140</v>
       </c>
       <c r="G98" s="3">
-        <v>46120</v>
+        <v>46133</v>
       </c>
       <c r="H98" s="3">
-        <v>46160</v>
+        <v>46133</v>
       </c>
       <c r="I98" s="3">
-        <v>46162</v>
+        <v>46136</v>
       </c>
       <c r="J98" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46120</v>
+        <v>46133</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6025,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6034,28 +6067,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F99" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G99" s="3">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="H99" s="3">
-        <v>46162</v>
+        <v>46134</v>
       </c>
       <c r="I99" s="3">
-        <v>46164</v>
+        <v>46139</v>
       </c>
       <c r="J99" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6075,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6084,28 +6117,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F100" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G100" s="3">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="H100" s="3">
-        <v>46162</v>
+        <v>46135</v>
       </c>
       <c r="I100" s="3">
-        <v>46164</v>
+        <v>46140</v>
       </c>
       <c r="J100" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6125,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6134,28 +6167,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F101" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G101" s="3">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="H101" s="3">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="I101" s="3">
-        <v>46155</v>
+        <v>46142</v>
       </c>
       <c r="J101" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K101" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L101" s="3">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6175,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6184,28 +6217,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F102" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G102" s="3">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="H102" s="3">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="I102" s="3">
+        <v>46142</v>
+      </c>
+      <c r="J102" t="s">
+        <v>34</v>
+      </c>
+      <c r="K102" t="s">
+        <v>100</v>
+      </c>
+      <c r="L102" s="3">
         <v>46136</v>
-      </c>
-      <c r="J102" t="s">
-        <v>20</v>
-      </c>
-      <c r="K102" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>46122</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6225,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6234,28 +6267,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G103" s="3">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="H103" s="3">
-        <v>46147</v>
+        <v>46139</v>
       </c>
       <c r="I103" s="3">
-        <v>46150</v>
+        <v>46142</v>
       </c>
       <c r="J103" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="K103" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L103" s="3">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6275,37 +6308,37 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
+        <v>231</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
+        <v>227</v>
+      </c>
+      <c r="F104" t="s">
         <v>228</v>
       </c>
-      <c r="C104" s="2">
-        <v>1</v>
-      </c>
-      <c r="D104" s="2">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
-        <v>229</v>
-      </c>
-      <c r="F104" t="s">
-        <v>230</v>
-      </c>
       <c r="G104" s="3">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="H104" s="3">
+        <v>46139</v>
+      </c>
+      <c r="I104" s="3">
+        <v>46142</v>
+      </c>
+      <c r="J104" t="s">
+        <v>13</v>
+      </c>
+      <c r="K104" t="s">
+        <v>100</v>
+      </c>
+      <c r="L104" s="3">
         <v>46136</v>
-      </c>
-      <c r="I104" s="3">
-        <v>46140</v>
-      </c>
-      <c r="J104" t="s">
-        <v>20</v>
-      </c>
-      <c r="K104" t="s">
-        <v>5</v>
-      </c>
-      <c r="L104" s="3">
-        <v>46125</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6325,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6334,28 +6367,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F105" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G105" s="3">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="H105" s="3">
-        <v>46150</v>
+        <v>46136</v>
       </c>
       <c r="I105" s="3">
-        <v>46156</v>
+        <v>46141</v>
       </c>
       <c r="J105" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="K105" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L105" s="3">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6375,37 +6408,37 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
+        <v>235</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
+        <v>233</v>
+      </c>
+      <c r="F106" t="s">
         <v>234</v>
       </c>
-      <c r="C106" s="2">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2">
-        <v>0</v>
-      </c>
-      <c r="E106" t="s">
-        <v>235</v>
-      </c>
-      <c r="F106" t="s">
-        <v>236</v>
-      </c>
       <c r="G106" s="3">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="H106" s="3">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="I106" s="3">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="J106" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K106" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L106" s="3">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6425,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6434,28 +6467,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F107" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="G107" s="3">
-        <v>46126</v>
+        <v>46136</v>
       </c>
       <c r="H107" s="3">
-        <v>46142</v>
+        <v>46136</v>
       </c>
       <c r="I107" s="3">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="J107" t="s">
-        <v>240</v>
+        <v>62</v>
       </c>
       <c r="K107" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L107" s="3">
-        <v>46126</v>
+        <v>46136</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6475,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6484,28 +6517,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F108" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G108" s="3">
-        <v>46126</v>
+        <v>46136</v>
       </c>
       <c r="H108" s="3">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="I108" s="3">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="J108" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="K108" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L108" s="3">
-        <v>46126</v>
+        <v>46136</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6525,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6534,28 +6567,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="F109" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="G109" s="3">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="H109" s="3">
-        <v>46178</v>
+        <v>46136</v>
       </c>
       <c r="I109" s="3">
-        <v>46181</v>
+        <v>46141</v>
       </c>
       <c r="J109" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K109" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L109" s="3">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6575,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6584,28 +6617,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>74</v>
+        <v>240</v>
       </c>
       <c r="F110" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="G110" s="3">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="H110" s="3">
+        <v>46170</v>
+      </c>
+      <c r="I110" s="3">
         <v>46174</v>
       </c>
-      <c r="I110" s="3">
-        <v>46177</v>
-      </c>
       <c r="J110" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6625,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6634,28 +6667,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F111" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G111" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="H111" s="3">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="I111" s="3">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="J111" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6675,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6684,28 +6717,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="F112" t="s">
-        <v>248</v>
+        <v>41</v>
       </c>
       <c r="G112" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="H112" s="3">
-        <v>46170</v>
+        <v>46139</v>
       </c>
       <c r="I112" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J112" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -6725,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -6740,22 +6773,22 @@
         <v>248</v>
       </c>
       <c r="G113" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="H113" s="3">
-        <v>46170</v>
+        <v>46140</v>
       </c>
       <c r="I113" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J113" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -6775,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -6784,28 +6817,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="F114" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="G114" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="H114" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="I114" s="3">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="J114" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -6825,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -6834,28 +6867,28 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>86</v>
+        <v>251</v>
       </c>
       <c r="F115" t="s">
-        <v>87</v>
+        <v>252</v>
       </c>
       <c r="G115" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="H115" s="3">
-        <v>46134</v>
+        <v>46183</v>
       </c>
       <c r="I115" s="3">
-        <v>46139</v>
+        <v>46190</v>
       </c>
       <c r="J115" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -6875,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -6884,28 +6917,28 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F116" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G116" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="H116" s="3">
-        <v>46135</v>
+        <v>46183</v>
       </c>
       <c r="I116" s="3">
+        <v>46190</v>
+      </c>
+      <c r="J116" t="s">
+        <v>131</v>
+      </c>
+      <c r="K116" t="s">
+        <v>5</v>
+      </c>
+      <c r="L116" s="3">
         <v>46140</v>
-      </c>
-      <c r="J116" t="s">
-        <v>46</v>
-      </c>
-      <c r="K116" t="s">
-        <v>5</v>
-      </c>
-      <c r="L116" s="3">
-        <v>46134</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -6925,7 +6958,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -6934,28 +6967,28 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F117" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G117" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H117" s="3">
-        <v>46139</v>
+        <v>46176</v>
       </c>
       <c r="I117" s="3">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="J117" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K117" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L117" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
@@ -6975,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -6984,28 +7017,28 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F118" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G118" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H118" s="3">
-        <v>46139</v>
+        <v>46176</v>
       </c>
       <c r="I118" s="3">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="J118" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="K118" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7025,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7034,28 +7067,28 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F119" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G119" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H119" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="I119" s="3">
-        <v>46142</v>
+        <v>46147</v>
       </c>
       <c r="J119" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K119" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7075,37 +7108,37 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
+        <v>261</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
         <v>262</v>
       </c>
-      <c r="C120" s="2">
-        <v>1</v>
-      </c>
-      <c r="D120" s="2">
-        <v>0</v>
-      </c>
-      <c r="E120" t="s">
-        <v>258</v>
-      </c>
       <c r="F120" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G120" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="H120" s="3">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="I120" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J120" t="s">
+        <v>62</v>
+      </c>
+      <c r="K120" t="s">
+        <v>5</v>
+      </c>
+      <c r="L120" s="3">
         <v>46142</v>
-      </c>
-      <c r="J120" t="s">
-        <v>46</v>
-      </c>
-      <c r="K120" t="s">
-        <v>120</v>
-      </c>
-      <c r="L120" s="3">
-        <v>46136</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
@@ -7125,37 +7158,37 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
+        <v>264</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" t="s">
+        <v>262</v>
+      </c>
+      <c r="F121" t="s">
         <v>263</v>
       </c>
-      <c r="C121" s="2">
-        <v>1</v>
-      </c>
-      <c r="D121" s="2">
-        <v>0</v>
-      </c>
-      <c r="E121" t="s">
-        <v>264</v>
-      </c>
-      <c r="F121" t="s">
-        <v>265</v>
-      </c>
       <c r="G121" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="H121" s="3">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="I121" s="3">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="J121" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K121" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7175,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7184,28 +7217,28 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F122" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G122" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="H122" s="3">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="I122" s="3">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="J122" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K122" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L122" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7225,7 +7258,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7234,28 +7267,28 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F123" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G123" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="H123" s="3">
-        <v>46136</v>
+        <v>46184</v>
       </c>
       <c r="I123" s="3">
-        <v>46141</v>
+        <v>46188</v>
       </c>
       <c r="J123" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K123" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7275,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7284,28 +7317,28 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F124" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G124" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="H124" s="3">
-        <v>46136</v>
+        <v>46184</v>
       </c>
       <c r="I124" s="3">
-        <v>46141</v>
+        <v>46188</v>
       </c>
       <c r="J124" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K124" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L124" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7325,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7334,28 +7367,28 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="F125" t="s">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="G125" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="H125" s="3">
-        <v>46136</v>
+        <v>46184</v>
       </c>
       <c r="I125" s="3">
-        <v>46141</v>
+        <v>46188</v>
       </c>
       <c r="J125" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K125" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="L125" s="3">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7375,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7384,28 +7417,28 @@
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F126" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="G126" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="H126" s="3">
-        <v>46170</v>
+        <v>46142</v>
       </c>
       <c r="I126" s="3">
-        <v>46174</v>
+        <v>46149</v>
       </c>
       <c r="J126" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7425,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7434,28 +7467,28 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="F127" t="s">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="G127" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="H127" s="3">
-        <v>46164</v>
+        <v>46142</v>
       </c>
       <c r="I127" s="3">
-        <v>46169</v>
+        <v>46149</v>
       </c>
       <c r="J127" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
       </c>
       <c r="L127" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7475,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7484,28 +7517,28 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="F128" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="G128" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="H128" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="I128" s="3">
+        <v>46149</v>
+      </c>
+      <c r="J128" t="s">
+        <v>111</v>
+      </c>
+      <c r="K128" t="s">
+        <v>5</v>
+      </c>
+      <c r="L128" s="3">
         <v>46142</v>
-      </c>
-      <c r="J128" t="s">
-        <v>48</v>
-      </c>
-      <c r="K128" t="s">
-        <v>5</v>
-      </c>
-      <c r="L128" s="3">
-        <v>46139</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7525,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7534,28 +7567,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="F129" t="s">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="G129" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H129" s="3">
-        <v>46140</v>
+        <v>46177</v>
       </c>
       <c r="I129" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J129" t="s">
+        <v>62</v>
+      </c>
+      <c r="K129" t="s">
+        <v>5</v>
+      </c>
+      <c r="L129" s="3">
         <v>46142</v>
-      </c>
-      <c r="J129" t="s">
-        <v>46</v>
-      </c>
-      <c r="K129" t="s">
-        <v>5</v>
-      </c>
-      <c r="L129" s="3">
-        <v>46140</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7575,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7584,28 +7617,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="F130" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="G130" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H130" s="3">
-        <v>46140</v>
+        <v>46177</v>
       </c>
       <c r="I130" s="3">
-        <v>46146</v>
+        <v>46183</v>
       </c>
       <c r="J130" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7625,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7634,28 +7667,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>282</v>
+        <v>164</v>
       </c>
       <c r="F131" t="s">
-        <v>283</v>
+        <v>165</v>
       </c>
       <c r="G131" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H131" s="3">
+        <v>46177</v>
+      </c>
+      <c r="I131" s="3">
         <v>46183</v>
       </c>
-      <c r="I131" s="3">
-        <v>46190</v>
-      </c>
       <c r="J131" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -7675,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -7684,28 +7717,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F132" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G132" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H132" s="3">
-        <v>46183</v>
+        <v>46204</v>
       </c>
       <c r="I132" s="3">
-        <v>46190</v>
+        <v>46206</v>
       </c>
       <c r="J132" t="s">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -7725,7 +7758,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -7734,28 +7767,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F133" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G133" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H133" s="3">
-        <v>46176</v>
+        <v>46163</v>
       </c>
       <c r="I133" s="3">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="J133" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -7775,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -7784,28 +7817,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F134" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G134" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H134" s="3">
-        <v>46176</v>
+        <v>46157</v>
       </c>
       <c r="I134" s="3">
-        <v>46182</v>
+        <v>46162</v>
       </c>
       <c r="J134" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -7825,7 +7858,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -7834,28 +7867,28 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F135" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G135" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H135" s="3">
-        <v>46140</v>
+        <v>46224</v>
       </c>
       <c r="I135" s="3">
-        <v>46147</v>
+        <v>46262</v>
       </c>
       <c r="J135" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -7872,10 +7905,10 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" t="s">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -7884,28 +7917,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F136" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G136" s="3">
-        <v>46043</v>
+        <v>46148</v>
       </c>
       <c r="H136" s="3">
-        <v>46051</v>
+        <v>46212</v>
       </c>
       <c r="I136" s="3">
-        <v>46057</v>
+        <v>46219</v>
       </c>
       <c r="J136" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K136" t="s">
-        <v>296</v>
+        <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46043</v>
+        <v>46148</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -7922,40 +7955,40 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" t="s">
+        <v>290</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" t="s">
+        <v>291</v>
+      </c>
+      <c r="F137" t="s">
         <v>292</v>
       </c>
-      <c r="B137" t="s">
-        <v>297</v>
-      </c>
-      <c r="C137" s="2">
-        <v>1</v>
-      </c>
-      <c r="D137" s="2">
-        <v>0</v>
-      </c>
-      <c r="E137" t="s">
-        <v>298</v>
-      </c>
-      <c r="F137" t="s">
-        <v>299</v>
-      </c>
       <c r="G137" s="3">
-        <v>46057</v>
+        <v>46148</v>
       </c>
       <c r="H137" s="3">
-        <v>46076</v>
+        <v>46197</v>
       </c>
       <c r="I137" s="3">
-        <v>46083</v>
+        <v>46202</v>
       </c>
       <c r="J137" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="K137" t="s">
-        <v>296</v>
+        <v>5</v>
       </c>
       <c r="L137" s="3">
-        <v>46057</v>
+        <v>46148</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -7972,10 +8005,10 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -7984,28 +8017,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="F138" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="G138" s="3">
-        <v>46114</v>
+        <v>46148</v>
       </c>
       <c r="H138" s="3">
+        <v>46191</v>
+      </c>
+      <c r="I138" s="3">
+        <v>46197</v>
+      </c>
+      <c r="J138" t="s">
+        <v>62</v>
+      </c>
+      <c r="K138" t="s">
+        <v>5</v>
+      </c>
+      <c r="L138" s="3">
         <v>46148</v>
-      </c>
-      <c r="I138" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J138" t="s">
-        <v>56</v>
-      </c>
-      <c r="K138" t="s">
-        <v>296</v>
-      </c>
-      <c r="L138" s="3">
-        <v>46114</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8022,10 +8055,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8034,28 +8067,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F139" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G139" s="3">
-        <v>46122</v>
+        <v>46148</v>
       </c>
       <c r="H139" s="3">
-        <v>46142</v>
+        <v>46204</v>
       </c>
       <c r="I139" s="3">
+        <v>46204</v>
+      </c>
+      <c r="J139" t="s">
+        <v>62</v>
+      </c>
+      <c r="K139" t="s">
+        <v>5</v>
+      </c>
+      <c r="L139" s="3">
         <v>46148</v>
-      </c>
-      <c r="J139" t="s">
-        <v>56</v>
-      </c>
-      <c r="K139" t="s">
-        <v>296</v>
-      </c>
-      <c r="L139" s="3">
-        <v>46122</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8072,10 +8105,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8084,28 +8117,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F140" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="G140" s="3">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="H140" s="3">
-        <v>46135</v>
+        <v>46199</v>
       </c>
       <c r="I140" s="3">
-        <v>46147</v>
+        <v>46204</v>
       </c>
       <c r="J140" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="K140" t="s">
-        <v>296</v>
+        <v>5</v>
       </c>
       <c r="L140" s="3">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8122,51 +8155,351 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="B141" t="s">
+        <v>302</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>303</v>
+      </c>
+      <c r="F141" t="s">
+        <v>304</v>
+      </c>
+      <c r="G141" s="3">
+        <v>46148</v>
+      </c>
+      <c r="H141" s="3">
+        <v>46279</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46281</v>
+      </c>
+      <c r="J141" t="s">
+        <v>62</v>
+      </c>
+      <c r="K141" t="s">
+        <v>5</v>
+      </c>
+      <c r="L141" s="3">
+        <v>46148</v>
+      </c>
+      <c r="M141" t="s">
+        <v>6</v>
+      </c>
+      <c r="N141" t="s">
+        <v>7</v>
+      </c>
+      <c r="O141" t="s">
+        <v>8</v>
+      </c>
+      <c r="P141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" t="s">
+        <v>305</v>
+      </c>
+      <c r="B142" t="s">
+        <v>306</v>
+      </c>
+      <c r="C142" s="2">
+        <v>1</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s">
+        <v>307</v>
+      </c>
+      <c r="F142" t="s">
+        <v>308</v>
+      </c>
+      <c r="G142" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H142" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I142" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J142" t="s">
+        <v>36</v>
+      </c>
+      <c r="K142" t="s">
         <v>309</v>
       </c>
-      <c r="C141" s="2">
-        <v>1</v>
-      </c>
-      <c r="D141" s="2">
-        <v>0</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="L142" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M142" t="s">
+        <v>6</v>
+      </c>
+      <c r="N142" t="s">
+        <v>7</v>
+      </c>
+      <c r="O142" t="s">
+        <v>8</v>
+      </c>
+      <c r="P142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" t="s">
+        <v>305</v>
+      </c>
+      <c r="B143" t="s">
         <v>310</v>
       </c>
-      <c r="F141" t="s">
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
         <v>311</v>
       </c>
-      <c r="G141" s="3">
+      <c r="F143" t="s">
+        <v>312</v>
+      </c>
+      <c r="G143" s="3">
+        <v>46057</v>
+      </c>
+      <c r="H143" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J143" t="s">
+        <v>21</v>
+      </c>
+      <c r="K143" t="s">
+        <v>309</v>
+      </c>
+      <c r="L143" s="3">
+        <v>46057</v>
+      </c>
+      <c r="M143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N143" t="s">
+        <v>7</v>
+      </c>
+      <c r="O143" t="s">
+        <v>8</v>
+      </c>
+      <c r="P143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144" t="s">
+        <v>305</v>
+      </c>
+      <c r="B144" t="s">
+        <v>313</v>
+      </c>
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2">
+        <v>0</v>
+      </c>
+      <c r="E144" t="s">
+        <v>314</v>
+      </c>
+      <c r="F144" t="s">
+        <v>315</v>
+      </c>
+      <c r="G144" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H144" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I144" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J144" t="s">
+        <v>34</v>
+      </c>
+      <c r="K144" t="s">
+        <v>309</v>
+      </c>
+      <c r="L144" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M144" t="s">
+        <v>6</v>
+      </c>
+      <c r="N144" t="s">
+        <v>7</v>
+      </c>
+      <c r="O144" t="s">
+        <v>8</v>
+      </c>
+      <c r="P144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" t="s">
+        <v>305</v>
+      </c>
+      <c r="B145" t="s">
+        <v>316</v>
+      </c>
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1</v>
+      </c>
+      <c r="E145" t="s">
+        <v>300</v>
+      </c>
+      <c r="F145" t="s">
+        <v>301</v>
+      </c>
+      <c r="G145" s="3">
+        <v>46122</v>
+      </c>
+      <c r="H145" s="3">
+        <v>46142</v>
+      </c>
+      <c r="I145" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J145" t="s">
+        <v>58</v>
+      </c>
+      <c r="K145" t="s">
+        <v>309</v>
+      </c>
+      <c r="L145" s="3">
+        <v>46122</v>
+      </c>
+      <c r="M145" t="s">
+        <v>6</v>
+      </c>
+      <c r="N145" t="s">
+        <v>7</v>
+      </c>
+      <c r="O145" t="s">
+        <v>8</v>
+      </c>
+      <c r="P145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146" t="s">
+        <v>305</v>
+      </c>
+      <c r="B146" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="E146" t="s">
+        <v>318</v>
+      </c>
+      <c r="F146" t="s">
+        <v>319</v>
+      </c>
+      <c r="G146" s="3">
+        <v>46135</v>
+      </c>
+      <c r="H146" s="3">
+        <v>46135</v>
+      </c>
+      <c r="I146" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J146" t="s">
+        <v>71</v>
+      </c>
+      <c r="K146" t="s">
+        <v>309</v>
+      </c>
+      <c r="L146" s="3">
+        <v>46135</v>
+      </c>
+      <c r="M146" t="s">
+        <v>6</v>
+      </c>
+      <c r="N146" t="s">
+        <v>7</v>
+      </c>
+      <c r="O146" t="s">
+        <v>8</v>
+      </c>
+      <c r="P146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147" t="s">
+        <v>305</v>
+      </c>
+      <c r="B147" t="s">
+        <v>320</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>321</v>
+      </c>
+      <c r="F147" t="s">
+        <v>322</v>
+      </c>
+      <c r="G147" s="3">
         <v>46140</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H147" s="3">
         <v>46140</v>
       </c>
-      <c r="I141" s="3">
+      <c r="I147" s="3">
         <v>46147</v>
       </c>
-      <c r="J141" t="s">
-        <v>48</v>
-      </c>
-      <c r="K141" t="s">
-        <v>296</v>
-      </c>
-      <c r="L141" s="3">
+      <c r="J147" t="s">
+        <v>34</v>
+      </c>
+      <c r="K147" t="s">
+        <v>309</v>
+      </c>
+      <c r="L147" s="3">
         <v>46140</v>
       </c>
-      <c r="M141" t="s">
-        <v>6</v>
-      </c>
-      <c r="N141" t="s">
-        <v>7</v>
-      </c>
-      <c r="O141" t="s">
-        <v>8</v>
-      </c>
-      <c r="P141" t="s">
+      <c r="M147" t="s">
+        <v>6</v>
+      </c>
+      <c r="N147" t="s">
+        <v>7</v>
+      </c>
+      <c r="O147" t="s">
+        <v>8</v>
+      </c>
+      <c r="P147" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="326">
   <si>
     <t>ZP02</t>
   </si>
@@ -184,12 +184,6 @@
     <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
   </si>
   <si>
-    <t>200006536</t>
-  </si>
-  <si>
-    <t>REL  PCNF DLV  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
     <t>200006537</t>
   </si>
   <si>
@@ -268,15 +262,6 @@
     <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
   </si>
   <si>
-    <t>200006574</t>
-  </si>
-  <si>
-    <t>080200014702</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
-  </si>
-  <si>
     <t>200006575</t>
   </si>
   <si>
@@ -409,7 +394,7 @@
     <t>REL  MSPT PRC  MANC SETC</t>
   </si>
   <si>
-    <t>200006616</t>
+    <t>200006617</t>
   </si>
   <si>
     <t>080200530800</t>
@@ -418,16 +403,10 @@
     <t>MVP-8機頭D15K,021581_#40,48F23,0</t>
   </si>
   <si>
-    <t>REL  PCNF DLV  PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006617</t>
-  </si>
-  <si>
     <t>200006618</t>
   </si>
   <si>
-    <t>200006622</t>
+    <t>200006623</t>
   </si>
   <si>
     <t>080100050703</t>
@@ -436,9 +415,6 @@
     <t>D20K 主軸,021608_A63,M50,CW</t>
   </si>
   <si>
-    <t>200006623</t>
-  </si>
-  <si>
     <t>200006624</t>
   </si>
   <si>
@@ -634,18 +610,6 @@
     <t>D12K 主軸,021274_BBT50,M50,C045</t>
   </si>
   <si>
-    <t>200006678</t>
-  </si>
-  <si>
-    <t>080200571500</t>
-  </si>
-  <si>
-    <t>L800機頭D15K,021616_#40,48F18,0</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF DLV  PRC  RMWB SETC</t>
-  </si>
-  <si>
     <t>200006681</t>
   </si>
   <si>
@@ -959,9 +923,6 @@
   </si>
   <si>
     <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
-  </si>
-  <si>
-    <t>630000351</t>
   </si>
   <si>
     <t>630000354</t>
@@ -1132,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P147"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1155,52 +1116,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="P1" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2314,25 +2275,25 @@
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G24" s="3">
         <v>46076</v>
       </c>
       <c r="H24" s="3">
-        <v>46156</v>
+        <v>46212</v>
       </c>
       <c r="I24" s="3">
-        <v>46161</v>
+        <v>46216</v>
       </c>
       <c r="J24" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -2358,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2408,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2417,22 +2378,22 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G26" s="3">
         <v>46076</v>
       </c>
       <c r="H26" s="3">
-        <v>46212</v>
+        <v>46206</v>
       </c>
       <c r="I26" s="3">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="J26" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -2482,7 +2443,7 @@
         <v>46211</v>
       </c>
       <c r="J27" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -2508,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2517,19 +2478,19 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G28" s="3">
         <v>46076</v>
       </c>
       <c r="H28" s="3">
-        <v>46206</v>
+        <v>46251</v>
       </c>
       <c r="I28" s="3">
-        <v>46211</v>
+        <v>46253</v>
       </c>
       <c r="J28" t="s">
         <v>36</v>
@@ -2558,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2608,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2617,22 +2578,22 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G30" s="3">
         <v>46076</v>
       </c>
       <c r="H30" s="3">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="I30" s="3">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="J30" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -2658,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2682,7 +2643,7 @@
         <v>46248</v>
       </c>
       <c r="J31" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -2708,37 +2669,37 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="2">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>55</v>
-      </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G32" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H32" s="3">
-        <v>46245</v>
+        <v>46155</v>
       </c>
       <c r="I32" s="3">
-        <v>46248</v>
+        <v>46160</v>
       </c>
       <c r="J32" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
       <c r="L32" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M32" t="s">
         <v>6</v>
@@ -2758,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2767,22 +2728,22 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G33" s="3">
         <v>46079</v>
       </c>
       <c r="H33" s="3">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="I33" s="3">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="J33" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -2808,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2817,28 +2778,28 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G34" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="H34" s="3">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="I34" s="3">
-        <v>46150</v>
+        <v>46171</v>
       </c>
       <c r="J34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -2858,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2867,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="G35" s="3">
         <v>46083</v>
@@ -2908,37 +2869,37 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="2">
-        <v>1</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0</v>
-      </c>
-      <c r="E36" t="s">
-        <v>23</v>
-      </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G36" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="H36" s="3">
-        <v>46148</v>
+        <v>46135</v>
       </c>
       <c r="I36" s="3">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="J36" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -2958,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -2967,28 +2928,28 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G37" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="H37" s="3">
-        <v>46135</v>
+        <v>46167</v>
       </c>
       <c r="I37" s="3">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -3008,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -3017,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G38" s="3">
         <v>46086</v>
@@ -3029,10 +2990,10 @@
         <v>46167</v>
       </c>
       <c r="I38" s="3">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="J38" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
@@ -3058,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3067,22 +3028,22 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G39" s="3">
         <v>46086</v>
       </c>
       <c r="H39" s="3">
-        <v>46112</v>
+        <v>46213</v>
       </c>
       <c r="I39" s="3">
-        <v>46125</v>
+        <v>46217</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
@@ -3108,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3117,22 +3078,22 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G40" s="3">
         <v>46086</v>
       </c>
       <c r="H40" s="3">
-        <v>46167</v>
+        <v>46191</v>
       </c>
       <c r="I40" s="3">
-        <v>46185</v>
+        <v>46210</v>
       </c>
       <c r="J40" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
@@ -3158,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3167,25 +3128,25 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G41" s="3">
         <v>46086</v>
       </c>
       <c r="H41" s="3">
-        <v>46213</v>
+        <v>46106</v>
       </c>
       <c r="I41" s="3">
-        <v>46217</v>
+        <v>46114</v>
       </c>
       <c r="J41" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L41" s="3">
         <v>46086</v>
@@ -3208,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3217,25 +3178,25 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F42" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G42" s="3">
         <v>46086</v>
       </c>
       <c r="H42" s="3">
-        <v>46191</v>
+        <v>46097</v>
       </c>
       <c r="I42" s="3">
-        <v>46210</v>
+        <v>46101</v>
       </c>
       <c r="J42" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="K42" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L42" s="3">
         <v>46086</v>
@@ -3258,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3267,25 +3228,25 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G43" s="3">
         <v>46086</v>
       </c>
       <c r="H43" s="3">
-        <v>46106</v>
+        <v>46153</v>
       </c>
       <c r="I43" s="3">
-        <v>46114</v>
+        <v>46171</v>
       </c>
       <c r="J43" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="K43" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L43" s="3">
         <v>46086</v>
@@ -3308,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3317,28 +3278,28 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G44" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H44" s="3">
-        <v>46097</v>
+        <v>46170</v>
       </c>
       <c r="I44" s="3">
-        <v>46101</v>
+        <v>46175</v>
       </c>
       <c r="J44" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L44" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3358,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3367,28 +3328,28 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G45" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H45" s="3">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="I45" s="3">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="J45" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L45" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3408,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3417,25 +3378,25 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F46" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G46" s="3">
         <v>46090</v>
       </c>
       <c r="H46" s="3">
-        <v>46170</v>
+        <v>46206</v>
       </c>
       <c r="I46" s="3">
-        <v>46175</v>
+        <v>46210</v>
       </c>
       <c r="J46" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="K46" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L46" s="3">
         <v>46090</v>
@@ -3458,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3467,25 +3428,25 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G47" s="3">
         <v>46090</v>
       </c>
       <c r="H47" s="3">
-        <v>46162</v>
+        <v>46202</v>
       </c>
       <c r="I47" s="3">
-        <v>46167</v>
+        <v>46205</v>
       </c>
       <c r="J47" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="K47" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L47" s="3">
         <v>46090</v>
@@ -3508,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3517,28 +3478,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G48" s="3">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="H48" s="3">
-        <v>46206</v>
+        <v>46105</v>
       </c>
       <c r="I48" s="3">
-        <v>46210</v>
+        <v>46107</v>
       </c>
       <c r="J48" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="K48" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3558,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3567,28 +3528,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F49" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G49" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="H49" s="3">
-        <v>46202</v>
+        <v>46092</v>
       </c>
       <c r="I49" s="3">
-        <v>46205</v>
+        <v>46094</v>
       </c>
       <c r="J49" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K49" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3608,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3617,28 +3578,28 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F50" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G50" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="H50" s="3">
-        <v>46105</v>
+        <v>46167</v>
       </c>
       <c r="I50" s="3">
-        <v>46107</v>
+        <v>46169</v>
       </c>
       <c r="J50" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3658,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3667,28 +3628,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F51" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="G51" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="H51" s="3">
-        <v>46092</v>
+        <v>46167</v>
       </c>
       <c r="I51" s="3">
-        <v>46094</v>
+        <v>46169</v>
       </c>
       <c r="J51" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3708,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3717,10 +3678,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G52" s="3">
         <v>46093</v>
@@ -3732,7 +3693,7 @@
         <v>46169</v>
       </c>
       <c r="J52" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
@@ -3758,31 +3719,31 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" t="s">
         <v>129</v>
-      </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" t="s">
-        <v>122</v>
-      </c>
-      <c r="F53" t="s">
-        <v>123</v>
       </c>
       <c r="G53" s="3">
         <v>46093</v>
       </c>
       <c r="H53" s="3">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="I53" s="3">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="J53" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
@@ -3817,22 +3778,22 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F54" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G54" s="3">
         <v>46093</v>
       </c>
       <c r="H54" s="3">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="I54" s="3">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="J54" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
@@ -3858,19 +3819,19 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
         <v>132</v>
       </c>
-      <c r="C55" s="2">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>133</v>
-      </c>
-      <c r="F55" t="s">
-        <v>134</v>
       </c>
       <c r="G55" s="3">
         <v>46093</v>
@@ -3879,10 +3840,10 @@
         <v>46161</v>
       </c>
       <c r="I55" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="J55" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
@@ -3908,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -3917,10 +3878,10 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" t="s">
         <v>133</v>
-      </c>
-      <c r="F56" t="s">
-        <v>134</v>
       </c>
       <c r="G56" s="3">
         <v>46093</v>
@@ -3929,10 +3890,10 @@
         <v>46161</v>
       </c>
       <c r="I56" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="J56" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="K56" t="s">
         <v>5</v>
@@ -3958,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -3967,28 +3928,28 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F57" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="G57" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="H57" s="3">
-        <v>46161</v>
+        <v>46219</v>
       </c>
       <c r="I57" s="3">
-        <v>46163</v>
+        <v>46223</v>
       </c>
       <c r="J57" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="K57" t="s">
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -4008,37 +3969,37 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>137</v>
+      </c>
+      <c r="F58" t="s">
         <v>138</v>
       </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
-        <v>139</v>
-      </c>
-      <c r="F58" t="s">
-        <v>140</v>
-      </c>
       <c r="G58" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="H58" s="3">
-        <v>46161</v>
+        <v>46212</v>
       </c>
       <c r="I58" s="3">
-        <v>46164</v>
+        <v>46218</v>
       </c>
       <c r="J58" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4058,37 +4019,37 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" t="s">
         <v>141</v>
       </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" t="s">
-        <v>139</v>
-      </c>
-      <c r="F59" t="s">
-        <v>140</v>
-      </c>
       <c r="G59" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H59" s="3">
-        <v>46161</v>
+        <v>46227</v>
       </c>
       <c r="I59" s="3">
-        <v>46164</v>
+        <v>46231</v>
       </c>
       <c r="J59" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K59" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L59" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4117,28 +4078,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="F60" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="G60" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H60" s="3">
-        <v>46161</v>
+        <v>46211</v>
       </c>
       <c r="I60" s="3">
-        <v>46164</v>
+        <v>46216</v>
       </c>
       <c r="J60" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="K60" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L60" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4167,28 +4128,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="F61" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="G61" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H61" s="3">
-        <v>46219</v>
+        <v>46205</v>
       </c>
       <c r="I61" s="3">
-        <v>46223</v>
+        <v>46210</v>
       </c>
       <c r="J61" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K61" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L61" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4208,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4217,28 +4178,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F62" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G62" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H62" s="3">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="I62" s="3">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="J62" t="s">
         <v>36</v>
       </c>
       <c r="K62" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L62" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4258,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4267,25 +4228,25 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G63" s="3">
         <v>46106</v>
       </c>
       <c r="H63" s="3">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="I63" s="3">
-        <v>46231</v>
+        <v>46224</v>
       </c>
       <c r="J63" t="s">
         <v>36</v>
       </c>
       <c r="K63" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L63" s="3">
         <v>46106</v>
@@ -4317,28 +4278,28 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="F64" t="s">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="G64" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H64" s="3">
-        <v>46211</v>
+        <v>46168</v>
       </c>
       <c r="I64" s="3">
-        <v>46216</v>
+        <v>46170</v>
       </c>
       <c r="J64" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K64" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4358,37 +4319,37 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
         <v>151</v>
       </c>
-      <c r="C65" s="2">
-        <v>1</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>152</v>
       </c>
-      <c r="F65" t="s">
-        <v>153</v>
-      </c>
       <c r="G65" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H65" s="3">
-        <v>46205</v>
+        <v>46168</v>
       </c>
       <c r="I65" s="3">
-        <v>46210</v>
+        <v>46170</v>
       </c>
       <c r="J65" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K65" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4417,28 +4378,28 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F66" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G66" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H66" s="3">
-        <v>46225</v>
+        <v>46168</v>
       </c>
       <c r="I66" s="3">
-        <v>46226</v>
+        <v>46170</v>
       </c>
       <c r="J66" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K66" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4458,37 +4419,37 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>156</v>
+      </c>
+      <c r="F67" t="s">
         <v>157</v>
       </c>
-      <c r="C67" s="2">
-        <v>1</v>
-      </c>
-      <c r="D67" s="2">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>119</v>
-      </c>
-      <c r="F67" t="s">
-        <v>120</v>
-      </c>
       <c r="G67" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H67" s="3">
-        <v>46219</v>
+        <v>46161</v>
       </c>
       <c r="I67" s="3">
-        <v>46224</v>
+        <v>46167</v>
       </c>
       <c r="J67" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K67" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M67" t="s">
         <v>6</v>
@@ -4517,22 +4478,22 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G68" s="3">
         <v>46113</v>
       </c>
       <c r="H68" s="3">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="I68" s="3">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="J68" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4558,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4567,22 +4528,22 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G69" s="3">
         <v>46113</v>
       </c>
       <c r="H69" s="3">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="I69" s="3">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="J69" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4608,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4617,22 +4578,22 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F70" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G70" s="3">
         <v>46113</v>
       </c>
       <c r="H70" s="3">
-        <v>46168</v>
+        <v>46232</v>
       </c>
       <c r="I70" s="3">
-        <v>46170</v>
+        <v>46234</v>
       </c>
       <c r="J70" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4658,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4667,22 +4628,22 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G71" s="3">
         <v>46113</v>
       </c>
       <c r="H71" s="3">
-        <v>46161</v>
+        <v>46232</v>
       </c>
       <c r="I71" s="3">
-        <v>46167</v>
+        <v>46234</v>
       </c>
       <c r="J71" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
@@ -4708,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4717,22 +4678,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F72" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G72" s="3">
         <v>46113</v>
       </c>
       <c r="H72" s="3">
-        <v>46161</v>
+        <v>46225</v>
       </c>
       <c r="I72" s="3">
-        <v>46167</v>
+        <v>46231</v>
       </c>
       <c r="J72" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
@@ -4758,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4767,22 +4728,22 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F73" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G73" s="3">
         <v>46113</v>
       </c>
       <c r="H73" s="3">
-        <v>46161</v>
+        <v>46225</v>
       </c>
       <c r="I73" s="3">
-        <v>46167</v>
+        <v>46231</v>
       </c>
       <c r="J73" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
@@ -4808,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4817,10 +4778,10 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F74" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G74" s="3">
         <v>46113</v>
@@ -4829,10 +4790,10 @@
         <v>46232</v>
       </c>
       <c r="I74" s="3">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="J74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
@@ -4858,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -4867,22 +4828,22 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F75" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="G75" s="3">
         <v>46113</v>
       </c>
       <c r="H75" s="3">
-        <v>46232</v>
+        <v>46224</v>
       </c>
       <c r="I75" s="3">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="J75" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
@@ -4908,37 +4869,37 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
+        <v>169</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0</v>
+      </c>
+      <c r="E76" t="s">
         <v>170</v>
       </c>
-      <c r="C76" s="2">
-        <v>1</v>
-      </c>
-      <c r="D76" s="2">
-        <v>0</v>
-      </c>
-      <c r="E76" t="s">
-        <v>164</v>
-      </c>
       <c r="F76" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G76" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H76" s="3">
-        <v>46225</v>
+        <v>46149</v>
       </c>
       <c r="I76" s="3">
-        <v>46231</v>
+        <v>46153</v>
       </c>
       <c r="J76" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -4958,37 +4919,37 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0</v>
+      </c>
+      <c r="E77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F77" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="2">
-        <v>1</v>
-      </c>
-      <c r="D77" s="2">
-        <v>0</v>
-      </c>
-      <c r="E77" t="s">
-        <v>164</v>
-      </c>
-      <c r="F77" t="s">
-        <v>165</v>
-      </c>
       <c r="G77" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H77" s="3">
-        <v>46225</v>
+        <v>46149</v>
       </c>
       <c r="I77" s="3">
-        <v>46231</v>
+        <v>46153</v>
       </c>
       <c r="J77" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -5008,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5017,28 +4978,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="F78" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="G78" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H78" s="3">
-        <v>46232</v>
+        <v>46141</v>
       </c>
       <c r="I78" s="3">
-        <v>46237</v>
+        <v>46148</v>
       </c>
       <c r="J78" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5058,7 +5019,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5067,28 +5028,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="F79" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="G79" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H79" s="3">
-        <v>46224</v>
+        <v>46141</v>
       </c>
       <c r="I79" s="3">
-        <v>46227</v>
+        <v>46148</v>
       </c>
       <c r="J79" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5108,37 +5069,37 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
+        <v>175</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0</v>
+      </c>
+      <c r="E80" t="s">
+        <v>176</v>
+      </c>
+      <c r="F80" t="s">
         <v>177</v>
       </c>
-      <c r="C80" s="2">
-        <v>1</v>
-      </c>
-      <c r="D80" s="2">
-        <v>0</v>
-      </c>
-      <c r="E80" t="s">
-        <v>178</v>
-      </c>
-      <c r="F80" t="s">
-        <v>179</v>
-      </c>
       <c r="G80" s="3">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="H80" s="3">
-        <v>46149</v>
+        <v>46160</v>
       </c>
       <c r="I80" s="3">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="J80" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5158,37 +5119,37 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="2">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
+        <v>179</v>
+      </c>
+      <c r="F81" t="s">
         <v>180</v>
       </c>
-      <c r="C81" s="2">
-        <v>1</v>
-      </c>
-      <c r="D81" s="2">
-        <v>0</v>
-      </c>
-      <c r="E81" t="s">
-        <v>178</v>
-      </c>
-      <c r="F81" t="s">
-        <v>179</v>
-      </c>
       <c r="G81" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H81" s="3">
-        <v>46149</v>
+        <v>46162</v>
       </c>
       <c r="I81" s="3">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="J81" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5217,28 +5178,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="F82" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="G82" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H82" s="3">
-        <v>46141</v>
+        <v>46153</v>
       </c>
       <c r="I82" s="3">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="J82" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5258,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5267,28 +5228,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="F83" t="s">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="G83" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H83" s="3">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="I83" s="3">
-        <v>46148</v>
+        <v>46136</v>
       </c>
       <c r="J83" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5308,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5317,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F84" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G84" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="H84" s="3">
-        <v>46160</v>
+        <v>46147</v>
       </c>
       <c r="I84" s="3">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="J84" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5358,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5367,28 +5328,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F85" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G85" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H85" s="3">
-        <v>46162</v>
+        <v>46136</v>
       </c>
       <c r="I85" s="3">
-        <v>46164</v>
+        <v>46140</v>
       </c>
       <c r="J85" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5408,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5417,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F86" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G86" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H86" s="3">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="I86" s="3">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="J86" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5458,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5467,28 +5428,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F87" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G87" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H87" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="I87" s="3">
-        <v>46136</v>
+        <v>46147</v>
       </c>
       <c r="J87" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5508,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5517,28 +5478,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="F88" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="G88" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="H88" s="3">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="I88" s="3">
-        <v>46150</v>
+        <v>46181</v>
       </c>
       <c r="J88" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5558,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5567,28 +5528,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>199</v>
+        <v>55</v>
       </c>
       <c r="F89" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="G89" s="3">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="H89" s="3">
-        <v>46136</v>
+        <v>46174</v>
       </c>
       <c r="I89" s="3">
-        <v>46140</v>
+        <v>46177</v>
       </c>
       <c r="J89" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5623,22 +5584,22 @@
         <v>203</v>
       </c>
       <c r="G90" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H90" s="3">
-        <v>46150</v>
+        <v>46170</v>
       </c>
       <c r="I90" s="3">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="J90" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5667,28 +5628,28 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F91" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G91" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H91" s="3">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="I91" s="3">
-        <v>46147</v>
+        <v>46171</v>
       </c>
       <c r="J91" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5708,37 +5669,37 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
       </c>
       <c r="D92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F92" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G92" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="H92" s="3">
-        <v>46142</v>
+        <v>46170</v>
       </c>
       <c r="I92" s="3">
-        <v>46147</v>
+        <v>46171</v>
       </c>
       <c r="J92" t="s">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -5758,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5767,28 +5728,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="F93" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="G93" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H93" s="3">
-        <v>46178</v>
+        <v>46133</v>
       </c>
       <c r="I93" s="3">
-        <v>46181</v>
+        <v>46136</v>
       </c>
       <c r="J93" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5808,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5817,28 +5778,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="F94" t="s">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="G94" s="3">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H94" s="3">
-        <v>46174</v>
+        <v>46134</v>
       </c>
       <c r="I94" s="3">
-        <v>46177</v>
+        <v>46139</v>
       </c>
       <c r="J94" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -5858,37 +5819,37 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0</v>
+      </c>
+      <c r="E95" t="s">
+        <v>212</v>
+      </c>
+      <c r="F95" t="s">
         <v>213</v>
       </c>
-      <c r="C95" s="2">
-        <v>1</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0</v>
-      </c>
-      <c r="E95" t="s">
-        <v>214</v>
-      </c>
-      <c r="F95" t="s">
-        <v>215</v>
-      </c>
       <c r="G95" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H95" s="3">
-        <v>46170</v>
+        <v>46135</v>
       </c>
       <c r="I95" s="3">
-        <v>46171</v>
+        <v>46140</v>
       </c>
       <c r="J95" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -5908,37 +5869,37 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
+        <v>214</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2">
+        <v>0</v>
+      </c>
+      <c r="E96" t="s">
+        <v>215</v>
+      </c>
+      <c r="F96" t="s">
         <v>216</v>
       </c>
-      <c r="C96" s="2">
-        <v>1</v>
-      </c>
-      <c r="D96" s="2">
-        <v>0</v>
-      </c>
-      <c r="E96" t="s">
-        <v>214</v>
-      </c>
-      <c r="F96" t="s">
-        <v>215</v>
-      </c>
       <c r="G96" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H96" s="3">
-        <v>46170</v>
+        <v>46139</v>
       </c>
       <c r="I96" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J96" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K96" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L96" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -5967,28 +5928,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F97" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G97" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H97" s="3">
-        <v>46170</v>
+        <v>46139</v>
       </c>
       <c r="I97" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J97" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K97" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L97" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -6017,28 +5978,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F98" t="s">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="G98" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H98" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="I98" s="3">
+        <v>46142</v>
+      </c>
+      <c r="J98" t="s">
+        <v>13</v>
+      </c>
+      <c r="K98" t="s">
+        <v>95</v>
+      </c>
+      <c r="L98" s="3">
         <v>46136</v>
-      </c>
-      <c r="J98" t="s">
-        <v>17</v>
-      </c>
-      <c r="K98" t="s">
-        <v>5</v>
-      </c>
-      <c r="L98" s="3">
-        <v>46133</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6058,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6067,28 +6028,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F99" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G99" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="H99" s="3">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="I99" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="J99" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K99" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L99" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6108,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6117,28 +6078,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F100" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G100" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="H100" s="3">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="I100" s="3">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="J100" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K100" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="L100" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6158,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6167,25 +6128,25 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F101" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G101" s="3">
         <v>46136</v>
       </c>
       <c r="H101" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I101" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J101" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="K101" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L101" s="3">
         <v>46136</v>
@@ -6208,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6217,25 +6178,25 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F102" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G102" s="3">
         <v>46136</v>
       </c>
       <c r="H102" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I102" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J102" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="K102" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L102" s="3">
         <v>46136</v>
@@ -6258,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6267,25 +6228,25 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F103" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G103" s="3">
         <v>46136</v>
       </c>
       <c r="H103" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I103" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J103" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="K103" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L103" s="3">
         <v>46136</v>
@@ -6308,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6317,25 +6278,25 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="F104" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="G104" s="3">
         <v>46136</v>
       </c>
       <c r="H104" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I104" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J104" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="K104" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L104" s="3">
         <v>46136</v>
@@ -6358,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6367,28 +6328,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F105" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G105" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H105" s="3">
-        <v>46136</v>
+        <v>46170</v>
       </c>
       <c r="I105" s="3">
-        <v>46141</v>
+        <v>46174</v>
       </c>
       <c r="J105" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="K105" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6408,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6417,28 +6378,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F106" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G106" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H106" s="3">
-        <v>46136</v>
+        <v>46164</v>
       </c>
       <c r="I106" s="3">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="J106" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K106" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6458,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6467,28 +6428,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="F107" t="s">
-        <v>234</v>
+        <v>41</v>
       </c>
       <c r="G107" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H107" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="I107" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="J107" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="K107" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6508,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6517,28 +6478,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F108" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G108" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H108" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I108" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="J108" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="K108" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6558,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6567,28 +6528,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>221</v>
+        <v>114</v>
       </c>
       <c r="F109" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="G109" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H109" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I109" s="3">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="J109" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K109" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6608,37 +6569,37 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
+        <v>238</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
         <v>239</v>
       </c>
-      <c r="C110" s="2">
-        <v>1</v>
-      </c>
-      <c r="D110" s="2">
-        <v>0</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>240</v>
       </c>
-      <c r="F110" t="s">
-        <v>241</v>
-      </c>
       <c r="G110" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H110" s="3">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="I110" s="3">
-        <v>46174</v>
+        <v>46190</v>
       </c>
       <c r="J110" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6658,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6667,28 +6628,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F111" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G111" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H111" s="3">
-        <v>46164</v>
+        <v>46183</v>
       </c>
       <c r="I111" s="3">
-        <v>46169</v>
+        <v>46190</v>
       </c>
       <c r="J111" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6708,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6717,28 +6678,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>243</v>
       </c>
       <c r="F112" t="s">
-        <v>41</v>
+        <v>244</v>
       </c>
       <c r="G112" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H112" s="3">
-        <v>46139</v>
+        <v>46176</v>
       </c>
       <c r="I112" s="3">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="J112" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -6758,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -6767,22 +6728,22 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F113" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G113" s="3">
         <v>46140</v>
       </c>
       <c r="H113" s="3">
-        <v>46140</v>
+        <v>46176</v>
       </c>
       <c r="I113" s="3">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="J113" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
@@ -6808,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -6817,10 +6778,10 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="F114" t="s">
-        <v>120</v>
+        <v>248</v>
       </c>
       <c r="G114" s="3">
         <v>46140</v>
@@ -6829,10 +6790,10 @@
         <v>46140</v>
       </c>
       <c r="I114" s="3">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="J114" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
@@ -6858,37 +6819,37 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
+        <v>249</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0</v>
+      </c>
+      <c r="E115" t="s">
         <v>250</v>
       </c>
-      <c r="C115" s="2">
-        <v>1</v>
-      </c>
-      <c r="D115" s="2">
-        <v>0</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>251</v>
       </c>
-      <c r="F115" t="s">
-        <v>252</v>
-      </c>
       <c r="G115" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H115" s="3">
-        <v>46183</v>
+        <v>46150</v>
       </c>
       <c r="I115" s="3">
-        <v>46190</v>
+        <v>46154</v>
       </c>
       <c r="J115" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -6908,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -6917,28 +6878,28 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
+        <v>250</v>
+      </c>
+      <c r="F116" t="s">
         <v>251</v>
       </c>
-      <c r="F116" t="s">
-        <v>252</v>
-      </c>
       <c r="G116" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H116" s="3">
-        <v>46183</v>
+        <v>46150</v>
       </c>
       <c r="I116" s="3">
-        <v>46190</v>
+        <v>46154</v>
       </c>
       <c r="J116" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -6958,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -6967,19 +6928,19 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F117" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G117" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H117" s="3">
-        <v>46176</v>
+        <v>46150</v>
       </c>
       <c r="I117" s="3">
-        <v>46182</v>
+        <v>46154</v>
       </c>
       <c r="J117" t="s">
         <v>36</v>
@@ -6988,7 +6949,7 @@
         <v>5</v>
       </c>
       <c r="L117" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
@@ -7008,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7017,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F118" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G118" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H118" s="3">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="I118" s="3">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="J118" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7058,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7067,28 +7028,28 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F119" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="G119" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H119" s="3">
-        <v>46140</v>
+        <v>46184</v>
       </c>
       <c r="I119" s="3">
-        <v>46147</v>
+        <v>46188</v>
       </c>
       <c r="J119" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7108,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7117,22 +7078,22 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F120" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G120" s="3">
         <v>46142</v>
       </c>
       <c r="H120" s="3">
-        <v>46150</v>
+        <v>46184</v>
       </c>
       <c r="I120" s="3">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="J120" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
@@ -7158,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7167,22 +7128,22 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="F121" t="s">
-        <v>263</v>
+        <v>157</v>
       </c>
       <c r="G121" s="3">
         <v>46142</v>
       </c>
       <c r="H121" s="3">
-        <v>46150</v>
+        <v>46142</v>
       </c>
       <c r="I121" s="3">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="J121" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
@@ -7208,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7217,22 +7178,22 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="F122" t="s">
-        <v>263</v>
+        <v>157</v>
       </c>
       <c r="G122" s="3">
         <v>46142</v>
       </c>
       <c r="H122" s="3">
-        <v>46150</v>
+        <v>46142</v>
       </c>
       <c r="I122" s="3">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="J122" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
@@ -7258,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7267,22 +7228,22 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="F123" t="s">
-        <v>263</v>
+        <v>157</v>
       </c>
       <c r="G123" s="3">
         <v>46142</v>
       </c>
       <c r="H123" s="3">
-        <v>46184</v>
+        <v>46142</v>
       </c>
       <c r="I123" s="3">
-        <v>46188</v>
+        <v>46149</v>
       </c>
       <c r="J123" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
@@ -7308,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7317,22 +7278,22 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="F124" t="s">
-        <v>263</v>
+        <v>157</v>
       </c>
       <c r="G124" s="3">
         <v>46142</v>
       </c>
       <c r="H124" s="3">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="I124" s="3">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="J124" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
@@ -7358,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7367,22 +7328,22 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="F125" t="s">
-        <v>263</v>
+        <v>157</v>
       </c>
       <c r="G125" s="3">
         <v>46142</v>
       </c>
       <c r="H125" s="3">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="I125" s="3">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="J125" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
@@ -7408,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7417,22 +7378,22 @@
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F126" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G126" s="3">
         <v>46142</v>
       </c>
       <c r="H126" s="3">
-        <v>46142</v>
+        <v>46177</v>
       </c>
       <c r="I126" s="3">
-        <v>46149</v>
+        <v>46183</v>
       </c>
       <c r="J126" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
@@ -7458,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7467,28 +7428,28 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="F127" t="s">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="G127" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H127" s="3">
-        <v>46142</v>
+        <v>46204</v>
       </c>
       <c r="I127" s="3">
-        <v>46149</v>
+        <v>46206</v>
       </c>
       <c r="J127" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
       </c>
       <c r="L127" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7508,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7517,28 +7478,28 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>164</v>
+        <v>267</v>
       </c>
       <c r="F128" t="s">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="G128" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H128" s="3">
-        <v>46142</v>
+        <v>46163</v>
       </c>
       <c r="I128" s="3">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="J128" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
       </c>
       <c r="L128" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7558,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7567,28 +7528,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="F129" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="G129" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H129" s="3">
-        <v>46177</v>
+        <v>46157</v>
       </c>
       <c r="I129" s="3">
-        <v>46183</v>
+        <v>46162</v>
       </c>
       <c r="J129" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
       </c>
       <c r="L129" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7608,37 +7569,37 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
+        <v>272</v>
+      </c>
+      <c r="C130" s="2">
+        <v>1</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0</v>
+      </c>
+      <c r="E130" t="s">
         <v>273</v>
       </c>
-      <c r="C130" s="2">
-        <v>1</v>
-      </c>
-      <c r="D130" s="2">
-        <v>0</v>
-      </c>
-      <c r="E130" t="s">
-        <v>164</v>
-      </c>
       <c r="F130" t="s">
-        <v>165</v>
+        <v>274</v>
       </c>
       <c r="G130" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H130" s="3">
-        <v>46177</v>
+        <v>46224</v>
       </c>
       <c r="I130" s="3">
-        <v>46183</v>
+        <v>46262</v>
       </c>
       <c r="J130" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7658,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7667,28 +7628,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F131" t="s">
-        <v>165</v>
+        <v>277</v>
       </c>
       <c r="G131" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H131" s="3">
-        <v>46177</v>
+        <v>46212</v>
       </c>
       <c r="I131" s="3">
-        <v>46183</v>
+        <v>46219</v>
       </c>
       <c r="J131" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -7708,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -7717,22 +7678,22 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F132" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G132" s="3">
         <v>46148</v>
       </c>
       <c r="H132" s="3">
-        <v>46204</v>
+        <v>46197</v>
       </c>
       <c r="I132" s="3">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="J132" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
@@ -7758,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -7767,22 +7728,22 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F133" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G133" s="3">
         <v>46148</v>
       </c>
       <c r="H133" s="3">
-        <v>46163</v>
+        <v>46191</v>
       </c>
       <c r="I133" s="3">
-        <v>46170</v>
+        <v>46197</v>
       </c>
       <c r="J133" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
@@ -7808,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -7817,22 +7778,22 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F134" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G134" s="3">
         <v>46148</v>
       </c>
       <c r="H134" s="3">
-        <v>46157</v>
+        <v>46204</v>
       </c>
       <c r="I134" s="3">
-        <v>46162</v>
+        <v>46204</v>
       </c>
       <c r="J134" t="s">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
@@ -7858,7 +7819,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -7867,22 +7828,22 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F135" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G135" s="3">
         <v>46148</v>
       </c>
       <c r="H135" s="3">
-        <v>46224</v>
+        <v>46199</v>
       </c>
       <c r="I135" s="3">
-        <v>46262</v>
+        <v>46204</v>
       </c>
       <c r="J135" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
@@ -7908,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -7917,22 +7878,22 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F136" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G136" s="3">
         <v>46148</v>
       </c>
       <c r="H136" s="3">
-        <v>46212</v>
+        <v>46279</v>
       </c>
       <c r="I136" s="3">
-        <v>46219</v>
+        <v>46281</v>
       </c>
       <c r="J136" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
@@ -7955,10 +7916,10 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="B137" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -7967,28 +7928,28 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F137" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G137" s="3">
-        <v>46148</v>
+        <v>46043</v>
       </c>
       <c r="H137" s="3">
-        <v>46197</v>
+        <v>46051</v>
       </c>
       <c r="I137" s="3">
-        <v>46202</v>
+        <v>46057</v>
       </c>
       <c r="J137" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K137" t="s">
-        <v>5</v>
+        <v>297</v>
       </c>
       <c r="L137" s="3">
-        <v>46148</v>
+        <v>46043</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -8005,10 +7966,10 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="B138" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -8017,28 +7978,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F138" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G138" s="3">
-        <v>46148</v>
+        <v>46057</v>
       </c>
       <c r="H138" s="3">
-        <v>46191</v>
+        <v>46076</v>
       </c>
       <c r="I138" s="3">
-        <v>46197</v>
+        <v>46083</v>
       </c>
       <c r="J138" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="K138" t="s">
-        <v>5</v>
+        <v>297</v>
       </c>
       <c r="L138" s="3">
-        <v>46148</v>
+        <v>46057</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8055,10 +8016,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="B139" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8067,28 +8028,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
+        <v>302</v>
+      </c>
+      <c r="F139" t="s">
+        <v>303</v>
+      </c>
+      <c r="G139" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H139" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I139" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J139" t="s">
+        <v>34</v>
+      </c>
+      <c r="K139" t="s">
         <v>297</v>
       </c>
-      <c r="F139" t="s">
-        <v>298</v>
-      </c>
-      <c r="G139" s="3">
-        <v>46148</v>
-      </c>
-      <c r="H139" s="3">
-        <v>46204</v>
-      </c>
-      <c r="I139" s="3">
-        <v>46204</v>
-      </c>
-      <c r="J139" t="s">
-        <v>62</v>
-      </c>
-      <c r="K139" t="s">
-        <v>5</v>
-      </c>
       <c r="L139" s="3">
-        <v>46148</v>
+        <v>46114</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8105,10 +8066,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="B140" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8117,28 +8078,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F140" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G140" s="3">
-        <v>46148</v>
+        <v>46135</v>
       </c>
       <c r="H140" s="3">
-        <v>46199</v>
+        <v>46135</v>
       </c>
       <c r="I140" s="3">
-        <v>46204</v>
+        <v>46147</v>
       </c>
       <c r="J140" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K140" t="s">
-        <v>5</v>
+        <v>297</v>
       </c>
       <c r="L140" s="3">
-        <v>46148</v>
+        <v>46135</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8155,10 +8116,10 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="B141" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C141" s="2">
         <v>1</v>
@@ -8167,28 +8128,28 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F141" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G141" s="3">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="H141" s="3">
-        <v>46279</v>
+        <v>46140</v>
       </c>
       <c r="I141" s="3">
-        <v>46281</v>
+        <v>46147</v>
       </c>
       <c r="J141" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="K141" t="s">
-        <v>5</v>
+        <v>297</v>
       </c>
       <c r="L141" s="3">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
@@ -8200,306 +8161,6 @@
         <v>8</v>
       </c>
       <c r="P141" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16">
-      <c r="A142" t="s">
-        <v>305</v>
-      </c>
-      <c r="B142" t="s">
-        <v>306</v>
-      </c>
-      <c r="C142" s="2">
-        <v>1</v>
-      </c>
-      <c r="D142" s="2">
-        <v>0</v>
-      </c>
-      <c r="E142" t="s">
-        <v>307</v>
-      </c>
-      <c r="F142" t="s">
-        <v>308</v>
-      </c>
-      <c r="G142" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H142" s="3">
-        <v>46051</v>
-      </c>
-      <c r="I142" s="3">
-        <v>46057</v>
-      </c>
-      <c r="J142" t="s">
-        <v>36</v>
-      </c>
-      <c r="K142" t="s">
-        <v>309</v>
-      </c>
-      <c r="L142" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M142" t="s">
-        <v>6</v>
-      </c>
-      <c r="N142" t="s">
-        <v>7</v>
-      </c>
-      <c r="O142" t="s">
-        <v>8</v>
-      </c>
-      <c r="P142" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16">
-      <c r="A143" t="s">
-        <v>305</v>
-      </c>
-      <c r="B143" t="s">
-        <v>310</v>
-      </c>
-      <c r="C143" s="2">
-        <v>1</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
-        <v>311</v>
-      </c>
-      <c r="F143" t="s">
-        <v>312</v>
-      </c>
-      <c r="G143" s="3">
-        <v>46057</v>
-      </c>
-      <c r="H143" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I143" s="3">
-        <v>46083</v>
-      </c>
-      <c r="J143" t="s">
-        <v>21</v>
-      </c>
-      <c r="K143" t="s">
-        <v>309</v>
-      </c>
-      <c r="L143" s="3">
-        <v>46057</v>
-      </c>
-      <c r="M143" t="s">
-        <v>6</v>
-      </c>
-      <c r="N143" t="s">
-        <v>7</v>
-      </c>
-      <c r="O143" t="s">
-        <v>8</v>
-      </c>
-      <c r="P143" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16">
-      <c r="A144" t="s">
-        <v>305</v>
-      </c>
-      <c r="B144" t="s">
-        <v>313</v>
-      </c>
-      <c r="C144" s="2">
-        <v>1</v>
-      </c>
-      <c r="D144" s="2">
-        <v>0</v>
-      </c>
-      <c r="E144" t="s">
-        <v>314</v>
-      </c>
-      <c r="F144" t="s">
-        <v>315</v>
-      </c>
-      <c r="G144" s="3">
-        <v>46114</v>
-      </c>
-      <c r="H144" s="3">
-        <v>46148</v>
-      </c>
-      <c r="I144" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J144" t="s">
-        <v>34</v>
-      </c>
-      <c r="K144" t="s">
-        <v>309</v>
-      </c>
-      <c r="L144" s="3">
-        <v>46114</v>
-      </c>
-      <c r="M144" t="s">
-        <v>6</v>
-      </c>
-      <c r="N144" t="s">
-        <v>7</v>
-      </c>
-      <c r="O144" t="s">
-        <v>8</v>
-      </c>
-      <c r="P144" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16">
-      <c r="A145" t="s">
-        <v>305</v>
-      </c>
-      <c r="B145" t="s">
-        <v>316</v>
-      </c>
-      <c r="C145" s="2">
-        <v>1</v>
-      </c>
-      <c r="D145" s="2">
-        <v>1</v>
-      </c>
-      <c r="E145" t="s">
-        <v>300</v>
-      </c>
-      <c r="F145" t="s">
-        <v>301</v>
-      </c>
-      <c r="G145" s="3">
-        <v>46122</v>
-      </c>
-      <c r="H145" s="3">
-        <v>46142</v>
-      </c>
-      <c r="I145" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J145" t="s">
-        <v>58</v>
-      </c>
-      <c r="K145" t="s">
-        <v>309</v>
-      </c>
-      <c r="L145" s="3">
-        <v>46122</v>
-      </c>
-      <c r="M145" t="s">
-        <v>6</v>
-      </c>
-      <c r="N145" t="s">
-        <v>7</v>
-      </c>
-      <c r="O145" t="s">
-        <v>8</v>
-      </c>
-      <c r="P145" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16">
-      <c r="A146" t="s">
-        <v>305</v>
-      </c>
-      <c r="B146" t="s">
-        <v>317</v>
-      </c>
-      <c r="C146" s="2">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>318</v>
-      </c>
-      <c r="F146" t="s">
-        <v>319</v>
-      </c>
-      <c r="G146" s="3">
-        <v>46135</v>
-      </c>
-      <c r="H146" s="3">
-        <v>46135</v>
-      </c>
-      <c r="I146" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J146" t="s">
-        <v>71</v>
-      </c>
-      <c r="K146" t="s">
-        <v>309</v>
-      </c>
-      <c r="L146" s="3">
-        <v>46135</v>
-      </c>
-      <c r="M146" t="s">
-        <v>6</v>
-      </c>
-      <c r="N146" t="s">
-        <v>7</v>
-      </c>
-      <c r="O146" t="s">
-        <v>8</v>
-      </c>
-      <c r="P146" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16">
-      <c r="A147" t="s">
-        <v>305</v>
-      </c>
-      <c r="B147" t="s">
-        <v>320</v>
-      </c>
-      <c r="C147" s="2">
-        <v>1</v>
-      </c>
-      <c r="D147" s="2">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>321</v>
-      </c>
-      <c r="F147" t="s">
-        <v>322</v>
-      </c>
-      <c r="G147" s="3">
-        <v>46140</v>
-      </c>
-      <c r="H147" s="3">
-        <v>46140</v>
-      </c>
-      <c r="I147" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J147" t="s">
-        <v>34</v>
-      </c>
-      <c r="K147" t="s">
-        <v>309</v>
-      </c>
-      <c r="L147" s="3">
-        <v>46140</v>
-      </c>
-      <c r="M147" t="s">
-        <v>6</v>
-      </c>
-      <c r="N147" t="s">
-        <v>7</v>
-      </c>
-      <c r="O147" t="s">
-        <v>8</v>
-      </c>
-      <c r="P147" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="344">
   <si>
     <t>ZP02</t>
   </si>
@@ -52,844 +52,922 @@
     <t>H1682機頭G6K,021314_#50,42F25,C</t>
   </si>
   <si>
+    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006482</t>
+  </si>
+  <si>
+    <t>080300029900</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,032731,G5K_1°-BBT50-45°-5K-C-F</t>
+  </si>
+  <si>
+    <t>200006483</t>
+  </si>
+  <si>
+    <t>080300028903</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006490</t>
+  </si>
+  <si>
+    <t>080300029103</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>200006500</t>
+  </si>
+  <si>
+    <t>080100092405</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006511</t>
+  </si>
+  <si>
+    <t>080200538802</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,55F23,C</t>
+  </si>
+  <si>
+    <t>200006512</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006513</t>
+  </si>
+  <si>
+    <t>200006514</t>
+  </si>
+  <si>
+    <t>200006516</t>
+  </si>
+  <si>
+    <t>080100116405</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BBT50,CW45</t>
+  </si>
+  <si>
+    <t>200006517</t>
+  </si>
+  <si>
+    <t>200006518</t>
+  </si>
+  <si>
+    <t>200006519</t>
+  </si>
+  <si>
+    <t>080200545001</t>
+  </si>
+  <si>
+    <t>H1370機頭G6K,011395_#50,55F23,C</t>
+  </si>
+  <si>
+    <t>200006520</t>
+  </si>
+  <si>
+    <t>200006521</t>
+  </si>
+  <si>
+    <t>200006522</t>
+  </si>
+  <si>
+    <t>200006533</t>
+  </si>
+  <si>
+    <t>080200546703</t>
+  </si>
+  <si>
+    <t>MVP11機頭D15K,031859_#40,38F18,C,AT8</t>
+  </si>
+  <si>
+    <t>200006534</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006537</t>
+  </si>
+  <si>
+    <t>200006538</t>
+  </si>
+  <si>
+    <t>200006539</t>
+  </si>
+  <si>
+    <t>080100156608</t>
+  </si>
+  <si>
+    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006540</t>
+  </si>
+  <si>
+    <t>200006541</t>
+  </si>
+  <si>
+    <t>200006542</t>
+  </si>
+  <si>
+    <t>200006543</t>
+  </si>
+  <si>
+    <t>200006544</t>
+  </si>
+  <si>
+    <t>200006554</t>
+  </si>
+  <si>
+    <t>080200037902</t>
+  </si>
+  <si>
+    <t>HSA機頭G6K,021563_1200,BBT50,55,045</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006555</t>
+  </si>
+  <si>
+    <t>080100035602</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,0045</t>
+  </si>
+  <si>
+    <t>200006567</t>
+  </si>
+  <si>
+    <t>080300028606</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,031911_1°-BBT50-45°-4K-C-F</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006568</t>
+  </si>
+  <si>
+    <t>200006569</t>
+  </si>
+  <si>
+    <t>080300030000</t>
+  </si>
+  <si>
+    <t>自動頭HF-AU,032731,G5K_1°-BT50-DIN-5K-C-F</t>
+  </si>
+  <si>
+    <t>200006573</t>
+  </si>
+  <si>
+    <t>080300024804</t>
+  </si>
+  <si>
+    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
+  </si>
+  <si>
+    <t>200006575</t>
+  </si>
+  <si>
+    <t>080300017908</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-0</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006576</t>
+  </si>
+  <si>
+    <t>080200408704</t>
+  </si>
+  <si>
+    <t>HMC機頭B10K,202488 _BBT50,F45</t>
+  </si>
+  <si>
+    <t>200006577</t>
+  </si>
+  <si>
+    <t>080100134803</t>
+  </si>
+  <si>
+    <t>B10K 主軸,021472_BBT50,F0CW45</t>
+  </si>
+  <si>
+    <t>200006578</t>
+  </si>
+  <si>
+    <t>080200020004</t>
+  </si>
+  <si>
+    <t>EA機頭HB10K,011050_Z1200,50FANUC,C45</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>200006579</t>
+  </si>
+  <si>
+    <t>080100021502</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006580</t>
+  </si>
+  <si>
+    <t>080300018208</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>200006585</t>
+  </si>
+  <si>
+    <t>080200033404</t>
+  </si>
+  <si>
+    <t>HSA機頭G6K,021563_780,BBT50,55,C45</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>200006586</t>
+  </si>
+  <si>
+    <t>080100036004</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,C045</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006587</t>
+  </si>
+  <si>
+    <t>080200548501</t>
+  </si>
+  <si>
+    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006588</t>
+  </si>
+  <si>
+    <t>080100094004</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006597</t>
+  </si>
+  <si>
+    <t>080200570000</t>
+  </si>
+  <si>
+    <t>5A95Q機頭BA24K,032918_A63,C</t>
+  </si>
+  <si>
+    <t>200006604</t>
+  </si>
+  <si>
+    <t>080200531201</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_A63,48F18,C</t>
+  </si>
+  <si>
+    <t>200006605</t>
+  </si>
+  <si>
+    <t>200006606</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>200006618</t>
+  </si>
+  <si>
+    <t>080200530800</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,48F23,0</t>
+  </si>
+  <si>
+    <t>200006624</t>
+  </si>
+  <si>
+    <t>080100050703</t>
+  </si>
+  <si>
+    <t>D20K 主軸,021608_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006634</t>
+  </si>
+  <si>
+    <t>200006635</t>
+  </si>
+  <si>
+    <t>080100090804</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>200006640</t>
+  </si>
+  <si>
+    <t>080200527500</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,38F18</t>
+  </si>
+  <si>
+    <t>200006642</t>
+  </si>
+  <si>
+    <t>200006643</t>
+  </si>
+  <si>
+    <t>080100113505</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CWDIN</t>
+  </si>
+  <si>
+    <t>200006644</t>
+  </si>
+  <si>
+    <t>080200557700</t>
+  </si>
+  <si>
+    <t>MVP-16機頭D15K,021451_#40,38F18,C</t>
+  </si>
+  <si>
+    <t>200006645</t>
+  </si>
+  <si>
+    <t>200006647</t>
+  </si>
+  <si>
+    <t>080200530400</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,0</t>
+  </si>
+  <si>
+    <t>200006648</t>
+  </si>
+  <si>
+    <t>200006649</t>
+  </si>
+  <si>
+    <t>200006650</t>
+  </si>
+  <si>
+    <t>080100090006</t>
+  </si>
+  <si>
+    <t>D15K 主軸,021177_BT40,M60,0W45</t>
+  </si>
+  <si>
+    <t>200006651</t>
+  </si>
+  <si>
+    <t>200006652</t>
+  </si>
+  <si>
+    <t>200006653</t>
+  </si>
+  <si>
+    <t>200006654</t>
+  </si>
+  <si>
+    <t>200006655</t>
+  </si>
+  <si>
+    <t>200006656</t>
+  </si>
+  <si>
+    <t>200006657</t>
+  </si>
+  <si>
+    <t>080200286503</t>
+  </si>
+  <si>
+    <t>H2110機頭G6K,011026_BT50,42F25,CAWDI</t>
+  </si>
+  <si>
+    <t>200006658</t>
+  </si>
+  <si>
+    <t>080100113504</t>
+  </si>
+  <si>
+    <t>200006659</t>
+  </si>
+  <si>
+    <t>080200530500</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,C</t>
+  </si>
+  <si>
     <t>REL  PRC  MACM RMWB SETC</t>
   </si>
   <si>
-    <t>200006482</t>
-  </si>
-  <si>
-    <t>080300029900</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,032731,G5K_1°-BBT50-45°-5K-C-F</t>
+    <t>200006660</t>
+  </si>
+  <si>
+    <t>200006661</t>
+  </si>
+  <si>
+    <t>200006662</t>
+  </si>
+  <si>
+    <t>200006666</t>
+  </si>
+  <si>
+    <t>080200532700</t>
+  </si>
+  <si>
+    <t>SP10機頭D12K,021256_#40,48F18</t>
+  </si>
+  <si>
+    <t>200006669</t>
+  </si>
+  <si>
+    <t>080200071201</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
+  </si>
+  <si>
+    <t>200006670</t>
+  </si>
+  <si>
+    <t>080200546201</t>
+  </si>
+  <si>
+    <t>MVP13機頭P12K,021677_#40,8YU-82,C</t>
+  </si>
+  <si>
+    <t>200006671</t>
+  </si>
+  <si>
+    <t>080200243400</t>
+  </si>
+  <si>
+    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>200006674</t>
+  </si>
+  <si>
+    <t>080100081204</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BBT40,8YU,CW45</t>
+  </si>
+  <si>
+    <t>200006675</t>
+  </si>
+  <si>
+    <t>080200244200</t>
+  </si>
+  <si>
+    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45I</t>
+  </si>
+  <si>
+    <t>200006676</t>
+  </si>
+  <si>
+    <t>080200235502</t>
+  </si>
+  <si>
+    <t>HEP機頭D12K,021573_780,BBT50,48,C45</t>
+  </si>
+  <si>
+    <t>200006677</t>
+  </si>
+  <si>
+    <t>080100045203</t>
+  </si>
+  <si>
+    <t>D12K 主軸,021274_BBT50,M50,C045</t>
+  </si>
+  <si>
+    <t>200006681</t>
+  </si>
+  <si>
+    <t>200006682</t>
+  </si>
+  <si>
+    <t>200006683</t>
+  </si>
+  <si>
+    <t>080200070801</t>
+  </si>
+  <si>
+    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
+  </si>
+  <si>
+    <t>200006684</t>
+  </si>
+  <si>
+    <t>200006685</t>
+  </si>
+  <si>
+    <t>200006686</t>
+  </si>
+  <si>
+    <t>080100050702</t>
+  </si>
+  <si>
+    <t>200006687</t>
+  </si>
+  <si>
+    <t>080200538402</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,48F23,0</t>
+  </si>
+  <si>
+    <t>200006690</t>
+  </si>
+  <si>
+    <t>080100113205</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CW45</t>
+  </si>
+  <si>
+    <t>200006691</t>
+  </si>
+  <si>
+    <t>200006692</t>
+  </si>
+  <si>
+    <t>200006693</t>
+  </si>
+  <si>
+    <t>080200538702</t>
+  </si>
+  <si>
+    <t>H1682機頭G6K,021314_#50,48F23,C</t>
+  </si>
+  <si>
+    <t>200006694</t>
+  </si>
+  <si>
+    <t>200006695</t>
+  </si>
+  <si>
+    <t>200006696</t>
+  </si>
+  <si>
+    <t>200006697</t>
+  </si>
+  <si>
+    <t>200006698</t>
+  </si>
+  <si>
+    <t>080200558601</t>
+  </si>
+  <si>
+    <t>MVP-16機頭D20K,021825_A63,38F18,C</t>
+  </si>
+  <si>
+    <t>200006699</t>
+  </si>
+  <si>
+    <t>080100050303</t>
+  </si>
+  <si>
+    <t>D20K 主軸,010683_A63,M50,CW</t>
+  </si>
+  <si>
+    <t>200006700</t>
+  </si>
+  <si>
+    <t>200006701</t>
+  </si>
+  <si>
+    <t>080200547500</t>
+  </si>
+  <si>
+    <t>MVP13機頭D15K,011237_#40,38F18</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006702</t>
+  </si>
+  <si>
+    <t>200006703</t>
+  </si>
+  <si>
+    <t>080200422904</t>
+  </si>
+  <si>
+    <t>HEP機頭G8K,011194_780,55A18,C</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>200006704</t>
   </si>
   <si>
     <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>200006483</t>
-  </si>
-  <si>
-    <t>080300028903</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BBT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006488</t>
-  </si>
-  <si>
-    <t>080300029103</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_2.5°-BBT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006489</t>
-  </si>
-  <si>
-    <t>200006490</t>
-  </si>
-  <si>
-    <t>200006500</t>
-  </si>
-  <si>
-    <t>080100092405</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021177_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006511</t>
-  </si>
-  <si>
-    <t>080200538802</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,55F23,C</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006512</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006513</t>
-  </si>
-  <si>
-    <t>200006514</t>
-  </si>
-  <si>
-    <t>200006516</t>
-  </si>
-  <si>
-    <t>080100116405</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BBT50,CW45</t>
-  </si>
-  <si>
-    <t>200006517</t>
-  </si>
-  <si>
-    <t>200006518</t>
-  </si>
-  <si>
-    <t>200006519</t>
-  </si>
-  <si>
-    <t>080200545001</t>
-  </si>
-  <si>
-    <t>H1370機頭G6K,011395_#50,55F23,C</t>
-  </si>
-  <si>
-    <t>200006520</t>
-  </si>
-  <si>
-    <t>200006521</t>
-  </si>
-  <si>
-    <t>200006522</t>
-  </si>
-  <si>
-    <t>200006533</t>
-  </si>
-  <si>
-    <t>080200546703</t>
-  </si>
-  <si>
-    <t>MVP11機頭D15K,031859_#40,38F18,C,AT8</t>
-  </si>
-  <si>
-    <t>200006534</t>
-  </si>
-  <si>
-    <t>200006535</t>
-  </si>
-  <si>
-    <t>080100156608</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006537</t>
-  </si>
-  <si>
-    <t>200006538</t>
-  </si>
-  <si>
-    <t>200006539</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>200006540</t>
-  </si>
-  <si>
-    <t>200006541</t>
-  </si>
-  <si>
-    <t>200006542</t>
-  </si>
-  <si>
-    <t>200006543</t>
-  </si>
-  <si>
-    <t>200006544</t>
-  </si>
-  <si>
-    <t>200006554</t>
-  </si>
-  <si>
-    <t>080200037902</t>
-  </si>
-  <si>
-    <t>HSA機頭G6K,021563_1200,BBT50,55,045</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006555</t>
-  </si>
-  <si>
-    <t>080100035602</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,0045</t>
-  </si>
-  <si>
-    <t>200006567</t>
-  </si>
-  <si>
-    <t>080300028606</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,031911_1°-BBT50-45°-4K-C-F</t>
-  </si>
-  <si>
-    <t>200006568</t>
-  </si>
-  <si>
-    <t>200006569</t>
-  </si>
-  <si>
-    <t>080300030000</t>
-  </si>
-  <si>
-    <t>自動頭HF-AU,032731,G5K_1°-BT50-DIN-5K-C-F</t>
-  </si>
-  <si>
-    <t>200006573</t>
-  </si>
-  <si>
-    <t>080300024804</t>
-  </si>
-  <si>
-    <t>手動頭HF-M90,020997_5°-BT50-45°-2K-0</t>
-  </si>
-  <si>
-    <t>200006575</t>
-  </si>
-  <si>
-    <t>080300017908</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-0</t>
-  </si>
-  <si>
-    <t>200006576</t>
-  </si>
-  <si>
-    <t>080200408704</t>
-  </si>
-  <si>
-    <t>HMC機頭B10K,202488 _BBT50,F45</t>
-  </si>
-  <si>
-    <t>200006577</t>
-  </si>
-  <si>
-    <t>080100134803</t>
-  </si>
-  <si>
-    <t>B10K 主軸,021472_BBT50,F0CW45</t>
-  </si>
-  <si>
-    <t>200006578</t>
-  </si>
-  <si>
-    <t>080200020004</t>
-  </si>
-  <si>
-    <t>EA機頭HB10K,011050_Z1200,50FANUC,C45</t>
-  </si>
-  <si>
-    <t>LUMI</t>
-  </si>
-  <si>
-    <t>200006579</t>
-  </si>
-  <si>
-    <t>080100021502</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
+    <t>200006705</t>
+  </si>
+  <si>
+    <t>080100037203</t>
+  </si>
+  <si>
+    <t>D8K 主軸,021274_BT50,M50,C045</t>
+  </si>
+  <si>
+    <t>200006706</t>
+  </si>
+  <si>
+    <t>200006707</t>
+  </si>
+  <si>
+    <t>080100045603</t>
+  </si>
+  <si>
+    <t>D12K 主軸,021274_BBT50,M50,CW45</t>
+  </si>
+  <si>
+    <t>200006708</t>
+  </si>
+  <si>
+    <t>080200546502</t>
+  </si>
+  <si>
+    <t>MVP11機頭D15K,031859_#40,32F18,0</t>
+  </si>
+  <si>
+    <t>200006709</t>
+  </si>
+  <si>
+    <t>200006710</t>
+  </si>
+  <si>
+    <t>200006711</t>
+  </si>
+  <si>
+    <t>200006712</t>
+  </si>
+  <si>
+    <t>200006713</t>
+  </si>
+  <si>
+    <t>200006714</t>
+  </si>
+  <si>
+    <t>200006715</t>
+  </si>
+  <si>
+    <t>200006716</t>
+  </si>
+  <si>
+    <t>200006717</t>
+  </si>
+  <si>
+    <t>200006718</t>
+  </si>
+  <si>
+    <t>200006719</t>
+  </si>
+  <si>
+    <t>200006720</t>
+  </si>
+  <si>
+    <t>080200551400</t>
+  </si>
+  <si>
+    <t>SP10機頭P12K,021023_#40,5GT-72,C</t>
+  </si>
+  <si>
+    <t>200006721</t>
+  </si>
+  <si>
+    <t>080200095202</t>
+  </si>
+  <si>
+    <t>HSA機頭G8K,011147_1000,55A22,C</t>
+  </si>
+  <si>
+    <t>200006722</t>
+  </si>
+  <si>
+    <t>080100048401</t>
+  </si>
+  <si>
+    <t>G8K 主軸,011119_BBT50,M50,C045</t>
+  </si>
+  <si>
+    <t>200006723</t>
+  </si>
+  <si>
+    <t>080200026005</t>
+  </si>
+  <si>
+    <t>PBM135機頭G2.5K,010831_BT50,MO1C45</t>
+  </si>
+  <si>
+    <t>200006724</t>
+  </si>
+  <si>
+    <t>080100033603</t>
+  </si>
+  <si>
+    <t>G2.5K主軸,010830_BT50,C045</t>
+  </si>
+  <si>
+    <t>200006725</t>
+  </si>
+  <si>
+    <t>080200483300</t>
+  </si>
+  <si>
+    <t>H1365機頭G8K,021863_#40,42F25,C</t>
+  </si>
+  <si>
+    <t>200006726</t>
+  </si>
+  <si>
+    <t>080100108701</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021534_BT40,CWDIN</t>
+  </si>
+  <si>
+    <t>200006727</t>
+  </si>
+  <si>
+    <t>080200563000</t>
+  </si>
+  <si>
+    <t>LG1370NEO機頭P12K,021964_#40,8YU-84,C</t>
+  </si>
+  <si>
+    <t>200006728</t>
+  </si>
+  <si>
+    <t>080100076704</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
+  </si>
+  <si>
+    <t>200006729</t>
+  </si>
+  <si>
+    <t>080200572200</t>
+  </si>
+  <si>
+    <t>L2100機頭D12K,021634_#40,48F23</t>
+  </si>
+  <si>
+    <t>200006730</t>
+  </si>
+  <si>
+    <t>080200014702</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
   </si>
   <si>
     <t>REL  MSPT PCNF PRC  RMWB SETC</t>
   </si>
   <si>
-    <t>200006580</t>
-  </si>
-  <si>
-    <t>080300018208</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>200006585</t>
-  </si>
-  <si>
-    <t>080200033404</t>
-  </si>
-  <si>
-    <t>HSA機頭G6K,021563_780,BBT50,55,C45</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>200006586</t>
-  </si>
-  <si>
-    <t>080100036004</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,C045</t>
-  </si>
-  <si>
-    <t>200006587</t>
-  </si>
-  <si>
-    <t>080200548501</t>
-  </si>
-  <si>
-    <t>LG1370 NEO機頭D15K,021941_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006588</t>
-  </si>
-  <si>
-    <t>080100094004</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006593</t>
-  </si>
-  <si>
-    <t>080200531201</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_A63,48F18,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>200006597</t>
-  </si>
-  <si>
-    <t>080200570000</t>
-  </si>
-  <si>
-    <t>5A95Q機頭BA24K,032918_A63,C</t>
-  </si>
-  <si>
-    <t>200006604</t>
-  </si>
-  <si>
-    <t>200006605</t>
-  </si>
-  <si>
-    <t>200006606</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>200006617</t>
-  </si>
-  <si>
-    <t>080200530800</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,48F23,0</t>
-  </si>
-  <si>
-    <t>200006618</t>
-  </si>
-  <si>
-    <t>200006623</t>
-  </si>
-  <si>
-    <t>080100050703</t>
-  </si>
-  <si>
-    <t>D20K 主軸,021608_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>200006624</t>
-  </si>
-  <si>
-    <t>200006634</t>
-  </si>
-  <si>
-    <t>200006635</t>
-  </si>
-  <si>
-    <t>080100090804</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>200006640</t>
-  </si>
-  <si>
-    <t>080200527500</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,38F18</t>
-  </si>
-  <si>
-    <t>200006642</t>
-  </si>
-  <si>
-    <t>200006643</t>
-  </si>
-  <si>
-    <t>080100113505</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CWDIN</t>
-  </si>
-  <si>
-    <t>200006644</t>
-  </si>
-  <si>
-    <t>080200557700</t>
-  </si>
-  <si>
-    <t>MVP-16機頭D15K,021451_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006645</t>
-  </si>
-  <si>
-    <t>200006647</t>
-  </si>
-  <si>
-    <t>080200530400</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,0</t>
-  </si>
-  <si>
-    <t>200006648</t>
-  </si>
-  <si>
-    <t>200006649</t>
-  </si>
-  <si>
-    <t>200006650</t>
-  </si>
-  <si>
-    <t>080100090006</t>
-  </si>
-  <si>
-    <t>D15K 主軸,021177_BT40,M60,0W45</t>
-  </si>
-  <si>
-    <t>200006651</t>
-  </si>
-  <si>
-    <t>200006652</t>
-  </si>
-  <si>
-    <t>200006653</t>
-  </si>
-  <si>
-    <t>200006654</t>
-  </si>
-  <si>
-    <t>200006655</t>
-  </si>
-  <si>
-    <t>200006656</t>
-  </si>
-  <si>
-    <t>200006657</t>
-  </si>
-  <si>
-    <t>080200286503</t>
-  </si>
-  <si>
-    <t>H2110機頭G6K,011026_BT50,42F25,CAWDI</t>
-  </si>
-  <si>
-    <t>200006658</t>
-  </si>
-  <si>
-    <t>080100113504</t>
-  </si>
-  <si>
-    <t>200006659</t>
-  </si>
-  <si>
-    <t>080200530500</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,C</t>
-  </si>
-  <si>
-    <t>200006660</t>
-  </si>
-  <si>
-    <t>200006661</t>
-  </si>
-  <si>
-    <t>200006662</t>
-  </si>
-  <si>
-    <t>200006666</t>
-  </si>
-  <si>
-    <t>080200532700</t>
-  </si>
-  <si>
-    <t>SP10機頭D12K,021256_#40,48F18</t>
-  </si>
-  <si>
-    <t>200006669</t>
-  </si>
-  <si>
-    <t>080200071201</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,CAW45</t>
-  </si>
-  <si>
-    <t>200006670</t>
-  </si>
-  <si>
-    <t>080200546201</t>
-  </si>
-  <si>
-    <t>MVP13機頭P12K,021677_#40,8YU-82,C</t>
-  </si>
-  <si>
-    <t>200006671</t>
-  </si>
-  <si>
-    <t>080200243400</t>
-  </si>
-  <si>
-    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45</t>
-  </si>
-  <si>
-    <t>200006674</t>
-  </si>
-  <si>
-    <t>080100081204</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BBT40,8YU,CW45</t>
-  </si>
-  <si>
-    <t>200006675</t>
-  </si>
-  <si>
-    <t>080200244200</t>
-  </si>
-  <si>
-    <t>MVP11機頭P12K,021415_BBT40,5GT,0AW45I</t>
-  </si>
-  <si>
-    <t>200006676</t>
-  </si>
-  <si>
-    <t>080200235502</t>
-  </si>
-  <si>
-    <t>HEP機頭D12K,021573_780,BBT50,48,C45</t>
-  </si>
-  <si>
-    <t>200006677</t>
-  </si>
-  <si>
-    <t>080100045203</t>
-  </si>
-  <si>
-    <t>D12K 主軸,021274_BBT50,M50,C045</t>
-  </si>
-  <si>
-    <t>200006681</t>
-  </si>
-  <si>
-    <t>200006682</t>
-  </si>
-  <si>
-    <t>200006683</t>
-  </si>
-  <si>
-    <t>080200070801</t>
-  </si>
-  <si>
-    <t>L800機頭P12K,021615_BBT40,5GT,0AW45</t>
-  </si>
-  <si>
-    <t>200006684</t>
-  </si>
-  <si>
-    <t>200006685</t>
-  </si>
-  <si>
-    <t>200006686</t>
-  </si>
-  <si>
-    <t>080100050702</t>
-  </si>
-  <si>
-    <t>200006687</t>
-  </si>
-  <si>
-    <t>080200538402</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,48F23,0</t>
-  </si>
-  <si>
-    <t>200006688</t>
-  </si>
-  <si>
-    <t>080100112405</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,0W45</t>
-  </si>
-  <si>
-    <t>200006689</t>
-  </si>
-  <si>
-    <t>080100113205</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CW45</t>
-  </si>
-  <si>
-    <t>200006690</t>
-  </si>
-  <si>
-    <t>200006691</t>
-  </si>
-  <si>
-    <t>200006692</t>
-  </si>
-  <si>
-    <t>200006693</t>
-  </si>
-  <si>
-    <t>080200538702</t>
-  </si>
-  <si>
-    <t>H1682機頭G6K,021314_#50,48F23,C</t>
-  </si>
-  <si>
-    <t>200006694</t>
-  </si>
-  <si>
-    <t>200006695</t>
-  </si>
-  <si>
-    <t>200006696</t>
-  </si>
-  <si>
-    <t>200006697</t>
-  </si>
-  <si>
-    <t>200006698</t>
-  </si>
-  <si>
-    <t>080200558601</t>
-  </si>
-  <si>
-    <t>MVP-16機頭D20K,021825_A63,38F18,C</t>
-  </si>
-  <si>
-    <t>200006699</t>
-  </si>
-  <si>
-    <t>080100050303</t>
-  </si>
-  <si>
-    <t>D20K 主軸,010683_A63,M50,CW</t>
-  </si>
-  <si>
-    <t>200006700</t>
-  </si>
-  <si>
-    <t>200006701</t>
-  </si>
-  <si>
-    <t>080200547500</t>
-  </si>
-  <si>
-    <t>MVP13機頭D15K,011237_#40,38F18</t>
-  </si>
-  <si>
-    <t>200006702</t>
-  </si>
-  <si>
-    <t>200006703</t>
-  </si>
-  <si>
-    <t>080200422904</t>
-  </si>
-  <si>
-    <t>HEP機頭G8K,011194_780,55A18,C</t>
-  </si>
-  <si>
-    <t>200006704</t>
-  </si>
-  <si>
-    <t>200006705</t>
-  </si>
-  <si>
-    <t>080100037203</t>
-  </si>
-  <si>
-    <t>D8K 主軸,021274_BT50,M50,C045</t>
-  </si>
-  <si>
-    <t>200006706</t>
-  </si>
-  <si>
-    <t>200006707</t>
-  </si>
-  <si>
-    <t>080100045603</t>
-  </si>
-  <si>
-    <t>D12K 主軸,021274_BBT50,M50,CW45</t>
-  </si>
-  <si>
-    <t>200006708</t>
-  </si>
-  <si>
-    <t>080200546502</t>
-  </si>
-  <si>
-    <t>MVP11機頭D15K,031859_#40,32F18,0</t>
-  </si>
-  <si>
-    <t>200006709</t>
-  </si>
-  <si>
-    <t>200006710</t>
-  </si>
-  <si>
-    <t>200006711</t>
-  </si>
-  <si>
-    <t>200006712</t>
-  </si>
-  <si>
-    <t>200006713</t>
-  </si>
-  <si>
-    <t>200006714</t>
-  </si>
-  <si>
-    <t>200006715</t>
-  </si>
-  <si>
-    <t>200006716</t>
-  </si>
-  <si>
-    <t>200006717</t>
-  </si>
-  <si>
-    <t>200006718</t>
-  </si>
-  <si>
-    <t>200006719</t>
-  </si>
-  <si>
-    <t>200006720</t>
-  </si>
-  <si>
-    <t>080200551400</t>
-  </si>
-  <si>
-    <t>SP10機頭P12K,021023_#40,5GT-72,C</t>
-  </si>
-  <si>
-    <t>200006721</t>
-  </si>
-  <si>
-    <t>080200095202</t>
-  </si>
-  <si>
-    <t>HSA機頭G8K,011147_1000,55A22,C</t>
-  </si>
-  <si>
-    <t>200006722</t>
-  </si>
-  <si>
-    <t>080100048401</t>
-  </si>
-  <si>
-    <t>G8K 主軸,011119_BBT50,M50,C045</t>
-  </si>
-  <si>
-    <t>200006723</t>
-  </si>
-  <si>
-    <t>080200026005</t>
-  </si>
-  <si>
-    <t>PBM135機頭G2.5K,010831_BT50,MO1C45</t>
-  </si>
-  <si>
-    <t>200006724</t>
-  </si>
-  <si>
-    <t>080100033603</t>
-  </si>
-  <si>
-    <t>G2.5K主軸,010830_BT50,C045</t>
-  </si>
-  <si>
-    <t>200006725</t>
-  </si>
-  <si>
-    <t>080200483300</t>
-  </si>
-  <si>
-    <t>H1365機頭G8K,021863_#40,42F25,C</t>
-  </si>
-  <si>
-    <t>200006726</t>
-  </si>
-  <si>
-    <t>080100108701</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021534_BT40,CWDIN</t>
-  </si>
-  <si>
-    <t>200006727</t>
-  </si>
-  <si>
-    <t>080200563000</t>
-  </si>
-  <si>
-    <t>LG1370NEO機頭P12K,021964_#40,8YU-84,C</t>
-  </si>
-  <si>
-    <t>200006728</t>
-  </si>
-  <si>
-    <t>080100076704</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
-  </si>
-  <si>
-    <t>200006729</t>
-  </si>
-  <si>
-    <t>080200572200</t>
-  </si>
-  <si>
-    <t>L2100機頭D12K,021634_#40,48F23</t>
+    <t>200006731</t>
+  </si>
+  <si>
+    <t>080100145601</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,0045</t>
+  </si>
+  <si>
+    <t>200006732</t>
+  </si>
+  <si>
+    <t>080300016308</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_2.5°-BT50-45°-4K-0</t>
+  </si>
+  <si>
+    <t>200006733</t>
+  </si>
+  <si>
+    <t>080200158503</t>
+  </si>
+  <si>
+    <t>SW機頭G6K,011282_780,BT50,48,045</t>
+  </si>
+  <si>
+    <t>200006734</t>
+  </si>
+  <si>
+    <t>080100022704</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BT50,0045</t>
+  </si>
+  <si>
+    <t>200006735</t>
+  </si>
+  <si>
+    <t>080200014502</t>
+  </si>
+  <si>
+    <t>EA機頭G6K,011166_Z1000,60A30,C</t>
+  </si>
+  <si>
+    <t>200006736</t>
+  </si>
+  <si>
+    <t>080100015101</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>200006737</t>
+  </si>
+  <si>
+    <t>200006738</t>
+  </si>
+  <si>
+    <t>080200548000</t>
+  </si>
+  <si>
+    <t>200006739</t>
+  </si>
+  <si>
+    <t>200006740</t>
+  </si>
+  <si>
+    <t>200006741</t>
+  </si>
+  <si>
+    <t>200006742</t>
+  </si>
+  <si>
+    <t>REL  PRC  LKD  MACM SETC</t>
+  </si>
+  <si>
+    <t>200006743</t>
   </si>
   <si>
     <t>ZP09</t>
@@ -907,15 +985,6 @@
     <t>PENNY</t>
   </si>
   <si>
-    <t>630000340</t>
-  </si>
-  <si>
-    <t>080100018301</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BBT50,M50E,C045</t>
-  </si>
-  <si>
     <t>630000349</t>
   </si>
   <si>
@@ -925,22 +994,7 @@
     <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
   </si>
   <si>
-    <t>630000354</t>
-  </si>
-  <si>
-    <t>080200017902</t>
-  </si>
-  <si>
-    <t>EA機頭G8K,011262_Z1200,55A22,C</t>
-  </si>
-  <si>
     <t>630000355</t>
-  </si>
-  <si>
-    <t>080100145601</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M50E,0045</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1093,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1116,52 +1170,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1293,7 +1347,7 @@
         <v>46146</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
@@ -1319,19 +1373,19 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
       </c>
       <c r="G5" s="3">
         <v>46055</v>
@@ -1343,7 +1397,7 @@
         <v>46140</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -1369,31 +1423,31 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
       </c>
       <c r="G6" s="3">
         <v>46058</v>
       </c>
       <c r="H6" s="3">
-        <v>46094</v>
+        <v>46122</v>
       </c>
       <c r="I6" s="3">
-        <v>46114</v>
+        <v>46142</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
@@ -1419,37 +1473,37 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7" s="3">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="H7" s="3">
-        <v>46094</v>
+        <v>46155</v>
       </c>
       <c r="I7" s="3">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="3">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="M7" t="s">
         <v>6</v>
@@ -1469,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -1478,28 +1532,28 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G8" s="3">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="H8" s="3">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="I8" s="3">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
       </c>
       <c r="L8" s="3">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="M8" t="s">
         <v>6</v>
@@ -1519,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1534,22 +1588,22 @@
         <v>29</v>
       </c>
       <c r="G9" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H9" s="3">
-        <v>46155</v>
+        <v>46174</v>
       </c>
       <c r="I9" s="3">
-        <v>46160</v>
+        <v>46177</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
       </c>
       <c r="L9" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M9" t="s">
         <v>6</v>
@@ -1569,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
@@ -1578,22 +1632,22 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G10" s="3">
         <v>46064</v>
       </c>
       <c r="H10" s="3">
-        <v>46146</v>
+        <v>46238</v>
       </c>
       <c r="I10" s="3">
-        <v>46149</v>
+        <v>46241</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
@@ -1619,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -1628,22 +1682,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G11" s="3">
         <v>46064</v>
       </c>
       <c r="H11" s="3">
-        <v>46174</v>
+        <v>46297</v>
       </c>
       <c r="I11" s="3">
-        <v>46177</v>
+        <v>46302</v>
       </c>
       <c r="J11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
@@ -1669,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1678,22 +1732,22 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G12" s="3">
         <v>46064</v>
       </c>
       <c r="H12" s="3">
-        <v>46238</v>
+        <v>46168</v>
       </c>
       <c r="I12" s="3">
-        <v>46241</v>
+        <v>46171</v>
       </c>
       <c r="J12" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
@@ -1719,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -1728,22 +1782,22 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G13" s="3">
         <v>46064</v>
       </c>
       <c r="H13" s="3">
-        <v>46297</v>
+        <v>46232</v>
       </c>
       <c r="I13" s="3">
-        <v>46302</v>
+        <v>46237</v>
       </c>
       <c r="J13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
@@ -1769,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -1778,22 +1832,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G14" s="3">
         <v>46064</v>
       </c>
       <c r="H14" s="3">
-        <v>46168</v>
+        <v>46289</v>
       </c>
       <c r="I14" s="3">
-        <v>46171</v>
+        <v>46296</v>
       </c>
       <c r="J14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1819,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -1834,16 +1888,16 @@
         <v>41</v>
       </c>
       <c r="G15" s="3">
-        <v>46064</v>
+        <v>46090</v>
       </c>
       <c r="H15" s="3">
-        <v>46232</v>
+        <v>46301</v>
       </c>
       <c r="I15" s="3">
-        <v>46237</v>
+        <v>46307</v>
       </c>
       <c r="J15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
@@ -1869,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -1887,13 +1941,13 @@
         <v>46064</v>
       </c>
       <c r="H16" s="3">
-        <v>46289</v>
+        <v>46301</v>
       </c>
       <c r="I16" s="3">
-        <v>46296</v>
+        <v>46307</v>
       </c>
       <c r="J16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1919,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -1928,22 +1982,22 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3">
-        <v>46090</v>
+        <v>46064</v>
       </c>
       <c r="H17" s="3">
-        <v>46301</v>
+        <v>46267</v>
       </c>
       <c r="I17" s="3">
-        <v>46307</v>
+        <v>46272</v>
       </c>
       <c r="J17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -1969,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1978,22 +2032,22 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3">
         <v>46064</v>
       </c>
       <c r="H18" s="3">
-        <v>46301</v>
+        <v>46267</v>
       </c>
       <c r="I18" s="3">
-        <v>46307</v>
+        <v>46272</v>
       </c>
       <c r="J18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -2019,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -2028,28 +2082,28 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H19" s="3">
-        <v>46267</v>
+        <v>46162</v>
       </c>
       <c r="I19" s="3">
-        <v>46272</v>
+        <v>46164</v>
       </c>
       <c r="J19" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
       <c r="L19" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M19" t="s">
         <v>6</v>
@@ -2069,37 +2123,37 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H20" s="3">
+        <v>46162</v>
+      </c>
+      <c r="I20" s="3">
+        <v>46164</v>
+      </c>
+      <c r="J20" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="2">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="3">
-        <v>46064</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46267</v>
-      </c>
-      <c r="I20" s="3">
-        <v>46272</v>
-      </c>
-      <c r="J20" t="s">
-        <v>36</v>
-      </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M20" t="s">
         <v>6</v>
@@ -2128,22 +2182,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G21" s="3">
         <v>46076</v>
       </c>
       <c r="H21" s="3">
-        <v>46162</v>
+        <v>46212</v>
       </c>
       <c r="I21" s="3">
-        <v>46164</v>
+        <v>46216</v>
       </c>
       <c r="J21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
@@ -2169,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2178,22 +2232,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G22" s="3">
         <v>46076</v>
       </c>
       <c r="H22" s="3">
-        <v>46162</v>
+        <v>46212</v>
       </c>
       <c r="I22" s="3">
-        <v>46164</v>
+        <v>46216</v>
       </c>
       <c r="J22" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -2219,31 +2273,31 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" t="s">
         <v>54</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
       </c>
       <c r="G23" s="3">
         <v>46076</v>
       </c>
       <c r="H23" s="3">
-        <v>46156</v>
+        <v>46206</v>
       </c>
       <c r="I23" s="3">
-        <v>46161</v>
+        <v>46211</v>
       </c>
       <c r="J23" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
@@ -2269,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -2278,22 +2332,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G24" s="3">
         <v>46076</v>
       </c>
       <c r="H24" s="3">
-        <v>46212</v>
+        <v>46206</v>
       </c>
       <c r="I24" s="3">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="J24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -2319,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2328,22 +2382,22 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G25" s="3">
         <v>46076</v>
       </c>
       <c r="H25" s="3">
-        <v>46212</v>
+        <v>46251</v>
       </c>
       <c r="I25" s="3">
-        <v>46216</v>
+        <v>46253</v>
       </c>
       <c r="J25" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
@@ -2369,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2378,22 +2432,22 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G26" s="3">
         <v>46076</v>
       </c>
       <c r="H26" s="3">
-        <v>46206</v>
+        <v>46251</v>
       </c>
       <c r="I26" s="3">
-        <v>46211</v>
+        <v>46253</v>
       </c>
       <c r="J26" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -2419,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2428,22 +2482,22 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G27" s="3">
         <v>46076</v>
       </c>
       <c r="H27" s="3">
-        <v>46206</v>
+        <v>46245</v>
       </c>
       <c r="I27" s="3">
-        <v>46211</v>
+        <v>46248</v>
       </c>
       <c r="J27" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -2469,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2478,22 +2532,22 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G28" s="3">
         <v>46076</v>
       </c>
       <c r="H28" s="3">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="I28" s="3">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="J28" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -2519,37 +2573,37 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="2">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" t="s">
-        <v>52</v>
-      </c>
       <c r="G29" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H29" s="3">
-        <v>46251</v>
+        <v>46155</v>
       </c>
       <c r="I29" s="3">
-        <v>46253</v>
+        <v>46160</v>
       </c>
       <c r="J29" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2569,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2578,28 +2632,28 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G30" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H30" s="3">
-        <v>46245</v>
+        <v>46147</v>
       </c>
       <c r="I30" s="3">
-        <v>46248</v>
+        <v>46150</v>
       </c>
       <c r="J30" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M30" t="s">
         <v>6</v>
@@ -2619,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2628,28 +2682,28 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G31" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H31" s="3">
-        <v>46245</v>
+        <v>46148</v>
       </c>
       <c r="I31" s="3">
-        <v>46248</v>
+        <v>46171</v>
       </c>
       <c r="J31" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
       <c r="L31" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="M31" t="s">
         <v>6</v>
@@ -2669,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2678,28 +2732,28 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="G32" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="H32" s="3">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="I32" s="3">
-        <v>46160</v>
+        <v>46171</v>
       </c>
       <c r="J32" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
       <c r="L32" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="M32" t="s">
         <v>6</v>
@@ -2719,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2728,28 +2782,28 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G33" s="3">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="H33" s="3">
-        <v>46147</v>
+        <v>46135</v>
       </c>
       <c r="I33" s="3">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="J33" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -2769,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2778,28 +2832,28 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G34" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H34" s="3">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="I34" s="3">
         <v>46171</v>
       </c>
       <c r="J34" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -2819,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -2828,28 +2882,28 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="G35" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H35" s="3">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="I35" s="3">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="J35" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -2869,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -2878,28 +2932,28 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G36" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="H36" s="3">
-        <v>46135</v>
+        <v>46213</v>
       </c>
       <c r="I36" s="3">
-        <v>46157</v>
+        <v>46217</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -2919,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -2928,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G37" s="3">
         <v>46086</v>
       </c>
       <c r="H37" s="3">
-        <v>46167</v>
+        <v>46191</v>
       </c>
       <c r="I37" s="3">
-        <v>46171</v>
+        <v>46210</v>
       </c>
       <c r="J37" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
@@ -2969,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -2978,25 +3032,25 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G38" s="3">
         <v>46086</v>
       </c>
       <c r="H38" s="3">
-        <v>46167</v>
+        <v>46106</v>
       </c>
       <c r="I38" s="3">
-        <v>46185</v>
+        <v>46114</v>
       </c>
       <c r="J38" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="K38" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L38" s="3">
         <v>46086</v>
@@ -3019,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3028,25 +3082,25 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G39" s="3">
         <v>46086</v>
       </c>
       <c r="H39" s="3">
-        <v>46213</v>
+        <v>46097</v>
       </c>
       <c r="I39" s="3">
-        <v>46217</v>
+        <v>46101</v>
       </c>
       <c r="J39" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="K39" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L39" s="3">
         <v>46086</v>
@@ -3069,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3078,25 +3132,25 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G40" s="3">
         <v>46086</v>
       </c>
       <c r="H40" s="3">
-        <v>46191</v>
+        <v>46153</v>
       </c>
       <c r="I40" s="3">
-        <v>46210</v>
+        <v>46171</v>
       </c>
       <c r="J40" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L40" s="3">
         <v>46086</v>
@@ -3119,37 +3173,37 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" s="3">
+        <v>46090</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46170</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46175</v>
+      </c>
+      <c r="J41" t="s">
+        <v>103</v>
+      </c>
+      <c r="K41" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="2">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41" s="3">
-        <v>46086</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46106</v>
-      </c>
-      <c r="I41" s="3">
-        <v>46114</v>
-      </c>
-      <c r="J41" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" t="s">
-        <v>95</v>
-      </c>
       <c r="L41" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3169,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3178,28 +3232,28 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G42" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H42" s="3">
-        <v>46097</v>
+        <v>46162</v>
       </c>
       <c r="I42" s="3">
-        <v>46101</v>
+        <v>46167</v>
       </c>
       <c r="J42" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L42" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3219,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3228,28 +3282,28 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F43" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G43" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H43" s="3">
-        <v>46153</v>
+        <v>46206</v>
       </c>
       <c r="I43" s="3">
-        <v>46171</v>
+        <v>46210</v>
       </c>
       <c r="J43" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="K43" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L43" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3269,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3278,25 +3332,25 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G44" s="3">
         <v>46090</v>
       </c>
       <c r="H44" s="3">
-        <v>46170</v>
+        <v>46202</v>
       </c>
       <c r="I44" s="3">
-        <v>46175</v>
+        <v>46205</v>
       </c>
       <c r="J44" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="K44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L44" s="3">
         <v>46090</v>
@@ -3319,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3328,28 +3382,28 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F45" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G45" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="H45" s="3">
-        <v>46162</v>
+        <v>46092</v>
       </c>
       <c r="I45" s="3">
-        <v>46167</v>
+        <v>46094</v>
       </c>
       <c r="J45" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="K45" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3369,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3378,28 +3432,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F46" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G46" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="H46" s="3">
-        <v>46206</v>
+        <v>46167</v>
       </c>
       <c r="I46" s="3">
-        <v>46210</v>
+        <v>46169</v>
       </c>
       <c r="J46" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K46" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3419,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3428,28 +3482,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G47" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="H47" s="3">
-        <v>46202</v>
+        <v>46167</v>
       </c>
       <c r="I47" s="3">
-        <v>46205</v>
+        <v>46169</v>
       </c>
       <c r="J47" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K47" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3469,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3478,28 +3532,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G48" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="H48" s="3">
-        <v>46105</v>
+        <v>46167</v>
       </c>
       <c r="I48" s="3">
-        <v>46107</v>
+        <v>46169</v>
       </c>
       <c r="J48" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3519,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3528,28 +3582,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F49" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G49" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="H49" s="3">
-        <v>46092</v>
+        <v>46161</v>
       </c>
       <c r="I49" s="3">
-        <v>46094</v>
+        <v>46163</v>
       </c>
       <c r="J49" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3569,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3578,22 +3632,22 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F50" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G50" s="3">
         <v>46093</v>
       </c>
       <c r="H50" s="3">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="I50" s="3">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="J50" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
@@ -3619,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3628,28 +3682,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F51" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G51" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="H51" s="3">
-        <v>46167</v>
+        <v>46219</v>
       </c>
       <c r="I51" s="3">
-        <v>46169</v>
+        <v>46223</v>
       </c>
       <c r="J51" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3669,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3678,28 +3732,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F52" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G52" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="H52" s="3">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="I52" s="3">
-        <v>46169</v>
+        <v>46218</v>
       </c>
       <c r="J52" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -3719,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -3728,28 +3782,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F53" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G53" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H53" s="3">
-        <v>46161</v>
+        <v>46227</v>
       </c>
       <c r="I53" s="3">
-        <v>46163</v>
+        <v>46231</v>
       </c>
       <c r="J53" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K53" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L53" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -3769,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3778,28 +3832,28 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="G54" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H54" s="3">
-        <v>46161</v>
+        <v>46211</v>
       </c>
       <c r="I54" s="3">
-        <v>46163</v>
+        <v>46216</v>
       </c>
       <c r="J54" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K54" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L54" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -3819,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -3828,28 +3882,28 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F55" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G55" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H55" s="3">
-        <v>46161</v>
+        <v>46205</v>
       </c>
       <c r="I55" s="3">
-        <v>46164</v>
+        <v>46210</v>
       </c>
       <c r="J55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K55" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L55" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -3869,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -3878,28 +3932,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F56" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G56" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="H56" s="3">
-        <v>46161</v>
+        <v>46225</v>
       </c>
       <c r="I56" s="3">
-        <v>46164</v>
+        <v>46226</v>
       </c>
       <c r="J56" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="K56" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L56" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -3919,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -3928,28 +3982,28 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G57" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H57" s="3">
         <v>46219</v>
       </c>
       <c r="I57" s="3">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J57" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K57" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L57" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -3969,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -3978,28 +4032,28 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F58" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G58" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="H58" s="3">
-        <v>46212</v>
+        <v>46168</v>
       </c>
       <c r="I58" s="3">
-        <v>46218</v>
+        <v>46170</v>
       </c>
       <c r="J58" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4019,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4028,28 +4082,28 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F59" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G59" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H59" s="3">
-        <v>46227</v>
+        <v>46168</v>
       </c>
       <c r="I59" s="3">
-        <v>46231</v>
+        <v>46170</v>
       </c>
       <c r="J59" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K59" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4069,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4078,28 +4132,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="G60" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H60" s="3">
-        <v>46211</v>
+        <v>46168</v>
       </c>
       <c r="I60" s="3">
-        <v>46216</v>
+        <v>46170</v>
       </c>
       <c r="J60" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K60" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4119,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4128,28 +4182,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F61" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G61" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H61" s="3">
-        <v>46205</v>
+        <v>46161</v>
       </c>
       <c r="I61" s="3">
-        <v>46210</v>
+        <v>46167</v>
       </c>
       <c r="J61" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K61" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4169,7 +4223,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4178,28 +4232,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F62" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G62" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H62" s="3">
-        <v>46225</v>
+        <v>46161</v>
       </c>
       <c r="I62" s="3">
-        <v>46226</v>
+        <v>46167</v>
       </c>
       <c r="J62" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="K62" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4219,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4228,28 +4282,28 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="G63" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H63" s="3">
-        <v>46219</v>
+        <v>46161</v>
       </c>
       <c r="I63" s="3">
-        <v>46224</v>
+        <v>46167</v>
       </c>
       <c r="J63" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="K63" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4269,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4278,22 +4332,22 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F64" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G64" s="3">
         <v>46113</v>
       </c>
       <c r="H64" s="3">
-        <v>46168</v>
+        <v>46232</v>
       </c>
       <c r="I64" s="3">
-        <v>46170</v>
+        <v>46234</v>
       </c>
       <c r="J64" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
@@ -4319,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4328,22 +4382,22 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F65" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G65" s="3">
         <v>46113</v>
       </c>
       <c r="H65" s="3">
-        <v>46168</v>
+        <v>46232</v>
       </c>
       <c r="I65" s="3">
-        <v>46170</v>
+        <v>46234</v>
       </c>
       <c r="J65" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4369,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4387,13 +4441,13 @@
         <v>46113</v>
       </c>
       <c r="H66" s="3">
-        <v>46168</v>
+        <v>46225</v>
       </c>
       <c r="I66" s="3">
-        <v>46170</v>
+        <v>46231</v>
       </c>
       <c r="J66" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
@@ -4419,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4428,22 +4482,22 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F67" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G67" s="3">
         <v>46113</v>
       </c>
       <c r="H67" s="3">
-        <v>46161</v>
+        <v>46225</v>
       </c>
       <c r="I67" s="3">
-        <v>46167</v>
+        <v>46231</v>
       </c>
       <c r="J67" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
@@ -4469,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4478,22 +4532,22 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G68" s="3">
         <v>46113</v>
       </c>
       <c r="H68" s="3">
-        <v>46161</v>
+        <v>46232</v>
       </c>
       <c r="I68" s="3">
-        <v>46167</v>
+        <v>46237</v>
       </c>
       <c r="J68" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4519,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4528,22 +4582,22 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F69" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="G69" s="3">
         <v>46113</v>
       </c>
       <c r="H69" s="3">
-        <v>46161</v>
+        <v>46224</v>
       </c>
       <c r="I69" s="3">
-        <v>46167</v>
+        <v>46227</v>
       </c>
       <c r="J69" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4569,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4578,28 +4632,28 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F70" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G70" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H70" s="3">
-        <v>46232</v>
+        <v>46149</v>
       </c>
       <c r="I70" s="3">
-        <v>46234</v>
+        <v>46153</v>
       </c>
       <c r="J70" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
       </c>
       <c r="L70" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M70" t="s">
         <v>6</v>
@@ -4619,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4628,28 +4682,28 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F71" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G71" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H71" s="3">
-        <v>46232</v>
+        <v>46149</v>
       </c>
       <c r="I71" s="3">
-        <v>46234</v>
+        <v>46153</v>
       </c>
       <c r="J71" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M71" t="s">
         <v>6</v>
@@ -4669,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4678,28 +4732,28 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F72" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G72" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H72" s="3">
-        <v>46225</v>
+        <v>46150</v>
       </c>
       <c r="I72" s="3">
-        <v>46231</v>
+        <v>46156</v>
       </c>
       <c r="J72" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M72" t="s">
         <v>6</v>
@@ -4719,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4728,28 +4782,28 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G73" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H73" s="3">
-        <v>46225</v>
+        <v>46150</v>
       </c>
       <c r="I73" s="3">
-        <v>46231</v>
+        <v>46156</v>
       </c>
       <c r="J73" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -4769,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4778,28 +4832,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F74" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G74" s="3">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="H74" s="3">
-        <v>46232</v>
+        <v>46160</v>
       </c>
       <c r="I74" s="3">
-        <v>46237</v>
+        <v>46162</v>
       </c>
       <c r="J74" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -4819,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -4828,28 +4882,28 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G75" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H75" s="3">
-        <v>46224</v>
+        <v>46162</v>
       </c>
       <c r="I75" s="3">
-        <v>46227</v>
+        <v>46164</v>
       </c>
       <c r="J75" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -4869,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4878,28 +4932,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F76" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G76" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H76" s="3">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="I76" s="3">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="J76" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -4919,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -4928,28 +4982,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F77" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G77" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H77" s="3">
-        <v>46149</v>
+        <v>46134</v>
       </c>
       <c r="I77" s="3">
-        <v>46153</v>
+        <v>46136</v>
       </c>
       <c r="J77" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -4969,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -4978,28 +5032,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="F78" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="G78" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H78" s="3">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="I78" s="3">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="J78" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5019,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5028,28 +5082,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="F79" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="G79" s="3">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="H79" s="3">
-        <v>46141</v>
+        <v>46136</v>
       </c>
       <c r="I79" s="3">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="J79" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5069,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5078,19 +5132,19 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F80" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G80" s="3">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="H80" s="3">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="I80" s="3">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="J80" t="s">
         <v>13</v>
@@ -5099,7 +5153,7 @@
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5119,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5128,28 +5182,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="F81" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G81" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H81" s="3">
-        <v>46162</v>
+        <v>46140</v>
       </c>
       <c r="I81" s="3">
-        <v>46164</v>
+        <v>46147</v>
       </c>
       <c r="J81" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5169,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5178,28 +5232,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="F82" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="G82" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="H82" s="3">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="I82" s="3">
-        <v>46155</v>
+        <v>46181</v>
       </c>
       <c r="J82" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5219,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5228,28 +5282,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F83" t="s">
-        <v>186</v>
+        <v>54</v>
       </c>
       <c r="G83" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="H83" s="3">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="I83" s="3">
-        <v>46136</v>
+        <v>46177</v>
       </c>
       <c r="J83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5269,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5278,28 +5332,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F84" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G84" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="H84" s="3">
-        <v>46147</v>
+        <v>46170</v>
       </c>
       <c r="I84" s="3">
-        <v>46150</v>
+        <v>46171</v>
       </c>
       <c r="J84" t="s">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5319,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5328,28 +5382,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G85" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H85" s="3">
-        <v>46136</v>
+        <v>46170</v>
       </c>
       <c r="I85" s="3">
-        <v>46140</v>
+        <v>46171</v>
       </c>
       <c r="J85" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5369,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5378,28 +5432,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F86" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G86" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H86" s="3">
-        <v>46150</v>
+        <v>46170</v>
       </c>
       <c r="I86" s="3">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="J86" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5419,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5428,28 +5482,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F87" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="G87" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H87" s="3">
-        <v>46140</v>
+        <v>46133</v>
       </c>
       <c r="I87" s="3">
-        <v>46147</v>
+        <v>46136</v>
       </c>
       <c r="J87" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5469,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5478,28 +5532,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="F88" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="G88" s="3">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H88" s="3">
-        <v>46178</v>
+        <v>46134</v>
       </c>
       <c r="I88" s="3">
-        <v>46181</v>
+        <v>46139</v>
       </c>
       <c r="J88" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5519,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5528,28 +5582,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
       <c r="F89" t="s">
-        <v>56</v>
+        <v>209</v>
       </c>
       <c r="G89" s="3">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="H89" s="3">
-        <v>46174</v>
+        <v>46139</v>
       </c>
       <c r="I89" s="3">
-        <v>46177</v>
+        <v>46142</v>
       </c>
       <c r="J89" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K89" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L89" s="3">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5569,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5578,28 +5632,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F90" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G90" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H90" s="3">
-        <v>46170</v>
+        <v>46139</v>
       </c>
       <c r="I90" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J90" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="K90" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L90" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5619,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5628,28 +5682,28 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F91" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G91" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H91" s="3">
-        <v>46170</v>
+        <v>46139</v>
       </c>
       <c r="I91" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
       <c r="J91" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="K91" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L91" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5669,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5678,28 +5732,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="F92" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G92" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H92" s="3">
-        <v>46170</v>
+        <v>46136</v>
       </c>
       <c r="I92" s="3">
-        <v>46171</v>
+        <v>46141</v>
       </c>
       <c r="J92" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K92" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L92" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -5719,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5728,28 +5782,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F93" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="G93" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="H93" s="3">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="I93" s="3">
+        <v>46141</v>
+      </c>
+      <c r="J93" t="s">
+        <v>55</v>
+      </c>
+      <c r="K93" t="s">
+        <v>92</v>
+      </c>
+      <c r="L93" s="3">
         <v>46136</v>
-      </c>
-      <c r="J93" t="s">
-        <v>17</v>
-      </c>
-      <c r="K93" t="s">
-        <v>5</v>
-      </c>
-      <c r="L93" s="3">
-        <v>46133</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5769,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5778,28 +5832,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F94" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G94" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="H94" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="I94" s="3">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="J94" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="K94" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L94" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -5819,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -5828,28 +5882,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G95" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="H95" s="3">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="I95" s="3">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="J95" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="K95" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L95" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -5869,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -5878,25 +5932,25 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F96" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="G96" s="3">
         <v>46136</v>
       </c>
       <c r="H96" s="3">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="I96" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="J96" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="K96" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L96" s="3">
         <v>46136</v>
@@ -5919,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -5928,28 +5982,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F97" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G97" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H97" s="3">
+        <v>46170</v>
+      </c>
+      <c r="I97" s="3">
+        <v>46174</v>
+      </c>
+      <c r="J97" t="s">
+        <v>122</v>
+      </c>
+      <c r="K97" t="s">
+        <v>5</v>
+      </c>
+      <c r="L97" s="3">
         <v>46139</v>
-      </c>
-      <c r="I97" s="3">
-        <v>46142</v>
-      </c>
-      <c r="J97" t="s">
-        <v>34</v>
-      </c>
-      <c r="K97" t="s">
-        <v>95</v>
-      </c>
-      <c r="L97" s="3">
-        <v>46136</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -5969,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -5978,28 +6032,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F98" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G98" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H98" s="3">
+        <v>46164</v>
+      </c>
+      <c r="I98" s="3">
+        <v>46169</v>
+      </c>
+      <c r="J98" t="s">
+        <v>167</v>
+      </c>
+      <c r="K98" t="s">
+        <v>5</v>
+      </c>
+      <c r="L98" s="3">
         <v>46139</v>
-      </c>
-      <c r="I98" s="3">
-        <v>46142</v>
-      </c>
-      <c r="J98" t="s">
-        <v>13</v>
-      </c>
-      <c r="K98" t="s">
-        <v>95</v>
-      </c>
-      <c r="L98" s="3">
-        <v>46136</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6019,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6028,13 +6082,13 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>215</v>
+        <v>35</v>
       </c>
       <c r="F99" t="s">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="G99" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H99" s="3">
         <v>46139</v>
@@ -6043,13 +6097,13 @@
         <v>46142</v>
       </c>
       <c r="J99" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="K99" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6069,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6078,28 +6132,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F100" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G100" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H100" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I100" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="J100" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="K100" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6119,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6128,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="F101" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="G101" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H101" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I101" s="3">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="J101" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6169,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6178,28 +6232,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F102" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G102" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H102" s="3">
-        <v>46136</v>
+        <v>46183</v>
       </c>
       <c r="I102" s="3">
-        <v>46141</v>
+        <v>46190</v>
       </c>
       <c r="J102" t="s">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="K102" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6219,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6228,28 +6282,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F103" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G103" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H103" s="3">
-        <v>46136</v>
+        <v>46183</v>
       </c>
       <c r="I103" s="3">
-        <v>46141</v>
+        <v>46190</v>
       </c>
       <c r="J103" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="K103" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6269,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6278,28 +6332,28 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="F104" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="G104" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="H104" s="3">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="I104" s="3">
-        <v>46141</v>
+        <v>46182</v>
       </c>
       <c r="J104" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="K104" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="L104" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6319,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6328,28 +6382,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F105" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G105" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H105" s="3">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="I105" s="3">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="J105" t="s">
-        <v>126</v>
+        <v>234</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6369,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6378,28 +6432,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="F106" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G106" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H106" s="3">
-        <v>46164</v>
+        <v>46140</v>
       </c>
       <c r="I106" s="3">
-        <v>46169</v>
+        <v>46147</v>
       </c>
       <c r="J106" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6419,7 +6473,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6428,28 +6482,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="F107" t="s">
-        <v>41</v>
+        <v>246</v>
       </c>
       <c r="G107" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="H107" s="3">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="I107" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J107" t="s">
+        <v>167</v>
+      </c>
+      <c r="K107" t="s">
+        <v>5</v>
+      </c>
+      <c r="L107" s="3">
         <v>46142</v>
-      </c>
-      <c r="J107" t="s">
-        <v>34</v>
-      </c>
-      <c r="K107" t="s">
-        <v>5</v>
-      </c>
-      <c r="L107" s="3">
-        <v>46139</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6469,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6478,28 +6532,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F108" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="G108" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H108" s="3">
-        <v>46140</v>
+        <v>46150</v>
       </c>
       <c r="I108" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J108" t="s">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s">
+        <v>5</v>
+      </c>
+      <c r="L108" s="3">
         <v>46142</v>
-      </c>
-      <c r="J108" t="s">
-        <v>30</v>
-      </c>
-      <c r="K108" t="s">
-        <v>5</v>
-      </c>
-      <c r="L108" s="3">
-        <v>46140</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6519,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6528,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>114</v>
+        <v>245</v>
       </c>
       <c r="F109" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="G109" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H109" s="3">
-        <v>46140</v>
+        <v>46150</v>
       </c>
       <c r="I109" s="3">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="J109" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6569,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6578,28 +6632,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F110" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G110" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H110" s="3">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="I110" s="3">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="J110" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6619,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6628,28 +6682,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F111" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G111" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H111" s="3">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="I111" s="3">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="J111" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6669,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6678,28 +6732,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F112" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G112" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H112" s="3">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="I112" s="3">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="J112" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -6719,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -6728,28 +6782,28 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="F113" t="s">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="G113" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H113" s="3">
-        <v>46176</v>
+        <v>46155</v>
       </c>
       <c r="I113" s="3">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="J113" t="s">
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -6769,7 +6823,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -6778,28 +6832,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="F114" t="s">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="G114" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H114" s="3">
-        <v>46140</v>
+        <v>46156</v>
       </c>
       <c r="I114" s="3">
-        <v>46147</v>
+        <v>46162</v>
       </c>
       <c r="J114" t="s">
-        <v>34</v>
+        <v>234</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -6819,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -6828,22 +6882,22 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="F115" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="G115" s="3">
         <v>46142</v>
       </c>
       <c r="H115" s="3">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="I115" s="3">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="J115" t="s">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
@@ -6869,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -6878,22 +6932,22 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="F116" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="G116" s="3">
         <v>46142</v>
       </c>
       <c r="H116" s="3">
-        <v>46150</v>
+        <v>46177</v>
       </c>
       <c r="I116" s="3">
-        <v>46154</v>
+        <v>46183</v>
       </c>
       <c r="J116" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
@@ -6919,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -6928,22 +6982,22 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="F117" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="G117" s="3">
         <v>46142</v>
       </c>
       <c r="H117" s="3">
-        <v>46150</v>
+        <v>46177</v>
       </c>
       <c r="I117" s="3">
-        <v>46154</v>
+        <v>46183</v>
       </c>
       <c r="J117" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
@@ -6969,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -6978,22 +7032,22 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="F118" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="G118" s="3">
         <v>46142</v>
       </c>
       <c r="H118" s="3">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="I118" s="3">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="J118" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
@@ -7019,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7028,28 +7082,28 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F119" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="G119" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H119" s="3">
-        <v>46184</v>
+        <v>46204</v>
       </c>
       <c r="I119" s="3">
-        <v>46188</v>
+        <v>46206</v>
       </c>
       <c r="J119" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7069,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7078,28 +7132,28 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F120" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="G120" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H120" s="3">
-        <v>46184</v>
+        <v>46163</v>
       </c>
       <c r="I120" s="3">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="J120" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
       </c>
       <c r="L120" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
@@ -7119,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7128,28 +7182,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="F121" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="G121" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H121" s="3">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="I121" s="3">
-        <v>46149</v>
+        <v>46162</v>
       </c>
       <c r="J121" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7169,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7178,28 +7232,28 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>156</v>
+        <v>268</v>
       </c>
       <c r="F122" t="s">
-        <v>157</v>
+        <v>269</v>
       </c>
       <c r="G122" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H122" s="3">
-        <v>46142</v>
+        <v>46185</v>
       </c>
       <c r="I122" s="3">
-        <v>46149</v>
+        <v>46226</v>
       </c>
       <c r="J122" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
       </c>
       <c r="L122" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7219,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7228,28 +7282,28 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>156</v>
+        <v>271</v>
       </c>
       <c r="F123" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="G123" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H123" s="3">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="I123" s="3">
-        <v>46149</v>
+        <v>46189</v>
       </c>
       <c r="J123" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7269,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7278,28 +7332,28 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>156</v>
+        <v>274</v>
       </c>
       <c r="F124" t="s">
-        <v>157</v>
+        <v>275</v>
       </c>
       <c r="G124" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H124" s="3">
-        <v>46177</v>
+        <v>46197</v>
       </c>
       <c r="I124" s="3">
-        <v>46183</v>
+        <v>46202</v>
       </c>
       <c r="J124" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
       </c>
       <c r="L124" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7319,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7328,28 +7382,28 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>156</v>
+        <v>277</v>
       </c>
       <c r="F125" t="s">
-        <v>157</v>
+        <v>278</v>
       </c>
       <c r="G125" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H125" s="3">
-        <v>46177</v>
+        <v>46191</v>
       </c>
       <c r="I125" s="3">
-        <v>46183</v>
+        <v>46197</v>
       </c>
       <c r="J125" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
       </c>
       <c r="L125" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7369,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7378,28 +7432,28 @@
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>156</v>
+        <v>280</v>
       </c>
       <c r="F126" t="s">
-        <v>157</v>
+        <v>281</v>
       </c>
       <c r="G126" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H126" s="3">
-        <v>46177</v>
+        <v>46204</v>
       </c>
       <c r="I126" s="3">
-        <v>46183</v>
+        <v>46204</v>
       </c>
       <c r="J126" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7419,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7428,22 +7482,22 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="F127" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="G127" s="3">
         <v>46148</v>
       </c>
       <c r="H127" s="3">
+        <v>46199</v>
+      </c>
+      <c r="I127" s="3">
         <v>46204</v>
       </c>
-      <c r="I127" s="3">
-        <v>46206</v>
-      </c>
       <c r="J127" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
@@ -7469,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7478,22 +7532,22 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="F128" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="G128" s="3">
         <v>46148</v>
       </c>
       <c r="H128" s="3">
-        <v>46163</v>
+        <v>46279</v>
       </c>
       <c r="I128" s="3">
-        <v>46170</v>
+        <v>46281</v>
       </c>
       <c r="J128" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
@@ -7519,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7528,28 +7582,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="F129" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="G129" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="H129" s="3">
-        <v>46157</v>
+        <v>46190</v>
       </c>
       <c r="I129" s="3">
-        <v>46162</v>
+        <v>46202</v>
       </c>
       <c r="J129" t="s">
-        <v>126</v>
+        <v>291</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
       </c>
       <c r="L129" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7569,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7578,28 +7632,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="F130" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="G130" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="H130" s="3">
-        <v>46224</v>
+        <v>46183</v>
       </c>
       <c r="I130" s="3">
-        <v>46262</v>
+        <v>46189</v>
       </c>
       <c r="J130" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7619,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7628,28 +7682,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="F131" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="G131" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="H131" s="3">
-        <v>46212</v>
+        <v>46237</v>
       </c>
       <c r="I131" s="3">
-        <v>46219</v>
+        <v>46255</v>
       </c>
       <c r="J131" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -7669,7 +7723,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -7678,28 +7732,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="F132" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="G132" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="H132" s="3">
-        <v>46197</v>
+        <v>46156</v>
       </c>
       <c r="I132" s="3">
-        <v>46202</v>
+        <v>46161</v>
       </c>
       <c r="J132" t="s">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -7719,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -7728,28 +7782,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="F133" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="G133" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="H133" s="3">
-        <v>46191</v>
+        <v>46153</v>
       </c>
       <c r="I133" s="3">
-        <v>46197</v>
+        <v>46156</v>
       </c>
       <c r="J133" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -7769,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -7778,28 +7832,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="F134" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="G134" s="3">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="H134" s="3">
-        <v>46204</v>
+        <v>46191</v>
       </c>
       <c r="I134" s="3">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="J134" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -7819,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -7828,28 +7882,28 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="F135" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="G135" s="3">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="H135" s="3">
-        <v>46199</v>
+        <v>46184</v>
       </c>
       <c r="I135" s="3">
-        <v>46204</v>
+        <v>46190</v>
       </c>
       <c r="J135" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -7869,7 +7923,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -7878,28 +7932,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>291</v>
+        <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>292</v>
+        <v>3</v>
       </c>
       <c r="G136" s="3">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="H136" s="3">
-        <v>46279</v>
+        <v>46240</v>
       </c>
       <c r="I136" s="3">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="J136" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -7916,10 +7970,10 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -7928,28 +7982,28 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="F137" t="s">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="G137" s="3">
-        <v>46043</v>
+        <v>46156</v>
       </c>
       <c r="H137" s="3">
-        <v>46051</v>
+        <v>46209</v>
       </c>
       <c r="I137" s="3">
-        <v>46057</v>
+        <v>46211</v>
       </c>
       <c r="J137" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K137" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="L137" s="3">
-        <v>46043</v>
+        <v>46156</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -7966,10 +8020,10 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -7978,28 +8032,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>299</v>
+        <v>53</v>
       </c>
       <c r="F138" t="s">
-        <v>300</v>
+        <v>54</v>
       </c>
       <c r="G138" s="3">
-        <v>46057</v>
+        <v>46156</v>
       </c>
       <c r="H138" s="3">
-        <v>46076</v>
+        <v>46203</v>
       </c>
       <c r="I138" s="3">
-        <v>46083</v>
+        <v>46206</v>
       </c>
       <c r="J138" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K138" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46057</v>
+        <v>46156</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8016,10 +8070,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8028,28 +8082,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="F139" t="s">
-        <v>303</v>
+        <v>260</v>
       </c>
       <c r="G139" s="3">
-        <v>46114</v>
+        <v>46156</v>
       </c>
       <c r="H139" s="3">
-        <v>46148</v>
+        <v>46336</v>
       </c>
       <c r="I139" s="3">
-        <v>46148</v>
+        <v>46338</v>
       </c>
       <c r="J139" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="K139" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="L139" s="3">
-        <v>46114</v>
+        <v>46156</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8066,10 +8120,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8078,28 +8132,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="F140" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="G140" s="3">
-        <v>46135</v>
+        <v>46156</v>
       </c>
       <c r="H140" s="3">
-        <v>46135</v>
+        <v>46336</v>
       </c>
       <c r="I140" s="3">
-        <v>46147</v>
+        <v>46338</v>
       </c>
       <c r="J140" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="K140" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="L140" s="3">
-        <v>46135</v>
+        <v>46156</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8116,51 +8170,251 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B141" t="s">
+        <v>316</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>181</v>
+      </c>
+      <c r="F141" t="s">
+        <v>182</v>
+      </c>
+      <c r="G141" s="3">
+        <v>46156</v>
+      </c>
+      <c r="H141" s="3">
+        <v>46164</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46168</v>
+      </c>
+      <c r="J141" t="s">
+        <v>317</v>
+      </c>
+      <c r="K141" t="s">
+        <v>5</v>
+      </c>
+      <c r="L141" s="3">
+        <v>46156</v>
+      </c>
+      <c r="M141" t="s">
+        <v>6</v>
+      </c>
+      <c r="N141" t="s">
+        <v>7</v>
+      </c>
+      <c r="O141" t="s">
+        <v>8</v>
+      </c>
+      <c r="P141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" t="s">
+        <v>318</v>
+      </c>
+      <c r="C142" s="2">
+        <v>1</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s">
+        <v>105</v>
+      </c>
+      <c r="F142" t="s">
+        <v>106</v>
+      </c>
+      <c r="G142" s="3">
+        <v>46156</v>
+      </c>
+      <c r="H142" s="3">
+        <v>46157</v>
+      </c>
+      <c r="I142" s="3">
+        <v>46162</v>
+      </c>
+      <c r="J142" t="s">
+        <v>31</v>
+      </c>
+      <c r="K142" t="s">
+        <v>5</v>
+      </c>
+      <c r="L142" s="3">
+        <v>46156</v>
+      </c>
+      <c r="M142" t="s">
+        <v>6</v>
+      </c>
+      <c r="N142" t="s">
+        <v>7</v>
+      </c>
+      <c r="O142" t="s">
+        <v>8</v>
+      </c>
+      <c r="P142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" t="s">
+        <v>320</v>
+      </c>
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
+        <v>321</v>
+      </c>
+      <c r="F143" t="s">
+        <v>322</v>
+      </c>
+      <c r="G143" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H143" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J143" t="s">
+        <v>31</v>
+      </c>
+      <c r="K143" t="s">
+        <v>323</v>
+      </c>
+      <c r="L143" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N143" t="s">
+        <v>7</v>
+      </c>
+      <c r="O143" t="s">
+        <v>8</v>
+      </c>
+      <c r="P143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144" t="s">
+        <v>319</v>
+      </c>
+      <c r="B144" t="s">
+        <v>324</v>
+      </c>
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2">
+        <v>0</v>
+      </c>
+      <c r="E144" t="s">
+        <v>325</v>
+      </c>
+      <c r="F144" t="s">
+        <v>326</v>
+      </c>
+      <c r="G144" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H144" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I144" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J144" t="s">
+        <v>49</v>
+      </c>
+      <c r="K144" t="s">
+        <v>323</v>
+      </c>
+      <c r="L144" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M144" t="s">
+        <v>6</v>
+      </c>
+      <c r="N144" t="s">
+        <v>7</v>
+      </c>
+      <c r="O144" t="s">
+        <v>8</v>
+      </c>
+      <c r="P144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" t="s">
+        <v>319</v>
+      </c>
+      <c r="B145" t="s">
+        <v>327</v>
+      </c>
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0</v>
+      </c>
+      <c r="E145" t="s">
         <v>293</v>
       </c>
-      <c r="B141" t="s">
-        <v>307</v>
-      </c>
-      <c r="C141" s="2">
-        <v>1</v>
-      </c>
-      <c r="D141" s="2">
-        <v>0</v>
-      </c>
-      <c r="E141" t="s">
-        <v>308</v>
-      </c>
-      <c r="F141" t="s">
-        <v>309</v>
-      </c>
-      <c r="G141" s="3">
+      <c r="F145" t="s">
+        <v>294</v>
+      </c>
+      <c r="G145" s="3">
         <v>46140</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H145" s="3">
         <v>46140</v>
       </c>
-      <c r="I141" s="3">
+      <c r="I145" s="3">
         <v>46147</v>
       </c>
-      <c r="J141" t="s">
-        <v>34</v>
-      </c>
-      <c r="K141" t="s">
-        <v>297</v>
-      </c>
-      <c r="L141" s="3">
+      <c r="J145" t="s">
+        <v>49</v>
+      </c>
+      <c r="K145" t="s">
+        <v>323</v>
+      </c>
+      <c r="L145" s="3">
         <v>46140</v>
       </c>
-      <c r="M141" t="s">
-        <v>6</v>
-      </c>
-      <c r="N141" t="s">
-        <v>7</v>
-      </c>
-      <c r="O141" t="s">
-        <v>8</v>
-      </c>
-      <c r="P141" t="s">
+      <c r="M145" t="s">
+        <v>6</v>
+      </c>
+      <c r="N145" t="s">
+        <v>7</v>
+      </c>
+      <c r="O145" t="s">
+        <v>8</v>
+      </c>
+      <c r="P145" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/入庫TECO狀態.XLSX
+++ b/Newdata/入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="343">
   <si>
     <t>ZP02</t>
   </si>
@@ -379,7 +379,7 @@
     <t>200006606</t>
   </si>
   <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
   </si>
   <si>
     <t>200006618</t>
@@ -713,9 +713,6 @@
   </si>
   <si>
     <t>HEP機頭G8K,011194_780,55A18,C</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
   </si>
   <si>
     <t>200006704</t>
@@ -1170,52 +1167,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -3447,7 +3444,7 @@
         <v>46169</v>
       </c>
       <c r="J46" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
@@ -3497,7 +3494,7 @@
         <v>46169</v>
       </c>
       <c r="J47" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
@@ -6247,7 +6244,7 @@
         <v>46190</v>
       </c>
       <c r="J102" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
@@ -6273,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6297,7 +6294,7 @@
         <v>46190</v>
       </c>
       <c r="J103" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
@@ -6323,19 +6320,19 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
+        <v>236</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
         <v>237</v>
       </c>
-      <c r="C104" s="2">
-        <v>1</v>
-      </c>
-      <c r="D104" s="2">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>238</v>
-      </c>
-      <c r="F104" t="s">
-        <v>239</v>
       </c>
       <c r="G104" s="3">
         <v>46140</v>
@@ -6373,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6382,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
+        <v>237</v>
+      </c>
+      <c r="F105" t="s">
         <v>238</v>
-      </c>
-      <c r="F105" t="s">
-        <v>239</v>
       </c>
       <c r="G105" s="3">
         <v>46140</v>
@@ -6397,7 +6394,7 @@
         <v>46182</v>
       </c>
       <c r="J105" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
@@ -6423,19 +6420,19 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
         <v>241</v>
       </c>
-      <c r="C106" s="2">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2">
-        <v>0</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>242</v>
-      </c>
-      <c r="F106" t="s">
-        <v>243</v>
       </c>
       <c r="G106" s="3">
         <v>46140</v>
@@ -6473,19 +6470,19 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
+        <v>243</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0</v>
+      </c>
+      <c r="E107" t="s">
         <v>244</v>
       </c>
-      <c r="C107" s="2">
-        <v>1</v>
-      </c>
-      <c r="D107" s="2">
-        <v>0</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>245</v>
-      </c>
-      <c r="F107" t="s">
-        <v>246</v>
       </c>
       <c r="G107" s="3">
         <v>46142</v>
@@ -6523,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6532,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
+        <v>244</v>
+      </c>
+      <c r="F108" t="s">
         <v>245</v>
-      </c>
-      <c r="F108" t="s">
-        <v>246</v>
       </c>
       <c r="G108" s="3">
         <v>46142</v>
@@ -6573,7 +6570,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6582,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
+        <v>244</v>
+      </c>
+      <c r="F109" t="s">
         <v>245</v>
-      </c>
-      <c r="F109" t="s">
-        <v>246</v>
       </c>
       <c r="G109" s="3">
         <v>46142</v>
@@ -6623,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6632,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
+        <v>244</v>
+      </c>
+      <c r="F110" t="s">
         <v>245</v>
-      </c>
-      <c r="F110" t="s">
-        <v>246</v>
       </c>
       <c r="G110" s="3">
         <v>46142</v>
@@ -6673,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6682,10 +6679,10 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
+        <v>244</v>
+      </c>
+      <c r="F111" t="s">
         <v>245</v>
-      </c>
-      <c r="F111" t="s">
-        <v>246</v>
       </c>
       <c r="G111" s="3">
         <v>46142</v>
@@ -6723,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6732,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
+        <v>244</v>
+      </c>
+      <c r="F112" t="s">
         <v>245</v>
-      </c>
-      <c r="F112" t="s">
-        <v>246</v>
       </c>
       <c r="G112" s="3">
         <v>46142</v>
@@ -6773,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -6797,7 +6794,7 @@
         <v>46160</v>
       </c>
       <c r="J113" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
@@ -6823,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -6847,7 +6844,7 @@
         <v>46162</v>
       </c>
       <c r="J114" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
@@ -6873,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -6897,7 +6894,7 @@
         <v>46162</v>
       </c>
       <c r="J115" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
@@ -6923,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -6973,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7023,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7073,19 +7070,19 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
+        <v>257</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
         <v>258</v>
       </c>
-      <c r="C119" s="2">
-        <v>1</v>
-      </c>
-      <c r="D119" s="2">
-        <v>0</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>259</v>
-      </c>
-      <c r="F119" t="s">
-        <v>260</v>
       </c>
       <c r="G119" s="3">
         <v>46148</v>
@@ -7123,19 +7120,19 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
+        <v>260</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
         <v>261</v>
       </c>
-      <c r="C120" s="2">
-        <v>1</v>
-      </c>
-      <c r="D120" s="2">
-        <v>0</v>
-      </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>262</v>
-      </c>
-      <c r="F120" t="s">
-        <v>263</v>
       </c>
       <c r="G120" s="3">
         <v>46148</v>
@@ -7173,19 +7170,19 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
+        <v>263</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" t="s">
         <v>264</v>
       </c>
-      <c r="C121" s="2">
-        <v>1</v>
-      </c>
-      <c r="D121" s="2">
-        <v>0</v>
-      </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>265</v>
-      </c>
-      <c r="F121" t="s">
-        <v>266</v>
       </c>
       <c r="G121" s="3">
         <v>46148</v>
@@ -7197,7 +7194,7 @@
         <v>46162</v>
       </c>
       <c r="J121" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
@@ -7223,19 +7220,19 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
+        <v>266</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0</v>
+      </c>
+      <c r="E122" t="s">
         <v>267</v>
       </c>
-      <c r="C122" s="2">
-        <v>1</v>
-      </c>
-      <c r="D122" s="2">
-        <v>0</v>
-      </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>268</v>
-      </c>
-      <c r="F122" t="s">
-        <v>269</v>
       </c>
       <c r="G122" s="3">
         <v>46148</v>
@@ -7273,19 +7270,19 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
+        <v>269</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
         <v>270</v>
       </c>
-      <c r="C123" s="2">
-        <v>1</v>
-      </c>
-      <c r="D123" s="2">
-        <v>0</v>
-      </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>271</v>
-      </c>
-      <c r="F123" t="s">
-        <v>272</v>
       </c>
       <c r="G123" s="3">
         <v>46148</v>
@@ -7323,19 +7320,19 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
+        <v>272</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124" t="s">
         <v>273</v>
       </c>
-      <c r="C124" s="2">
-        <v>1</v>
-      </c>
-      <c r="D124" s="2">
-        <v>0</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>274</v>
-      </c>
-      <c r="F124" t="s">
-        <v>275</v>
       </c>
       <c r="G124" s="3">
         <v>46148</v>
@@ -7373,19 +7370,19 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
+        <v>275</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" t="s">
         <v>276</v>
       </c>
-      <c r="C125" s="2">
-        <v>1</v>
-      </c>
-      <c r="D125" s="2">
-        <v>0</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>277</v>
-      </c>
-      <c r="F125" t="s">
-        <v>278</v>
       </c>
       <c r="G125" s="3">
         <v>46148</v>
@@ -7423,19 +7420,19 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
+        <v>278</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
         <v>279</v>
       </c>
-      <c r="C126" s="2">
-        <v>1</v>
-      </c>
-      <c r="D126" s="2">
-        <v>0</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>280</v>
-      </c>
-      <c r="F126" t="s">
-        <v>281</v>
       </c>
       <c r="G126" s="3">
         <v>46148</v>
@@ -7473,19 +7470,19 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
+        <v>281</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" t="s">
         <v>282</v>
       </c>
-      <c r="C127" s="2">
-        <v>1</v>
-      </c>
-      <c r="D127" s="2">
-        <v>0</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>283</v>
-      </c>
-      <c r="F127" t="s">
-        <v>284</v>
       </c>
       <c r="G127" s="3">
         <v>46148</v>
@@ -7523,19 +7520,19 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
+        <v>284</v>
+      </c>
+      <c r="C128" s="2">
+        <v>1</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
         <v>285</v>
       </c>
-      <c r="C128" s="2">
-        <v>1</v>
-      </c>
-      <c r="D128" s="2">
-        <v>0</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>286</v>
-      </c>
-      <c r="F128" t="s">
-        <v>287</v>
       </c>
       <c r="G128" s="3">
         <v>46148</v>
@@ -7573,19 +7570,19 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
+        <v>287</v>
+      </c>
+      <c r="C129" s="2">
+        <v>1</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0</v>
+      </c>
+      <c r="E129" t="s">
         <v>288</v>
       </c>
-      <c r="C129" s="2">
-        <v>1</v>
-      </c>
-      <c r="D129" s="2">
-        <v>0</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>289</v>
-      </c>
-      <c r="F129" t="s">
-        <v>290</v>
       </c>
       <c r="G129" s="3">
         <v>46153</v>
@@ -7597,7 +7594,7 @@
         <v>46202</v>
       </c>
       <c r="J129" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
@@ -7623,19 +7620,19 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
+        <v>291</v>
+      </c>
+      <c r="C130" s="2">
+        <v>1</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0</v>
+      </c>
+      <c r="E130" t="s">
         <v>292</v>
       </c>
-      <c r="C130" s="2">
-        <v>1</v>
-      </c>
-      <c r="D130" s="2">
-        <v>0</v>
-      </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>293</v>
-      </c>
-      <c r="F130" t="s">
-        <v>294</v>
       </c>
       <c r="G130" s="3">
         <v>46153</v>
@@ -7673,19 +7670,19 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
+        <v>294</v>
+      </c>
+      <c r="C131" s="2">
+        <v>1</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0</v>
+      </c>
+      <c r="E131" t="s">
         <v>295</v>
       </c>
-      <c r="C131" s="2">
-        <v>1</v>
-      </c>
-      <c r="D131" s="2">
-        <v>0</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>296</v>
-      </c>
-      <c r="F131" t="s">
-        <v>297</v>
       </c>
       <c r="G131" s="3">
         <v>46153</v>
@@ -7723,19 +7720,19 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
+        <v>297</v>
+      </c>
+      <c r="C132" s="2">
+        <v>1</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0</v>
+      </c>
+      <c r="E132" t="s">
         <v>298</v>
       </c>
-      <c r="C132" s="2">
-        <v>1</v>
-      </c>
-      <c r="D132" s="2">
-        <v>0</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>299</v>
-      </c>
-      <c r="F132" t="s">
-        <v>300</v>
       </c>
       <c r="G132" s="3">
         <v>46153</v>
@@ -7747,7 +7744,7 @@
         <v>46161</v>
       </c>
       <c r="J132" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
@@ -7773,19 +7770,19 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
+        <v>300</v>
+      </c>
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
+      <c r="D133" s="2">
+        <v>0</v>
+      </c>
+      <c r="E133" t="s">
         <v>301</v>
       </c>
-      <c r="C133" s="2">
-        <v>1</v>
-      </c>
-      <c r="D133" s="2">
-        <v>0</v>
-      </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>302</v>
-      </c>
-      <c r="F133" t="s">
-        <v>303</v>
       </c>
       <c r="G133" s="3">
         <v>46153</v>
@@ -7797,7 +7794,7 @@
         <v>46156</v>
       </c>
       <c r="J133" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
@@ -7823,19 +7820,19 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
+        <v>303</v>
+      </c>
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s">
         <v>304</v>
       </c>
-      <c r="C134" s="2">
-        <v>1</v>
-      </c>
-      <c r="D134" s="2">
-        <v>0</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
         <v>305</v>
-      </c>
-      <c r="F134" t="s">
-        <v>306</v>
       </c>
       <c r="G134" s="3">
         <v>46154</v>
@@ -7873,19 +7870,19 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
+        <v>306</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
         <v>307</v>
       </c>
-      <c r="C135" s="2">
-        <v>1</v>
-      </c>
-      <c r="D135" s="2">
-        <v>0</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>308</v>
-      </c>
-      <c r="F135" t="s">
-        <v>309</v>
       </c>
       <c r="G135" s="3">
         <v>46154</v>
@@ -7923,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -7973,16 +7970,16 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
+        <v>310</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" t="s">
         <v>311</v>
-      </c>
-      <c r="C137" s="2">
-        <v>1</v>
-      </c>
-      <c r="D137" s="2">
-        <v>0</v>
-      </c>
-      <c r="E137" t="s">
-        <v>312</v>
       </c>
       <c r="F137" t="s">
         <v>228</v>
@@ -8023,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -8073,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8082,10 +8079,10 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
+        <v>258</v>
+      </c>
+      <c r="F139" t="s">
         <v>259</v>
-      </c>
-      <c r="F139" t="s">
-        <v>260</v>
       </c>
       <c r="G139" s="3">
         <v>46156</v>
@@ -8123,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8132,10 +8129,10 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
+        <v>258</v>
+      </c>
+      <c r="F140" t="s">
         <v>259</v>
-      </c>
-      <c r="F140" t="s">
-        <v>260</v>
       </c>
       <c r="G140" s="3">
         <v>46156</v>
@@ -8173,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C141" s="2">
         <v>1</v>
@@ -8197,7 +8194,7 @@
         <v>46168</v>
       </c>
       <c r="J141" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K141" t="s">
         <v>5</v>
@@ -8223,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C142" s="2">
         <v>1</v>
@@ -8247,7 +8244,7 @@
         <v>46162</v>
       </c>
       <c r="J142" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="K142" t="s">
         <v>5</v>
@@ -8270,22 +8267,22 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" t="s">
         <v>319</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
         <v>320</v>
       </c>
-      <c r="C143" s="2">
-        <v>1</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>321</v>
-      </c>
-      <c r="F143" t="s">
-        <v>322</v>
       </c>
       <c r="G143" s="3">
         <v>46043</v>
@@ -8300,7 +8297,7 @@
         <v>31</v>
       </c>
       <c r="K143" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L143" s="3">
         <v>46043</v>
@@ -8320,22 +8317,22 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B144" t="s">
+        <v>323</v>
+      </c>
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2">
+        <v>0</v>
+      </c>
+      <c r="E144" t="s">
         <v>324</v>
       </c>
-      <c r="C144" s="2">
-        <v>1</v>
-      </c>
-      <c r="D144" s="2">
-        <v>0</v>
-      </c>
-      <c r="E144" t="s">
+      <c r="F144" t="s">
         <v>325</v>
-      </c>
-      <c r="F144" t="s">
-        <v>326</v>
       </c>
       <c r="G144" s="3">
         <v>46114</v>
@@ -8350,7 +8347,7 @@
         <v>49</v>
       </c>
       <c r="K144" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L144" s="3">
         <v>46114</v>
@@ -8370,10 +8367,10 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B145" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C145" s="2">
         <v>1</v>
@@ -8382,10 +8379,10 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
+        <v>292</v>
+      </c>
+      <c r="F145" t="s">
         <v>293</v>
-      </c>
-      <c r="F145" t="s">
-        <v>294</v>
       </c>
       <c r="G145" s="3">
         <v>46140</v>
@@ -8400,7 +8397,7 @@
         <v>49</v>
       </c>
       <c r="K145" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L145" s="3">
         <v>46140</v>
